--- a/docs/Baseline比較結果.xlsx
+++ b/docs/Baseline比較結果.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff0\OneDrive\桌面\115_NTUT_Thesis\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\ntut\115_NTUT_Thesis\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2280CCC-65A7-4AC5-939E-71D95FFD3E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03C00C69-3782-435B-919D-15860345E014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9DD6E340-DFE3-4B7E-9025-343BD89F474F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{9DD6E340-DFE3-4B7E-9025-343BD89F474F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="76">
   <si>
     <t>Distance</t>
   </si>
@@ -271,71 +271,6 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> Gap(%)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>類</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>R</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>類</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>RC</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>類</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -380,6 +315,136 @@
   </si>
   <si>
     <t>Total</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>C1</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>類</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>C2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>類</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>R1</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>類</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>R2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>類</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>RC1</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>類</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>RC2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>類</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -680,9 +745,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -714,6 +776,9 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1051,7 +1116,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CECA5DF5-0F01-4635-876C-42C0D830CD54}">
-  <dimension ref="A1:P62"/>
+  <dimension ref="A1:P65"/>
   <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="11.875" customWidth="1"/>
@@ -1068,35 +1133,35 @@
   <sheetData>
     <row r="1" spans="1:16" ht="17.25" customHeight="1" thickBot="1">
       <c r="A1" s="4"/>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="23"/>
-      <c r="D1" s="18" t="s">
+      <c r="C1" s="22"/>
+      <c r="D1" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="23"/>
-      <c r="F1" s="24" t="s">
+      <c r="E1" s="22"/>
+      <c r="F1" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="23"/>
-      <c r="H1" s="18" t="s">
+      <c r="G1" s="22"/>
+      <c r="H1" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="18" t="s">
+      <c r="I1" s="22"/>
+      <c r="J1" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="K1" s="23"/>
-      <c r="L1" s="18" t="s">
+      <c r="K1" s="22"/>
+      <c r="L1" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="M1" s="23"/>
-      <c r="N1" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
     </row>
     <row r="2" spans="1:16" ht="17.25" thickBot="1">
       <c r="A2" s="5" t="s">
@@ -1139,39 +1204,39 @@
         <v>0</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="17.25" thickBot="1">
       <c r="A3" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B3" s="20" t="str">
-        <f>COUNTA(A4:A20) &amp; " 筆"</f>
-        <v>17 筆</v>
-      </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
-      <c r="L3" s="21"/>
-      <c r="M3" s="22"/>
+        <v>70</v>
+      </c>
+      <c r="B3" s="19" t="str">
+        <f>COUNTA(A4:A12) &amp; " 筆"</f>
+        <v>9 筆</v>
+      </c>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
+      <c r="M3" s="21"/>
       <c r="N3" s="1">
+        <v>4</v>
+      </c>
+      <c r="O3" s="1">
         <v>5</v>
-      </c>
-      <c r="O3" s="1">
-        <v>12</v>
       </c>
       <c r="P3" s="1">
         <v>0</v>
@@ -1206,19 +1271,19 @@
         <v>828.94</v>
       </c>
       <c r="J4" s="7">
-        <f t="shared" ref="J4:J20" si="0">ROUND(((F4-D4)/D4)*100,2)</f>
+        <f t="shared" ref="J4:J12" si="0">ROUND(((F4-D4)/D4)*100,2)</f>
         <v>0</v>
       </c>
       <c r="K4" s="7">
-        <f t="shared" ref="K4:K20" si="1">ROUND(((G4-E4)/E4)*100,2)</f>
+        <f t="shared" ref="K4:K12" si="1">ROUND(((G4-E4)/E4)*100,2)</f>
         <v>0</v>
       </c>
       <c r="L4" s="1">
-        <f t="shared" ref="L4:L20" si="2">ROUND(((F4-H4)/H4)*100,2)</f>
+        <f t="shared" ref="L4:L12" si="2">ROUND(((F4-H4)/H4)*100,2)</f>
         <v>0</v>
       </c>
       <c r="M4" s="1">
-        <f t="shared" ref="M4:M20" si="3">ROUND(((G4-I4)/I4)*100,2)</f>
+        <f t="shared" ref="M4:M12" si="3">ROUND(((G4-I4)/I4)*100,2)</f>
         <v>0</v>
       </c>
       <c r="N4" s="9"/>
@@ -1270,8 +1335,8 @@
         <v>0</v>
       </c>
       <c r="N5" s="12"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="14"/>
+      <c r="O5" s="24"/>
+      <c r="P5" s="13"/>
     </row>
     <row r="6" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A6" s="6" t="s">
@@ -1318,8 +1383,8 @@
         <v>0</v>
       </c>
       <c r="N6" s="12"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="14"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="13"/>
     </row>
     <row r="7" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A7" s="6" t="s">
@@ -1366,8 +1431,8 @@
         <v>0</v>
       </c>
       <c r="N7" s="12"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="14"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="13"/>
     </row>
     <row r="8" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A8" s="6" t="s">
@@ -1414,8 +1479,8 @@
         <v>0</v>
       </c>
       <c r="N8" s="12"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="14"/>
+      <c r="O8" s="24"/>
+      <c r="P8" s="13"/>
     </row>
     <row r="9" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A9" s="6" t="s">
@@ -1462,8 +1527,8 @@
         <v>0</v>
       </c>
       <c r="N9" s="12"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="14"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="13"/>
     </row>
     <row r="10" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A10" s="6" t="s">
@@ -1510,8 +1575,8 @@
         <v>0</v>
       </c>
       <c r="N10" s="12"/>
-      <c r="O10" s="13"/>
-      <c r="P10" s="14"/>
+      <c r="O10" s="24"/>
+      <c r="P10" s="13"/>
     </row>
     <row r="11" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A11" s="6" t="s">
@@ -1558,8 +1623,8 @@
         <v>0</v>
       </c>
       <c r="N11" s="12"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="14"/>
+      <c r="O11" s="24"/>
+      <c r="P11" s="13"/>
     </row>
     <row r="12" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A12" s="6" t="s">
@@ -1605,61 +1670,42 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N12" s="12"/>
-      <c r="O12" s="13"/>
-      <c r="P12" s="14"/>
-    </row>
-    <row r="13" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
+      <c r="N12" s="14"/>
+      <c r="O12" s="15"/>
+      <c r="P12" s="16"/>
+    </row>
+    <row r="13" spans="1:16" ht="17.25" customHeight="1" collapsed="1" thickBot="1">
       <c r="A13" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="1">
-        <v>3</v>
-      </c>
-      <c r="C13" s="1">
-        <v>591.55999999999995</v>
-      </c>
-      <c r="D13" s="1">
-        <v>3</v>
-      </c>
-      <c r="E13" s="1">
-        <v>591.55999999999995</v>
-      </c>
-      <c r="F13" s="7">
-        <v>3</v>
-      </c>
-      <c r="G13" s="7">
-        <v>591.55999999999995</v>
-      </c>
-      <c r="H13" s="1">
-        <v>3</v>
-      </c>
-      <c r="I13" s="1">
-        <v>591.55999999999995</v>
-      </c>
-      <c r="J13" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K13" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L13" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M13" s="1">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N13" s="12"/>
-      <c r="O13" s="13"/>
-      <c r="P13" s="14"/>
+        <v>71</v>
+      </c>
+      <c r="B13" s="19" t="str">
+        <f>COUNTA(A14:A21) &amp; " 筆"</f>
+        <v>8 筆</v>
+      </c>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="21"/>
+      <c r="N13" s="1">
+        <v>1</v>
+      </c>
+      <c r="O13" s="1">
+        <v>7</v>
+      </c>
+      <c r="P13" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A14" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" s="1">
         <v>3</v>
@@ -1686,849 +1732,849 @@
         <v>591.55999999999995</v>
       </c>
       <c r="J14" s="7">
-        <f t="shared" si="0"/>
+        <f>ROUND(((F14-D14)/D14)*100,2)</f>
         <v>0</v>
       </c>
       <c r="K14" s="7">
-        <f t="shared" si="1"/>
+        <f>ROUND(((G14-E14)/E14)*100,2)</f>
         <v>0</v>
       </c>
       <c r="L14" s="1">
-        <f t="shared" si="2"/>
+        <f>ROUND(((F14-H14)/H14)*100,2)</f>
         <v>0</v>
       </c>
       <c r="M14" s="1">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N14" s="12"/>
-      <c r="O14" s="13"/>
-      <c r="P14" s="14"/>
+        <f>ROUND(((G14-I14)/I14)*100,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="9"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="11"/>
     </row>
     <row r="15" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A15" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" s="1">
         <v>3</v>
       </c>
       <c r="C15" s="1">
-        <v>621.30999999999995</v>
+        <v>591.55999999999995</v>
       </c>
       <c r="D15" s="1">
         <v>3</v>
       </c>
       <c r="E15" s="1">
-        <v>591.16999999999996</v>
+        <v>591.55999999999995</v>
       </c>
       <c r="F15" s="7">
         <v>3</v>
       </c>
       <c r="G15" s="7">
-        <v>591.16999999999996</v>
+        <v>591.55999999999995</v>
       </c>
       <c r="H15" s="1">
         <v>3</v>
       </c>
       <c r="I15" s="1">
-        <v>591.16999999999996</v>
+        <v>591.55999999999995</v>
       </c>
       <c r="J15" s="7">
-        <f t="shared" si="0"/>
+        <f>ROUND(((F15-D15)/D15)*100,2)</f>
         <v>0</v>
       </c>
       <c r="K15" s="7">
-        <f t="shared" si="1"/>
+        <f>ROUND(((G15-E15)/E15)*100,2)</f>
         <v>0</v>
       </c>
       <c r="L15" s="1">
-        <f t="shared" si="2"/>
+        <f>ROUND(((F15-H15)/H15)*100,2)</f>
         <v>0</v>
       </c>
       <c r="M15" s="1">
-        <f t="shared" si="3"/>
+        <f>ROUND(((G15-I15)/I15)*100,2)</f>
         <v>0</v>
       </c>
       <c r="N15" s="12"/>
-      <c r="O15" s="13"/>
-      <c r="P15" s="14"/>
+      <c r="O15" s="24"/>
+      <c r="P15" s="13"/>
     </row>
     <row r="16" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A16" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16" s="1">
         <v>3</v>
       </c>
       <c r="C16" s="1">
-        <v>639.92999999999995</v>
+        <v>621.30999999999995</v>
       </c>
       <c r="D16" s="1">
         <v>3</v>
       </c>
       <c r="E16" s="1">
-        <v>594.51</v>
-      </c>
-      <c r="F16" s="2">
-        <v>3</v>
-      </c>
-      <c r="G16" s="2">
-        <v>593.92999999999995</v>
+        <v>591.16999999999996</v>
+      </c>
+      <c r="F16" s="7">
+        <v>3</v>
+      </c>
+      <c r="G16" s="7">
+        <v>591.16999999999996</v>
       </c>
       <c r="H16" s="1">
         <v>3</v>
       </c>
       <c r="I16" s="1">
-        <v>590.6</v>
-      </c>
-      <c r="J16" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="2">
-        <f t="shared" si="1"/>
-        <v>-0.1</v>
+        <v>591.16999999999996</v>
+      </c>
+      <c r="J16" s="7">
+        <f>ROUND(((F16-D16)/D16)*100,2)</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="7">
+        <f>ROUND(((G16-E16)/E16)*100,2)</f>
+        <v>0</v>
       </c>
       <c r="L16" s="1">
-        <f t="shared" si="2"/>
+        <f>ROUND(((F16-H16)/H16)*100,2)</f>
         <v>0</v>
       </c>
       <c r="M16" s="1">
-        <f t="shared" si="3"/>
-        <v>0.56000000000000005</v>
+        <f>ROUND(((G16-I16)/I16)*100,2)</f>
+        <v>0</v>
       </c>
       <c r="N16" s="12"/>
-      <c r="O16" s="13"/>
-      <c r="P16" s="14"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="13"/>
     </row>
     <row r="17" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A17" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C17" s="1">
-        <v>638.4</v>
+        <v>639.92999999999995</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
       </c>
       <c r="E17" s="1">
-        <v>588.88</v>
-      </c>
-      <c r="F17" s="7">
-        <v>3</v>
-      </c>
-      <c r="G17" s="7">
-        <v>588.88</v>
+        <v>594.51</v>
+      </c>
+      <c r="F17" s="2">
+        <v>3</v>
+      </c>
+      <c r="G17" s="2">
+        <v>593.92999999999995</v>
       </c>
       <c r="H17" s="1">
         <v>3</v>
       </c>
       <c r="I17" s="1">
-        <v>588.85</v>
-      </c>
-      <c r="J17" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K17" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>590.6</v>
+      </c>
+      <c r="J17" s="2">
+        <f>ROUND(((F17-D17)/D17)*100,2)</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="2">
+        <f>ROUND(((G17-E17)/E17)*100,2)</f>
+        <v>-0.1</v>
       </c>
       <c r="L17" s="1">
-        <f t="shared" si="2"/>
+        <f>ROUND(((F17-H17)/H17)*100,2)</f>
         <v>0</v>
       </c>
       <c r="M17" s="1">
-        <f t="shared" si="3"/>
-        <v>0.01</v>
+        <f>ROUND(((G17-I17)/I17)*100,2)</f>
+        <v>0.56000000000000005</v>
       </c>
       <c r="N17" s="12"/>
-      <c r="O17" s="13"/>
-      <c r="P17" s="14"/>
+      <c r="O17" s="24"/>
+      <c r="P17" s="13"/>
     </row>
     <row r="18" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A18" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C18" s="1">
-        <v>637.19000000000005</v>
+        <v>638.4</v>
       </c>
       <c r="D18" s="1">
         <v>3</v>
       </c>
       <c r="E18" s="1">
-        <v>588.49</v>
+        <v>588.88</v>
       </c>
       <c r="F18" s="7">
         <v>3</v>
       </c>
       <c r="G18" s="7">
-        <v>588.49</v>
+        <v>588.88</v>
       </c>
       <c r="H18" s="1">
         <v>3</v>
       </c>
       <c r="I18" s="1">
-        <v>588.49</v>
+        <v>588.85</v>
       </c>
       <c r="J18" s="7">
-        <f t="shared" si="0"/>
+        <f>ROUND(((F18-D18)/D18)*100,2)</f>
         <v>0</v>
       </c>
       <c r="K18" s="7">
-        <f t="shared" si="1"/>
+        <f>ROUND(((G18-E18)/E18)*100,2)</f>
         <v>0</v>
       </c>
       <c r="L18" s="1">
-        <f t="shared" si="2"/>
+        <f>ROUND(((F18-H18)/H18)*100,2)</f>
         <v>0</v>
       </c>
       <c r="M18" s="1">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>ROUND(((G18-I18)/I18)*100,2)</f>
+        <v>0.01</v>
       </c>
       <c r="N18" s="12"/>
-      <c r="O18" s="13"/>
-      <c r="P18" s="14"/>
+      <c r="O18" s="24"/>
+      <c r="P18" s="13"/>
     </row>
     <row r="19" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A19" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B19" s="1">
         <v>3</v>
       </c>
       <c r="C19" s="1">
-        <v>732.1</v>
+        <v>637.19000000000005</v>
       </c>
       <c r="D19" s="1">
         <v>3</v>
       </c>
       <c r="E19" s="1">
-        <v>588.29</v>
+        <v>588.49</v>
       </c>
       <c r="F19" s="7">
         <v>3</v>
       </c>
       <c r="G19" s="7">
-        <v>588.29</v>
+        <v>588.49</v>
       </c>
       <c r="H19" s="1">
         <v>3</v>
       </c>
       <c r="I19" s="1">
-        <v>588.29</v>
+        <v>588.49</v>
       </c>
       <c r="J19" s="7">
-        <f t="shared" si="0"/>
+        <f>ROUND(((F19-D19)/D19)*100,2)</f>
         <v>0</v>
       </c>
       <c r="K19" s="7">
-        <f t="shared" si="1"/>
+        <f>ROUND(((G19-E19)/E19)*100,2)</f>
         <v>0</v>
       </c>
       <c r="L19" s="1">
-        <f t="shared" si="2"/>
+        <f>ROUND(((F19-H19)/H19)*100,2)</f>
         <v>0</v>
       </c>
       <c r="M19" s="1">
-        <f t="shared" si="3"/>
+        <f>ROUND(((G19-I19)/I19)*100,2)</f>
         <v>0</v>
       </c>
       <c r="N19" s="12"/>
-      <c r="O19" s="13"/>
-      <c r="P19" s="14"/>
+      <c r="O19" s="24"/>
+      <c r="P19" s="13"/>
     </row>
     <row r="20" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A20" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="1">
+        <v>3</v>
+      </c>
+      <c r="C20" s="1">
+        <v>732.1</v>
+      </c>
+      <c r="D20" s="1">
+        <v>3</v>
+      </c>
+      <c r="E20" s="1">
+        <v>588.29</v>
+      </c>
+      <c r="F20" s="7">
+        <v>3</v>
+      </c>
+      <c r="G20" s="7">
+        <v>588.29</v>
+      </c>
+      <c r="H20" s="1">
+        <v>3</v>
+      </c>
+      <c r="I20" s="1">
+        <v>588.29</v>
+      </c>
+      <c r="J20" s="7">
+        <f>ROUND(((F20-D20)/D20)*100,2)</f>
+        <v>0</v>
+      </c>
+      <c r="K20" s="7">
+        <f>ROUND(((G20-E20)/E20)*100,2)</f>
+        <v>0</v>
+      </c>
+      <c r="L20" s="1">
+        <f>ROUND(((F20-H20)/H20)*100,2)</f>
+        <v>0</v>
+      </c>
+      <c r="M20" s="1">
+        <f>ROUND(((G20-I20)/I20)*100,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N20" s="12"/>
+      <c r="O20" s="24"/>
+      <c r="P20" s="13"/>
+    </row>
+    <row r="21" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
+      <c r="A21" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="1">
-        <v>3</v>
-      </c>
-      <c r="C20" s="1">
+      <c r="B21" s="1">
+        <v>3</v>
+      </c>
+      <c r="C21" s="1">
         <v>606.83000000000004</v>
       </c>
-      <c r="D20" s="1">
-        <v>3</v>
-      </c>
-      <c r="E20" s="1">
+      <c r="D21" s="1">
+        <v>3</v>
+      </c>
+      <c r="E21" s="1">
         <v>588.32000000000005</v>
       </c>
-      <c r="F20" s="7">
-        <v>3</v>
-      </c>
-      <c r="G20" s="7">
+      <c r="F21" s="7">
+        <v>3</v>
+      </c>
+      <c r="G21" s="7">
         <v>588.32000000000005</v>
       </c>
-      <c r="H20" s="1">
-        <v>3</v>
-      </c>
-      <c r="I20" s="1">
+      <c r="H21" s="1">
+        <v>3</v>
+      </c>
+      <c r="I21" s="1">
         <v>588.32000000000005</v>
       </c>
-      <c r="J20" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K20" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L20" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M20" s="1">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N20" s="15"/>
-      <c r="O20" s="16"/>
-      <c r="P20" s="17"/>
-    </row>
-    <row r="21" spans="1:16" ht="17.25" collapsed="1" thickBot="1">
-      <c r="A21" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B21" s="20" t="str">
-        <f>COUNTA(A22:A44) &amp; " 筆"</f>
-        <v>23 筆</v>
-      </c>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="21"/>
-      <c r="M21" s="22"/>
-      <c r="N21" s="1">
-        <v>11</v>
-      </c>
-      <c r="O21" s="1">
-        <v>0</v>
-      </c>
-      <c r="P21" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
-      <c r="A22" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B22" s="1">
-        <v>20</v>
-      </c>
-      <c r="C22" s="1">
-        <v>1754.01</v>
-      </c>
-      <c r="D22" s="1">
-        <v>19</v>
-      </c>
-      <c r="E22" s="1">
-        <v>1656.55</v>
-      </c>
-      <c r="F22" s="3">
-        <v>20</v>
-      </c>
-      <c r="G22" s="3">
-        <v>1645.01</v>
-      </c>
-      <c r="H22" s="1">
-        <v>19</v>
-      </c>
-      <c r="I22" s="1">
-        <v>1650.8</v>
-      </c>
-      <c r="J22" s="3">
-        <f t="shared" ref="J22:J44" si="4">ROUND(((F22-D22)/D22)*100,2)</f>
-        <v>5.26</v>
-      </c>
-      <c r="K22" s="3">
-        <f t="shared" ref="K22:K44" si="5">ROUND(((G22-E22)/E22)*100,2)</f>
-        <v>-0.7</v>
-      </c>
-      <c r="L22" s="1">
-        <f t="shared" ref="L22:L44" si="6">ROUND(((F22-H22)/H22)*100,2)</f>
-        <v>5.26</v>
-      </c>
-      <c r="M22" s="1">
-        <f t="shared" ref="M22:M44" si="7">ROUND(((G22-I22)/I22)*100,2)</f>
-        <v>-0.35</v>
-      </c>
-      <c r="N22" s="9"/>
-      <c r="O22" s="10"/>
-      <c r="P22" s="11"/>
+      <c r="J21" s="7">
+        <f>ROUND(((F21-D21)/D21)*100,2)</f>
+        <v>0</v>
+      </c>
+      <c r="K21" s="7">
+        <f>ROUND(((G21-E21)/E21)*100,2)</f>
+        <v>0</v>
+      </c>
+      <c r="L21" s="1">
+        <f>ROUND(((F21-H21)/H21)*100,2)</f>
+        <v>0</v>
+      </c>
+      <c r="M21" s="1">
+        <f>ROUND(((G21-I21)/I21)*100,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N21" s="14"/>
+      <c r="O21" s="15"/>
+      <c r="P21" s="16"/>
+    </row>
+    <row r="22" spans="1:16" ht="17.25" customHeight="1" collapsed="1" thickBot="1">
+      <c r="A22" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" s="19" t="str">
+        <f>COUNTA(A23:A34) &amp; " 筆"</f>
+        <v>12 筆</v>
+      </c>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="21"/>
+      <c r="N22" s="1">
+        <v>5</v>
+      </c>
+      <c r="O22" s="1">
+        <v>0</v>
+      </c>
+      <c r="P22" s="1">
+        <v>7</v>
+      </c>
     </row>
     <row r="23" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A23" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="1">
         <v>20</v>
       </c>
-      <c r="B23" s="1">
+      <c r="C23" s="1">
+        <v>1754.01</v>
+      </c>
+      <c r="D23" s="1">
+        <v>19</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1656.55</v>
+      </c>
+      <c r="F23" s="3">
+        <v>20</v>
+      </c>
+      <c r="G23" s="3">
+        <v>1645.01</v>
+      </c>
+      <c r="H23" s="1">
+        <v>19</v>
+      </c>
+      <c r="I23" s="1">
+        <v>1650.8</v>
+      </c>
+      <c r="J23" s="3">
+        <f t="shared" ref="J23:J34" si="4">ROUND(((F23-D23)/D23)*100,2)</f>
+        <v>5.26</v>
+      </c>
+      <c r="K23" s="3">
+        <f t="shared" ref="K23:K34" si="5">ROUND(((G23-E23)/E23)*100,2)</f>
+        <v>-0.7</v>
+      </c>
+      <c r="L23" s="1">
+        <f t="shared" ref="L23:L34" si="6">ROUND(((F23-H23)/H23)*100,2)</f>
+        <v>5.26</v>
+      </c>
+      <c r="M23" s="1">
+        <f t="shared" ref="M23:M34" si="7">ROUND(((G23-I23)/I23)*100,2)</f>
+        <v>-0.35</v>
+      </c>
+      <c r="N23" s="9"/>
+      <c r="O23" s="10"/>
+      <c r="P23" s="11"/>
+    </row>
+    <row r="24" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
+      <c r="A24" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="1">
         <v>18</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C24" s="1">
         <v>1676.48</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D24" s="1">
         <v>18</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E24" s="1">
         <v>1476.85</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F24" s="2">
         <v>18</v>
       </c>
-      <c r="G23" s="2">
+      <c r="G24" s="2">
         <v>1466.25</v>
       </c>
-      <c r="H23" s="1">
+      <c r="H24" s="1">
         <v>17</v>
       </c>
-      <c r="I23" s="1">
+      <c r="I24" s="1">
         <v>1486.12</v>
       </c>
-      <c r="J23" s="2">
+      <c r="J24" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K23" s="2">
+      <c r="K24" s="2">
         <f t="shared" si="5"/>
         <v>-0.72</v>
       </c>
-      <c r="L23" s="1">
+      <c r="L24" s="1">
         <f t="shared" si="6"/>
         <v>5.88</v>
       </c>
-      <c r="M23" s="1">
+      <c r="M24" s="1">
         <f t="shared" si="7"/>
         <v>-1.34</v>
       </c>
-      <c r="N23" s="12"/>
-      <c r="O23" s="13"/>
-      <c r="P23" s="14"/>
-    </row>
-    <row r="24" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
-      <c r="A24" s="6" t="s">
+      <c r="N24" s="12"/>
+      <c r="O24" s="24"/>
+      <c r="P24" s="13"/>
+    </row>
+    <row r="25" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
+      <c r="A25" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B25" s="1">
         <v>15</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C25" s="1">
         <v>1463.66</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D25" s="1">
         <v>14</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E25" s="1">
         <v>1230.07</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F25" s="2">
         <v>14</v>
       </c>
-      <c r="G24" s="2">
+      <c r="G25" s="2">
         <v>1201.52</v>
       </c>
-      <c r="H24" s="1">
+      <c r="H25" s="1">
         <v>13</v>
       </c>
-      <c r="I24" s="1">
+      <c r="I25" s="1">
         <v>1292.68</v>
       </c>
-      <c r="J24" s="2">
+      <c r="J25" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K24" s="2">
+      <c r="K25" s="2">
         <f t="shared" si="5"/>
         <v>-2.3199999999999998</v>
       </c>
-      <c r="L24" s="1">
+      <c r="L25" s="1">
         <f t="shared" si="6"/>
         <v>7.69</v>
       </c>
-      <c r="M24" s="1">
+      <c r="M25" s="1">
         <f t="shared" si="7"/>
         <v>-7.05</v>
       </c>
-      <c r="N24" s="12"/>
-      <c r="O24" s="13"/>
-      <c r="P24" s="14"/>
-    </row>
-    <row r="25" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
-      <c r="A25" s="6" t="s">
+      <c r="N25" s="12"/>
+      <c r="O25" s="24"/>
+      <c r="P25" s="13"/>
+    </row>
+    <row r="26" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
+      <c r="A26" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B26" s="1">
         <v>12</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C26" s="1">
         <v>1182.78</v>
       </c>
-      <c r="D25" s="1">
-        <v>10</v>
-      </c>
-      <c r="E25" s="1">
+      <c r="D26" s="1">
+        <v>10</v>
+      </c>
+      <c r="E26" s="1">
         <v>1010.55</v>
       </c>
-      <c r="F25" s="2">
-        <v>10</v>
-      </c>
-      <c r="G25" s="2">
+      <c r="F26" s="2">
+        <v>10</v>
+      </c>
+      <c r="G26" s="2">
         <v>991.94</v>
       </c>
-      <c r="H25" s="1">
+      <c r="H26" s="1">
         <v>9</v>
       </c>
-      <c r="I25" s="1">
+      <c r="I26" s="1">
         <v>1007.31</v>
       </c>
-      <c r="J25" s="2">
+      <c r="J26" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K25" s="2">
+      <c r="K26" s="2">
         <f t="shared" si="5"/>
         <v>-1.84</v>
       </c>
-      <c r="L25" s="1">
+      <c r="L26" s="1">
         <f t="shared" si="6"/>
         <v>11.11</v>
       </c>
-      <c r="M25" s="1">
+      <c r="M26" s="1">
         <f t="shared" si="7"/>
         <v>-1.53</v>
       </c>
-      <c r="N25" s="12"/>
-      <c r="O25" s="13"/>
-      <c r="P25" s="14"/>
-    </row>
-    <row r="26" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
-      <c r="A26" s="6" t="s">
+      <c r="N26" s="12"/>
+      <c r="O26" s="24"/>
+      <c r="P26" s="13"/>
+    </row>
+    <row r="27" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
+      <c r="A27" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B27" s="1">
         <v>15</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C27" s="1">
         <v>1567.15</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D27" s="1">
         <v>14</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E27" s="1">
         <v>1395.68</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F27" s="3">
         <v>15</v>
       </c>
-      <c r="G26" s="3">
+      <c r="G27" s="3">
         <v>1389.17</v>
       </c>
-      <c r="H26" s="1">
+      <c r="H27" s="1">
         <v>14</v>
       </c>
-      <c r="I26" s="1">
+      <c r="I27" s="1">
         <v>1377.11</v>
       </c>
-      <c r="J26" s="3">
+      <c r="J27" s="3">
         <f t="shared" si="4"/>
         <v>7.14</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K27" s="3">
         <f t="shared" si="5"/>
         <v>-0.47</v>
       </c>
-      <c r="L26" s="1">
+      <c r="L27" s="1">
         <f t="shared" si="6"/>
         <v>7.14</v>
       </c>
-      <c r="M26" s="1">
+      <c r="M27" s="1">
         <f t="shared" si="7"/>
         <v>0.88</v>
       </c>
-      <c r="N26" s="12"/>
-      <c r="O26" s="13"/>
-      <c r="P26" s="14"/>
-    </row>
-    <row r="27" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
-      <c r="A27" s="6" t="s">
+      <c r="N27" s="12"/>
+      <c r="O27" s="24"/>
+      <c r="P27" s="13"/>
+    </row>
+    <row r="28" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
+      <c r="A28" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B28" s="1">
         <v>14</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C28" s="1">
         <v>1405.56</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D28" s="1">
         <v>13</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E28" s="1">
         <v>1261.6099999999999</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F28" s="3">
         <v>13</v>
       </c>
-      <c r="G27" s="3">
+      <c r="G28" s="3">
         <v>1278.1600000000001</v>
       </c>
-      <c r="H27" s="1">
+      <c r="H28" s="1">
         <v>12</v>
       </c>
-      <c r="I27" s="1">
+      <c r="I28" s="1">
         <v>1252.03</v>
       </c>
-      <c r="J27" s="3">
+      <c r="J28" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K28" s="3">
         <f t="shared" si="5"/>
         <v>1.31</v>
       </c>
-      <c r="L27" s="1">
+      <c r="L28" s="1">
         <f t="shared" si="6"/>
         <v>8.33</v>
       </c>
-      <c r="M27" s="1">
+      <c r="M28" s="1">
         <f t="shared" si="7"/>
         <v>2.09</v>
       </c>
-      <c r="N27" s="12"/>
-      <c r="O27" s="13"/>
-      <c r="P27" s="14"/>
-    </row>
-    <row r="28" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
-      <c r="A28" s="6" t="s">
+      <c r="N28" s="12"/>
+      <c r="O28" s="24"/>
+      <c r="P28" s="13"/>
+    </row>
+    <row r="29" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
+      <c r="A29" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B29" s="1">
         <v>12</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C29" s="1">
         <v>1260.24</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D29" s="1">
         <v>11</v>
       </c>
-      <c r="E28" s="1">
+      <c r="E29" s="1">
         <v>1103.77</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F29" s="2">
         <v>11</v>
       </c>
-      <c r="G28" s="2">
+      <c r="G29" s="2">
         <v>1098.19</v>
       </c>
-      <c r="H28" s="1">
-        <v>10</v>
-      </c>
-      <c r="I28" s="1">
+      <c r="H29" s="1">
+        <v>10</v>
+      </c>
+      <c r="I29" s="1">
         <v>1104.6600000000001</v>
       </c>
-      <c r="J28" s="2">
+      <c r="J29" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K28" s="2">
+      <c r="K29" s="2">
         <f t="shared" si="5"/>
         <v>-0.51</v>
       </c>
-      <c r="L28" s="1">
+      <c r="L29" s="1">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="M28" s="1">
+      <c r="M29" s="1">
         <f t="shared" si="7"/>
         <v>-0.59</v>
       </c>
-      <c r="N28" s="12"/>
-      <c r="O28" s="13"/>
-      <c r="P28" s="14"/>
-    </row>
-    <row r="29" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
-      <c r="A29" s="6" t="s">
+      <c r="N29" s="12"/>
+      <c r="O29" s="24"/>
+      <c r="P29" s="13"/>
+    </row>
+    <row r="30" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
+      <c r="A30" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B30" s="1">
         <v>11</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C30" s="1">
         <v>1126.8800000000001</v>
       </c>
-      <c r="D29" s="1">
-        <v>10</v>
-      </c>
-      <c r="E29" s="1">
+      <c r="D30" s="1">
+        <v>10</v>
+      </c>
+      <c r="E30" s="1">
         <v>966.99</v>
       </c>
-      <c r="F29" s="2">
-        <v>10</v>
-      </c>
-      <c r="G29" s="2">
+      <c r="F30" s="2">
+        <v>10</v>
+      </c>
+      <c r="G30" s="2">
         <v>953.55</v>
       </c>
-      <c r="H29" s="1">
+      <c r="H30" s="1">
         <v>9</v>
       </c>
-      <c r="I29" s="1">
+      <c r="I30" s="1">
         <v>960.88</v>
       </c>
-      <c r="J29" s="2">
+      <c r="J30" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K29" s="2">
+      <c r="K30" s="2">
         <f t="shared" si="5"/>
         <v>-1.39</v>
       </c>
-      <c r="L29" s="1">
+      <c r="L30" s="1">
         <f t="shared" si="6"/>
         <v>11.11</v>
       </c>
-      <c r="M29" s="1">
+      <c r="M30" s="1">
         <f t="shared" si="7"/>
         <v>-0.76</v>
       </c>
-      <c r="N29" s="12"/>
-      <c r="O29" s="13"/>
-      <c r="P29" s="14"/>
-    </row>
-    <row r="30" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
-      <c r="A30" s="6" t="s">
+      <c r="N30" s="12"/>
+      <c r="O30" s="24"/>
+      <c r="P30" s="13"/>
+    </row>
+    <row r="31" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
+      <c r="A31" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B31" s="1">
         <v>13</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C31" s="1">
         <v>1386.28</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D31" s="1">
         <v>12</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E31" s="1">
         <v>1200.2</v>
       </c>
-      <c r="F30" s="3">
+      <c r="F31" s="3">
         <v>13</v>
       </c>
-      <c r="G30" s="3">
+      <c r="G31" s="3">
         <v>1179.8</v>
       </c>
-      <c r="H30" s="1">
+      <c r="H31" s="1">
         <v>11</v>
       </c>
-      <c r="I30" s="1">
+      <c r="I31" s="1">
         <v>1194.73</v>
       </c>
-      <c r="J30" s="3">
+      <c r="J31" s="3">
         <f t="shared" si="4"/>
         <v>8.33</v>
       </c>
-      <c r="K30" s="3">
+      <c r="K31" s="3">
         <f t="shared" si="5"/>
         <v>-1.7</v>
       </c>
-      <c r="L30" s="1">
+      <c r="L31" s="1">
         <f t="shared" si="6"/>
         <v>18.18</v>
       </c>
-      <c r="M30" s="1">
+      <c r="M31" s="1">
         <f t="shared" si="7"/>
         <v>-1.25</v>
       </c>
-      <c r="N30" s="12"/>
-      <c r="O30" s="13"/>
-      <c r="P30" s="14"/>
-    </row>
-    <row r="31" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
-      <c r="A31" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31" s="1">
-        <v>13</v>
-      </c>
-      <c r="C31" s="1">
-        <v>1289.46</v>
-      </c>
-      <c r="D31" s="1">
-        <v>11</v>
-      </c>
-      <c r="E31" s="1">
-        <v>1127.28</v>
-      </c>
-      <c r="F31" s="3">
-        <v>12</v>
-      </c>
-      <c r="G31" s="3">
-        <v>1114.3</v>
-      </c>
-      <c r="H31" s="1">
-        <v>10</v>
-      </c>
-      <c r="I31" s="1">
-        <v>1118.8399999999999</v>
-      </c>
-      <c r="J31" s="3">
-        <f t="shared" si="4"/>
-        <v>9.09</v>
-      </c>
-      <c r="K31" s="3">
-        <f t="shared" si="5"/>
-        <v>-1.1499999999999999</v>
-      </c>
-      <c r="L31" s="1">
-        <f t="shared" si="6"/>
-        <v>20</v>
-      </c>
-      <c r="M31" s="1">
-        <f t="shared" si="7"/>
-        <v>-0.41</v>
-      </c>
       <c r="N31" s="12"/>
-      <c r="O31" s="13"/>
-      <c r="P31" s="14"/>
+      <c r="O31" s="24"/>
+      <c r="P31" s="13"/>
     </row>
     <row r="32" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A32" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B32" s="1">
         <v>13</v>
       </c>
       <c r="C32" s="1">
-        <v>1309.6400000000001</v>
+        <v>1289.46</v>
       </c>
       <c r="D32" s="1">
         <v>11</v>
       </c>
       <c r="E32" s="1">
-        <v>1096.3800000000001</v>
+        <v>1127.28</v>
       </c>
       <c r="F32" s="3">
         <v>12</v>
       </c>
       <c r="G32" s="3">
-        <v>1090.1600000000001</v>
+        <v>1114.3</v>
       </c>
       <c r="H32" s="1">
         <v>10</v>
       </c>
       <c r="I32" s="1">
-        <v>1096.72</v>
+        <v>1118.8399999999999</v>
       </c>
       <c r="J32" s="3">
         <f t="shared" si="4"/>
@@ -2536,7 +2582,7 @@
       </c>
       <c r="K32" s="3">
         <f t="shared" si="5"/>
-        <v>-0.56999999999999995</v>
+        <v>-1.1499999999999999</v>
       </c>
       <c r="L32" s="1">
         <f t="shared" si="6"/>
@@ -2544,1433 +2590,1545 @@
       </c>
       <c r="M32" s="1">
         <f t="shared" si="7"/>
-        <v>-0.6</v>
+        <v>-0.41</v>
       </c>
       <c r="N32" s="12"/>
-      <c r="O32" s="13"/>
-      <c r="P32" s="14"/>
+      <c r="O32" s="24"/>
+      <c r="P32" s="13"/>
     </row>
     <row r="33" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A33" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B33" s="1">
+        <v>13</v>
+      </c>
+      <c r="C33" s="1">
+        <v>1309.6400000000001</v>
+      </c>
+      <c r="D33" s="1">
         <v>11</v>
       </c>
-      <c r="C33" s="1">
-        <v>1181.53</v>
-      </c>
-      <c r="D33" s="1">
-        <v>9</v>
-      </c>
       <c r="E33" s="1">
-        <v>982.14</v>
+        <v>1096.3800000000001</v>
       </c>
       <c r="F33" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G33" s="3">
-        <v>984.72</v>
+        <v>1090.1600000000001</v>
       </c>
       <c r="H33" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I33" s="1">
-        <v>982.14</v>
+        <v>1096.72</v>
       </c>
       <c r="J33" s="3">
         <f t="shared" si="4"/>
-        <v>11.11</v>
+        <v>9.09</v>
       </c>
       <c r="K33" s="3">
         <f t="shared" si="5"/>
-        <v>0.26</v>
+        <v>-0.56999999999999995</v>
       </c>
       <c r="L33" s="1">
         <f t="shared" si="6"/>
-        <v>11.11</v>
+        <v>20</v>
       </c>
       <c r="M33" s="1">
         <f t="shared" si="7"/>
-        <v>0.26</v>
+        <v>-0.6</v>
       </c>
       <c r="N33" s="12"/>
-      <c r="O33" s="13"/>
-      <c r="P33" s="14"/>
+      <c r="O33" s="24"/>
+      <c r="P33" s="13"/>
     </row>
     <row r="34" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A34" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B34" s="1">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C34" s="1">
-        <v>1687.77</v>
+        <v>1181.53</v>
       </c>
       <c r="D34" s="1">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E34" s="1">
-        <v>1442.28</v>
+        <v>982.14</v>
       </c>
       <c r="F34" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G34" s="3">
-        <v>1234.68</v>
+        <v>984.72</v>
       </c>
       <c r="H34" s="1">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I34" s="1">
-        <v>1252.3699999999999</v>
+        <v>982.14</v>
       </c>
       <c r="J34" s="3">
         <f t="shared" si="4"/>
-        <v>50</v>
+        <v>11.11</v>
       </c>
       <c r="K34" s="3">
         <f t="shared" si="5"/>
-        <v>-14.39</v>
+        <v>0.26</v>
       </c>
       <c r="L34" s="1">
         <f t="shared" si="6"/>
-        <v>50</v>
+        <v>11.11</v>
       </c>
       <c r="M34" s="1">
         <f t="shared" si="7"/>
-        <v>-1.41</v>
-      </c>
-      <c r="N34" s="12"/>
-      <c r="O34" s="13"/>
-      <c r="P34" s="14"/>
-    </row>
-    <row r="35" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
-      <c r="A35" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B35" s="1">
-        <v>4</v>
-      </c>
-      <c r="C35" s="1">
-        <v>1513.5</v>
-      </c>
-      <c r="D35" s="1">
-        <v>4</v>
-      </c>
-      <c r="E35" s="1">
-        <v>1212.49</v>
-      </c>
-      <c r="F35" s="3">
+        <v>0.26</v>
+      </c>
+      <c r="N34" s="14"/>
+      <c r="O34" s="15"/>
+      <c r="P34" s="16"/>
+    </row>
+    <row r="35" spans="1:16" ht="18" customHeight="1" collapsed="1" thickBot="1">
+      <c r="A35" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B35" s="19" t="str">
+        <f>COUNTA(A36:A46) &amp; " 筆"</f>
+        <v>11 筆</v>
+      </c>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+      <c r="H35" s="20"/>
+      <c r="I35" s="20"/>
+      <c r="J35" s="20"/>
+      <c r="K35" s="20"/>
+      <c r="L35" s="20"/>
+      <c r="M35" s="21"/>
+      <c r="N35" s="1">
         <v>6</v>
       </c>
-      <c r="G35" s="3">
-        <v>1103.74</v>
-      </c>
-      <c r="H35" s="1">
-        <v>3</v>
-      </c>
-      <c r="I35" s="1">
-        <v>1191.7</v>
-      </c>
-      <c r="J35" s="3">
-        <f t="shared" si="4"/>
-        <v>50</v>
-      </c>
-      <c r="K35" s="3">
-        <f t="shared" si="5"/>
-        <v>-8.9700000000000006</v>
-      </c>
-      <c r="L35" s="1">
-        <f t="shared" si="6"/>
-        <v>100</v>
-      </c>
-      <c r="M35" s="1">
-        <f t="shared" si="7"/>
-        <v>-7.38</v>
-      </c>
-      <c r="N35" s="12"/>
-      <c r="O35" s="13"/>
-      <c r="P35" s="14"/>
+      <c r="O35" s="1">
+        <v>0</v>
+      </c>
+      <c r="P35" s="1">
+        <v>5</v>
+      </c>
     </row>
     <row r="36" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A36" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B36" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C36" s="1">
-        <v>1425.91</v>
+        <v>1687.77</v>
       </c>
       <c r="D36" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E36" s="1">
-        <v>1197.67</v>
+        <v>1442.28</v>
       </c>
       <c r="F36" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G36" s="3">
-        <v>964.76</v>
+        <v>1234.68</v>
       </c>
       <c r="H36" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I36" s="1">
-        <v>939.5</v>
+        <v>1252.3699999999999</v>
       </c>
       <c r="J36" s="3">
-        <f t="shared" si="4"/>
-        <v>66.67</v>
+        <f>ROUND(((F36-D36)/D36)*100,2)</f>
+        <v>50</v>
       </c>
       <c r="K36" s="3">
-        <f t="shared" si="5"/>
-        <v>-19.45</v>
+        <f>ROUND(((G36-E36)/E36)*100,2)</f>
+        <v>-14.39</v>
       </c>
       <c r="L36" s="1">
-        <f t="shared" si="6"/>
-        <v>66.67</v>
+        <f>ROUND(((F36-H36)/H36)*100,2)</f>
+        <v>50</v>
       </c>
       <c r="M36" s="1">
-        <f t="shared" si="7"/>
-        <v>2.69</v>
-      </c>
-      <c r="N36" s="12"/>
-      <c r="O36" s="13"/>
-      <c r="P36" s="14"/>
+        <f>ROUND(((G36-I36)/I36)*100,2)</f>
+        <v>-1.41</v>
+      </c>
+      <c r="N36" s="9"/>
+      <c r="O36" s="10"/>
+      <c r="P36" s="11"/>
     </row>
     <row r="37" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A37" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B37" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C37" s="1">
-        <v>1122.0899999999999</v>
+        <v>1513.5</v>
       </c>
       <c r="D37" s="1">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E37" s="1">
-        <v>854.31</v>
-      </c>
-      <c r="F37" s="2">
-        <v>4</v>
-      </c>
-      <c r="G37" s="2">
-        <v>766.23</v>
+        <v>1212.49</v>
+      </c>
+      <c r="F37" s="3">
+        <v>6</v>
+      </c>
+      <c r="G37" s="3">
+        <v>1103.74</v>
       </c>
       <c r="H37" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I37" s="1">
-        <v>825.52</v>
-      </c>
-      <c r="J37" s="2">
-        <f t="shared" si="4"/>
-        <v>-60</v>
-      </c>
-      <c r="K37" s="2">
-        <f t="shared" si="5"/>
-        <v>-10.31</v>
+        <v>1191.7</v>
+      </c>
+      <c r="J37" s="3">
+        <f>ROUND(((F37-D37)/D37)*100,2)</f>
+        <v>50</v>
+      </c>
+      <c r="K37" s="3">
+        <f>ROUND(((G37-E37)/E37)*100,2)</f>
+        <v>-8.9700000000000006</v>
       </c>
       <c r="L37" s="1">
-        <f t="shared" si="6"/>
+        <f>ROUND(((F37-H37)/H37)*100,2)</f>
         <v>100</v>
       </c>
       <c r="M37" s="1">
-        <f t="shared" si="7"/>
-        <v>-7.18</v>
+        <f>ROUND(((G37-I37)/I37)*100,2)</f>
+        <v>-7.38</v>
       </c>
       <c r="N37" s="12"/>
-      <c r="O37" s="13"/>
-      <c r="P37" s="14"/>
+      <c r="O37" s="24"/>
+      <c r="P37" s="13"/>
     </row>
     <row r="38" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A38" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B38" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C38" s="1">
-        <v>1454.03</v>
+        <v>1425.91</v>
       </c>
       <c r="D38" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E38" s="1">
-        <v>1337.65</v>
-      </c>
-      <c r="F38" s="2">
-        <v>4</v>
-      </c>
-      <c r="G38" s="2">
-        <v>1078.75</v>
+        <v>1197.67</v>
+      </c>
+      <c r="F38" s="3">
+        <v>5</v>
+      </c>
+      <c r="G38" s="3">
+        <v>964.76</v>
       </c>
       <c r="H38" s="1">
         <v>3</v>
       </c>
       <c r="I38" s="1">
-        <v>994.43</v>
-      </c>
-      <c r="J38" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K38" s="2">
-        <f t="shared" si="5"/>
-        <v>-19.350000000000001</v>
+        <v>939.5</v>
+      </c>
+      <c r="J38" s="3">
+        <f>ROUND(((F38-D38)/D38)*100,2)</f>
+        <v>66.67</v>
+      </c>
+      <c r="K38" s="3">
+        <f>ROUND(((G38-E38)/E38)*100,2)</f>
+        <v>-19.45</v>
       </c>
       <c r="L38" s="1">
-        <f t="shared" si="6"/>
-        <v>33.33</v>
+        <f>ROUND(((F38-H38)/H38)*100,2)</f>
+        <v>66.67</v>
       </c>
       <c r="M38" s="1">
-        <f t="shared" si="7"/>
-        <v>8.48</v>
+        <f>ROUND(((G38-I38)/I38)*100,2)</f>
+        <v>2.69</v>
       </c>
       <c r="N38" s="12"/>
-      <c r="O38" s="13"/>
-      <c r="P38" s="14"/>
+      <c r="O38" s="24"/>
+      <c r="P38" s="13"/>
     </row>
     <row r="39" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A39" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B39" s="1">
         <v>3</v>
       </c>
       <c r="C39" s="1">
-        <v>1268.71</v>
+        <v>1122.0899999999999</v>
       </c>
       <c r="D39" s="1">
+        <v>10</v>
+      </c>
+      <c r="E39" s="1">
+        <v>854.31</v>
+      </c>
+      <c r="F39" s="2">
         <v>4</v>
       </c>
-      <c r="E39" s="1">
-        <v>1114.76</v>
-      </c>
-      <c r="F39" s="2">
-        <v>3</v>
-      </c>
       <c r="G39" s="2">
-        <v>1005.14</v>
+        <v>766.23</v>
       </c>
       <c r="H39" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I39" s="1">
-        <v>906.14</v>
+        <v>825.52</v>
       </c>
       <c r="J39" s="2">
-        <f t="shared" si="4"/>
-        <v>-25</v>
+        <f>ROUND(((F39-D39)/D39)*100,2)</f>
+        <v>-60</v>
       </c>
       <c r="K39" s="2">
-        <f t="shared" si="5"/>
-        <v>-9.83</v>
+        <f>ROUND(((G39-E39)/E39)*100,2)</f>
+        <v>-10.31</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>ROUND(((F39-H39)/H39)*100,2)</f>
+        <v>100</v>
       </c>
       <c r="M39" s="1">
-        <f t="shared" si="7"/>
-        <v>10.93</v>
+        <f>ROUND(((G39-I39)/I39)*100,2)</f>
+        <v>-7.18</v>
       </c>
       <c r="N39" s="12"/>
-      <c r="O39" s="13"/>
-      <c r="P39" s="14"/>
+      <c r="O39" s="24"/>
+      <c r="P39" s="13"/>
     </row>
     <row r="40" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A40" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B40" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C40" s="1">
-        <v>1207.1500000000001</v>
+        <v>1454.03</v>
       </c>
       <c r="D40" s="1">
         <v>4</v>
       </c>
       <c r="E40" s="1">
-        <v>1055.71</v>
+        <v>1337.65</v>
       </c>
       <c r="F40" s="2">
         <v>4</v>
       </c>
       <c r="G40" s="2">
-        <v>865.63</v>
+        <v>1078.75</v>
       </c>
       <c r="H40" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I40" s="1">
-        <v>890.61</v>
+        <v>994.43</v>
       </c>
       <c r="J40" s="2">
-        <f t="shared" si="4"/>
+        <f>ROUND(((F40-D40)/D40)*100,2)</f>
         <v>0</v>
       </c>
       <c r="K40" s="2">
-        <f t="shared" si="5"/>
-        <v>-18</v>
+        <f>ROUND(((G40-E40)/E40)*100,2)</f>
+        <v>-19.350000000000001</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="6"/>
-        <v>100</v>
+        <f>ROUND(((F40-H40)/H40)*100,2)</f>
+        <v>33.33</v>
       </c>
       <c r="M40" s="1">
-        <f t="shared" si="7"/>
-        <v>-2.8</v>
+        <f>ROUND(((G40-I40)/I40)*100,2)</f>
+        <v>8.48</v>
       </c>
       <c r="N40" s="12"/>
-      <c r="O40" s="13"/>
-      <c r="P40" s="14"/>
+      <c r="O40" s="24"/>
+      <c r="P40" s="13"/>
     </row>
     <row r="41" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A41" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B41" s="1">
         <v>3</v>
       </c>
       <c r="C41" s="1">
-        <v>970.12</v>
+        <v>1268.71</v>
       </c>
       <c r="D41" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E41" s="1">
-        <v>860.53</v>
+        <v>1114.76</v>
       </c>
       <c r="F41" s="2">
         <v>3</v>
       </c>
       <c r="G41" s="2">
-        <v>727.64</v>
+        <v>1005.14</v>
       </c>
       <c r="H41" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I41" s="1">
-        <v>726.82</v>
+        <v>906.14</v>
       </c>
       <c r="J41" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f>ROUND(((F41-D41)/D41)*100,2)</f>
+        <v>-25</v>
       </c>
       <c r="K41" s="2">
-        <f t="shared" si="5"/>
-        <v>-15.44</v>
+        <f>ROUND(((G41-E41)/E41)*100,2)</f>
+        <v>-9.83</v>
       </c>
       <c r="L41" s="1">
-        <f t="shared" si="6"/>
-        <v>50</v>
+        <f>ROUND(((F41-H41)/H41)*100,2)</f>
+        <v>0</v>
       </c>
       <c r="M41" s="1">
-        <f t="shared" si="7"/>
-        <v>0.11</v>
+        <f>ROUND(((G41-I41)/I41)*100,2)</f>
+        <v>10.93</v>
       </c>
       <c r="N41" s="12"/>
-      <c r="O41" s="13"/>
-      <c r="P41" s="14"/>
+      <c r="O41" s="24"/>
+      <c r="P41" s="13"/>
     </row>
     <row r="42" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A42" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B42" s="1">
         <v>3</v>
       </c>
       <c r="C42" s="1">
-        <v>1341.3</v>
+        <v>1207.1500000000001</v>
       </c>
       <c r="D42" s="1">
+        <v>4</v>
+      </c>
+      <c r="E42" s="1">
+        <v>1055.71</v>
+      </c>
+      <c r="F42" s="2">
+        <v>4</v>
+      </c>
+      <c r="G42" s="2">
+        <v>865.63</v>
+      </c>
+      <c r="H42" s="1">
         <v>2</v>
       </c>
-      <c r="E42" s="1">
-        <v>895.46749999999997</v>
-      </c>
-      <c r="F42" s="3">
-        <v>4</v>
-      </c>
-      <c r="G42" s="3">
-        <v>912.61</v>
-      </c>
-      <c r="H42" s="1">
-        <v>3</v>
-      </c>
       <c r="I42" s="1">
-        <v>909.16</v>
-      </c>
-      <c r="J42" s="3">
-        <f t="shared" si="4"/>
+        <v>890.61</v>
+      </c>
+      <c r="J42" s="2">
+        <f>ROUND(((F42-D42)/D42)*100,2)</f>
+        <v>0</v>
+      </c>
+      <c r="K42" s="2">
+        <f>ROUND(((G42-E42)/E42)*100,2)</f>
+        <v>-18</v>
+      </c>
+      <c r="L42" s="1">
+        <f>ROUND(((F42-H42)/H42)*100,2)</f>
         <v>100</v>
       </c>
-      <c r="K42" s="3">
-        <f t="shared" si="5"/>
-        <v>1.91</v>
-      </c>
-      <c r="L42" s="1">
-        <f t="shared" si="6"/>
-        <v>33.33</v>
-      </c>
       <c r="M42" s="1">
-        <f t="shared" si="7"/>
-        <v>0.38</v>
+        <f>ROUND(((G42-I42)/I42)*100,2)</f>
+        <v>-2.8</v>
       </c>
       <c r="N42" s="12"/>
-      <c r="O42" s="13"/>
-      <c r="P42" s="14"/>
+      <c r="O42" s="24"/>
+      <c r="P42" s="13"/>
     </row>
     <row r="43" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A43" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B43" s="1">
         <v>3</v>
       </c>
       <c r="C43" s="1">
-        <v>1519.76</v>
+        <v>970.12</v>
       </c>
       <c r="D43" s="1">
+        <v>3</v>
+      </c>
+      <c r="E43" s="1">
+        <v>860.53</v>
+      </c>
+      <c r="F43" s="2">
+        <v>3</v>
+      </c>
+      <c r="G43" s="2">
+        <v>727.64</v>
+      </c>
+      <c r="H43" s="1">
         <v>2</v>
       </c>
-      <c r="E43" s="1">
-        <v>942.94849999999997</v>
-      </c>
-      <c r="F43" s="3">
-        <v>4</v>
-      </c>
-      <c r="G43" s="3">
-        <v>1022.23</v>
-      </c>
-      <c r="H43" s="1">
-        <v>3</v>
-      </c>
       <c r="I43" s="1">
-        <v>939.37</v>
-      </c>
-      <c r="J43" s="3">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="K43" s="3">
-        <f t="shared" si="5"/>
-        <v>8.41</v>
+        <v>726.82</v>
+      </c>
+      <c r="J43" s="2">
+        <f>ROUND(((F43-D43)/D43)*100,2)</f>
+        <v>0</v>
+      </c>
+      <c r="K43" s="2">
+        <f>ROUND(((G43-E43)/E43)*100,2)</f>
+        <v>-15.44</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="6"/>
-        <v>33.33</v>
+        <f>ROUND(((F43-H43)/H43)*100,2)</f>
+        <v>50</v>
       </c>
       <c r="M43" s="1">
-        <f t="shared" si="7"/>
-        <v>8.82</v>
+        <f>ROUND(((G43-I43)/I43)*100,2)</f>
+        <v>0.11</v>
       </c>
       <c r="N43" s="12"/>
-      <c r="O43" s="13"/>
-      <c r="P43" s="14"/>
+      <c r="O43" s="24"/>
+      <c r="P43" s="13"/>
     </row>
     <row r="44" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A44" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="1">
+        <v>3</v>
+      </c>
+      <c r="C44" s="1">
+        <v>1341.3</v>
+      </c>
+      <c r="D44" s="1">
+        <v>2</v>
+      </c>
+      <c r="E44" s="1">
+        <v>895.46749999999997</v>
+      </c>
+      <c r="F44" s="3">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3">
+        <v>912.61</v>
+      </c>
+      <c r="H44" s="1">
+        <v>3</v>
+      </c>
+      <c r="I44" s="1">
+        <v>909.16</v>
+      </c>
+      <c r="J44" s="3">
+        <f>ROUND(((F44-D44)/D44)*100,2)</f>
+        <v>100</v>
+      </c>
+      <c r="K44" s="3">
+        <f>ROUND(((G44-E44)/E44)*100,2)</f>
+        <v>1.91</v>
+      </c>
+      <c r="L44" s="1">
+        <f>ROUND(((F44-H44)/H44)*100,2)</f>
+        <v>33.33</v>
+      </c>
+      <c r="M44" s="1">
+        <f>ROUND(((G44-I44)/I44)*100,2)</f>
+        <v>0.38</v>
+      </c>
+      <c r="N44" s="12"/>
+      <c r="O44" s="24"/>
+      <c r="P44" s="13"/>
+    </row>
+    <row r="45" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
+      <c r="A45" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="1">
+        <v>3</v>
+      </c>
+      <c r="C45" s="1">
+        <v>1519.76</v>
+      </c>
+      <c r="D45" s="1">
+        <v>2</v>
+      </c>
+      <c r="E45" s="1">
+        <v>942.94849999999997</v>
+      </c>
+      <c r="F45" s="3">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3">
+        <v>1022.23</v>
+      </c>
+      <c r="H45" s="1">
+        <v>3</v>
+      </c>
+      <c r="I45" s="1">
+        <v>939.37</v>
+      </c>
+      <c r="J45" s="3">
+        <f>ROUND(((F45-D45)/D45)*100,2)</f>
+        <v>100</v>
+      </c>
+      <c r="K45" s="3">
+        <f>ROUND(((G45-E45)/E45)*100,2)</f>
+        <v>8.41</v>
+      </c>
+      <c r="L45" s="1">
+        <f>ROUND(((F45-H45)/H45)*100,2)</f>
+        <v>33.33</v>
+      </c>
+      <c r="M45" s="1">
+        <f>ROUND(((G45-I45)/I45)*100,2)</f>
+        <v>8.82</v>
+      </c>
+      <c r="N45" s="12"/>
+      <c r="O45" s="24"/>
+      <c r="P45" s="13"/>
+    </row>
+    <row r="46" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
+      <c r="A46" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B44" s="1">
-        <v>3</v>
-      </c>
-      <c r="C44" s="1">
+      <c r="B46" s="1">
+        <v>3</v>
+      </c>
+      <c r="C46" s="1">
         <v>1113.53</v>
       </c>
-      <c r="D44" s="1">
-        <v>3</v>
-      </c>
-      <c r="E44" s="1">
+      <c r="D46" s="1">
+        <v>3</v>
+      </c>
+      <c r="E46" s="1">
         <v>1049.6199999999999</v>
       </c>
-      <c r="F44" s="2">
-        <v>3</v>
-      </c>
-      <c r="G44" s="2">
+      <c r="F46" s="2">
+        <v>3</v>
+      </c>
+      <c r="G46" s="2">
         <v>802.69</v>
       </c>
-      <c r="H44" s="1">
+      <c r="H46" s="1">
         <v>2</v>
       </c>
-      <c r="I44" s="1">
+      <c r="I46" s="1">
         <v>885.71</v>
       </c>
-      <c r="J44" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K44" s="2">
-        <f t="shared" si="5"/>
+      <c r="J46" s="2">
+        <f>ROUND(((F46-D46)/D46)*100,2)</f>
+        <v>0</v>
+      </c>
+      <c r="K46" s="2">
+        <f>ROUND(((G46-E46)/E46)*100,2)</f>
         <v>-23.53</v>
       </c>
-      <c r="L44" s="1">
-        <f t="shared" si="6"/>
+      <c r="L46" s="1">
+        <f>ROUND(((F46-H46)/H46)*100,2)</f>
         <v>50</v>
       </c>
-      <c r="M44" s="1">
-        <f t="shared" si="7"/>
+      <c r="M46" s="1">
+        <f>ROUND(((G46-I46)/I46)*100,2)</f>
         <v>-9.3699999999999992</v>
       </c>
-      <c r="N44" s="15"/>
-      <c r="O44" s="16"/>
-      <c r="P44" s="17"/>
-    </row>
-    <row r="45" spans="1:16" ht="17.25" collapsed="1" thickBot="1">
-      <c r="A45" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="B45" s="20" t="str">
-        <f>COUNTA(A46:A61) &amp; " 筆"</f>
-        <v>16 筆</v>
-      </c>
-      <c r="C45" s="21"/>
-      <c r="D45" s="21"/>
-      <c r="E45" s="21"/>
-      <c r="F45" s="21"/>
-      <c r="G45" s="21"/>
-      <c r="H45" s="21"/>
-      <c r="I45" s="21"/>
-      <c r="J45" s="21"/>
-      <c r="K45" s="21"/>
-      <c r="L45" s="21"/>
-      <c r="M45" s="22"/>
-      <c r="N45" s="1">
-        <v>6</v>
-      </c>
-      <c r="O45" s="1">
-        <v>0</v>
-      </c>
-      <c r="P45" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" ht="17.25" hidden="1" outlineLevel="1" thickBot="1">
-      <c r="A46" s="5" t="s">
+      <c r="N46" s="14"/>
+      <c r="O46" s="15"/>
+      <c r="P46" s="16"/>
+    </row>
+    <row r="47" spans="1:16" ht="18" customHeight="1" collapsed="1" thickBot="1">
+      <c r="A47" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B47" s="19" t="str">
+        <f>COUNTA(A48:A55) &amp; " 筆"</f>
+        <v>8 筆</v>
+      </c>
+      <c r="C47" s="20"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="20"/>
+      <c r="H47" s="20"/>
+      <c r="I47" s="20"/>
+      <c r="J47" s="20"/>
+      <c r="K47" s="20"/>
+      <c r="L47" s="20"/>
+      <c r="M47" s="21"/>
+      <c r="N47" s="1">
+        <v>5</v>
+      </c>
+      <c r="O47" s="1">
+        <v>0</v>
+      </c>
+      <c r="P47" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" ht="17.25" hidden="1" outlineLevel="1" thickBot="1">
+      <c r="A48" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B48" s="1">
         <v>16</v>
       </c>
-      <c r="C46" s="1">
+      <c r="C48" s="1">
         <v>1828</v>
       </c>
-      <c r="D46" s="1">
+      <c r="D48" s="1">
         <v>16</v>
       </c>
-      <c r="E46" s="1">
+      <c r="E48" s="1">
         <v>1656.59</v>
       </c>
-      <c r="F46" s="2">
+      <c r="F48" s="2">
         <v>16</v>
       </c>
-      <c r="G46" s="2">
+      <c r="G48" s="2">
         <v>1652.36</v>
       </c>
-      <c r="H46" s="1">
+      <c r="H48" s="1">
         <v>14</v>
       </c>
-      <c r="I46" s="1">
+      <c r="I48" s="1">
         <v>1696.95</v>
       </c>
-      <c r="J46" s="2">
-        <f t="shared" ref="J46:J61" si="8">ROUND(((F46-D46)/D46)*100,2)</f>
-        <v>0</v>
-      </c>
-      <c r="K46" s="2">
-        <f t="shared" ref="K46:K61" si="9">ROUND(((G46-E46)/E46)*100,2)</f>
+      <c r="J48" s="2">
+        <f t="shared" ref="J48:J55" si="8">ROUND(((F48-D48)/D48)*100,2)</f>
+        <v>0</v>
+      </c>
+      <c r="K48" s="2">
+        <f t="shared" ref="K48:K55" si="9">ROUND(((G48-E48)/E48)*100,2)</f>
         <v>-0.26</v>
       </c>
-      <c r="L46" s="1">
-        <f t="shared" ref="L46:L61" si="10">ROUND(((F46-H46)/H46)*100,2)</f>
+      <c r="L48" s="1">
+        <f t="shared" ref="L48:L55" si="10">ROUND(((F48-H48)/H48)*100,2)</f>
         <v>14.29</v>
       </c>
-      <c r="M46" s="1">
-        <f t="shared" ref="M46:M61" si="11">ROUND(((G46-I46)/I46)*100,2)</f>
+      <c r="M48" s="1">
+        <f t="shared" ref="M48:M55" si="11">ROUND(((G48-I48)/I48)*100,2)</f>
         <v>-2.63</v>
       </c>
-      <c r="N46" s="9"/>
-      <c r="O46" s="10"/>
-      <c r="P46" s="11"/>
-    </row>
-    <row r="47" spans="1:16" ht="17.25" hidden="1" outlineLevel="1" thickBot="1">
-      <c r="A47" s="5" t="s">
+      <c r="N48" s="9"/>
+      <c r="O48" s="10"/>
+      <c r="P48" s="11"/>
+    </row>
+    <row r="49" spans="1:16" ht="17.25" hidden="1" outlineLevel="1" thickBot="1">
+      <c r="A49" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B47" s="1">
+      <c r="B49" s="1">
         <v>15</v>
       </c>
-      <c r="C47" s="1">
+      <c r="C49" s="1">
         <v>1671.75</v>
       </c>
-      <c r="D47" s="1">
+      <c r="D49" s="1">
         <v>13</v>
       </c>
-      <c r="E47" s="1">
+      <c r="E49" s="1">
         <v>1532.25</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F49" s="3">
         <v>14</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G49" s="3">
         <v>1486.88</v>
       </c>
-      <c r="H47" s="1">
+      <c r="H49" s="1">
         <v>12</v>
       </c>
-      <c r="I47" s="1">
+      <c r="I49" s="1">
         <v>1554.75</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J49" s="3">
         <f t="shared" si="8"/>
         <v>7.69</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K49" s="3">
         <f t="shared" si="9"/>
         <v>-2.96</v>
       </c>
-      <c r="L47" s="1">
+      <c r="L49" s="1">
         <f t="shared" si="10"/>
         <v>16.670000000000002</v>
       </c>
-      <c r="M47" s="1">
+      <c r="M49" s="1">
         <f t="shared" si="11"/>
         <v>-4.37</v>
       </c>
-      <c r="N47" s="12"/>
-      <c r="O47" s="13"/>
-      <c r="P47" s="14"/>
-    </row>
-    <row r="48" spans="1:16" ht="17.25" hidden="1" outlineLevel="1" thickBot="1">
-      <c r="A48" s="5" t="s">
+      <c r="N49" s="12"/>
+      <c r="O49" s="24"/>
+      <c r="P49" s="13"/>
+    </row>
+    <row r="50" spans="1:16" ht="17.25" hidden="1" outlineLevel="1" thickBot="1">
+      <c r="A50" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B48" s="1">
+      <c r="B50" s="1">
         <v>13</v>
       </c>
-      <c r="C48" s="1">
+      <c r="C50" s="1">
         <v>1417.78</v>
       </c>
-      <c r="D48" s="1">
+      <c r="D50" s="1">
         <v>12</v>
       </c>
-      <c r="E48" s="1">
+      <c r="E50" s="1">
         <v>1344.03</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F50" s="2">
         <v>12</v>
       </c>
-      <c r="G48" s="2">
+      <c r="G50" s="2">
         <v>1297.3499999999999</v>
       </c>
-      <c r="H48" s="1">
+      <c r="H50" s="1">
         <v>11</v>
       </c>
-      <c r="I48" s="1">
+      <c r="I50" s="1">
         <v>1261.67</v>
       </c>
-      <c r="J48" s="2">
+      <c r="J50" s="2">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="K48" s="2">
+      <c r="K50" s="2">
         <f t="shared" si="9"/>
         <v>-3.47</v>
       </c>
-      <c r="L48" s="1">
+      <c r="L50" s="1">
         <f t="shared" si="10"/>
         <v>9.09</v>
       </c>
-      <c r="M48" s="1">
+      <c r="M50" s="1">
         <f t="shared" si="11"/>
         <v>2.83</v>
       </c>
-      <c r="N48" s="12"/>
-      <c r="O48" s="13"/>
-      <c r="P48" s="14"/>
-    </row>
-    <row r="49" spans="1:16" ht="17.25" hidden="1" outlineLevel="1" thickBot="1">
-      <c r="A49" s="5" t="s">
+      <c r="N50" s="12"/>
+      <c r="O50" s="24"/>
+      <c r="P50" s="13"/>
+    </row>
+    <row r="51" spans="1:16" ht="17.25" hidden="1" outlineLevel="1" thickBot="1">
+      <c r="A51" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B49" s="1">
+      <c r="B51" s="1">
         <v>12</v>
       </c>
-      <c r="C49" s="1">
+      <c r="C51" s="1">
         <v>1312.42</v>
       </c>
-      <c r="D49" s="1">
+      <c r="D51" s="1">
         <v>11</v>
       </c>
-      <c r="E49" s="1">
+      <c r="E51" s="1">
         <v>1184.9000000000001</v>
       </c>
-      <c r="F49" s="2">
-        <v>10</v>
-      </c>
-      <c r="G49" s="2">
+      <c r="F51" s="2">
+        <v>10</v>
+      </c>
+      <c r="G51" s="2">
         <v>1173.68</v>
       </c>
-      <c r="H49" s="1">
-        <v>10</v>
-      </c>
-      <c r="I49" s="1">
+      <c r="H51" s="1">
+        <v>10</v>
+      </c>
+      <c r="I51" s="1">
         <v>1135.48</v>
       </c>
-      <c r="J49" s="2">
+      <c r="J51" s="2">
         <f t="shared" si="8"/>
         <v>-9.09</v>
       </c>
-      <c r="K49" s="2">
+      <c r="K51" s="2">
         <f t="shared" si="9"/>
         <v>-0.95</v>
       </c>
-      <c r="L49" s="1">
+      <c r="L51" s="1">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="M49" s="1">
+      <c r="M51" s="1">
         <f t="shared" si="11"/>
         <v>3.36</v>
       </c>
-      <c r="N49" s="12"/>
-      <c r="O49" s="13"/>
-      <c r="P49" s="14"/>
-    </row>
-    <row r="50" spans="1:16" ht="17.25" hidden="1" outlineLevel="1" thickBot="1">
-      <c r="A50" s="5" t="s">
+      <c r="N51" s="12"/>
+      <c r="O51" s="24"/>
+      <c r="P51" s="13"/>
+    </row>
+    <row r="52" spans="1:16" ht="17.25" hidden="1" outlineLevel="1" thickBot="1">
+      <c r="A52" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B50" s="1">
+      <c r="B52" s="1">
         <v>17</v>
       </c>
-      <c r="C50" s="1">
+      <c r="C52" s="1">
         <v>1751.5</v>
       </c>
-      <c r="D50" s="1">
+      <c r="D52" s="1">
         <v>14</v>
       </c>
-      <c r="E50" s="1">
+      <c r="E52" s="1">
         <v>1662.01</v>
       </c>
-      <c r="F50" s="3">
+      <c r="F52" s="3">
         <v>15</v>
       </c>
-      <c r="G50" s="3">
+      <c r="G52" s="3">
         <v>1555.81</v>
       </c>
-      <c r="H50" s="1">
+      <c r="H52" s="1">
         <v>13</v>
       </c>
-      <c r="I50" s="1">
+      <c r="I52" s="1">
         <v>1629.44</v>
       </c>
-      <c r="J50" s="3">
+      <c r="J52" s="3">
         <f t="shared" si="8"/>
         <v>7.14</v>
       </c>
-      <c r="K50" s="3">
+      <c r="K52" s="3">
         <f t="shared" si="9"/>
         <v>-6.39</v>
       </c>
-      <c r="L50" s="1">
+      <c r="L52" s="1">
         <f t="shared" si="10"/>
         <v>15.38</v>
       </c>
-      <c r="M50" s="1">
+      <c r="M52" s="1">
         <f t="shared" si="11"/>
         <v>-4.5199999999999996</v>
       </c>
-      <c r="N50" s="12"/>
-      <c r="O50" s="13"/>
-      <c r="P50" s="14"/>
-    </row>
-    <row r="51" spans="1:16" ht="17.25" hidden="1" outlineLevel="1" thickBot="1">
-      <c r="A51" s="5" t="s">
+      <c r="N52" s="12"/>
+      <c r="O52" s="24"/>
+      <c r="P52" s="13"/>
+    </row>
+    <row r="53" spans="1:16" ht="17.25" hidden="1" outlineLevel="1" thickBot="1">
+      <c r="A53" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B51" s="1">
+      <c r="B53" s="1">
         <v>14</v>
       </c>
-      <c r="C51" s="1">
+      <c r="C53" s="1">
         <v>1597.59</v>
       </c>
-      <c r="D51" s="1">
+      <c r="D53" s="1">
         <v>12</v>
       </c>
-      <c r="E51" s="1">
+      <c r="E53" s="1">
         <v>1344.03</v>
       </c>
-      <c r="F51" s="3">
+      <c r="F53" s="3">
         <v>13</v>
       </c>
-      <c r="G51" s="3">
+      <c r="G53" s="3">
         <v>1405.73</v>
       </c>
-      <c r="H51" s="1">
+      <c r="H53" s="1">
         <v>11</v>
       </c>
-      <c r="I51" s="1">
+      <c r="I53" s="1">
         <v>1424.73</v>
       </c>
-      <c r="J51" s="3">
+      <c r="J53" s="3">
         <f t="shared" si="8"/>
         <v>8.33</v>
       </c>
-      <c r="K51" s="3">
+      <c r="K53" s="3">
         <f t="shared" si="9"/>
         <v>4.59</v>
       </c>
-      <c r="L51" s="1">
+      <c r="L53" s="1">
         <f t="shared" si="10"/>
         <v>18.18</v>
       </c>
-      <c r="M51" s="1">
+      <c r="M53" s="1">
         <f t="shared" si="11"/>
         <v>-1.33</v>
       </c>
-      <c r="N51" s="12"/>
-      <c r="O51" s="13"/>
-      <c r="P51" s="14"/>
-    </row>
-    <row r="52" spans="1:16" ht="17.25" hidden="1" outlineLevel="1" thickBot="1">
-      <c r="A52" s="5" t="s">
+      <c r="N53" s="12"/>
+      <c r="O53" s="24"/>
+      <c r="P53" s="13"/>
+    </row>
+    <row r="54" spans="1:16" ht="17.25" hidden="1" outlineLevel="1" thickBot="1">
+      <c r="A54" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B52" s="1">
+      <c r="B54" s="1">
         <v>13</v>
       </c>
-      <c r="C52" s="1">
+      <c r="C54" s="1">
         <v>1519.67</v>
       </c>
-      <c r="D52" s="1">
+      <c r="D54" s="1">
         <v>12</v>
       </c>
-      <c r="E52" s="1">
+      <c r="E54" s="1">
         <v>1263.07</v>
       </c>
-      <c r="F52" s="2">
+      <c r="F54" s="2">
         <v>12</v>
       </c>
-      <c r="G52" s="2">
+      <c r="G54" s="2">
         <v>1251.25</v>
       </c>
-      <c r="H52" s="1">
+      <c r="H54" s="1">
         <v>11</v>
       </c>
-      <c r="I52" s="1">
+      <c r="I54" s="1">
         <v>1230.48</v>
       </c>
-      <c r="J52" s="2">
+      <c r="J54" s="2">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="K52" s="2">
+      <c r="K54" s="2">
         <f t="shared" si="9"/>
         <v>-0.94</v>
       </c>
-      <c r="L52" s="1">
+      <c r="L54" s="1">
         <f t="shared" si="10"/>
         <v>9.09</v>
       </c>
-      <c r="M52" s="1">
+      <c r="M54" s="1">
         <f t="shared" si="11"/>
         <v>1.69</v>
       </c>
-      <c r="N52" s="12"/>
-      <c r="O52" s="13"/>
-      <c r="P52" s="14"/>
-    </row>
-    <row r="53" spans="1:16" ht="17.25" hidden="1" outlineLevel="1" thickBot="1">
-      <c r="A53" s="5" t="s">
+      <c r="N54" s="12"/>
+      <c r="O54" s="24"/>
+      <c r="P54" s="13"/>
+    </row>
+    <row r="55" spans="1:16" ht="17.25" hidden="1" outlineLevel="1" thickBot="1">
+      <c r="A55" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="1">
+      <c r="B55" s="1">
         <v>12</v>
       </c>
-      <c r="C53" s="1">
+      <c r="C55" s="1">
         <v>1376.49</v>
       </c>
-      <c r="D53" s="1">
+      <c r="D55" s="1">
         <v>11</v>
       </c>
-      <c r="E53" s="1">
+      <c r="E55" s="1">
         <v>1144.94</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F55" s="2">
         <v>11</v>
       </c>
-      <c r="G53" s="2">
+      <c r="G55" s="2">
         <v>1140.6600000000001</v>
       </c>
-      <c r="H53" s="1">
-        <v>10</v>
-      </c>
-      <c r="I53" s="1">
+      <c r="H55" s="1">
+        <v>10</v>
+      </c>
+      <c r="I55" s="1">
         <v>1139.82</v>
       </c>
-      <c r="J53" s="2">
+      <c r="J55" s="2">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="K53" s="2">
+      <c r="K55" s="2">
         <f t="shared" si="9"/>
         <v>-0.37</v>
       </c>
-      <c r="L53" s="1">
+      <c r="L55" s="1">
         <f t="shared" si="10"/>
         <v>10</v>
       </c>
-      <c r="M53" s="1">
+      <c r="M55" s="1">
         <f t="shared" si="11"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="N53" s="12"/>
-      <c r="O53" s="13"/>
-      <c r="P53" s="14"/>
-    </row>
-    <row r="54" spans="1:16" ht="17.25" hidden="1" outlineLevel="1" thickBot="1">
-      <c r="A54" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B54" s="1">
-        <v>5</v>
-      </c>
-      <c r="C54" s="1">
-        <v>1892.21</v>
-      </c>
-      <c r="D54" s="1">
-        <v>4</v>
-      </c>
-      <c r="E54" s="1">
-        <v>1442.28</v>
-      </c>
-      <c r="F54" s="3">
-        <v>6</v>
-      </c>
-      <c r="G54" s="3">
-        <v>1389.68</v>
-      </c>
-      <c r="H54" s="1">
-        <v>4</v>
-      </c>
-      <c r="I54" s="1">
-        <v>1406.94</v>
-      </c>
-      <c r="J54" s="3">
-        <f t="shared" si="8"/>
-        <v>50</v>
-      </c>
-      <c r="K54" s="3">
-        <f t="shared" si="9"/>
-        <v>-3.65</v>
-      </c>
-      <c r="L54" s="1">
-        <f t="shared" si="10"/>
-        <v>50</v>
-      </c>
-      <c r="M54" s="1">
-        <f t="shared" si="11"/>
-        <v>-1.23</v>
-      </c>
-      <c r="N54" s="12"/>
-      <c r="O54" s="13"/>
-      <c r="P54" s="14"/>
-    </row>
-    <row r="55" spans="1:16" ht="17.25" hidden="1" outlineLevel="1" thickBot="1">
-      <c r="A55" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B55" s="1">
-        <v>4</v>
-      </c>
-      <c r="C55" s="1">
-        <v>1843.2</v>
-      </c>
-      <c r="D55" s="1">
-        <v>4</v>
-      </c>
-      <c r="E55" s="1">
-        <v>1212.49</v>
-      </c>
-      <c r="F55" s="3">
-        <v>6</v>
-      </c>
-      <c r="G55" s="3">
-        <v>1225.8699999999999</v>
-      </c>
-      <c r="H55" s="1">
-        <v>3</v>
-      </c>
-      <c r="I55" s="1">
-        <v>1365.65</v>
-      </c>
-      <c r="J55" s="3">
-        <f t="shared" si="8"/>
-        <v>50</v>
-      </c>
-      <c r="K55" s="3">
-        <f t="shared" si="9"/>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="L55" s="1">
-        <f t="shared" si="10"/>
-        <v>100</v>
-      </c>
-      <c r="M55" s="1">
-        <f t="shared" si="11"/>
-        <v>-10.24</v>
-      </c>
-      <c r="N55" s="12"/>
-      <c r="O55" s="13"/>
-      <c r="P55" s="14"/>
-    </row>
-    <row r="56" spans="1:16" ht="17.25" hidden="1" outlineLevel="1" thickBot="1">
-      <c r="A56" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B56" s="1">
-        <v>4</v>
-      </c>
-      <c r="C56" s="1">
-        <v>1514.02</v>
-      </c>
-      <c r="D56" s="1">
-        <v>3</v>
-      </c>
-      <c r="E56" s="1">
-        <v>1197.67</v>
-      </c>
-      <c r="F56" s="3">
-        <v>5</v>
-      </c>
-      <c r="G56" s="3">
-        <v>1021.41</v>
-      </c>
-      <c r="H56" s="1">
-        <v>3</v>
-      </c>
-      <c r="I56" s="1">
-        <v>1049.6199999999999</v>
-      </c>
-      <c r="J56" s="3">
-        <f t="shared" si="8"/>
-        <v>66.67</v>
-      </c>
-      <c r="K56" s="3">
-        <f t="shared" si="9"/>
-        <v>-14.72</v>
-      </c>
-      <c r="L56" s="1">
-        <f t="shared" si="10"/>
-        <v>66.67</v>
-      </c>
-      <c r="M56" s="1">
-        <f t="shared" si="11"/>
-        <v>-2.69</v>
-      </c>
-      <c r="N56" s="12"/>
-      <c r="O56" s="13"/>
-      <c r="P56" s="14"/>
+      <c r="N55" s="14"/>
+      <c r="O55" s="15"/>
+      <c r="P55" s="16"/>
+    </row>
+    <row r="56" spans="1:16" ht="17.25" collapsed="1" thickBot="1">
+      <c r="A56" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B56" s="19" t="str">
+        <f>COUNTA(A57:A64) &amp; " 筆"</f>
+        <v>8 筆</v>
+      </c>
+      <c r="C56" s="20"/>
+      <c r="D56" s="20"/>
+      <c r="E56" s="20"/>
+      <c r="F56" s="20"/>
+      <c r="G56" s="20"/>
+      <c r="H56" s="20"/>
+      <c r="I56" s="20"/>
+      <c r="J56" s="20"/>
+      <c r="K56" s="20"/>
+      <c r="L56" s="20"/>
+      <c r="M56" s="21"/>
+      <c r="N56" s="1">
+        <v>1</v>
+      </c>
+      <c r="O56" s="1">
+        <v>0</v>
+      </c>
+      <c r="P56" s="1">
+        <v>7</v>
+      </c>
     </row>
     <row r="57" spans="1:16" ht="17.25" hidden="1" outlineLevel="1" thickBot="1">
       <c r="A57" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B57" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C57" s="1">
-        <v>1196.08</v>
+        <v>1892.21</v>
       </c>
       <c r="D57" s="1">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E57" s="1">
-        <v>854.31</v>
-      </c>
-      <c r="F57" s="2">
+        <v>1442.28</v>
+      </c>
+      <c r="F57" s="3">
+        <v>6</v>
+      </c>
+      <c r="G57" s="3">
+        <v>1389.68</v>
+      </c>
+      <c r="H57" s="1">
         <v>4</v>
       </c>
-      <c r="G57" s="2">
-        <v>842.82</v>
-      </c>
-      <c r="H57" s="1">
-        <v>3</v>
-      </c>
       <c r="I57" s="1">
-        <v>798.46</v>
-      </c>
-      <c r="J57" s="2">
-        <f t="shared" si="8"/>
-        <v>-60</v>
-      </c>
-      <c r="K57" s="2">
-        <f t="shared" si="9"/>
-        <v>-1.34</v>
+        <v>1406.94</v>
+      </c>
+      <c r="J57" s="3">
+        <f>ROUND(((F57-D57)/D57)*100,2)</f>
+        <v>50</v>
+      </c>
+      <c r="K57" s="3">
+        <f>ROUND(((G57-E57)/E57)*100,2)</f>
+        <v>-3.65</v>
       </c>
       <c r="L57" s="1">
-        <f t="shared" si="10"/>
-        <v>33.33</v>
+        <f>ROUND(((F57-H57)/H57)*100,2)</f>
+        <v>50</v>
       </c>
       <c r="M57" s="1">
-        <f t="shared" si="11"/>
-        <v>5.56</v>
-      </c>
-      <c r="N57" s="12"/>
-      <c r="O57" s="13"/>
-      <c r="P57" s="14"/>
+        <f>ROUND(((G57-I57)/I57)*100,2)</f>
+        <v>-1.23</v>
+      </c>
+      <c r="N57" s="9"/>
+      <c r="O57" s="10"/>
+      <c r="P57" s="11"/>
     </row>
     <row r="58" spans="1:16" ht="17.25" hidden="1" outlineLevel="1" thickBot="1">
       <c r="A58" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B58" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C58" s="1">
-        <v>1981.75</v>
+        <v>1843.2</v>
       </c>
       <c r="D58" s="1">
         <v>4</v>
       </c>
       <c r="E58" s="1">
-        <v>1337.65</v>
+        <v>1212.49</v>
       </c>
       <c r="F58" s="3">
         <v>6</v>
       </c>
       <c r="G58" s="3">
-        <v>1288.45</v>
+        <v>1225.8699999999999</v>
       </c>
       <c r="H58" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I58" s="1">
-        <v>1297.6500000000001</v>
+        <v>1365.65</v>
       </c>
       <c r="J58" s="3">
-        <f t="shared" si="8"/>
+        <f>ROUND(((F58-D58)/D58)*100,2)</f>
         <v>50</v>
       </c>
       <c r="K58" s="3">
-        <f t="shared" si="9"/>
-        <v>-3.68</v>
+        <f>ROUND(((G58-E58)/E58)*100,2)</f>
+        <v>1.1000000000000001</v>
       </c>
       <c r="L58" s="1">
-        <f t="shared" si="10"/>
-        <v>50</v>
+        <f>ROUND(((F58-H58)/H58)*100,2)</f>
+        <v>100</v>
       </c>
       <c r="M58" s="1">
-        <f t="shared" si="11"/>
-        <v>-0.71</v>
+        <f>ROUND(((G58-I58)/I58)*100,2)</f>
+        <v>-10.24</v>
       </c>
       <c r="N58" s="12"/>
-      <c r="O58" s="13"/>
-      <c r="P58" s="14"/>
+      <c r="O58" s="24"/>
+      <c r="P58" s="13"/>
     </row>
     <row r="59" spans="1:16" ht="17.25" hidden="1" outlineLevel="1" thickBot="1">
       <c r="A59" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B59" s="1">
         <v>4</v>
       </c>
       <c r="C59" s="1">
-        <v>1644.44</v>
+        <v>1514.02</v>
       </c>
       <c r="D59" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E59" s="1">
-        <v>1114.76</v>
+        <v>1197.67</v>
       </c>
       <c r="F59" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G59" s="3">
-        <v>1234.22</v>
+        <v>1021.41</v>
       </c>
       <c r="H59" s="1">
         <v>3</v>
       </c>
       <c r="I59" s="1">
-        <v>1146.32</v>
+        <v>1049.6199999999999</v>
       </c>
       <c r="J59" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f>ROUND(((F59-D59)/D59)*100,2)</f>
+        <v>66.67</v>
       </c>
       <c r="K59" s="3">
-        <f t="shared" si="9"/>
-        <v>10.72</v>
+        <f>ROUND(((G59-E59)/E59)*100,2)</f>
+        <v>-14.72</v>
       </c>
       <c r="L59" s="1">
-        <f t="shared" si="10"/>
-        <v>33.33</v>
+        <f>ROUND(((F59-H59)/H59)*100,2)</f>
+        <v>66.67</v>
       </c>
       <c r="M59" s="1">
-        <f t="shared" si="11"/>
-        <v>7.67</v>
+        <f>ROUND(((G59-I59)/I59)*100,2)</f>
+        <v>-2.69</v>
       </c>
       <c r="N59" s="12"/>
-      <c r="O59" s="13"/>
-      <c r="P59" s="14"/>
+      <c r="O59" s="24"/>
+      <c r="P59" s="13"/>
     </row>
     <row r="60" spans="1:16" ht="17.25" hidden="1" outlineLevel="1" thickBot="1">
       <c r="A60" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B60" s="1">
+        <v>3</v>
+      </c>
+      <c r="C60" s="1">
+        <v>1196.08</v>
+      </c>
+      <c r="D60" s="1">
+        <v>10</v>
+      </c>
+      <c r="E60" s="1">
+        <v>854.31</v>
+      </c>
+      <c r="F60" s="2">
         <v>4</v>
       </c>
-      <c r="C60" s="1">
-        <v>1599.2</v>
-      </c>
-      <c r="D60" s="1">
-        <v>4</v>
-      </c>
-      <c r="E60" s="1">
-        <v>1055.71</v>
-      </c>
-      <c r="F60" s="3">
-        <v>4</v>
-      </c>
-      <c r="G60" s="3">
-        <v>1134.8699999999999</v>
+      <c r="G60" s="2">
+        <v>842.82</v>
       </c>
       <c r="H60" s="1">
         <v>3</v>
       </c>
       <c r="I60" s="1">
-        <v>1061.1400000000001</v>
-      </c>
-      <c r="J60" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K60" s="3">
-        <f t="shared" si="9"/>
-        <v>7.5</v>
+        <v>798.46</v>
+      </c>
+      <c r="J60" s="2">
+        <f>ROUND(((F60-D60)/D60)*100,2)</f>
+        <v>-60</v>
+      </c>
+      <c r="K60" s="2">
+        <f>ROUND(((G60-E60)/E60)*100,2)</f>
+        <v>-1.34</v>
       </c>
       <c r="L60" s="1">
-        <f t="shared" si="10"/>
+        <f>ROUND(((F60-H60)/H60)*100,2)</f>
         <v>33.33</v>
       </c>
       <c r="M60" s="1">
-        <f t="shared" si="11"/>
-        <v>6.95</v>
+        <f>ROUND(((G60-I60)/I60)*100,2)</f>
+        <v>5.56</v>
       </c>
       <c r="N60" s="12"/>
-      <c r="O60" s="13"/>
-      <c r="P60" s="14"/>
+      <c r="O60" s="24"/>
+      <c r="P60" s="13"/>
     </row>
     <row r="61" spans="1:16" ht="17.25" hidden="1" outlineLevel="1" thickBot="1">
       <c r="A61" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B61" s="1">
+        <v>5</v>
+      </c>
+      <c r="C61" s="1">
+        <v>1981.75</v>
+      </c>
+      <c r="D61" s="1">
+        <v>4</v>
+      </c>
+      <c r="E61" s="1">
+        <v>1337.65</v>
+      </c>
+      <c r="F61" s="3">
+        <v>6</v>
+      </c>
+      <c r="G61" s="3">
+        <v>1288.45</v>
+      </c>
+      <c r="H61" s="1">
+        <v>4</v>
+      </c>
+      <c r="I61" s="1">
+        <v>1297.6500000000001</v>
+      </c>
+      <c r="J61" s="3">
+        <f>ROUND(((F61-D61)/D61)*100,2)</f>
+        <v>50</v>
+      </c>
+      <c r="K61" s="3">
+        <f>ROUND(((G61-E61)/E61)*100,2)</f>
+        <v>-3.68</v>
+      </c>
+      <c r="L61" s="1">
+        <f>ROUND(((F61-H61)/H61)*100,2)</f>
+        <v>50</v>
+      </c>
+      <c r="M61" s="1">
+        <f>ROUND(((G61-I61)/I61)*100,2)</f>
+        <v>-0.71</v>
+      </c>
+      <c r="N61" s="12"/>
+      <c r="O61" s="24"/>
+      <c r="P61" s="13"/>
+    </row>
+    <row r="62" spans="1:16" ht="17.25" hidden="1" outlineLevel="1" thickBot="1">
+      <c r="A62" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B62" s="1">
+        <v>4</v>
+      </c>
+      <c r="C62" s="1">
+        <v>1644.44</v>
+      </c>
+      <c r="D62" s="1">
+        <v>4</v>
+      </c>
+      <c r="E62" s="1">
+        <v>1114.76</v>
+      </c>
+      <c r="F62" s="3">
+        <v>4</v>
+      </c>
+      <c r="G62" s="3">
+        <v>1234.22</v>
+      </c>
+      <c r="H62" s="1">
+        <v>3</v>
+      </c>
+      <c r="I62" s="1">
+        <v>1146.32</v>
+      </c>
+      <c r="J62" s="3">
+        <f>ROUND(((F62-D62)/D62)*100,2)</f>
+        <v>0</v>
+      </c>
+      <c r="K62" s="3">
+        <f>ROUND(((G62-E62)/E62)*100,2)</f>
+        <v>10.72</v>
+      </c>
+      <c r="L62" s="1">
+        <f>ROUND(((F62-H62)/H62)*100,2)</f>
+        <v>33.33</v>
+      </c>
+      <c r="M62" s="1">
+        <f>ROUND(((G62-I62)/I62)*100,2)</f>
+        <v>7.67</v>
+      </c>
+      <c r="N62" s="12"/>
+      <c r="O62" s="24"/>
+      <c r="P62" s="13"/>
+    </row>
+    <row r="63" spans="1:16" ht="17.25" hidden="1" outlineLevel="1" thickBot="1">
+      <c r="A63" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B63" s="1">
+        <v>4</v>
+      </c>
+      <c r="C63" s="1">
+        <v>1599.2</v>
+      </c>
+      <c r="D63" s="1">
+        <v>4</v>
+      </c>
+      <c r="E63" s="1">
+        <v>1055.71</v>
+      </c>
+      <c r="F63" s="3">
+        <v>4</v>
+      </c>
+      <c r="G63" s="3">
+        <v>1134.8699999999999</v>
+      </c>
+      <c r="H63" s="1">
+        <v>3</v>
+      </c>
+      <c r="I63" s="1">
+        <v>1061.1400000000001</v>
+      </c>
+      <c r="J63" s="3">
+        <f>ROUND(((F63-D63)/D63)*100,2)</f>
+        <v>0</v>
+      </c>
+      <c r="K63" s="3">
+        <f>ROUND(((G63-E63)/E63)*100,2)</f>
+        <v>7.5</v>
+      </c>
+      <c r="L63" s="1">
+        <f>ROUND(((F63-H63)/H63)*100,2)</f>
+        <v>33.33</v>
+      </c>
+      <c r="M63" s="1">
+        <f>ROUND(((G63-I63)/I63)*100,2)</f>
+        <v>6.95</v>
+      </c>
+      <c r="N63" s="12"/>
+      <c r="O63" s="24"/>
+      <c r="P63" s="13"/>
+    </row>
+    <row r="64" spans="1:16" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
+      <c r="A64" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B61" s="1">
-        <v>3</v>
-      </c>
-      <c r="C61" s="1">
+      <c r="B64" s="1">
+        <v>3</v>
+      </c>
+      <c r="C64" s="1">
         <v>1203.03</v>
       </c>
-      <c r="D61" s="1">
-        <v>3</v>
-      </c>
-      <c r="E61" s="1">
+      <c r="D64" s="1">
+        <v>3</v>
+      </c>
+      <c r="E64" s="1">
         <v>860.53</v>
       </c>
-      <c r="F61" s="3">
-        <v>3</v>
-      </c>
-      <c r="G61" s="3">
+      <c r="F64" s="3">
+        <v>3</v>
+      </c>
+      <c r="G64" s="3">
         <v>892.49</v>
       </c>
-      <c r="H61" s="1">
-        <v>3</v>
-      </c>
-      <c r="I61" s="1">
+      <c r="H64" s="1">
+        <v>3</v>
+      </c>
+      <c r="I64" s="1">
         <v>828.14</v>
       </c>
-      <c r="J61" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K61" s="3">
-        <f t="shared" si="9"/>
+      <c r="J64" s="3">
+        <f>ROUND(((F64-D64)/D64)*100,2)</f>
+        <v>0</v>
+      </c>
+      <c r="K64" s="3">
+        <f>ROUND(((G64-E64)/E64)*100,2)</f>
         <v>3.71</v>
       </c>
-      <c r="L61" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="M61" s="1">
-        <f t="shared" si="11"/>
+      <c r="L64" s="1">
+        <f>ROUND(((F64-H64)/H64)*100,2)</f>
+        <v>0</v>
+      </c>
+      <c r="M64" s="1">
+        <f>ROUND(((G64-I64)/I64)*100,2)</f>
         <v>7.77</v>
       </c>
-      <c r="N61" s="15"/>
-      <c r="O61" s="16"/>
-      <c r="P61" s="17"/>
-    </row>
-    <row r="62" spans="1:16" ht="17.25" collapsed="1" thickBot="1">
-      <c r="A62" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B62" s="20" t="str">
-        <f>"總共 " &amp; SUM(N62:P62) &amp; " 筆"</f>
+      <c r="N64" s="14"/>
+      <c r="O64" s="15"/>
+      <c r="P64" s="16"/>
+    </row>
+    <row r="65" spans="1:16" ht="15.75" customHeight="1" collapsed="1" thickBot="1">
+      <c r="A65" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B65" s="19" t="str">
+        <f>"總共 " &amp; SUM(N65:P65) &amp; " 筆"</f>
         <v>總共 56 筆</v>
       </c>
-      <c r="C62" s="21"/>
-      <c r="D62" s="21"/>
-      <c r="E62" s="21"/>
-      <c r="F62" s="21"/>
-      <c r="G62" s="21"/>
-      <c r="H62" s="21"/>
-      <c r="I62" s="21"/>
-      <c r="J62" s="21"/>
-      <c r="K62" s="21"/>
-      <c r="L62" s="21"/>
-      <c r="M62" s="22"/>
-      <c r="N62" s="1">
-        <f>N3+N21+N45</f>
+      <c r="C65" s="20"/>
+      <c r="D65" s="20"/>
+      <c r="E65" s="20"/>
+      <c r="F65" s="20"/>
+      <c r="G65" s="20"/>
+      <c r="H65" s="20"/>
+      <c r="I65" s="20"/>
+      <c r="J65" s="20"/>
+      <c r="K65" s="20"/>
+      <c r="L65" s="20"/>
+      <c r="M65" s="21"/>
+      <c r="N65" s="1">
+        <f>N3+N13+N22+N35+N47+N56</f>
         <v>22</v>
       </c>
-      <c r="O62" s="1">
-        <f t="shared" ref="O62:P62" si="12">O3+O21+O45</f>
+      <c r="O65" s="1">
+        <f t="shared" ref="O65:P65" si="12">O3+O13+O22+O35+O47+O56</f>
         <v>12</v>
       </c>
-      <c r="P62" s="1">
+      <c r="P65" s="1">
         <f t="shared" si="12"/>
         <v>22</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="N46:P61"/>
-    <mergeCell ref="N22:P44"/>
-    <mergeCell ref="N4:P20"/>
+  <mergeCells count="20">
+    <mergeCell ref="B65:M65"/>
+    <mergeCell ref="B35:M35"/>
+    <mergeCell ref="B47:M47"/>
+    <mergeCell ref="B56:M56"/>
+    <mergeCell ref="N4:P12"/>
+    <mergeCell ref="N57:P64"/>
+    <mergeCell ref="N48:P55"/>
+    <mergeCell ref="N36:P46"/>
+    <mergeCell ref="N23:P34"/>
+    <mergeCell ref="N14:P21"/>
     <mergeCell ref="N1:P1"/>
-    <mergeCell ref="B62:M62"/>
     <mergeCell ref="B3:M3"/>
-    <mergeCell ref="B21:M21"/>
-    <mergeCell ref="B45:M45"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
+    <mergeCell ref="B13:M13"/>
+    <mergeCell ref="B22:M22"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/Baseline比較結果.xlsx
+++ b/docs/Baseline比較結果.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff0\OneDrive\桌面\115_NTUT_Thesis\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23B5E3AA-D3C5-4DD9-B79B-11121D3D5034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44737BCC-7B91-4382-9C6B-CE68FC5065C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="22200" windowHeight="20985" xr2:uid="{9DD6E340-DFE3-4B7E-9025-343BD89F474F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9DD6E340-DFE3-4B7E-9025-343BD89F474F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -36,8 +36,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="86">
   <si>
     <t>Distance</t>
   </si>
@@ -535,6 +557,18 @@
   </si>
   <si>
     <t>L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Win</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lose</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tie</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -856,9 +890,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -866,6 +897,9 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1206,7 +1240,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CECA5DF5-0F01-4635-876C-42C0D830CD54}">
-  <dimension ref="A1:W71"/>
+  <sheetPr codeName="工作表1"/>
+  <dimension ref="A1:Z71"/>
   <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="11.875" customWidth="1"/>
@@ -1225,7 +1260,7 @@
     <col min="16" max="16" width="8.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="17.25" customHeight="1" thickBot="1">
+    <row r="1" spans="1:26" ht="17.25" customHeight="1" thickBot="1">
       <c r="A1" s="4"/>
       <c r="B1" s="18" t="s">
         <v>59</v>
@@ -1262,15 +1297,15 @@
       <c r="R1" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
+      <c r="S1" s="23"/>
+      <c r="T1" s="23"/>
       <c r="U1" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="V1" s="20"/>
-      <c r="W1" s="20"/>
-    </row>
-    <row r="2" spans="1:23" ht="17.25" thickBot="1">
+      <c r="V1" s="23"/>
+      <c r="W1" s="23"/>
+    </row>
+    <row r="2" spans="1:26" ht="17.25" thickBot="1">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
@@ -1341,49 +1376,55 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="17.25" thickBot="1">
+    <row r="3" spans="1:26" ht="17.25" thickBot="1">
       <c r="A3" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="21" t="str">
+      <c r="B3" s="20" t="str">
         <f>COUNTA(A4:A12) &amp; " 筆"</f>
         <v>9 筆</v>
       </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="22"/>
-      <c r="L3" s="22"/>
-      <c r="M3" s="22"/>
-      <c r="N3" s="22"/>
-      <c r="O3" s="22"/>
-      <c r="P3" s="22"/>
-      <c r="Q3" s="23"/>
-      <c r="R3" s="1">
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="21"/>
+      <c r="N3" s="21"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="21"/>
+      <c r="Q3" s="22"/>
+      <c r="R3" s="1" cm="1">
+        <f t="array" ref="R3">CountColor($F4:$F12,$Y$4)</f>
         <v>4</v>
       </c>
-      <c r="S3" s="1">
+      <c r="S3" s="1" cm="1">
+        <f t="array" ref="S3">CountColor($F4:$F12,$Y$5)</f>
         <v>5</v>
       </c>
-      <c r="T3" s="1">
-        <v>0</v>
-      </c>
-      <c r="U3" s="1">
+      <c r="T3" s="1" cm="1">
+        <f t="array" ref="T3">CountColor($F4:$F12,$Y$6)</f>
+        <v>0</v>
+      </c>
+      <c r="U3" s="1" cm="1">
+        <f t="array" ref="U3">CountColor($H4:$H12,$Y$4)</f>
         <v>4</v>
       </c>
-      <c r="V3" s="1">
+      <c r="V3" s="1" cm="1">
+        <f t="array" ref="V3">CountColor($H4:$H12,$Y$5)</f>
         <v>5</v>
       </c>
-      <c r="W3" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
+      <c r="W3" s="1" cm="1">
+        <f t="array" ref="W3">CountColor($H4:$H12,$Y$6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A4" s="6" t="s">
         <v>2</v>
       </c>
@@ -1447,8 +1488,12 @@
       <c r="U4" s="9"/>
       <c r="V4" s="10"/>
       <c r="W4" s="11"/>
-    </row>
-    <row r="5" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
+      <c r="Y4" s="2"/>
+      <c r="Z4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A5" s="6" t="s">
         <v>3</v>
       </c>
@@ -1512,8 +1557,12 @@
       <c r="U5" s="12"/>
       <c r="V5" s="13"/>
       <c r="W5" s="14"/>
-    </row>
-    <row r="6" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
+      <c r="Y5" s="7"/>
+      <c r="Z5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A6" s="6" t="s">
         <v>4</v>
       </c>
@@ -1577,8 +1626,12 @@
       <c r="U6" s="12"/>
       <c r="V6" s="13"/>
       <c r="W6" s="14"/>
-    </row>
-    <row r="7" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
+      <c r="Y6" s="3"/>
+      <c r="Z6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A7" s="6" t="s">
         <v>5</v>
       </c>
@@ -1598,13 +1651,13 @@
         <v>10</v>
       </c>
       <c r="G7" s="2">
+        <v>826.37</v>
+      </c>
+      <c r="H7" s="2">
+        <v>10</v>
+      </c>
+      <c r="I7" s="2">
         <v>824.78</v>
-      </c>
-      <c r="H7" s="2">
-        <v>10</v>
-      </c>
-      <c r="I7" s="2">
-        <v>826.37</v>
       </c>
       <c r="J7" s="1">
         <v>10</v>
@@ -1618,7 +1671,7 @@
       </c>
       <c r="M7" s="1">
         <f t="shared" si="1"/>
-        <v>-4.5599999999999996</v>
+        <v>-4.38</v>
       </c>
       <c r="N7" s="1">
         <f t="shared" si="4"/>
@@ -1626,7 +1679,7 @@
       </c>
       <c r="O7" s="1">
         <f t="shared" si="5"/>
-        <v>-4.38</v>
+        <v>-4.5599999999999996</v>
       </c>
       <c r="P7" s="1">
         <f t="shared" si="2"/>
@@ -1634,7 +1687,7 @@
       </c>
       <c r="Q7" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="R7" s="12"/>
       <c r="S7" s="13"/>
@@ -1643,7 +1696,7 @@
       <c r="V7" s="13"/>
       <c r="W7" s="14"/>
     </row>
-    <row r="8" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
+    <row r="8" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A8" s="6" t="s">
         <v>6</v>
       </c>
@@ -1708,7 +1761,7 @@
       <c r="V8" s="13"/>
       <c r="W8" s="14"/>
     </row>
-    <row r="9" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
+    <row r="9" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
@@ -1773,7 +1826,7 @@
       <c r="V9" s="13"/>
       <c r="W9" s="14"/>
     </row>
-    <row r="10" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
+    <row r="10" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A10" s="6" t="s">
         <v>8</v>
       </c>
@@ -1838,7 +1891,7 @@
       <c r="V10" s="13"/>
       <c r="W10" s="14"/>
     </row>
-    <row r="11" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
+    <row r="11" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
@@ -1903,7 +1956,7 @@
       <c r="V11" s="13"/>
       <c r="W11" s="14"/>
     </row>
-    <row r="12" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
+    <row r="12" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A12" s="6" t="s">
         <v>10</v>
       </c>
@@ -1968,7 +2021,7 @@
       <c r="V12" s="13"/>
       <c r="W12" s="14"/>
     </row>
-    <row r="13" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
+    <row r="13" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A13" s="6" t="s">
         <v>76</v>
       </c>
@@ -1994,15 +2047,13 @@
       </c>
       <c r="G13" s="1">
         <f t="shared" si="6"/>
+        <v>828.55666666666684</v>
+      </c>
+      <c r="H13" s="1">
+        <v>10</v>
+      </c>
+      <c r="I13" s="1">
         <v>828.38000000000022</v>
-      </c>
-      <c r="H13" s="1">
-        <f t="shared" si="6"/>
-        <v>10</v>
-      </c>
-      <c r="I13" s="1">
-        <f t="shared" si="6"/>
-        <v>828.55666666666684</v>
       </c>
       <c r="J13" s="1">
         <f t="shared" si="6"/>
@@ -2012,12 +2063,12 @@
         <f t="shared" si="6"/>
         <v>828.38000000000022</v>
       </c>
-      <c r="L13" s="21"/>
-      <c r="M13" s="22"/>
-      <c r="N13" s="22"/>
-      <c r="O13" s="22"/>
-      <c r="P13" s="22"/>
-      <c r="Q13" s="23"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="21"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="22"/>
       <c r="R13" s="15"/>
       <c r="S13" s="16"/>
       <c r="T13" s="17"/>
@@ -2025,29 +2076,29 @@
       <c r="V13" s="16"/>
       <c r="W13" s="17"/>
     </row>
-    <row r="14" spans="1:23" ht="17.25" customHeight="1" thickBot="1">
+    <row r="14" spans="1:26" ht="17.25" customHeight="1" thickBot="1">
       <c r="A14" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B14" s="21" t="str">
+      <c r="B14" s="20" t="str">
         <f>COUNTA(A15:A22) &amp; " 筆"</f>
         <v>8 筆</v>
       </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="22"/>
-      <c r="N14" s="22"/>
-      <c r="O14" s="22"/>
-      <c r="P14" s="22"/>
-      <c r="Q14" s="23"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="22"/>
       <c r="R14" s="1">
         <v>1</v>
       </c>
@@ -2058,16 +2109,16 @@
         <v>0</v>
       </c>
       <c r="U14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="1">
         <v>7</v>
       </c>
       <c r="W14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A15" s="6" t="s">
         <v>11</v>
       </c>
@@ -2132,7 +2183,7 @@
       <c r="V15" s="10"/>
       <c r="W15" s="11"/>
     </row>
-    <row r="16" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
+    <row r="16" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A16" s="6" t="s">
         <v>12</v>
       </c>
@@ -2284,11 +2335,11 @@
       <c r="G18" s="2">
         <v>593.92999999999995</v>
       </c>
-      <c r="H18" s="2">
-        <v>3</v>
-      </c>
-      <c r="I18" s="2">
-        <v>593.92999999999995</v>
+      <c r="H18" s="3">
+        <v>3</v>
+      </c>
+      <c r="I18" s="3">
+        <v>612.39</v>
       </c>
       <c r="J18" s="1">
         <v>3</v>
@@ -2310,7 +2361,7 @@
       </c>
       <c r="O18" s="1">
         <f t="shared" si="5"/>
-        <v>-0.1</v>
+        <v>3.01</v>
       </c>
       <c r="P18" s="1">
         <f t="shared" si="8"/>
@@ -2616,12 +2667,10 @@
         <v>590.28</v>
       </c>
       <c r="H23" s="1">
-        <f t="shared" ref="H23" si="10">ROUND(SUM(H15:H22)/COUNTA(H15:H22),2)</f>
         <v>3</v>
       </c>
       <c r="I23" s="1">
-        <f t="shared" ref="I23" si="11">ROUND(SUM(I15:I22)/COUNTA(I15:I22),2)</f>
-        <v>590.28</v>
+        <v>592.58249999999998</v>
       </c>
       <c r="J23" s="1">
         <f t="shared" si="9"/>
@@ -2631,12 +2680,12 @@
         <f t="shared" si="9"/>
         <v>589.86</v>
       </c>
-      <c r="L23" s="21"/>
-      <c r="M23" s="22"/>
-      <c r="N23" s="22"/>
-      <c r="O23" s="22"/>
-      <c r="P23" s="22"/>
-      <c r="Q23" s="23"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="21"/>
+      <c r="N23" s="21"/>
+      <c r="O23" s="21"/>
+      <c r="P23" s="21"/>
+      <c r="Q23" s="22"/>
       <c r="R23" s="15"/>
       <c r="S23" s="16"/>
       <c r="T23" s="17"/>
@@ -2648,33 +2697,33 @@
       <c r="A24" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B24" s="21" t="str">
+      <c r="B24" s="20" t="str">
         <f>COUNTA(A25:A36) &amp; " 筆"</f>
         <v>12 筆</v>
       </c>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="22"/>
-      <c r="K24" s="22"/>
-      <c r="L24" s="22"/>
-      <c r="M24" s="22"/>
-      <c r="N24" s="22"/>
-      <c r="O24" s="22"/>
-      <c r="P24" s="22"/>
-      <c r="Q24" s="23"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="21"/>
+      <c r="L24" s="21"/>
+      <c r="M24" s="21"/>
+      <c r="N24" s="21"/>
+      <c r="O24" s="21"/>
+      <c r="P24" s="21"/>
+      <c r="Q24" s="22"/>
       <c r="R24" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S24" s="1">
         <v>0</v>
       </c>
       <c r="T24" s="1">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U24" s="1">
         <v>2</v>
@@ -2702,17 +2751,17 @@
       <c r="E25" s="1">
         <v>1656.55</v>
       </c>
-      <c r="F25" s="3">
-        <v>20</v>
-      </c>
-      <c r="G25" s="3">
-        <v>1645.01</v>
-      </c>
-      <c r="H25" s="2">
+      <c r="F25" s="2">
         <v>19</v>
       </c>
-      <c r="I25" s="2">
+      <c r="G25" s="2">
         <v>1653.16</v>
+      </c>
+      <c r="H25" s="3">
+        <v>19</v>
+      </c>
+      <c r="I25" s="3">
+        <v>1924.82</v>
       </c>
       <c r="J25" s="1">
         <v>19</v>
@@ -2721,12 +2770,12 @@
         <v>1650.8</v>
       </c>
       <c r="L25" s="1">
-        <f t="shared" ref="L25:L36" si="12">ROUND(((F25-D25)/D25)*100,2)</f>
-        <v>5.26</v>
+        <f t="shared" ref="L25:L36" si="10">ROUND(((F25-D25)/D25)*100,2)</f>
+        <v>0</v>
       </c>
       <c r="M25" s="1">
-        <f t="shared" ref="M25:M36" si="13">ROUND(((G25-E25)/E25)*100,2)</f>
-        <v>-0.7</v>
+        <f t="shared" ref="M25:M36" si="11">ROUND(((G25-E25)/E25)*100,2)</f>
+        <v>-0.2</v>
       </c>
       <c r="N25" s="1">
         <f t="shared" si="4"/>
@@ -2734,15 +2783,15 @@
       </c>
       <c r="O25" s="1">
         <f t="shared" si="5"/>
-        <v>-0.2</v>
+        <v>16.190000000000001</v>
       </c>
       <c r="P25" s="1">
-        <f t="shared" ref="P25:P36" si="14">ROUND(((F25-J25)/J25)*100,2)</f>
-        <v>5.26</v>
+        <f t="shared" ref="P25:P36" si="12">ROUND(((F25-J25)/J25)*100,2)</f>
+        <v>0</v>
       </c>
       <c r="Q25" s="1">
-        <f t="shared" ref="Q25:Q36" si="15">ROUND(((G25-K25)/K25)*100,2)</f>
-        <v>-0.35</v>
+        <f t="shared" ref="Q25:Q36" si="13">ROUND(((G25-K25)/K25)*100,2)</f>
+        <v>0.14000000000000001</v>
       </c>
       <c r="R25" s="9"/>
       <c r="S25" s="10"/>
@@ -2767,17 +2816,17 @@
       <c r="E26" s="1">
         <v>1476.85</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="3">
         <v>18</v>
       </c>
-      <c r="G26" s="2">
-        <v>1466.25</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="G26" s="3">
+        <v>1486.68</v>
+      </c>
+      <c r="H26" s="2">
         <v>18</v>
       </c>
-      <c r="I26" s="3">
-        <v>1486.68</v>
+      <c r="I26" s="2">
+        <v>1473.1</v>
       </c>
       <c r="J26" s="1">
         <v>17</v>
@@ -2786,12 +2835,12 @@
         <v>1486.12</v>
       </c>
       <c r="L26" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M26" s="1">
-        <f t="shared" si="13"/>
-        <v>-0.72</v>
+        <f t="shared" si="11"/>
+        <v>0.67</v>
       </c>
       <c r="N26" s="1">
         <f t="shared" si="4"/>
@@ -2799,15 +2848,15 @@
       </c>
       <c r="O26" s="1">
         <f t="shared" si="5"/>
-        <v>0.67</v>
+        <v>-0.25</v>
       </c>
       <c r="P26" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>5.88</v>
       </c>
       <c r="Q26" s="1">
-        <f t="shared" si="15"/>
-        <v>-1.34</v>
+        <f t="shared" si="13"/>
+        <v>0.04</v>
       </c>
       <c r="R26" s="12"/>
       <c r="S26" s="13"/>
@@ -2833,16 +2882,16 @@
         <v>1230.07</v>
       </c>
       <c r="F27" s="2">
+        <v>13</v>
+      </c>
+      <c r="G27" s="2">
+        <v>1572.9</v>
+      </c>
+      <c r="H27" s="2">
         <v>14</v>
       </c>
-      <c r="G27" s="2">
-        <v>1201.52</v>
-      </c>
-      <c r="H27" s="2">
-        <v>13</v>
-      </c>
       <c r="I27" s="2">
-        <v>1572.9</v>
+        <v>1221.75</v>
       </c>
       <c r="J27" s="1">
         <v>13</v>
@@ -2851,28 +2900,28 @@
         <v>1292.68</v>
       </c>
       <c r="L27" s="1">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>-7.14</v>
       </c>
       <c r="M27" s="1">
-        <f t="shared" si="13"/>
-        <v>-2.3199999999999998</v>
+        <f t="shared" si="11"/>
+        <v>27.87</v>
       </c>
       <c r="N27" s="1">
         <f t="shared" si="4"/>
-        <v>-7.14</v>
+        <v>0</v>
       </c>
       <c r="O27" s="1">
         <f t="shared" si="5"/>
-        <v>27.87</v>
+        <v>-0.68</v>
       </c>
       <c r="P27" s="1">
-        <f t="shared" si="14"/>
-        <v>7.69</v>
+        <f t="shared" si="12"/>
+        <v>0</v>
       </c>
       <c r="Q27" s="1">
-        <f t="shared" si="15"/>
-        <v>-7.05</v>
+        <f t="shared" si="13"/>
+        <v>21.68</v>
       </c>
       <c r="R27" s="12"/>
       <c r="S27" s="13"/>
@@ -2897,17 +2946,17 @@
       <c r="E28" s="1">
         <v>1010.55</v>
       </c>
-      <c r="F28" s="2">
-        <v>10</v>
-      </c>
-      <c r="G28" s="2">
-        <v>991.94</v>
+      <c r="F28" s="3">
+        <v>10</v>
+      </c>
+      <c r="G28" s="3">
+        <v>1026</v>
       </c>
       <c r="H28" s="3">
         <v>10</v>
       </c>
       <c r="I28" s="3">
-        <v>1026</v>
+        <v>1036.96</v>
       </c>
       <c r="J28" s="1">
         <v>9</v>
@@ -2916,12 +2965,12 @@
         <v>1007.31</v>
       </c>
       <c r="L28" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M28" s="1">
-        <f t="shared" si="13"/>
-        <v>-1.84</v>
+        <f t="shared" si="11"/>
+        <v>1.53</v>
       </c>
       <c r="N28" s="1">
         <f t="shared" si="4"/>
@@ -2929,15 +2978,15 @@
       </c>
       <c r="O28" s="1">
         <f t="shared" si="5"/>
-        <v>1.53</v>
+        <v>2.61</v>
       </c>
       <c r="P28" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>11.11</v>
       </c>
       <c r="Q28" s="1">
-        <f t="shared" si="15"/>
-        <v>-1.53</v>
+        <f t="shared" si="13"/>
+        <v>1.86</v>
       </c>
       <c r="R28" s="12"/>
       <c r="S28" s="13"/>
@@ -2963,16 +3012,16 @@
         <v>1395.68</v>
       </c>
       <c r="F29" s="3">
+        <v>14</v>
+      </c>
+      <c r="G29" s="3">
+        <v>1688.63</v>
+      </c>
+      <c r="H29" s="3">
         <v>15</v>
       </c>
-      <c r="G29" s="3">
-        <v>1389.17</v>
-      </c>
-      <c r="H29" s="3">
-        <v>14</v>
-      </c>
       <c r="I29" s="3">
-        <v>1688.63</v>
+        <v>1387.54</v>
       </c>
       <c r="J29" s="1">
         <v>14</v>
@@ -2981,28 +3030,28 @@
         <v>1377.11</v>
       </c>
       <c r="L29" s="1">
-        <f t="shared" si="12"/>
-        <v>7.14</v>
+        <f t="shared" si="10"/>
+        <v>0</v>
       </c>
       <c r="M29" s="1">
-        <f t="shared" si="13"/>
-        <v>-0.47</v>
+        <f t="shared" si="11"/>
+        <v>20.99</v>
       </c>
       <c r="N29" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="O29" s="1">
         <f t="shared" si="5"/>
-        <v>20.99</v>
+        <v>-0.57999999999999996</v>
       </c>
       <c r="P29" s="1">
-        <f t="shared" si="14"/>
-        <v>7.14</v>
+        <f t="shared" si="12"/>
+        <v>0</v>
       </c>
       <c r="Q29" s="1">
-        <f t="shared" si="15"/>
-        <v>0.88</v>
+        <f t="shared" si="13"/>
+        <v>22.62</v>
       </c>
       <c r="R29" s="12"/>
       <c r="S29" s="13"/>
@@ -3031,13 +3080,13 @@
         <v>13</v>
       </c>
       <c r="G30" s="3">
-        <v>1278.1600000000001</v>
+        <v>1285.3599999999999</v>
       </c>
       <c r="H30" s="3">
         <v>13</v>
       </c>
       <c r="I30" s="3">
-        <v>1285.3599999999999</v>
+        <v>1269.31</v>
       </c>
       <c r="J30" s="1">
         <v>12</v>
@@ -3046,12 +3095,12 @@
         <v>1252.03</v>
       </c>
       <c r="L30" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M30" s="1">
-        <f t="shared" si="13"/>
-        <v>1.31</v>
+        <f t="shared" si="11"/>
+        <v>1.88</v>
       </c>
       <c r="N30" s="1">
         <f t="shared" si="4"/>
@@ -3059,15 +3108,15 @@
       </c>
       <c r="O30" s="1">
         <f t="shared" si="5"/>
-        <v>1.88</v>
+        <v>0.61</v>
       </c>
       <c r="P30" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>8.33</v>
       </c>
       <c r="Q30" s="1">
-        <f t="shared" si="15"/>
-        <v>2.09</v>
+        <f t="shared" si="13"/>
+        <v>2.66</v>
       </c>
       <c r="R30" s="12"/>
       <c r="S30" s="13"/>
@@ -3092,17 +3141,17 @@
       <c r="E31" s="1">
         <v>1103.77</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="3">
         <v>11</v>
       </c>
-      <c r="G31" s="2">
-        <v>1098.19</v>
+      <c r="G31" s="3">
+        <v>1127.3900000000001</v>
       </c>
       <c r="H31" s="3">
         <v>11</v>
       </c>
       <c r="I31" s="3">
-        <v>1127.3900000000001</v>
+        <v>1111.8</v>
       </c>
       <c r="J31" s="1">
         <v>10</v>
@@ -3111,12 +3160,12 @@
         <v>1104.6600000000001</v>
       </c>
       <c r="L31" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M31" s="1">
-        <f t="shared" si="13"/>
-        <v>-0.51</v>
+        <f t="shared" si="11"/>
+        <v>2.14</v>
       </c>
       <c r="N31" s="1">
         <f t="shared" si="4"/>
@@ -3124,15 +3173,15 @@
       </c>
       <c r="O31" s="1">
         <f t="shared" si="5"/>
-        <v>2.14</v>
+        <v>0.73</v>
       </c>
       <c r="P31" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="Q31" s="1">
-        <f t="shared" si="15"/>
-        <v>-0.59</v>
+        <f t="shared" si="13"/>
+        <v>2.06</v>
       </c>
       <c r="R31" s="12"/>
       <c r="S31" s="13"/>
@@ -3157,17 +3206,17 @@
       <c r="E32" s="1">
         <v>966.99</v>
       </c>
-      <c r="F32" s="2">
-        <v>10</v>
-      </c>
-      <c r="G32" s="2">
-        <v>953.55</v>
+      <c r="F32" s="3">
+        <v>10</v>
+      </c>
+      <c r="G32" s="3">
+        <v>1005.63</v>
       </c>
       <c r="H32" s="3">
         <v>10</v>
       </c>
       <c r="I32" s="3">
-        <v>1005.63</v>
+        <v>984.72</v>
       </c>
       <c r="J32" s="1">
         <v>9</v>
@@ -3176,12 +3225,12 @@
         <v>960.88</v>
       </c>
       <c r="L32" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M32" s="1">
-        <f t="shared" si="13"/>
-        <v>-1.39</v>
+        <f t="shared" si="11"/>
+        <v>4</v>
       </c>
       <c r="N32" s="1">
         <f t="shared" si="4"/>
@@ -3189,15 +3238,15 @@
       </c>
       <c r="O32" s="1">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>1.83</v>
       </c>
       <c r="P32" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>11.11</v>
       </c>
       <c r="Q32" s="1">
-        <f t="shared" si="15"/>
-        <v>-0.76</v>
+        <f t="shared" si="13"/>
+        <v>4.66</v>
       </c>
       <c r="R32" s="12"/>
       <c r="S32" s="13"/>
@@ -3223,16 +3272,16 @@
         <v>1200.2</v>
       </c>
       <c r="F33" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G33" s="3">
-        <v>1179.8</v>
+        <v>1255.48</v>
       </c>
       <c r="H33" s="3">
         <v>12</v>
       </c>
       <c r="I33" s="3">
-        <v>1255.48</v>
+        <v>1205.78</v>
       </c>
       <c r="J33" s="1">
         <v>11</v>
@@ -3241,12 +3290,12 @@
         <v>1194.73</v>
       </c>
       <c r="L33" s="1">
-        <f t="shared" si="12"/>
-        <v>8.33</v>
+        <f t="shared" si="10"/>
+        <v>0</v>
       </c>
       <c r="M33" s="1">
-        <f t="shared" si="13"/>
-        <v>-1.7</v>
+        <f t="shared" si="11"/>
+        <v>4.6100000000000003</v>
       </c>
       <c r="N33" s="1">
         <f t="shared" si="4"/>
@@ -3254,15 +3303,15 @@
       </c>
       <c r="O33" s="1">
         <f t="shared" si="5"/>
-        <v>4.6100000000000003</v>
+        <v>0.46</v>
       </c>
       <c r="P33" s="1">
-        <f t="shared" si="14"/>
-        <v>18.18</v>
+        <f t="shared" si="12"/>
+        <v>9.09</v>
       </c>
       <c r="Q33" s="1">
-        <f t="shared" si="15"/>
-        <v>-1.25</v>
+        <f t="shared" si="13"/>
+        <v>5.08</v>
       </c>
       <c r="R33" s="12"/>
       <c r="S33" s="13"/>
@@ -3288,16 +3337,16 @@
         <v>1127.28</v>
       </c>
       <c r="F34" s="3">
+        <v>11</v>
+      </c>
+      <c r="G34" s="3">
+        <v>1151.1199999999999</v>
+      </c>
+      <c r="H34" s="3">
         <v>12</v>
       </c>
-      <c r="G34" s="3">
-        <v>1114.3</v>
-      </c>
-      <c r="H34" s="3">
-        <v>11</v>
-      </c>
       <c r="I34" s="3">
-        <v>1151.1199999999999</v>
+        <v>1108.9100000000001</v>
       </c>
       <c r="J34" s="1">
         <v>10</v>
@@ -3306,28 +3355,28 @@
         <v>1118.8399999999999</v>
       </c>
       <c r="L34" s="1">
-        <f t="shared" si="12"/>
-        <v>9.09</v>
+        <f t="shared" si="10"/>
+        <v>0</v>
       </c>
       <c r="M34" s="1">
-        <f t="shared" si="13"/>
-        <v>-1.1499999999999999</v>
+        <f t="shared" si="11"/>
+        <v>2.11</v>
       </c>
       <c r="N34" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9.09</v>
       </c>
       <c r="O34" s="1">
         <f t="shared" si="5"/>
-        <v>2.11</v>
+        <v>-1.63</v>
       </c>
       <c r="P34" s="1">
-        <f t="shared" si="14"/>
-        <v>20</v>
+        <f t="shared" si="12"/>
+        <v>10</v>
       </c>
       <c r="Q34" s="1">
-        <f t="shared" si="15"/>
-        <v>-0.41</v>
+        <f t="shared" si="13"/>
+        <v>2.89</v>
       </c>
       <c r="R34" s="12"/>
       <c r="S34" s="13"/>
@@ -3353,16 +3402,16 @@
         <v>1096.3800000000001</v>
       </c>
       <c r="F35" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G35" s="3">
-        <v>1090.1600000000001</v>
+        <v>1161.68</v>
       </c>
       <c r="H35" s="3">
         <v>11</v>
       </c>
       <c r="I35" s="3">
-        <v>1161.68</v>
+        <v>1366.23</v>
       </c>
       <c r="J35" s="1">
         <v>10</v>
@@ -3371,12 +3420,12 @@
         <v>1096.72</v>
       </c>
       <c r="L35" s="1">
-        <f t="shared" si="12"/>
-        <v>9.09</v>
+        <f t="shared" si="10"/>
+        <v>0</v>
       </c>
       <c r="M35" s="1">
-        <f t="shared" si="13"/>
-        <v>-0.56999999999999995</v>
+        <f t="shared" si="11"/>
+        <v>5.96</v>
       </c>
       <c r="N35" s="1">
         <f t="shared" si="4"/>
@@ -3384,15 +3433,15 @@
       </c>
       <c r="O35" s="1">
         <f t="shared" si="5"/>
-        <v>5.96</v>
+        <v>24.61</v>
       </c>
       <c r="P35" s="1">
-        <f t="shared" si="14"/>
-        <v>20</v>
+        <f t="shared" si="12"/>
+        <v>10</v>
       </c>
       <c r="Q35" s="1">
-        <f t="shared" si="15"/>
-        <v>-0.6</v>
+        <f t="shared" si="13"/>
+        <v>5.92</v>
       </c>
       <c r="R35" s="12"/>
       <c r="S35" s="13"/>
@@ -3421,13 +3470,13 @@
         <v>10</v>
       </c>
       <c r="G36" s="3">
-        <v>984.72</v>
+        <v>1035.94</v>
       </c>
       <c r="H36" s="3">
         <v>10</v>
       </c>
       <c r="I36" s="3">
-        <v>1035.94</v>
+        <v>1004.83</v>
       </c>
       <c r="J36" s="1">
         <v>9</v>
@@ -3436,12 +3485,12 @@
         <v>982.14</v>
       </c>
       <c r="L36" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>11.11</v>
       </c>
       <c r="M36" s="1">
-        <f t="shared" si="13"/>
-        <v>0.26</v>
+        <f t="shared" si="11"/>
+        <v>5.48</v>
       </c>
       <c r="N36" s="1">
         <f t="shared" si="4"/>
@@ -3449,15 +3498,15 @@
       </c>
       <c r="O36" s="1">
         <f t="shared" si="5"/>
+        <v>2.31</v>
+      </c>
+      <c r="P36" s="1">
+        <f t="shared" si="12"/>
+        <v>11.11</v>
+      </c>
+      <c r="Q36" s="1">
+        <f t="shared" si="13"/>
         <v>5.48</v>
-      </c>
-      <c r="P36" s="1">
-        <f t="shared" si="14"/>
-        <v>11.11</v>
-      </c>
-      <c r="Q36" s="1">
-        <f t="shared" si="15"/>
-        <v>0.26</v>
       </c>
       <c r="R36" s="12"/>
       <c r="S36" s="13"/>
@@ -3475,7 +3524,7 @@
         <v>13.92</v>
       </c>
       <c r="C37" s="1">
-        <f t="shared" ref="C37:K37" si="16">ROUND(SUM(C25:C36)/COUNTA(C25:C36),2)</f>
+        <f t="shared" ref="C37:K37" si="14">ROUND(SUM(C25:C36)/COUNTA(C25:C36),2)</f>
         <v>1383.64</v>
       </c>
       <c r="D37" s="1">
@@ -3483,39 +3532,39 @@
         <v>12.67</v>
       </c>
       <c r="E37" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>1209.01</v>
       </c>
       <c r="F37" s="1">
         <f>ROUND(SUM(F25:F36)/COUNTA(F25:F36),2)</f>
-        <v>13.17</v>
+        <v>12.67</v>
       </c>
       <c r="G37" s="1">
-        <f t="shared" si="16"/>
-        <v>1199.4000000000001</v>
+        <f t="shared" si="14"/>
+        <v>1287.5</v>
       </c>
       <c r="H37" s="1">
         <f>ROUND(SUM(H25:H36)/COUNTA(H25:H36),2)</f>
-        <v>12.67</v>
+        <v>12.92</v>
       </c>
       <c r="I37" s="1">
-        <f t="shared" ref="I37" si="17">ROUND(SUM(I25:I36)/COUNTA(I25:I36),2)</f>
-        <v>1287.5</v>
+        <f t="shared" ref="I37" si="15">ROUND(SUM(I25:I36)/COUNTA(I25:I36),2)</f>
+        <v>1257.98</v>
       </c>
       <c r="J37" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>11.92</v>
       </c>
       <c r="K37" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>1210.3399999999999</v>
       </c>
-      <c r="L37" s="21"/>
-      <c r="M37" s="22"/>
-      <c r="N37" s="22"/>
-      <c r="O37" s="22"/>
-      <c r="P37" s="22"/>
-      <c r="Q37" s="23"/>
+      <c r="L37" s="20"/>
+      <c r="M37" s="21"/>
+      <c r="N37" s="21"/>
+      <c r="O37" s="21"/>
+      <c r="P37" s="21"/>
+      <c r="Q37" s="22"/>
       <c r="R37" s="15"/>
       <c r="S37" s="16"/>
       <c r="T37" s="17"/>
@@ -3527,33 +3576,33 @@
       <c r="A38" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B38" s="21" t="str">
+      <c r="B38" s="20" t="str">
         <f>COUNTA(A39:A49) &amp; " 筆"</f>
         <v>11 筆</v>
       </c>
-      <c r="C38" s="22"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="22"/>
-      <c r="F38" s="22"/>
-      <c r="G38" s="22"/>
-      <c r="H38" s="22"/>
-      <c r="I38" s="22"/>
-      <c r="J38" s="22"/>
-      <c r="K38" s="22"/>
-      <c r="L38" s="22"/>
-      <c r="M38" s="22"/>
-      <c r="N38" s="22"/>
-      <c r="O38" s="22"/>
-      <c r="P38" s="22"/>
-      <c r="Q38" s="23"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
+      <c r="I38" s="21"/>
+      <c r="J38" s="21"/>
+      <c r="K38" s="21"/>
+      <c r="L38" s="21"/>
+      <c r="M38" s="21"/>
+      <c r="N38" s="21"/>
+      <c r="O38" s="21"/>
+      <c r="P38" s="21"/>
+      <c r="Q38" s="22"/>
       <c r="R38" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="S38" s="1">
         <v>0</v>
       </c>
       <c r="T38" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U38" s="1">
         <v>9</v>
@@ -3581,17 +3630,17 @@
       <c r="E39" s="1">
         <v>1442.28</v>
       </c>
-      <c r="F39" s="3">
-        <v>6</v>
-      </c>
-      <c r="G39" s="3">
-        <v>1234.68</v>
+      <c r="F39" s="2">
+        <v>4</v>
+      </c>
+      <c r="G39" s="2">
+        <v>1308.44</v>
       </c>
       <c r="H39" s="2">
         <v>4</v>
       </c>
       <c r="I39" s="2">
-        <v>1308.44</v>
+        <v>1303.8599999999999</v>
       </c>
       <c r="J39" s="1">
         <v>4</v>
@@ -3600,12 +3649,12 @@
         <v>1252.3699999999999</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" ref="L39:L49" si="18">ROUND(((F39-D39)/D39)*100,2)</f>
-        <v>50</v>
+        <f t="shared" ref="L39:L49" si="16">ROUND(((F39-D39)/D39)*100,2)</f>
+        <v>0</v>
       </c>
       <c r="M39" s="1">
-        <f t="shared" ref="M39:M49" si="19">ROUND(((G39-E39)/E39)*100,2)</f>
-        <v>-14.39</v>
+        <f t="shared" ref="M39:M49" si="17">ROUND(((G39-E39)/E39)*100,2)</f>
+        <v>-9.2799999999999994</v>
       </c>
       <c r="N39" s="1">
         <f t="shared" si="4"/>
@@ -3613,15 +3662,15 @@
       </c>
       <c r="O39" s="1">
         <f t="shared" si="5"/>
-        <v>-9.2799999999999994</v>
+        <v>-9.6</v>
       </c>
       <c r="P39" s="1">
-        <f t="shared" ref="P39:P49" si="20">ROUND(((F39-J39)/J39)*100,2)</f>
-        <v>50</v>
+        <f t="shared" ref="P39:P49" si="18">ROUND(((F39-J39)/J39)*100,2)</f>
+        <v>0</v>
       </c>
       <c r="Q39" s="1">
-        <f t="shared" ref="Q39:Q49" si="21">ROUND(((G39-K39)/K39)*100,2)</f>
-        <v>-1.41</v>
+        <f t="shared" ref="Q39:Q49" si="19">ROUND(((G39-K39)/K39)*100,2)</f>
+        <v>4.4800000000000004</v>
       </c>
       <c r="R39" s="9"/>
       <c r="S39" s="10"/>
@@ -3646,17 +3695,17 @@
       <c r="E40" s="1">
         <v>1212.49</v>
       </c>
-      <c r="F40" s="3">
-        <v>6</v>
-      </c>
-      <c r="G40" s="3">
-        <v>1103.74</v>
+      <c r="F40" s="2">
+        <v>3</v>
+      </c>
+      <c r="G40" s="2">
+        <v>1759.75</v>
       </c>
       <c r="H40" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I40" s="2">
-        <v>1759.75</v>
+        <v>1119.92</v>
       </c>
       <c r="J40" s="1">
         <v>3</v>
@@ -3665,28 +3714,28 @@
         <v>1191.7</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="18"/>
-        <v>50</v>
+        <f t="shared" si="16"/>
+        <v>-25</v>
       </c>
       <c r="M40" s="1">
-        <f t="shared" si="19"/>
-        <v>-8.9700000000000006</v>
+        <f t="shared" si="17"/>
+        <v>45.14</v>
       </c>
       <c r="N40" s="1">
         <f t="shared" si="4"/>
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="O40" s="1">
         <f t="shared" si="5"/>
-        <v>45.14</v>
+        <v>-7.63</v>
       </c>
       <c r="P40" s="1">
-        <f t="shared" si="20"/>
-        <v>100</v>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="Q40" s="1">
-        <f t="shared" si="21"/>
-        <v>-7.38</v>
+        <f t="shared" si="19"/>
+        <v>47.67</v>
       </c>
       <c r="R40" s="12"/>
       <c r="S40" s="13"/>
@@ -3711,17 +3760,17 @@
       <c r="E41" s="1">
         <v>1197.67</v>
       </c>
-      <c r="F41" s="3">
-        <v>5</v>
-      </c>
-      <c r="G41" s="3">
-        <v>964.76</v>
+      <c r="F41" s="2">
+        <v>3</v>
+      </c>
+      <c r="G41" s="2">
+        <v>986.47</v>
       </c>
       <c r="H41" s="2">
         <v>3</v>
       </c>
       <c r="I41" s="2">
-        <v>986.47</v>
+        <v>965.38</v>
       </c>
       <c r="J41" s="1">
         <v>3</v>
@@ -3730,12 +3779,12 @@
         <v>939.5</v>
       </c>
       <c r="L41" s="1">
-        <f t="shared" si="18"/>
-        <v>66.67</v>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="M41" s="1">
-        <f t="shared" si="19"/>
-        <v>-19.45</v>
+        <f t="shared" si="17"/>
+        <v>-17.63</v>
       </c>
       <c r="N41" s="1">
         <f t="shared" si="4"/>
@@ -3743,15 +3792,15 @@
       </c>
       <c r="O41" s="1">
         <f t="shared" si="5"/>
-        <v>-17.63</v>
+        <v>-19.399999999999999</v>
       </c>
       <c r="P41" s="1">
-        <f t="shared" si="20"/>
-        <v>66.67</v>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="Q41" s="1">
-        <f t="shared" si="21"/>
-        <v>2.69</v>
+        <f t="shared" si="19"/>
+        <v>5</v>
       </c>
       <c r="R41" s="12"/>
       <c r="S41" s="13"/>
@@ -3777,16 +3826,16 @@
         <v>854.31</v>
       </c>
       <c r="F42" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G42" s="2">
-        <v>766.23</v>
+        <v>763.8</v>
       </c>
       <c r="H42" s="2">
         <v>3</v>
       </c>
       <c r="I42" s="2">
-        <v>763.8</v>
+        <v>777.61</v>
       </c>
       <c r="J42" s="1">
         <v>2</v>
@@ -3795,12 +3844,12 @@
         <v>825.52</v>
       </c>
       <c r="L42" s="1">
-        <f t="shared" si="18"/>
-        <v>-60</v>
+        <f t="shared" si="16"/>
+        <v>-70</v>
       </c>
       <c r="M42" s="1">
-        <f t="shared" si="19"/>
-        <v>-10.31</v>
+        <f t="shared" si="17"/>
+        <v>-10.59</v>
       </c>
       <c r="N42" s="1">
         <f t="shared" si="4"/>
@@ -3808,15 +3857,15 @@
       </c>
       <c r="O42" s="1">
         <f t="shared" si="5"/>
-        <v>-10.59</v>
+        <v>-8.98</v>
       </c>
       <c r="P42" s="1">
-        <f t="shared" si="20"/>
-        <v>100</v>
+        <f t="shared" si="18"/>
+        <v>50</v>
       </c>
       <c r="Q42" s="1">
-        <f t="shared" si="21"/>
-        <v>-7.18</v>
+        <f t="shared" si="19"/>
+        <v>-7.48</v>
       </c>
       <c r="R42" s="12"/>
       <c r="S42" s="13"/>
@@ -3842,16 +3891,16 @@
         <v>1337.65</v>
       </c>
       <c r="F43" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G43" s="2">
-        <v>1078.75</v>
+        <v>1067.95</v>
       </c>
       <c r="H43" s="2">
         <v>3</v>
       </c>
       <c r="I43" s="2">
-        <v>1067.95</v>
+        <v>1059.71</v>
       </c>
       <c r="J43" s="1">
         <v>3</v>
@@ -3860,12 +3909,12 @@
         <v>994.43</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f t="shared" si="16"/>
+        <v>-25</v>
       </c>
       <c r="M43" s="1">
-        <f t="shared" si="19"/>
-        <v>-19.350000000000001</v>
+        <f t="shared" si="17"/>
+        <v>-20.16</v>
       </c>
       <c r="N43" s="1">
         <f t="shared" si="4"/>
@@ -3873,15 +3922,15 @@
       </c>
       <c r="O43" s="1">
         <f t="shared" si="5"/>
-        <v>-20.16</v>
+        <v>-20.78</v>
       </c>
       <c r="P43" s="1">
-        <f t="shared" si="20"/>
-        <v>33.33</v>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="Q43" s="1">
-        <f t="shared" si="21"/>
-        <v>8.48</v>
+        <f t="shared" si="19"/>
+        <v>7.39</v>
       </c>
       <c r="R43" s="12"/>
       <c r="S43" s="13"/>
@@ -3910,13 +3959,13 @@
         <v>3</v>
       </c>
       <c r="G44" s="2">
-        <v>1005.14</v>
+        <v>967.52</v>
       </c>
       <c r="H44" s="2">
         <v>3</v>
       </c>
       <c r="I44" s="2">
-        <v>967.52</v>
+        <v>931.88</v>
       </c>
       <c r="J44" s="1">
         <v>3</v>
@@ -3925,12 +3974,12 @@
         <v>906.14</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>-25</v>
       </c>
       <c r="M44" s="1">
-        <f t="shared" si="19"/>
-        <v>-9.83</v>
+        <f t="shared" si="17"/>
+        <v>-13.21</v>
       </c>
       <c r="N44" s="1">
         <f t="shared" si="4"/>
@@ -3938,15 +3987,15 @@
       </c>
       <c r="O44" s="1">
         <f t="shared" si="5"/>
-        <v>-13.21</v>
+        <v>-16.41</v>
       </c>
       <c r="P44" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q44" s="1">
-        <f t="shared" si="21"/>
-        <v>10.93</v>
+        <f t="shared" si="19"/>
+        <v>6.77</v>
       </c>
       <c r="R44" s="12"/>
       <c r="S44" s="13"/>
@@ -3972,16 +4021,16 @@
         <v>1055.71</v>
       </c>
       <c r="F45" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G45" s="2">
-        <v>865.63</v>
+        <v>853.49</v>
       </c>
       <c r="H45" s="2">
         <v>3</v>
       </c>
       <c r="I45" s="2">
-        <v>853.49</v>
+        <v>849.32</v>
       </c>
       <c r="J45" s="1">
         <v>2</v>
@@ -3990,12 +4039,12 @@
         <v>890.61</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f t="shared" si="16"/>
+        <v>-25</v>
       </c>
       <c r="M45" s="1">
-        <f t="shared" si="19"/>
-        <v>-18</v>
+        <f t="shared" si="17"/>
+        <v>-19.149999999999999</v>
       </c>
       <c r="N45" s="1">
         <f t="shared" si="4"/>
@@ -4003,15 +4052,15 @@
       </c>
       <c r="O45" s="1">
         <f t="shared" si="5"/>
-        <v>-19.149999999999999</v>
+        <v>-19.55</v>
       </c>
       <c r="P45" s="1">
-        <f t="shared" si="20"/>
-        <v>100</v>
+        <f t="shared" si="18"/>
+        <v>50</v>
       </c>
       <c r="Q45" s="1">
-        <f t="shared" si="21"/>
-        <v>-2.8</v>
+        <f t="shared" si="19"/>
+        <v>-4.17</v>
       </c>
       <c r="R45" s="12"/>
       <c r="S45" s="13"/>
@@ -4037,16 +4086,16 @@
         <v>860.53</v>
       </c>
       <c r="F46" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G46" s="2">
-        <v>727.64</v>
+        <v>739.55</v>
       </c>
       <c r="H46" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I46" s="2">
-        <v>739.55</v>
+        <v>728.84</v>
       </c>
       <c r="J46" s="1">
         <v>2</v>
@@ -4055,28 +4104,28 @@
         <v>726.82</v>
       </c>
       <c r="L46" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f t="shared" si="16"/>
+        <v>-33.33</v>
       </c>
       <c r="M46" s="1">
-        <f t="shared" si="19"/>
-        <v>-15.44</v>
+        <f t="shared" si="17"/>
+        <v>-14.06</v>
       </c>
       <c r="N46" s="1">
         <f t="shared" si="4"/>
-        <v>-33.33</v>
+        <v>0</v>
       </c>
       <c r="O46" s="1">
         <f t="shared" si="5"/>
-        <v>-14.06</v>
+        <v>-15.3</v>
       </c>
       <c r="P46" s="1">
-        <f t="shared" si="20"/>
-        <v>50</v>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="Q46" s="1">
-        <f t="shared" si="21"/>
-        <v>0.11</v>
+        <f t="shared" si="19"/>
+        <v>1.75</v>
       </c>
       <c r="R46" s="12"/>
       <c r="S46" s="13"/>
@@ -4102,16 +4151,16 @@
         <v>895.46749999999997</v>
       </c>
       <c r="F47" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G47" s="3">
-        <v>912.61</v>
+        <v>957.21</v>
       </c>
       <c r="H47" s="3">
         <v>3</v>
       </c>
       <c r="I47" s="3">
-        <v>957.21</v>
+        <v>959.23</v>
       </c>
       <c r="J47" s="1">
         <v>3</v>
@@ -4120,12 +4169,12 @@
         <v>909.16</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="18"/>
-        <v>100</v>
+        <f t="shared" si="16"/>
+        <v>50</v>
       </c>
       <c r="M47" s="1">
-        <f t="shared" si="19"/>
-        <v>1.91</v>
+        <f t="shared" si="17"/>
+        <v>6.9</v>
       </c>
       <c r="N47" s="1">
         <f t="shared" si="4"/>
@@ -4133,15 +4182,15 @@
       </c>
       <c r="O47" s="1">
         <f t="shared" si="5"/>
-        <v>6.9</v>
+        <v>7.12</v>
       </c>
       <c r="P47" s="1">
-        <f t="shared" si="20"/>
-        <v>33.33</v>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="Q47" s="1">
-        <f t="shared" si="21"/>
-        <v>0.38</v>
+        <f t="shared" si="19"/>
+        <v>5.29</v>
       </c>
       <c r="R47" s="12"/>
       <c r="S47" s="13"/>
@@ -4167,16 +4216,16 @@
         <v>942.94849999999997</v>
       </c>
       <c r="F48" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G48" s="3">
-        <v>1022.23</v>
+        <v>993.95</v>
       </c>
       <c r="H48" s="3">
         <v>3</v>
       </c>
       <c r="I48" s="3">
-        <v>993.95</v>
+        <v>984.59</v>
       </c>
       <c r="J48" s="1">
         <v>3</v>
@@ -4185,12 +4234,12 @@
         <v>939.37</v>
       </c>
       <c r="L48" s="1">
-        <f t="shared" si="18"/>
-        <v>100</v>
+        <f t="shared" si="16"/>
+        <v>50</v>
       </c>
       <c r="M48" s="1">
-        <f t="shared" si="19"/>
-        <v>8.41</v>
+        <f t="shared" si="17"/>
+        <v>5.41</v>
       </c>
       <c r="N48" s="1">
         <f t="shared" si="4"/>
@@ -4198,15 +4247,15 @@
       </c>
       <c r="O48" s="1">
         <f t="shared" si="5"/>
-        <v>5.41</v>
+        <v>4.42</v>
       </c>
       <c r="P48" s="1">
-        <f t="shared" si="20"/>
-        <v>33.33</v>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="Q48" s="1">
-        <f t="shared" si="21"/>
-        <v>8.82</v>
+        <f t="shared" si="19"/>
+        <v>5.81</v>
       </c>
       <c r="R48" s="12"/>
       <c r="S48" s="13"/>
@@ -4235,13 +4284,13 @@
         <v>3</v>
       </c>
       <c r="G49" s="2">
-        <v>802.69</v>
+        <v>820.45</v>
       </c>
       <c r="H49" s="2">
         <v>3</v>
       </c>
       <c r="I49" s="2">
-        <v>820.45</v>
+        <v>804.22</v>
       </c>
       <c r="J49" s="1">
         <v>2</v>
@@ -4250,12 +4299,12 @@
         <v>885.71</v>
       </c>
       <c r="L49" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M49" s="1">
-        <f t="shared" si="19"/>
-        <v>-23.53</v>
+        <f t="shared" si="17"/>
+        <v>-21.83</v>
       </c>
       <c r="N49" s="1">
         <f t="shared" si="4"/>
@@ -4263,15 +4312,15 @@
       </c>
       <c r="O49" s="1">
         <f t="shared" si="5"/>
-        <v>-21.83</v>
+        <v>-23.38</v>
       </c>
       <c r="P49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>50</v>
       </c>
       <c r="Q49" s="1">
-        <f t="shared" si="21"/>
-        <v>-9.3699999999999992</v>
+        <f t="shared" si="19"/>
+        <v>-7.37</v>
       </c>
       <c r="R49" s="12"/>
       <c r="S49" s="13"/>
@@ -4289,47 +4338,47 @@
         <v>3.27</v>
       </c>
       <c r="C50" s="1">
-        <f t="shared" ref="C50:K50" si="22">ROUND(SUM(C39:C49)/COUNTA(C39:C49),2)</f>
+        <f t="shared" ref="C50:K50" si="20">ROUND(SUM(C39:C49)/COUNTA(C39:C49),2)</f>
         <v>1329.44</v>
       </c>
       <c r="D50" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>3.91</v>
       </c>
       <c r="E50" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>1087.5899999999999</v>
       </c>
       <c r="F50" s="1">
-        <f t="shared" si="22"/>
-        <v>4.18</v>
+        <f t="shared" si="20"/>
+        <v>3</v>
       </c>
       <c r="G50" s="1">
         <f>ROUND(SUM(G39:G49)/COUNTA(G39:G49),2)</f>
-        <v>953.1</v>
+        <v>1019.87</v>
       </c>
       <c r="H50" s="1">
         <f>ROUND(SUM(H39:H49)/COUNTA(H39:H49),2)</f>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="I50" s="1">
         <f>ROUND(SUM(I39:I49)/COUNTA(I39:I49),2)</f>
-        <v>1019.87</v>
+        <v>953.14</v>
       </c>
       <c r="J50" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>2.73</v>
       </c>
       <c r="K50" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>951.03</v>
       </c>
-      <c r="L50" s="21"/>
-      <c r="M50" s="22"/>
-      <c r="N50" s="22"/>
-      <c r="O50" s="22"/>
-      <c r="P50" s="22"/>
-      <c r="Q50" s="23"/>
+      <c r="L50" s="20"/>
+      <c r="M50" s="21"/>
+      <c r="N50" s="21"/>
+      <c r="O50" s="21"/>
+      <c r="P50" s="21"/>
+      <c r="Q50" s="22"/>
       <c r="R50" s="15"/>
       <c r="S50" s="16"/>
       <c r="T50" s="17"/>
@@ -4341,25 +4390,25 @@
       <c r="A51" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B51" s="21" t="str">
+      <c r="B51" s="20" t="str">
         <f>COUNTA(A52:A59) &amp; " 筆"</f>
         <v>8 筆</v>
       </c>
-      <c r="C51" s="22"/>
-      <c r="D51" s="22"/>
-      <c r="E51" s="22"/>
-      <c r="F51" s="22"/>
-      <c r="G51" s="22"/>
-      <c r="H51" s="22"/>
-      <c r="I51" s="22"/>
-      <c r="J51" s="22"/>
-      <c r="K51" s="22"/>
-      <c r="L51" s="22"/>
-      <c r="M51" s="22"/>
-      <c r="N51" s="22"/>
-      <c r="O51" s="22"/>
-      <c r="P51" s="22"/>
-      <c r="Q51" s="23"/>
+      <c r="C51" s="21"/>
+      <c r="D51" s="21"/>
+      <c r="E51" s="21"/>
+      <c r="F51" s="21"/>
+      <c r="G51" s="21"/>
+      <c r="H51" s="21"/>
+      <c r="I51" s="21"/>
+      <c r="J51" s="21"/>
+      <c r="K51" s="21"/>
+      <c r="L51" s="21"/>
+      <c r="M51" s="21"/>
+      <c r="N51" s="21"/>
+      <c r="O51" s="21"/>
+      <c r="P51" s="21"/>
+      <c r="Q51" s="22"/>
       <c r="R51" s="1">
         <v>5</v>
       </c>
@@ -4370,13 +4419,13 @@
         <v>3</v>
       </c>
       <c r="U51" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V51" s="1">
         <v>0</v>
       </c>
       <c r="W51" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
@@ -4396,16 +4445,16 @@
         <v>1656.59</v>
       </c>
       <c r="F52" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G52" s="2">
-        <v>1652.36</v>
+        <v>1687.93</v>
       </c>
       <c r="H52" s="2">
         <v>15</v>
       </c>
       <c r="I52" s="2">
-        <v>1687.93</v>
+        <v>1645.68</v>
       </c>
       <c r="J52" s="1">
         <v>14</v>
@@ -4414,12 +4463,12 @@
         <v>1696.95</v>
       </c>
       <c r="L52" s="1">
-        <f t="shared" ref="L52:L59" si="23">ROUND(((F52-D52)/D52)*100,2)</f>
-        <v>0</v>
+        <f t="shared" ref="L52:L59" si="21">ROUND(((F52-D52)/D52)*100,2)</f>
+        <v>-6.25</v>
       </c>
       <c r="M52" s="1">
-        <f t="shared" ref="M52:M59" si="24">ROUND(((G52-E52)/E52)*100,2)</f>
-        <v>-0.26</v>
+        <f t="shared" ref="M52:M59" si="22">ROUND(((G52-E52)/E52)*100,2)</f>
+        <v>1.89</v>
       </c>
       <c r="N52" s="1">
         <f t="shared" si="4"/>
@@ -4427,15 +4476,15 @@
       </c>
       <c r="O52" s="1">
         <f t="shared" si="5"/>
-        <v>1.89</v>
+        <v>-0.66</v>
       </c>
       <c r="P52" s="1">
-        <f t="shared" ref="P52:P59" si="25">ROUND(((F52-J52)/J52)*100,2)</f>
-        <v>14.29</v>
+        <f t="shared" ref="P52:P59" si="23">ROUND(((F52-J52)/J52)*100,2)</f>
+        <v>7.14</v>
       </c>
       <c r="Q52" s="1">
-        <f t="shared" ref="Q52:Q59" si="26">ROUND(((G52-K52)/K52)*100,2)</f>
-        <v>-2.63</v>
+        <f t="shared" ref="Q52:Q59" si="24">ROUND(((G52-K52)/K52)*100,2)</f>
+        <v>-0.53</v>
       </c>
       <c r="R52" s="9"/>
       <c r="S52" s="10"/>
@@ -4460,17 +4509,17 @@
       <c r="E53" s="1">
         <v>1532.25</v>
       </c>
-      <c r="F53" s="3">
-        <v>14</v>
-      </c>
-      <c r="G53" s="3">
-        <v>1486.88</v>
+      <c r="F53" s="2">
+        <v>13</v>
+      </c>
+      <c r="G53" s="2">
+        <v>1507.94</v>
       </c>
       <c r="H53" s="2">
         <v>13</v>
       </c>
       <c r="I53" s="2">
-        <v>1507.94</v>
+        <v>1511.64</v>
       </c>
       <c r="J53" s="1">
         <v>12</v>
@@ -4479,12 +4528,12 @@
         <v>1554.75</v>
       </c>
       <c r="L53" s="1">
-        <f t="shared" si="23"/>
-        <v>7.69</v>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
       <c r="M53" s="1">
-        <f t="shared" si="24"/>
-        <v>-2.96</v>
+        <f t="shared" si="22"/>
+        <v>-1.59</v>
       </c>
       <c r="N53" s="1">
         <f t="shared" si="4"/>
@@ -4492,15 +4541,15 @@
       </c>
       <c r="O53" s="1">
         <f t="shared" si="5"/>
-        <v>-1.59</v>
+        <v>-1.35</v>
       </c>
       <c r="P53" s="1">
-        <f t="shared" si="25"/>
-        <v>16.670000000000002</v>
+        <f t="shared" si="23"/>
+        <v>8.33</v>
       </c>
       <c r="Q53" s="1">
-        <f t="shared" si="26"/>
-        <v>-4.37</v>
+        <f t="shared" si="24"/>
+        <v>-3.01</v>
       </c>
       <c r="R53" s="12"/>
       <c r="S53" s="13"/>
@@ -4526,16 +4575,16 @@
         <v>1344.03</v>
       </c>
       <c r="F54" s="2">
+        <v>11</v>
+      </c>
+      <c r="G54" s="2">
+        <v>1516.36</v>
+      </c>
+      <c r="H54" s="2">
         <v>12</v>
       </c>
-      <c r="G54" s="2">
-        <v>1297.3499999999999</v>
-      </c>
-      <c r="H54" s="2">
-        <v>11</v>
-      </c>
       <c r="I54" s="2">
-        <v>1516.36</v>
+        <v>1294.26</v>
       </c>
       <c r="J54" s="1">
         <v>11</v>
@@ -4544,28 +4593,28 @@
         <v>1261.67</v>
       </c>
       <c r="L54" s="1">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f t="shared" si="21"/>
+        <v>-8.33</v>
       </c>
       <c r="M54" s="1">
-        <f t="shared" si="24"/>
-        <v>-3.47</v>
+        <f t="shared" si="22"/>
+        <v>12.82</v>
       </c>
       <c r="N54" s="1">
         <f t="shared" si="4"/>
-        <v>-8.33</v>
+        <v>0</v>
       </c>
       <c r="O54" s="1">
         <f t="shared" si="5"/>
-        <v>12.82</v>
+        <v>-3.7</v>
       </c>
       <c r="P54" s="1">
-        <f t="shared" si="25"/>
-        <v>9.09</v>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="Q54" s="1">
-        <f t="shared" si="26"/>
-        <v>2.83</v>
+        <f t="shared" si="24"/>
+        <v>20.190000000000001</v>
       </c>
       <c r="R54" s="12"/>
       <c r="S54" s="13"/>
@@ -4594,13 +4643,13 @@
         <v>10</v>
       </c>
       <c r="G55" s="2">
-        <v>1173.68</v>
+        <v>1336.1</v>
       </c>
       <c r="H55" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I55" s="2">
-        <v>1336.1</v>
+        <v>1182.05</v>
       </c>
       <c r="J55" s="1">
         <v>10</v>
@@ -4609,28 +4658,28 @@
         <v>1135.48</v>
       </c>
       <c r="L55" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>-9.09</v>
       </c>
       <c r="M55" s="1">
-        <f t="shared" si="24"/>
-        <v>-0.95</v>
+        <f t="shared" si="22"/>
+        <v>12.76</v>
       </c>
       <c r="N55" s="1">
         <f t="shared" si="4"/>
-        <v>-9.09</v>
+        <v>0</v>
       </c>
       <c r="O55" s="1">
         <f t="shared" si="5"/>
-        <v>12.76</v>
+        <v>-0.24</v>
       </c>
       <c r="P55" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="Q55" s="1">
-        <f t="shared" si="26"/>
-        <v>3.36</v>
+        <f t="shared" si="24"/>
+        <v>17.670000000000002</v>
       </c>
       <c r="R55" s="12"/>
       <c r="S55" s="13"/>
@@ -4656,16 +4705,16 @@
         <v>1662.01</v>
       </c>
       <c r="F56" s="3">
+        <v>14</v>
+      </c>
+      <c r="G56" s="3">
+        <v>1902.43</v>
+      </c>
+      <c r="H56" s="3">
         <v>15</v>
       </c>
-      <c r="G56" s="3">
-        <v>1555.81</v>
-      </c>
-      <c r="H56" s="3">
-        <v>14</v>
-      </c>
       <c r="I56" s="3">
-        <v>1902.43</v>
+        <v>1554.54</v>
       </c>
       <c r="J56" s="1">
         <v>13</v>
@@ -4674,28 +4723,28 @@
         <v>1629.44</v>
       </c>
       <c r="L56" s="1">
-        <f t="shared" si="23"/>
-        <v>7.14</v>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
       <c r="M56" s="1">
-        <f t="shared" si="24"/>
-        <v>-6.39</v>
+        <f t="shared" si="22"/>
+        <v>14.47</v>
       </c>
       <c r="N56" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="O56" s="1">
         <f t="shared" si="5"/>
-        <v>14.47</v>
+        <v>-6.47</v>
       </c>
       <c r="P56" s="1">
-        <f t="shared" si="25"/>
-        <v>15.38</v>
+        <f t="shared" si="23"/>
+        <v>7.69</v>
       </c>
       <c r="Q56" s="1">
-        <f t="shared" si="26"/>
-        <v>-4.5199999999999996</v>
+        <f t="shared" si="24"/>
+        <v>16.75</v>
       </c>
       <c r="R56" s="12"/>
       <c r="S56" s="13"/>
@@ -4721,16 +4770,16 @@
         <v>1344.03</v>
       </c>
       <c r="F57" s="3">
+        <v>12</v>
+      </c>
+      <c r="G57" s="3">
+        <v>1663.23</v>
+      </c>
+      <c r="H57" s="3">
         <v>13</v>
       </c>
-      <c r="G57" s="3">
-        <v>1405.73</v>
-      </c>
-      <c r="H57" s="3">
-        <v>12</v>
-      </c>
       <c r="I57" s="3">
-        <v>1663.23</v>
+        <v>1407.11</v>
       </c>
       <c r="J57" s="1">
         <v>11</v>
@@ -4739,28 +4788,28 @@
         <v>1424.73</v>
       </c>
       <c r="L57" s="1">
-        <f t="shared" si="23"/>
-        <v>8.33</v>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
       <c r="M57" s="1">
-        <f t="shared" si="24"/>
-        <v>4.59</v>
+        <f t="shared" si="22"/>
+        <v>23.75</v>
       </c>
       <c r="N57" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="O57" s="1">
         <f t="shared" si="5"/>
-        <v>23.75</v>
+        <v>4.6900000000000004</v>
       </c>
       <c r="P57" s="1">
-        <f t="shared" si="25"/>
-        <v>18.18</v>
+        <f t="shared" si="23"/>
+        <v>9.09</v>
       </c>
       <c r="Q57" s="1">
-        <f t="shared" si="26"/>
-        <v>-1.33</v>
+        <f t="shared" si="24"/>
+        <v>16.739999999999998</v>
       </c>
       <c r="R57" s="12"/>
       <c r="S57" s="13"/>
@@ -4786,16 +4835,16 @@
         <v>1263.07</v>
       </c>
       <c r="F58" s="2">
+        <v>11</v>
+      </c>
+      <c r="G58" s="2">
+        <v>1529.97</v>
+      </c>
+      <c r="H58" s="2">
         <v>12</v>
       </c>
-      <c r="G58" s="2">
-        <v>1251.25</v>
-      </c>
-      <c r="H58" s="2">
-        <v>11</v>
-      </c>
       <c r="I58" s="2">
-        <v>1529.97</v>
+        <v>1257.58</v>
       </c>
       <c r="J58" s="1">
         <v>11</v>
@@ -4804,28 +4853,28 @@
         <v>1230.48</v>
       </c>
       <c r="L58" s="1">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f t="shared" si="21"/>
+        <v>-8.33</v>
       </c>
       <c r="M58" s="1">
-        <f t="shared" si="24"/>
-        <v>-0.94</v>
+        <f t="shared" si="22"/>
+        <v>21.13</v>
       </c>
       <c r="N58" s="1">
         <f t="shared" si="4"/>
-        <v>-8.33</v>
+        <v>0</v>
       </c>
       <c r="O58" s="1">
         <f t="shared" si="5"/>
-        <v>21.13</v>
+        <v>-0.43</v>
       </c>
       <c r="P58" s="1">
-        <f t="shared" si="25"/>
-        <v>9.09</v>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="Q58" s="1">
-        <f t="shared" si="26"/>
-        <v>1.69</v>
+        <f t="shared" si="24"/>
+        <v>24.34</v>
       </c>
       <c r="R58" s="12"/>
       <c r="S58" s="13"/>
@@ -4850,17 +4899,17 @@
       <c r="E59" s="1">
         <v>1144.94</v>
       </c>
-      <c r="F59" s="2">
+      <c r="F59" s="3">
         <v>11</v>
       </c>
-      <c r="G59" s="2">
-        <v>1140.6600000000001</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="G59" s="3">
+        <v>1145.69</v>
+      </c>
+      <c r="H59" s="2">
         <v>11</v>
       </c>
-      <c r="I59" s="3">
-        <v>1145.69</v>
+      <c r="I59" s="2">
+        <v>1137.42</v>
       </c>
       <c r="J59" s="1">
         <v>10</v>
@@ -4869,12 +4918,12 @@
         <v>1139.82</v>
       </c>
       <c r="L59" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M59" s="1">
-        <f t="shared" si="24"/>
-        <v>-0.37</v>
+        <f t="shared" si="22"/>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="N59" s="1">
         <f t="shared" si="4"/>
@@ -4882,15 +4931,15 @@
       </c>
       <c r="O59" s="1">
         <f t="shared" si="5"/>
-        <v>7.0000000000000007E-2</v>
+        <v>-0.66</v>
       </c>
       <c r="P59" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="Q59" s="1">
-        <f t="shared" si="26"/>
-        <v>7.0000000000000007E-2</v>
+        <f t="shared" si="24"/>
+        <v>0.51</v>
       </c>
       <c r="R59" s="12"/>
       <c r="S59" s="13"/>
@@ -4908,47 +4957,47 @@
         <v>14</v>
       </c>
       <c r="C60" s="1">
-        <f t="shared" ref="C60:K60" si="27">ROUND(SUM(C52:C59)/COUNTA(C52:C59),2)</f>
+        <f t="shared" ref="C60:K60" si="25">ROUND(SUM(C52:C59)/COUNTA(C52:C59),2)</f>
         <v>1559.4</v>
       </c>
       <c r="D60" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>12.63</v>
       </c>
       <c r="E60" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>1391.48</v>
       </c>
       <c r="F60" s="1">
-        <f t="shared" si="27"/>
-        <v>12.88</v>
+        <f t="shared" si="25"/>
+        <v>12.13</v>
       </c>
       <c r="G60" s="1">
-        <f t="shared" si="27"/>
-        <v>1370.47</v>
+        <f t="shared" si="25"/>
+        <v>1536.21</v>
       </c>
       <c r="H60" s="1">
-        <f t="shared" ref="H60" si="28">ROUND(SUM(H52:H59)/COUNTA(H52:H59),2)</f>
-        <v>12.13</v>
+        <f t="shared" ref="H60" si="26">ROUND(SUM(H52:H59)/COUNTA(H52:H59),2)</f>
+        <v>12.75</v>
       </c>
       <c r="I60" s="1">
-        <f t="shared" ref="I60" si="29">ROUND(SUM(I52:I59)/COUNTA(I52:I59),2)</f>
-        <v>1536.21</v>
+        <f t="shared" ref="I60" si="27">ROUND(SUM(I52:I59)/COUNTA(I52:I59),2)</f>
+        <v>1373.79</v>
       </c>
       <c r="J60" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>11.5</v>
       </c>
       <c r="K60" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>1384.17</v>
       </c>
-      <c r="L60" s="21"/>
-      <c r="M60" s="22"/>
-      <c r="N60" s="22"/>
-      <c r="O60" s="22"/>
-      <c r="P60" s="22"/>
-      <c r="Q60" s="23"/>
+      <c r="L60" s="20"/>
+      <c r="M60" s="21"/>
+      <c r="N60" s="21"/>
+      <c r="O60" s="21"/>
+      <c r="P60" s="21"/>
+      <c r="Q60" s="22"/>
       <c r="R60" s="15"/>
       <c r="S60" s="16"/>
       <c r="T60" s="17"/>
@@ -4960,42 +5009,42 @@
       <c r="A61" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B61" s="21" t="str">
+      <c r="B61" s="20" t="str">
         <f>COUNTA(A62:A69) &amp; " 筆"</f>
         <v>8 筆</v>
       </c>
-      <c r="C61" s="22"/>
-      <c r="D61" s="22"/>
-      <c r="E61" s="22"/>
-      <c r="F61" s="22"/>
-      <c r="G61" s="22"/>
-      <c r="H61" s="22"/>
-      <c r="I61" s="22"/>
-      <c r="J61" s="22"/>
-      <c r="K61" s="22"/>
-      <c r="L61" s="22"/>
-      <c r="M61" s="22"/>
-      <c r="N61" s="22"/>
-      <c r="O61" s="22"/>
-      <c r="P61" s="22"/>
-      <c r="Q61" s="23"/>
+      <c r="C61" s="21"/>
+      <c r="D61" s="21"/>
+      <c r="E61" s="21"/>
+      <c r="F61" s="21"/>
+      <c r="G61" s="21"/>
+      <c r="H61" s="21"/>
+      <c r="I61" s="21"/>
+      <c r="J61" s="21"/>
+      <c r="K61" s="21"/>
+      <c r="L61" s="21"/>
+      <c r="M61" s="21"/>
+      <c r="N61" s="21"/>
+      <c r="O61" s="21"/>
+      <c r="P61" s="21"/>
+      <c r="Q61" s="22"/>
       <c r="R61" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S61" s="1">
         <v>0</v>
       </c>
       <c r="T61" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U61" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V61" s="1">
         <v>0</v>
       </c>
       <c r="W61" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
@@ -5015,16 +5064,16 @@
         <v>1442.28</v>
       </c>
       <c r="F62" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G62" s="3">
-        <v>1389.68</v>
+        <v>1465.57</v>
       </c>
       <c r="H62" s="3">
         <v>4</v>
       </c>
       <c r="I62" s="3">
-        <v>1465.57</v>
+        <v>1557.23</v>
       </c>
       <c r="J62" s="1">
         <v>4</v>
@@ -5033,12 +5082,12 @@
         <v>1406.94</v>
       </c>
       <c r="L62" s="1">
-        <f t="shared" ref="L62:M69" si="30">ROUND(((F62-D62)/D62)*100,2)</f>
-        <v>50</v>
+        <f t="shared" ref="L62:M69" si="28">ROUND(((F62-D62)/D62)*100,2)</f>
+        <v>0</v>
       </c>
       <c r="M62" s="1">
-        <f t="shared" si="30"/>
-        <v>-3.65</v>
+        <f t="shared" si="28"/>
+        <v>1.61</v>
       </c>
       <c r="N62" s="1">
         <f t="shared" si="4"/>
@@ -5046,15 +5095,15 @@
       </c>
       <c r="O62" s="1">
         <f t="shared" si="5"/>
-        <v>1.61</v>
+        <v>7.97</v>
       </c>
       <c r="P62" s="1">
-        <f t="shared" ref="P62:Q69" si="31">ROUND(((F62-J62)/J62)*100,2)</f>
-        <v>50</v>
+        <f t="shared" ref="P62:Q69" si="29">ROUND(((F62-J62)/J62)*100,2)</f>
+        <v>0</v>
       </c>
       <c r="Q62" s="1">
-        <f t="shared" si="31"/>
-        <v>-1.23</v>
+        <f t="shared" si="29"/>
+        <v>4.17</v>
       </c>
       <c r="R62" s="9"/>
       <c r="S62" s="10"/>
@@ -5080,16 +5129,16 @@
         <v>1212.49</v>
       </c>
       <c r="F63" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G63" s="3">
-        <v>1225.8699999999999</v>
-      </c>
-      <c r="H63" s="3">
+        <v>1251.74</v>
+      </c>
+      <c r="H63" s="2">
         <v>4</v>
       </c>
-      <c r="I63" s="3">
-        <v>1251.74</v>
+      <c r="I63" s="2">
+        <v>1192.8699999999999</v>
       </c>
       <c r="J63" s="1">
         <v>3</v>
@@ -5098,12 +5147,12 @@
         <v>1365.65</v>
       </c>
       <c r="L63" s="1">
-        <f t="shared" si="30"/>
-        <v>50</v>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="M63" s="1">
-        <f t="shared" si="30"/>
-        <v>1.1000000000000001</v>
+        <f t="shared" si="28"/>
+        <v>3.24</v>
       </c>
       <c r="N63" s="1">
         <f t="shared" si="4"/>
@@ -5111,15 +5160,15 @@
       </c>
       <c r="O63" s="1">
         <f t="shared" si="5"/>
-        <v>3.24</v>
+        <v>-1.62</v>
       </c>
       <c r="P63" s="1">
-        <f t="shared" si="31"/>
-        <v>100</v>
+        <f t="shared" si="29"/>
+        <v>33.33</v>
       </c>
       <c r="Q63" s="1">
-        <f t="shared" si="31"/>
-        <v>-10.24</v>
+        <f t="shared" si="29"/>
+        <v>-8.34</v>
       </c>
       <c r="R63" s="12"/>
       <c r="S63" s="13"/>
@@ -5144,17 +5193,17 @@
       <c r="E64" s="1">
         <v>1197.67</v>
       </c>
-      <c r="F64" s="3">
-        <v>5</v>
-      </c>
-      <c r="G64" s="3">
-        <v>1021.41</v>
-      </c>
-      <c r="H64" s="2">
-        <v>3</v>
-      </c>
-      <c r="I64" s="2">
+      <c r="F64" s="2">
+        <v>3</v>
+      </c>
+      <c r="G64" s="2">
         <v>1134.53</v>
+      </c>
+      <c r="H64" s="3">
+        <v>3</v>
+      </c>
+      <c r="I64" s="3">
+        <v>1264.51</v>
       </c>
       <c r="J64" s="1">
         <v>3</v>
@@ -5163,12 +5212,12 @@
         <v>1049.6199999999999</v>
       </c>
       <c r="L64" s="1">
-        <f t="shared" si="30"/>
-        <v>66.67</v>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="M64" s="1">
-        <f t="shared" si="30"/>
-        <v>-14.72</v>
+        <f t="shared" si="28"/>
+        <v>-5.27</v>
       </c>
       <c r="N64" s="1">
         <f t="shared" si="4"/>
@@ -5176,15 +5225,15 @@
       </c>
       <c r="O64" s="1">
         <f t="shared" si="5"/>
-        <v>-5.27</v>
+        <v>5.58</v>
       </c>
       <c r="P64" s="1">
-        <f t="shared" si="31"/>
-        <v>66.67</v>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
       <c r="Q64" s="1">
-        <f t="shared" si="31"/>
-        <v>-2.69</v>
+        <f t="shared" si="29"/>
+        <v>8.09</v>
       </c>
       <c r="R64" s="12"/>
       <c r="S64" s="13"/>
@@ -5210,16 +5259,16 @@
         <v>854.31</v>
       </c>
       <c r="F65" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G65" s="2">
-        <v>842.82</v>
+        <v>817.78</v>
       </c>
       <c r="H65" s="2">
         <v>3</v>
       </c>
       <c r="I65" s="2">
-        <v>817.78</v>
+        <v>861.84</v>
       </c>
       <c r="J65" s="1">
         <v>3</v>
@@ -5228,12 +5277,12 @@
         <v>798.46</v>
       </c>
       <c r="L65" s="1">
-        <f t="shared" si="30"/>
-        <v>-60</v>
+        <f t="shared" si="28"/>
+        <v>-70</v>
       </c>
       <c r="M65" s="1">
-        <f t="shared" si="30"/>
-        <v>-1.34</v>
+        <f t="shared" si="28"/>
+        <v>-4.28</v>
       </c>
       <c r="N65" s="1">
         <f t="shared" si="4"/>
@@ -5241,15 +5290,15 @@
       </c>
       <c r="O65" s="1">
         <f t="shared" si="5"/>
-        <v>-4.28</v>
+        <v>0.88</v>
       </c>
       <c r="P65" s="1">
-        <f t="shared" si="31"/>
-        <v>33.33</v>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
       <c r="Q65" s="1">
-        <f t="shared" si="31"/>
-        <v>5.56</v>
+        <f t="shared" si="29"/>
+        <v>2.42</v>
       </c>
       <c r="R65" s="12"/>
       <c r="S65" s="13"/>
@@ -5275,16 +5324,16 @@
         <v>1337.65</v>
       </c>
       <c r="F66" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G66" s="3">
-        <v>1288.45</v>
+        <v>1379.81</v>
       </c>
       <c r="H66" s="3">
         <v>4</v>
       </c>
       <c r="I66" s="3">
-        <v>1379.81</v>
+        <v>1496.11</v>
       </c>
       <c r="J66" s="1">
         <v>4</v>
@@ -5293,12 +5342,12 @@
         <v>1297.6500000000001</v>
       </c>
       <c r="L66" s="1">
-        <f t="shared" si="30"/>
-        <v>50</v>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="M66" s="1">
-        <f t="shared" si="30"/>
-        <v>-3.68</v>
+        <f t="shared" si="28"/>
+        <v>3.15</v>
       </c>
       <c r="N66" s="1">
         <f t="shared" si="4"/>
@@ -5306,15 +5355,15 @@
       </c>
       <c r="O66" s="1">
         <f t="shared" si="5"/>
-        <v>3.15</v>
+        <v>11.85</v>
       </c>
       <c r="P66" s="1">
-        <f t="shared" si="31"/>
-        <v>50</v>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
       <c r="Q66" s="1">
-        <f t="shared" si="31"/>
-        <v>-0.71</v>
+        <f t="shared" si="29"/>
+        <v>6.33</v>
       </c>
       <c r="R66" s="12"/>
       <c r="S66" s="13"/>
@@ -5339,17 +5388,17 @@
       <c r="E67" s="1">
         <v>1114.76</v>
       </c>
-      <c r="F67" s="3">
+      <c r="F67" s="2">
+        <v>3</v>
+      </c>
+      <c r="G67" s="2">
+        <v>1265.18</v>
+      </c>
+      <c r="H67" s="3">
         <v>4</v>
       </c>
-      <c r="G67" s="3">
-        <v>1234.22</v>
-      </c>
-      <c r="H67" s="2">
-        <v>3</v>
-      </c>
-      <c r="I67" s="2">
-        <v>1265.18</v>
+      <c r="I67" s="3">
+        <v>1186.08</v>
       </c>
       <c r="J67" s="1">
         <v>3</v>
@@ -5358,28 +5407,28 @@
         <v>1146.32</v>
       </c>
       <c r="L67" s="1">
-        <f t="shared" si="30"/>
-        <v>0</v>
+        <f t="shared" si="28"/>
+        <v>-25</v>
       </c>
       <c r="M67" s="1">
-        <f t="shared" si="30"/>
-        <v>10.72</v>
+        <f t="shared" si="28"/>
+        <v>13.49</v>
       </c>
       <c r="N67" s="1">
         <f t="shared" si="4"/>
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="O67" s="1">
         <f t="shared" si="5"/>
-        <v>13.49</v>
+        <v>6.4</v>
       </c>
       <c r="P67" s="1">
-        <f t="shared" si="31"/>
-        <v>33.33</v>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
       <c r="Q67" s="1">
-        <f t="shared" si="31"/>
-        <v>7.67</v>
+        <f t="shared" si="29"/>
+        <v>10.37</v>
       </c>
       <c r="R67" s="12"/>
       <c r="S67" s="13"/>
@@ -5404,17 +5453,17 @@
       <c r="E68" s="1">
         <v>1055.71</v>
       </c>
-      <c r="F68" s="3">
+      <c r="F68" s="2">
+        <v>3</v>
+      </c>
+      <c r="G68" s="2">
+        <v>1117.1400000000001</v>
+      </c>
+      <c r="H68" s="3">
         <v>4</v>
       </c>
-      <c r="G68" s="3">
-        <v>1134.8699999999999</v>
-      </c>
-      <c r="H68" s="2">
-        <v>3</v>
-      </c>
-      <c r="I68" s="2">
-        <v>1117.1400000000001</v>
+      <c r="I68" s="3">
+        <v>1087.31</v>
       </c>
       <c r="J68" s="1">
         <v>3</v>
@@ -5423,28 +5472,28 @@
         <v>1061.1400000000001</v>
       </c>
       <c r="L68" s="1">
-        <f t="shared" si="30"/>
-        <v>0</v>
+        <f t="shared" si="28"/>
+        <v>-25</v>
       </c>
       <c r="M68" s="1">
-        <f t="shared" si="30"/>
-        <v>7.5</v>
+        <f t="shared" si="28"/>
+        <v>5.82</v>
       </c>
       <c r="N68" s="1">
         <f t="shared" si="4"/>
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="O68" s="1">
         <f t="shared" si="5"/>
-        <v>5.82</v>
+        <v>2.99</v>
       </c>
       <c r="P68" s="1">
-        <f t="shared" si="31"/>
-        <v>33.33</v>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
       <c r="Q68" s="1">
-        <f t="shared" si="31"/>
-        <v>6.95</v>
+        <f t="shared" si="29"/>
+        <v>5.28</v>
       </c>
       <c r="R68" s="12"/>
       <c r="S68" s="13"/>
@@ -5473,13 +5522,13 @@
         <v>3</v>
       </c>
       <c r="G69" s="3">
-        <v>892.49</v>
+        <v>870.55</v>
       </c>
       <c r="H69" s="3">
         <v>3</v>
       </c>
       <c r="I69" s="3">
-        <v>870.55</v>
+        <v>878.71</v>
       </c>
       <c r="J69" s="1">
         <v>3</v>
@@ -5488,28 +5537,28 @@
         <v>828.14</v>
       </c>
       <c r="L69" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="M69" s="1">
+        <f t="shared" si="28"/>
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="N69" s="1">
+        <f t="shared" ref="N69:O69" si="30">ROUND(((H69-D69)/D69)*100,2)</f>
+        <v>0</v>
+      </c>
+      <c r="O69" s="1">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="M69" s="1">
-        <f t="shared" si="30"/>
-        <v>3.71</v>
-      </c>
-      <c r="N69" s="1">
-        <f t="shared" ref="N69:O69" si="32">ROUND(((H69-D69)/D69)*100,2)</f>
-        <v>0</v>
-      </c>
-      <c r="O69" s="1">
-        <f t="shared" si="32"/>
-        <v>1.1599999999999999</v>
+        <v>2.11</v>
       </c>
       <c r="P69" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="Q69" s="1">
-        <f t="shared" si="31"/>
-        <v>7.77</v>
+        <f t="shared" si="29"/>
+        <v>5.12</v>
       </c>
       <c r="R69" s="12"/>
       <c r="S69" s="13"/>
@@ -5527,47 +5576,47 @@
         <v>4</v>
       </c>
       <c r="C70" s="1">
-        <f t="shared" ref="C70:K70" si="33">ROUND(SUM(C62:C69)/COUNTA(C62:C69),2)</f>
+        <f t="shared" ref="C70:K70" si="31">ROUND(SUM(C62:C69)/COUNTA(C62:C69),2)</f>
         <v>1609.24</v>
       </c>
       <c r="D70" s="1">
+        <f t="shared" si="31"/>
+        <v>4.5</v>
+      </c>
+      <c r="E70" s="1">
+        <f t="shared" si="31"/>
+        <v>1134.43</v>
+      </c>
+      <c r="F70" s="1">
+        <f t="shared" ref="F70:H70" si="32">ROUND(SUM(F62:F69)/COUNTA(F62:F69),2)</f>
+        <v>3.38</v>
+      </c>
+      <c r="G70" s="1">
+        <f t="shared" ref="G70:I70" si="33">ROUND(SUM(G62:G69)/COUNTA(G62:G69),2)</f>
+        <v>1162.79</v>
+      </c>
+      <c r="H70" s="1">
+        <f t="shared" si="32"/>
+        <v>3.63</v>
+      </c>
+      <c r="I70" s="1">
         <f t="shared" si="33"/>
-        <v>4.5</v>
-      </c>
-      <c r="E70" s="1">
-        <f t="shared" si="33"/>
-        <v>1134.43</v>
-      </c>
-      <c r="F70" s="1">
-        <f t="shared" si="33"/>
-        <v>4.75</v>
-      </c>
-      <c r="G70" s="1">
-        <f t="shared" si="33"/>
-        <v>1128.73</v>
-      </c>
-      <c r="H70" s="1">
-        <f t="shared" ref="H70" si="34">ROUND(SUM(H62:H69)/COUNTA(H62:H69),2)</f>
-        <v>3.38</v>
-      </c>
-      <c r="I70" s="1">
-        <f t="shared" ref="I70" si="35">ROUND(SUM(I62:I69)/COUNTA(I62:I69),2)</f>
-        <v>1162.79</v>
+        <v>1190.58</v>
       </c>
       <c r="J70" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>3.25</v>
       </c>
       <c r="K70" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1119.24</v>
       </c>
-      <c r="L70" s="21"/>
-      <c r="M70" s="22"/>
-      <c r="N70" s="22"/>
-      <c r="O70" s="22"/>
-      <c r="P70" s="22"/>
-      <c r="Q70" s="23"/>
+      <c r="L70" s="20"/>
+      <c r="M70" s="21"/>
+      <c r="N70" s="21"/>
+      <c r="O70" s="21"/>
+      <c r="P70" s="21"/>
+      <c r="Q70" s="22"/>
       <c r="R70" s="15"/>
       <c r="S70" s="16"/>
       <c r="T70" s="17"/>
@@ -5579,48 +5628,48 @@
       <c r="A71" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B71" s="21" t="str">
+      <c r="B71" s="20" t="str">
         <f>"總共 " &amp; SUM(R71:T71) &amp; " 筆"</f>
         <v>總共 56 筆</v>
       </c>
-      <c r="C71" s="22"/>
-      <c r="D71" s="22"/>
-      <c r="E71" s="22"/>
-      <c r="F71" s="22"/>
-      <c r="G71" s="22"/>
-      <c r="H71" s="22"/>
-      <c r="I71" s="22"/>
-      <c r="J71" s="22"/>
-      <c r="K71" s="22"/>
-      <c r="L71" s="22"/>
-      <c r="M71" s="22"/>
-      <c r="N71" s="22"/>
-      <c r="O71" s="22"/>
-      <c r="P71" s="22"/>
-      <c r="Q71" s="23"/>
+      <c r="C71" s="21"/>
+      <c r="D71" s="21"/>
+      <c r="E71" s="21"/>
+      <c r="F71" s="21"/>
+      <c r="G71" s="21"/>
+      <c r="H71" s="21"/>
+      <c r="I71" s="21"/>
+      <c r="J71" s="21"/>
+      <c r="K71" s="21"/>
+      <c r="L71" s="21"/>
+      <c r="M71" s="21"/>
+      <c r="N71" s="21"/>
+      <c r="O71" s="21"/>
+      <c r="P71" s="21"/>
+      <c r="Q71" s="22"/>
       <c r="R71" s="1">
-        <f t="shared" ref="R71:W71" si="36">R3+R14+R24+R38+R51+R61</f>
-        <v>22</v>
+        <f t="shared" ref="R71:W71" si="34">R3+R14+R24+R38+R51+R61</f>
+        <v>25</v>
       </c>
       <c r="S71" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>12</v>
       </c>
       <c r="T71" s="1">
-        <f t="shared" si="36"/>
-        <v>22</v>
+        <f t="shared" si="34"/>
+        <v>19</v>
       </c>
       <c r="U71" s="1">
-        <f t="shared" si="36"/>
-        <v>25</v>
+        <f t="shared" si="34"/>
+        <v>23</v>
       </c>
       <c r="V71" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>12</v>
       </c>
       <c r="W71" s="1">
-        <f t="shared" si="36"/>
-        <v>19</v>
+        <f t="shared" si="34"/>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -5636,21 +5685,14 @@
     <mergeCell ref="B24:Q24"/>
     <mergeCell ref="L23:Q23"/>
     <mergeCell ref="L70:Q70"/>
-    <mergeCell ref="R1:T1"/>
-    <mergeCell ref="B3:Q3"/>
+    <mergeCell ref="R62:T70"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="J1:K1"/>
-    <mergeCell ref="R62:T70"/>
     <mergeCell ref="H1:I1"/>
-    <mergeCell ref="U1:W1"/>
-    <mergeCell ref="U4:W13"/>
-    <mergeCell ref="U15:W23"/>
-    <mergeCell ref="U25:W37"/>
-    <mergeCell ref="U39:W50"/>
     <mergeCell ref="U52:W60"/>
     <mergeCell ref="U62:W70"/>
     <mergeCell ref="N1:O1"/>
@@ -5660,6 +5702,13 @@
     <mergeCell ref="R39:T50"/>
     <mergeCell ref="L60:Q60"/>
     <mergeCell ref="R52:T60"/>
+    <mergeCell ref="U1:W1"/>
+    <mergeCell ref="U4:W13"/>
+    <mergeCell ref="U15:W23"/>
+    <mergeCell ref="U25:W37"/>
+    <mergeCell ref="U39:W50"/>
+    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="B3:Q3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5669,6 +5718,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B952BE11-689F-4F20-B9C8-AF036BD8E39C}">
+  <sheetPr codeName="工作表2"/>
   <dimension ref="A1:E70"/>
   <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="1"/>
   <cols>
@@ -5679,7 +5729,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.25" thickBot="1">
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="23" t="s">
         <v>61</v>
       </c>
       <c r="C1" s="19"/>
@@ -5709,13 +5759,13 @@
       <c r="A3" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="21">
+      <c r="B3" s="20">
         <f>COUNTA(A4:A12)</f>
         <v>9</v>
       </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="23"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="22"/>
     </row>
     <row r="4" spans="1:5" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A4" s="6" t="s">
@@ -5857,12 +5907,12 @@
       <c r="A14" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B14" s="21">
+      <c r="B14" s="20">
         <v>8</v>
       </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="23"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="22"/>
     </row>
     <row r="15" spans="1:5" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A15" s="6" t="s">
@@ -5991,12 +6041,12 @@
       <c r="A24" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B24" s="21">
+      <c r="B24" s="20">
         <v>12</v>
       </c>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="23"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="22"/>
     </row>
     <row r="25" spans="1:5" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A25" s="6" t="s">
@@ -6177,12 +6227,12 @@
       <c r="A38" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B38" s="21">
+      <c r="B38" s="20">
         <v>11</v>
       </c>
-      <c r="C38" s="22"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="23"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="22"/>
     </row>
     <row r="39" spans="1:5" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A39" s="6" t="s">
@@ -6350,12 +6400,12 @@
       <c r="A51" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B51" s="21">
+      <c r="B51" s="20">
         <v>8</v>
       </c>
-      <c r="C51" s="22"/>
-      <c r="D51" s="22"/>
-      <c r="E51" s="23"/>
+      <c r="C51" s="21"/>
+      <c r="D51" s="21"/>
+      <c r="E51" s="22"/>
     </row>
     <row r="52" spans="1:5" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A52" s="5" t="s">
@@ -6484,12 +6534,12 @@
       <c r="A61" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B61" s="21">
+      <c r="B61" s="20">
         <v>8</v>
       </c>
-      <c r="C61" s="22"/>
-      <c r="D61" s="22"/>
-      <c r="E61" s="23"/>
+      <c r="C61" s="21"/>
+      <c r="D61" s="21"/>
+      <c r="E61" s="22"/>
     </row>
     <row r="62" spans="1:5" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A62" s="5" t="s">

--- a/docs/Baseline比較結果.xlsx
+++ b/docs/Baseline比較結果.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff0\OneDrive\桌面\115_NTUT_Thesis\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44737BCC-7B91-4382-9C6B-CE68FC5065C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4F020FC-B152-4C7C-B817-480E83A24099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9DD6E340-DFE3-4B7E-9025-343BD89F474F}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{9DD6E340-DFE3-4B7E-9025-343BD89F474F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -857,6 +857,15 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -890,19 +899,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1262,48 +1262,48 @@
   <sheetData>
     <row r="1" spans="1:26" ht="17.25" customHeight="1" thickBot="1">
       <c r="A1" s="4"/>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="19"/>
-      <c r="D1" s="18" t="s">
+      <c r="C1" s="22"/>
+      <c r="D1" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="19"/>
-      <c r="F1" s="24" t="s">
+      <c r="E1" s="22"/>
+      <c r="F1" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="19"/>
-      <c r="H1" s="18" t="s">
+      <c r="G1" s="22"/>
+      <c r="H1" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="I1" s="19"/>
-      <c r="J1" s="18" t="s">
+      <c r="I1" s="22"/>
+      <c r="J1" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="K1" s="19"/>
-      <c r="L1" s="18" t="s">
+      <c r="K1" s="22"/>
+      <c r="L1" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="M1" s="19"/>
-      <c r="N1" s="18" t="s">
+      <c r="M1" s="22"/>
+      <c r="N1" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="O1" s="19"/>
-      <c r="P1" s="18" t="s">
+      <c r="O1" s="22"/>
+      <c r="P1" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="18" t="s">
+      <c r="Q1" s="22"/>
+      <c r="R1" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="S1" s="23"/>
-      <c r="T1" s="23"/>
-      <c r="U1" s="18" t="s">
+      <c r="S1" s="24"/>
+      <c r="T1" s="24"/>
+      <c r="U1" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="V1" s="23"/>
-      <c r="W1" s="23"/>
+      <c r="V1" s="24"/>
+      <c r="W1" s="24"/>
     </row>
     <row r="2" spans="1:26" ht="17.25" thickBot="1">
       <c r="A2" s="5" t="s">
@@ -1380,25 +1380,25 @@
       <c r="A3" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="20" t="str">
+      <c r="B3" s="9" t="str">
         <f>COUNTA(A4:A12) &amp; " 筆"</f>
         <v>9 筆</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
-      <c r="L3" s="21"/>
-      <c r="M3" s="21"/>
-      <c r="N3" s="21"/>
-      <c r="O3" s="21"/>
-      <c r="P3" s="21"/>
-      <c r="Q3" s="22"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="11"/>
       <c r="R3" s="1" cm="1">
         <f t="array" ref="R3">CountColor($F4:$F12,$Y$4)</f>
         <v>4</v>
@@ -1482,12 +1482,12 @@
         <f t="shared" ref="Q4:Q12" si="3">ROUND(((G4-K4)/K4)*100,2)</f>
         <v>0</v>
       </c>
-      <c r="R4" s="9"/>
-      <c r="S4" s="10"/>
-      <c r="T4" s="11"/>
-      <c r="U4" s="9"/>
-      <c r="V4" s="10"/>
-      <c r="W4" s="11"/>
+      <c r="R4" s="12"/>
+      <c r="S4" s="13"/>
+      <c r="T4" s="14"/>
+      <c r="U4" s="12"/>
+      <c r="V4" s="13"/>
+      <c r="W4" s="14"/>
       <c r="Y4" s="2"/>
       <c r="Z4" t="s">
         <v>83</v>
@@ -1551,12 +1551,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R5" s="12"/>
-      <c r="S5" s="13"/>
-      <c r="T5" s="14"/>
-      <c r="U5" s="12"/>
-      <c r="V5" s="13"/>
-      <c r="W5" s="14"/>
+      <c r="R5" s="15"/>
+      <c r="S5" s="16"/>
+      <c r="T5" s="17"/>
+      <c r="U5" s="15"/>
+      <c r="V5" s="16"/>
+      <c r="W5" s="17"/>
       <c r="Y5" s="7"/>
       <c r="Z5" t="s">
         <v>85</v>
@@ -1620,12 +1620,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R6" s="12"/>
-      <c r="S6" s="13"/>
-      <c r="T6" s="14"/>
-      <c r="U6" s="12"/>
-      <c r="V6" s="13"/>
-      <c r="W6" s="14"/>
+      <c r="R6" s="15"/>
+      <c r="S6" s="16"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="15"/>
+      <c r="V6" s="16"/>
+      <c r="W6" s="17"/>
       <c r="Y6" s="3"/>
       <c r="Z6" t="s">
         <v>84</v>
@@ -1689,12 +1689,12 @@
         <f t="shared" si="3"/>
         <v>0.19</v>
       </c>
-      <c r="R7" s="12"/>
-      <c r="S7" s="13"/>
-      <c r="T7" s="14"/>
-      <c r="U7" s="12"/>
-      <c r="V7" s="13"/>
-      <c r="W7" s="14"/>
+      <c r="R7" s="15"/>
+      <c r="S7" s="16"/>
+      <c r="T7" s="17"/>
+      <c r="U7" s="15"/>
+      <c r="V7" s="16"/>
+      <c r="W7" s="17"/>
     </row>
     <row r="8" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A8" s="6" t="s">
@@ -1754,12 +1754,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R8" s="12"/>
-      <c r="S8" s="13"/>
-      <c r="T8" s="14"/>
-      <c r="U8" s="12"/>
-      <c r="V8" s="13"/>
-      <c r="W8" s="14"/>
+      <c r="R8" s="15"/>
+      <c r="S8" s="16"/>
+      <c r="T8" s="17"/>
+      <c r="U8" s="15"/>
+      <c r="V8" s="16"/>
+      <c r="W8" s="17"/>
     </row>
     <row r="9" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A9" s="6" t="s">
@@ -1819,12 +1819,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R9" s="12"/>
-      <c r="S9" s="13"/>
-      <c r="T9" s="14"/>
-      <c r="U9" s="12"/>
-      <c r="V9" s="13"/>
-      <c r="W9" s="14"/>
+      <c r="R9" s="15"/>
+      <c r="S9" s="16"/>
+      <c r="T9" s="17"/>
+      <c r="U9" s="15"/>
+      <c r="V9" s="16"/>
+      <c r="W9" s="17"/>
     </row>
     <row r="10" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A10" s="6" t="s">
@@ -1884,12 +1884,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R10" s="12"/>
-      <c r="S10" s="13"/>
-      <c r="T10" s="14"/>
-      <c r="U10" s="12"/>
-      <c r="V10" s="13"/>
-      <c r="W10" s="14"/>
+      <c r="R10" s="15"/>
+      <c r="S10" s="16"/>
+      <c r="T10" s="17"/>
+      <c r="U10" s="15"/>
+      <c r="V10" s="16"/>
+      <c r="W10" s="17"/>
     </row>
     <row r="11" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A11" s="6" t="s">
@@ -1949,12 +1949,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R11" s="12"/>
-      <c r="S11" s="13"/>
-      <c r="T11" s="14"/>
-      <c r="U11" s="12"/>
-      <c r="V11" s="13"/>
-      <c r="W11" s="14"/>
+      <c r="R11" s="15"/>
+      <c r="S11" s="16"/>
+      <c r="T11" s="17"/>
+      <c r="U11" s="15"/>
+      <c r="V11" s="16"/>
+      <c r="W11" s="17"/>
     </row>
     <row r="12" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A12" s="6" t="s">
@@ -2014,12 +2014,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R12" s="12"/>
-      <c r="S12" s="13"/>
-      <c r="T12" s="14"/>
-      <c r="U12" s="12"/>
-      <c r="V12" s="13"/>
-      <c r="W12" s="14"/>
+      <c r="R12" s="15"/>
+      <c r="S12" s="16"/>
+      <c r="T12" s="17"/>
+      <c r="U12" s="15"/>
+      <c r="V12" s="16"/>
+      <c r="W12" s="17"/>
     </row>
     <row r="13" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A13" s="6" t="s">
@@ -2063,58 +2063,64 @@
         <f t="shared" si="6"/>
         <v>828.38000000000022</v>
       </c>
-      <c r="L13" s="20"/>
-      <c r="M13" s="21"/>
-      <c r="N13" s="21"/>
-      <c r="O13" s="21"/>
-      <c r="P13" s="21"/>
-      <c r="Q13" s="22"/>
-      <c r="R13" s="15"/>
-      <c r="S13" s="16"/>
-      <c r="T13" s="17"/>
-      <c r="U13" s="15"/>
-      <c r="V13" s="16"/>
-      <c r="W13" s="17"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="11"/>
+      <c r="R13" s="18"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="20"/>
+      <c r="U13" s="18"/>
+      <c r="V13" s="19"/>
+      <c r="W13" s="20"/>
     </row>
     <row r="14" spans="1:26" ht="17.25" customHeight="1" thickBot="1">
       <c r="A14" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B14" s="20" t="str">
+      <c r="B14" s="9" t="str">
         <f>COUNTA(A15:A22) &amp; " 筆"</f>
         <v>8 筆</v>
       </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="21"/>
-      <c r="M14" s="21"/>
-      <c r="N14" s="21"/>
-      <c r="O14" s="21"/>
-      <c r="P14" s="21"/>
-      <c r="Q14" s="22"/>
-      <c r="R14" s="1">
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="1" cm="1">
+        <f t="array" ref="R14">CountColor($F15:$F22,$Y$4)</f>
         <v>1</v>
       </c>
-      <c r="S14" s="1">
+      <c r="S14" s="1" cm="1">
+        <f t="array" ref="S14">CountColor($F15:$F22,$Y$5)</f>
         <v>7</v>
       </c>
-      <c r="T14" s="1">
-        <v>0</v>
-      </c>
-      <c r="U14" s="1">
-        <v>0</v>
-      </c>
-      <c r="V14" s="1">
+      <c r="T14" s="1" cm="1">
+        <f t="array" ref="T14">CountColor($F15:$F22,$Y$6)</f>
+        <v>0</v>
+      </c>
+      <c r="U14" s="1" cm="1">
+        <f t="array" ref="U14">CountColor($H15:$H22,$Y$4)</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="1" cm="1">
+        <f t="array" ref="V14">CountColor($H15:$H22,$Y$5)</f>
         <v>7</v>
       </c>
-      <c r="W14" s="1">
+      <c r="W14" s="1" cm="1">
+        <f t="array" ref="W14">CountColor($H15:$H22,$Y$6)</f>
         <v>1</v>
       </c>
     </row>
@@ -2176,12 +2182,12 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="R15" s="9"/>
-      <c r="S15" s="10"/>
-      <c r="T15" s="11"/>
-      <c r="U15" s="9"/>
-      <c r="V15" s="10"/>
-      <c r="W15" s="11"/>
+      <c r="R15" s="12"/>
+      <c r="S15" s="13"/>
+      <c r="T15" s="14"/>
+      <c r="U15" s="12"/>
+      <c r="V15" s="13"/>
+      <c r="W15" s="14"/>
     </row>
     <row r="16" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A16" s="6" t="s">
@@ -2241,12 +2247,12 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="R16" s="12"/>
-      <c r="S16" s="13"/>
-      <c r="T16" s="14"/>
-      <c r="U16" s="12"/>
-      <c r="V16" s="13"/>
-      <c r="W16" s="14"/>
+      <c r="R16" s="15"/>
+      <c r="S16" s="16"/>
+      <c r="T16" s="17"/>
+      <c r="U16" s="15"/>
+      <c r="V16" s="16"/>
+      <c r="W16" s="17"/>
     </row>
     <row r="17" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A17" s="6" t="s">
@@ -2306,12 +2312,12 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="R17" s="12"/>
-      <c r="S17" s="13"/>
-      <c r="T17" s="14"/>
-      <c r="U17" s="12"/>
-      <c r="V17" s="13"/>
-      <c r="W17" s="14"/>
+      <c r="R17" s="15"/>
+      <c r="S17" s="16"/>
+      <c r="T17" s="17"/>
+      <c r="U17" s="15"/>
+      <c r="V17" s="16"/>
+      <c r="W17" s="17"/>
     </row>
     <row r="18" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A18" s="6" t="s">
@@ -2371,12 +2377,12 @@
         <f t="shared" si="8"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="R18" s="12"/>
-      <c r="S18" s="13"/>
-      <c r="T18" s="14"/>
-      <c r="U18" s="12"/>
-      <c r="V18" s="13"/>
-      <c r="W18" s="14"/>
+      <c r="R18" s="15"/>
+      <c r="S18" s="16"/>
+      <c r="T18" s="17"/>
+      <c r="U18" s="15"/>
+      <c r="V18" s="16"/>
+      <c r="W18" s="17"/>
     </row>
     <row r="19" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A19" s="6" t="s">
@@ -2436,12 +2442,12 @@
         <f t="shared" si="8"/>
         <v>0.01</v>
       </c>
-      <c r="R19" s="12"/>
-      <c r="S19" s="13"/>
-      <c r="T19" s="14"/>
-      <c r="U19" s="12"/>
-      <c r="V19" s="13"/>
-      <c r="W19" s="14"/>
+      <c r="R19" s="15"/>
+      <c r="S19" s="16"/>
+      <c r="T19" s="17"/>
+      <c r="U19" s="15"/>
+      <c r="V19" s="16"/>
+      <c r="W19" s="17"/>
     </row>
     <row r="20" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A20" s="6" t="s">
@@ -2501,12 +2507,12 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="R20" s="12"/>
-      <c r="S20" s="13"/>
-      <c r="T20" s="14"/>
-      <c r="U20" s="12"/>
-      <c r="V20" s="13"/>
-      <c r="W20" s="14"/>
+      <c r="R20" s="15"/>
+      <c r="S20" s="16"/>
+      <c r="T20" s="17"/>
+      <c r="U20" s="15"/>
+      <c r="V20" s="16"/>
+      <c r="W20" s="17"/>
     </row>
     <row r="21" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A21" s="6" t="s">
@@ -2566,12 +2572,12 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="R21" s="12"/>
-      <c r="S21" s="13"/>
-      <c r="T21" s="14"/>
-      <c r="U21" s="12"/>
-      <c r="V21" s="13"/>
-      <c r="W21" s="14"/>
+      <c r="R21" s="15"/>
+      <c r="S21" s="16"/>
+      <c r="T21" s="17"/>
+      <c r="U21" s="15"/>
+      <c r="V21" s="16"/>
+      <c r="W21" s="17"/>
     </row>
     <row r="22" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A22" s="6" t="s">
@@ -2631,12 +2637,12 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="R22" s="12"/>
-      <c r="S22" s="13"/>
-      <c r="T22" s="14"/>
-      <c r="U22" s="12"/>
-      <c r="V22" s="13"/>
-      <c r="W22" s="14"/>
+      <c r="R22" s="15"/>
+      <c r="S22" s="16"/>
+      <c r="T22" s="17"/>
+      <c r="U22" s="15"/>
+      <c r="V22" s="16"/>
+      <c r="W22" s="17"/>
     </row>
     <row r="23" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A23" s="6" t="s">
@@ -2680,59 +2686,62 @@
         <f t="shared" si="9"/>
         <v>589.86</v>
       </c>
-      <c r="L23" s="20"/>
-      <c r="M23" s="21"/>
-      <c r="N23" s="21"/>
-      <c r="O23" s="21"/>
-      <c r="P23" s="21"/>
-      <c r="Q23" s="22"/>
-      <c r="R23" s="15"/>
-      <c r="S23" s="16"/>
-      <c r="T23" s="17"/>
-      <c r="U23" s="15"/>
-      <c r="V23" s="16"/>
-      <c r="W23" s="17"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="10"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="11"/>
+      <c r="R23" s="18"/>
+      <c r="S23" s="19"/>
+      <c r="T23" s="20"/>
+      <c r="U23" s="18"/>
+      <c r="V23" s="19"/>
+      <c r="W23" s="20"/>
     </row>
     <row r="24" spans="1:23" ht="17.25" customHeight="1" thickBot="1">
       <c r="A24" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B24" s="20" t="str">
+      <c r="B24" s="9" t="str">
         <f>COUNTA(A25:A36) &amp; " 筆"</f>
         <v>12 筆</v>
       </c>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="21"/>
-      <c r="I24" s="21"/>
-      <c r="J24" s="21"/>
-      <c r="K24" s="21"/>
-      <c r="L24" s="21"/>
-      <c r="M24" s="21"/>
-      <c r="N24" s="21"/>
-      <c r="O24" s="21"/>
-      <c r="P24" s="21"/>
-      <c r="Q24" s="22"/>
-      <c r="R24" s="1">
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="10"/>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="11"/>
+      <c r="R24" s="1" cm="1">
+        <f t="array" ref="R24">CountColor($F25:$F36,$Y$4)</f>
         <v>2</v>
       </c>
-      <c r="S24" s="1">
-        <v>0</v>
-      </c>
-      <c r="T24" s="1">
+      <c r="S24" s="1" cm="1">
+        <f t="array" ref="S24">CountColor($F25:$F36,$Y$5)</f>
+        <v>0</v>
+      </c>
+      <c r="T24" s="1" cm="1">
+        <f t="array" ref="T24">CountColor($F25:$F36,$Y$6)</f>
         <v>10</v>
       </c>
       <c r="U24" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V24" s="1">
         <v>0</v>
       </c>
       <c r="W24" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
@@ -2757,11 +2766,11 @@
       <c r="G25" s="2">
         <v>1653.16</v>
       </c>
-      <c r="H25" s="3">
+      <c r="H25" s="2">
         <v>19</v>
       </c>
-      <c r="I25" s="3">
-        <v>1924.82</v>
+      <c r="I25" s="2">
+        <v>1653.53</v>
       </c>
       <c r="J25" s="1">
         <v>19</v>
@@ -2783,7 +2792,7 @@
       </c>
       <c r="O25" s="1">
         <f t="shared" si="5"/>
-        <v>16.190000000000001</v>
+        <v>-0.18</v>
       </c>
       <c r="P25" s="1">
         <f t="shared" ref="P25:P36" si="12">ROUND(((F25-J25)/J25)*100,2)</f>
@@ -2793,12 +2802,12 @@
         <f t="shared" ref="Q25:Q36" si="13">ROUND(((G25-K25)/K25)*100,2)</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="R25" s="9"/>
-      <c r="S25" s="10"/>
-      <c r="T25" s="11"/>
-      <c r="U25" s="9"/>
-      <c r="V25" s="10"/>
-      <c r="W25" s="11"/>
+      <c r="R25" s="12"/>
+      <c r="S25" s="13"/>
+      <c r="T25" s="14"/>
+      <c r="U25" s="12"/>
+      <c r="V25" s="13"/>
+      <c r="W25" s="14"/>
     </row>
     <row r="26" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A26" s="6" t="s">
@@ -2823,10 +2832,10 @@
         <v>1486.68</v>
       </c>
       <c r="H26" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I26" s="2">
-        <v>1473.1</v>
+        <v>1497.23</v>
       </c>
       <c r="J26" s="1">
         <v>17</v>
@@ -2844,11 +2853,11 @@
       </c>
       <c r="N26" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-5.56</v>
       </c>
       <c r="O26" s="1">
         <f t="shared" si="5"/>
-        <v>-0.25</v>
+        <v>1.38</v>
       </c>
       <c r="P26" s="1">
         <f t="shared" si="12"/>
@@ -2858,12 +2867,12 @@
         <f t="shared" si="13"/>
         <v>0.04</v>
       </c>
-      <c r="R26" s="12"/>
-      <c r="S26" s="13"/>
-      <c r="T26" s="14"/>
-      <c r="U26" s="12"/>
-      <c r="V26" s="13"/>
-      <c r="W26" s="14"/>
+      <c r="R26" s="15"/>
+      <c r="S26" s="16"/>
+      <c r="T26" s="17"/>
+      <c r="U26" s="15"/>
+      <c r="V26" s="16"/>
+      <c r="W26" s="17"/>
     </row>
     <row r="27" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A27" s="6" t="s">
@@ -2888,10 +2897,10 @@
         <v>1572.9</v>
       </c>
       <c r="H27" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I27" s="2">
-        <v>1221.75</v>
+        <v>1322.8</v>
       </c>
       <c r="J27" s="1">
         <v>13</v>
@@ -2909,11 +2918,11 @@
       </c>
       <c r="N27" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-7.14</v>
       </c>
       <c r="O27" s="1">
         <f t="shared" si="5"/>
-        <v>-0.68</v>
+        <v>7.54</v>
       </c>
       <c r="P27" s="1">
         <f t="shared" si="12"/>
@@ -2923,12 +2932,12 @@
         <f t="shared" si="13"/>
         <v>21.68</v>
       </c>
-      <c r="R27" s="12"/>
-      <c r="S27" s="13"/>
-      <c r="T27" s="14"/>
-      <c r="U27" s="12"/>
-      <c r="V27" s="13"/>
-      <c r="W27" s="14"/>
+      <c r="R27" s="15"/>
+      <c r="S27" s="16"/>
+      <c r="T27" s="17"/>
+      <c r="U27" s="15"/>
+      <c r="V27" s="16"/>
+      <c r="W27" s="17"/>
     </row>
     <row r="28" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A28" s="6" t="s">
@@ -2956,7 +2965,7 @@
         <v>10</v>
       </c>
       <c r="I28" s="3">
-        <v>1036.96</v>
+        <v>1015.76</v>
       </c>
       <c r="J28" s="1">
         <v>9</v>
@@ -2978,7 +2987,7 @@
       </c>
       <c r="O28" s="1">
         <f t="shared" si="5"/>
-        <v>2.61</v>
+        <v>0.52</v>
       </c>
       <c r="P28" s="1">
         <f t="shared" si="12"/>
@@ -2988,12 +2997,12 @@
         <f t="shared" si="13"/>
         <v>1.86</v>
       </c>
-      <c r="R28" s="12"/>
-      <c r="S28" s="13"/>
-      <c r="T28" s="14"/>
-      <c r="U28" s="12"/>
-      <c r="V28" s="13"/>
-      <c r="W28" s="14"/>
+      <c r="R28" s="15"/>
+      <c r="S28" s="16"/>
+      <c r="T28" s="17"/>
+      <c r="U28" s="15"/>
+      <c r="V28" s="16"/>
+      <c r="W28" s="17"/>
     </row>
     <row r="29" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A29" s="6" t="s">
@@ -3018,10 +3027,10 @@
         <v>1688.63</v>
       </c>
       <c r="H29" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I29" s="3">
-        <v>1387.54</v>
+        <v>1436.85</v>
       </c>
       <c r="J29" s="1">
         <v>14</v>
@@ -3039,11 +3048,11 @@
       </c>
       <c r="N29" s="1">
         <f t="shared" si="4"/>
-        <v>7.14</v>
+        <v>0</v>
       </c>
       <c r="O29" s="1">
         <f t="shared" si="5"/>
-        <v>-0.57999999999999996</v>
+        <v>2.95</v>
       </c>
       <c r="P29" s="1">
         <f t="shared" si="12"/>
@@ -3053,12 +3062,12 @@
         <f t="shared" si="13"/>
         <v>22.62</v>
       </c>
-      <c r="R29" s="12"/>
-      <c r="S29" s="13"/>
-      <c r="T29" s="14"/>
-      <c r="U29" s="12"/>
-      <c r="V29" s="13"/>
-      <c r="W29" s="14"/>
+      <c r="R29" s="15"/>
+      <c r="S29" s="16"/>
+      <c r="T29" s="17"/>
+      <c r="U29" s="15"/>
+      <c r="V29" s="16"/>
+      <c r="W29" s="17"/>
     </row>
     <row r="30" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A30" s="6" t="s">
@@ -3082,11 +3091,11 @@
       <c r="G30" s="3">
         <v>1285.3599999999999</v>
       </c>
-      <c r="H30" s="3">
-        <v>13</v>
-      </c>
-      <c r="I30" s="3">
-        <v>1269.31</v>
+      <c r="H30" s="2">
+        <v>12</v>
+      </c>
+      <c r="I30" s="2">
+        <v>1324.48</v>
       </c>
       <c r="J30" s="1">
         <v>12</v>
@@ -3104,11 +3113,11 @@
       </c>
       <c r="N30" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-7.69</v>
       </c>
       <c r="O30" s="1">
         <f t="shared" si="5"/>
-        <v>0.61</v>
+        <v>4.9800000000000004</v>
       </c>
       <c r="P30" s="1">
         <f t="shared" si="12"/>
@@ -3118,12 +3127,12 @@
         <f t="shared" si="13"/>
         <v>2.66</v>
       </c>
-      <c r="R30" s="12"/>
-      <c r="S30" s="13"/>
-      <c r="T30" s="14"/>
-      <c r="U30" s="12"/>
-      <c r="V30" s="13"/>
-      <c r="W30" s="14"/>
+      <c r="R30" s="15"/>
+      <c r="S30" s="16"/>
+      <c r="T30" s="17"/>
+      <c r="U30" s="15"/>
+      <c r="V30" s="16"/>
+      <c r="W30" s="17"/>
     </row>
     <row r="31" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A31" s="6" t="s">
@@ -3151,7 +3160,7 @@
         <v>11</v>
       </c>
       <c r="I31" s="3">
-        <v>1111.8</v>
+        <v>1106.51</v>
       </c>
       <c r="J31" s="1">
         <v>10</v>
@@ -3173,7 +3182,7 @@
       </c>
       <c r="O31" s="1">
         <f t="shared" si="5"/>
-        <v>0.73</v>
+        <v>0.25</v>
       </c>
       <c r="P31" s="1">
         <f t="shared" si="12"/>
@@ -3183,12 +3192,12 @@
         <f t="shared" si="13"/>
         <v>2.06</v>
       </c>
-      <c r="R31" s="12"/>
-      <c r="S31" s="13"/>
-      <c r="T31" s="14"/>
-      <c r="U31" s="12"/>
-      <c r="V31" s="13"/>
-      <c r="W31" s="14"/>
+      <c r="R31" s="15"/>
+      <c r="S31" s="16"/>
+      <c r="T31" s="17"/>
+      <c r="U31" s="15"/>
+      <c r="V31" s="16"/>
+      <c r="W31" s="17"/>
     </row>
     <row r="32" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A32" s="6" t="s">
@@ -3216,7 +3225,7 @@
         <v>10</v>
       </c>
       <c r="I32" s="3">
-        <v>984.72</v>
+        <v>983.23</v>
       </c>
       <c r="J32" s="1">
         <v>9</v>
@@ -3238,7 +3247,7 @@
       </c>
       <c r="O32" s="1">
         <f t="shared" si="5"/>
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="P32" s="1">
         <f t="shared" si="12"/>
@@ -3248,12 +3257,12 @@
         <f t="shared" si="13"/>
         <v>4.66</v>
       </c>
-      <c r="R32" s="12"/>
-      <c r="S32" s="13"/>
-      <c r="T32" s="14"/>
-      <c r="U32" s="12"/>
-      <c r="V32" s="13"/>
-      <c r="W32" s="14"/>
+      <c r="R32" s="15"/>
+      <c r="S32" s="16"/>
+      <c r="T32" s="17"/>
+      <c r="U32" s="15"/>
+      <c r="V32" s="16"/>
+      <c r="W32" s="17"/>
     </row>
     <row r="33" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A33" s="6" t="s">
@@ -3281,7 +3290,7 @@
         <v>12</v>
       </c>
       <c r="I33" s="3">
-        <v>1205.78</v>
+        <v>1214.8399999999999</v>
       </c>
       <c r="J33" s="1">
         <v>11</v>
@@ -3303,7 +3312,7 @@
       </c>
       <c r="O33" s="1">
         <f t="shared" si="5"/>
-        <v>0.46</v>
+        <v>1.22</v>
       </c>
       <c r="P33" s="1">
         <f t="shared" si="12"/>
@@ -3313,12 +3322,12 @@
         <f t="shared" si="13"/>
         <v>5.08</v>
       </c>
-      <c r="R33" s="12"/>
-      <c r="S33" s="13"/>
-      <c r="T33" s="14"/>
-      <c r="U33" s="12"/>
-      <c r="V33" s="13"/>
-      <c r="W33" s="14"/>
+      <c r="R33" s="15"/>
+      <c r="S33" s="16"/>
+      <c r="T33" s="17"/>
+      <c r="U33" s="15"/>
+      <c r="V33" s="16"/>
+      <c r="W33" s="17"/>
     </row>
     <row r="34" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A34" s="6" t="s">
@@ -3342,11 +3351,11 @@
       <c r="G34" s="3">
         <v>1151.1199999999999</v>
       </c>
-      <c r="H34" s="3">
-        <v>12</v>
-      </c>
-      <c r="I34" s="3">
-        <v>1108.9100000000001</v>
+      <c r="H34" s="2">
+        <v>11</v>
+      </c>
+      <c r="I34" s="2">
+        <v>1119.33</v>
       </c>
       <c r="J34" s="1">
         <v>10</v>
@@ -3364,11 +3373,11 @@
       </c>
       <c r="N34" s="1">
         <f t="shared" si="4"/>
-        <v>9.09</v>
+        <v>0</v>
       </c>
       <c r="O34" s="1">
         <f t="shared" si="5"/>
-        <v>-1.63</v>
+        <v>-0.71</v>
       </c>
       <c r="P34" s="1">
         <f t="shared" si="12"/>
@@ -3378,12 +3387,12 @@
         <f t="shared" si="13"/>
         <v>2.89</v>
       </c>
-      <c r="R34" s="12"/>
-      <c r="S34" s="13"/>
-      <c r="T34" s="14"/>
-      <c r="U34" s="12"/>
-      <c r="V34" s="13"/>
-      <c r="W34" s="14"/>
+      <c r="R34" s="15"/>
+      <c r="S34" s="16"/>
+      <c r="T34" s="17"/>
+      <c r="U34" s="15"/>
+      <c r="V34" s="16"/>
+      <c r="W34" s="17"/>
     </row>
     <row r="35" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A35" s="6" t="s">
@@ -3411,7 +3420,7 @@
         <v>11</v>
       </c>
       <c r="I35" s="3">
-        <v>1366.23</v>
+        <v>1138.82</v>
       </c>
       <c r="J35" s="1">
         <v>10</v>
@@ -3433,7 +3442,7 @@
       </c>
       <c r="O35" s="1">
         <f t="shared" si="5"/>
-        <v>24.61</v>
+        <v>3.87</v>
       </c>
       <c r="P35" s="1">
         <f t="shared" si="12"/>
@@ -3443,12 +3452,12 @@
         <f t="shared" si="13"/>
         <v>5.92</v>
       </c>
-      <c r="R35" s="12"/>
-      <c r="S35" s="13"/>
-      <c r="T35" s="14"/>
-      <c r="U35" s="12"/>
-      <c r="V35" s="13"/>
-      <c r="W35" s="14"/>
+      <c r="R35" s="15"/>
+      <c r="S35" s="16"/>
+      <c r="T35" s="17"/>
+      <c r="U35" s="15"/>
+      <c r="V35" s="16"/>
+      <c r="W35" s="17"/>
     </row>
     <row r="36" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A36" s="6" t="s">
@@ -3476,7 +3485,7 @@
         <v>10</v>
       </c>
       <c r="I36" s="3">
-        <v>1004.83</v>
+        <v>1005.83</v>
       </c>
       <c r="J36" s="1">
         <v>9</v>
@@ -3498,7 +3507,7 @@
       </c>
       <c r="O36" s="1">
         <f t="shared" si="5"/>
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="P36" s="1">
         <f t="shared" si="12"/>
@@ -3508,12 +3517,12 @@
         <f t="shared" si="13"/>
         <v>5.48</v>
       </c>
-      <c r="R36" s="12"/>
-      <c r="S36" s="13"/>
-      <c r="T36" s="14"/>
-      <c r="U36" s="12"/>
-      <c r="V36" s="13"/>
-      <c r="W36" s="14"/>
+      <c r="R36" s="15"/>
+      <c r="S36" s="16"/>
+      <c r="T36" s="17"/>
+      <c r="U36" s="15"/>
+      <c r="V36" s="16"/>
+      <c r="W36" s="17"/>
     </row>
     <row r="37" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A37" s="6" t="s">
@@ -3545,11 +3554,11 @@
       </c>
       <c r="H37" s="1">
         <f>ROUND(SUM(H25:H36)/COUNTA(H25:H36),2)</f>
-        <v>12.92</v>
+        <v>12.5</v>
       </c>
       <c r="I37" s="1">
-        <f t="shared" ref="I37" si="15">ROUND(SUM(I25:I36)/COUNTA(I25:I36),2)</f>
-        <v>1257.98</v>
+        <f>ROUND(SUM(I25:I36)/COUNTA(I25:I36),2)</f>
+        <v>1234.93</v>
       </c>
       <c r="J37" s="1">
         <f t="shared" si="14"/>
@@ -3559,49 +3568,52 @@
         <f t="shared" si="14"/>
         <v>1210.3399999999999</v>
       </c>
-      <c r="L37" s="20"/>
-      <c r="M37" s="21"/>
-      <c r="N37" s="21"/>
-      <c r="O37" s="21"/>
-      <c r="P37" s="21"/>
-      <c r="Q37" s="22"/>
-      <c r="R37" s="15"/>
-      <c r="S37" s="16"/>
-      <c r="T37" s="17"/>
-      <c r="U37" s="15"/>
-      <c r="V37" s="16"/>
-      <c r="W37" s="17"/>
+      <c r="L37" s="9"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="10"/>
+      <c r="P37" s="10"/>
+      <c r="Q37" s="11"/>
+      <c r="R37" s="18"/>
+      <c r="S37" s="19"/>
+      <c r="T37" s="20"/>
+      <c r="U37" s="18"/>
+      <c r="V37" s="19"/>
+      <c r="W37" s="20"/>
     </row>
     <row r="38" spans="1:23" ht="18" customHeight="1" thickBot="1">
       <c r="A38" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B38" s="20" t="str">
+      <c r="B38" s="9" t="str">
         <f>COUNTA(A39:A49) &amp; " 筆"</f>
         <v>11 筆</v>
       </c>
-      <c r="C38" s="21"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21"/>
-      <c r="G38" s="21"/>
-      <c r="H38" s="21"/>
-      <c r="I38" s="21"/>
-      <c r="J38" s="21"/>
-      <c r="K38" s="21"/>
-      <c r="L38" s="21"/>
-      <c r="M38" s="21"/>
-      <c r="N38" s="21"/>
-      <c r="O38" s="21"/>
-      <c r="P38" s="21"/>
-      <c r="Q38" s="22"/>
-      <c r="R38" s="1">
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="10"/>
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="10"/>
+      <c r="O38" s="10"/>
+      <c r="P38" s="10"/>
+      <c r="Q38" s="11"/>
+      <c r="R38" s="1" cm="1">
+        <f t="array" ref="R38">CountColor($F39:$F49,$Y$4)</f>
         <v>9</v>
       </c>
-      <c r="S38" s="1">
-        <v>0</v>
-      </c>
-      <c r="T38" s="1">
+      <c r="S38" s="1" cm="1">
+        <f t="array" ref="S38">CountColor($F39:$F49,$Y$5)</f>
+        <v>0</v>
+      </c>
+      <c r="T38" s="1" cm="1">
+        <f t="array" ref="T38">CountColor($F39:$F49,$Y$6)</f>
         <v>2</v>
       </c>
       <c r="U38" s="1">
@@ -3640,7 +3652,7 @@
         <v>4</v>
       </c>
       <c r="I39" s="2">
-        <v>1303.8599999999999</v>
+        <v>1302.83</v>
       </c>
       <c r="J39" s="1">
         <v>4</v>
@@ -3649,11 +3661,11 @@
         <v>1252.3699999999999</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" ref="L39:L49" si="16">ROUND(((F39-D39)/D39)*100,2)</f>
+        <f t="shared" ref="L39:L49" si="15">ROUND(((F39-D39)/D39)*100,2)</f>
         <v>0</v>
       </c>
       <c r="M39" s="1">
-        <f t="shared" ref="M39:M49" si="17">ROUND(((G39-E39)/E39)*100,2)</f>
+        <f t="shared" ref="M39:M49" si="16">ROUND(((G39-E39)/E39)*100,2)</f>
         <v>-9.2799999999999994</v>
       </c>
       <c r="N39" s="1">
@@ -3662,22 +3674,22 @@
       </c>
       <c r="O39" s="1">
         <f t="shared" si="5"/>
-        <v>-9.6</v>
+        <v>-9.67</v>
       </c>
       <c r="P39" s="1">
-        <f t="shared" ref="P39:P49" si="18">ROUND(((F39-J39)/J39)*100,2)</f>
+        <f t="shared" ref="P39:P49" si="17">ROUND(((F39-J39)/J39)*100,2)</f>
         <v>0</v>
       </c>
       <c r="Q39" s="1">
-        <f t="shared" ref="Q39:Q49" si="19">ROUND(((G39-K39)/K39)*100,2)</f>
+        <f t="shared" ref="Q39:Q49" si="18">ROUND(((G39-K39)/K39)*100,2)</f>
         <v>4.4800000000000004</v>
       </c>
-      <c r="R39" s="9"/>
-      <c r="S39" s="10"/>
-      <c r="T39" s="11"/>
-      <c r="U39" s="9"/>
-      <c r="V39" s="10"/>
-      <c r="W39" s="11"/>
+      <c r="R39" s="12"/>
+      <c r="S39" s="13"/>
+      <c r="T39" s="14"/>
+      <c r="U39" s="12"/>
+      <c r="V39" s="13"/>
+      <c r="W39" s="14"/>
     </row>
     <row r="40" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A40" s="6" t="s">
@@ -3702,10 +3714,10 @@
         <v>1759.75</v>
       </c>
       <c r="H40" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I40" s="2">
-        <v>1119.92</v>
+        <v>1406.77</v>
       </c>
       <c r="J40" s="1">
         <v>3</v>
@@ -3714,35 +3726,35 @@
         <v>1191.7</v>
       </c>
       <c r="L40" s="1">
+        <f t="shared" si="15"/>
+        <v>-25</v>
+      </c>
+      <c r="M40" s="1">
         <f t="shared" si="16"/>
-        <v>-25</v>
-      </c>
-      <c r="M40" s="1">
-        <f t="shared" si="17"/>
         <v>45.14</v>
       </c>
       <c r="N40" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="O40" s="1">
         <f t="shared" si="5"/>
-        <v>-7.63</v>
+        <v>16.02</v>
       </c>
       <c r="P40" s="1">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Q40" s="1">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="Q40" s="1">
-        <f t="shared" si="19"/>
         <v>47.67</v>
       </c>
-      <c r="R40" s="12"/>
-      <c r="S40" s="13"/>
-      <c r="T40" s="14"/>
-      <c r="U40" s="12"/>
-      <c r="V40" s="13"/>
-      <c r="W40" s="14"/>
+      <c r="R40" s="15"/>
+      <c r="S40" s="16"/>
+      <c r="T40" s="17"/>
+      <c r="U40" s="15"/>
+      <c r="V40" s="16"/>
+      <c r="W40" s="17"/>
     </row>
     <row r="41" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A41" s="6" t="s">
@@ -3770,7 +3782,7 @@
         <v>3</v>
       </c>
       <c r="I41" s="2">
-        <v>965.38</v>
+        <v>984.76</v>
       </c>
       <c r="J41" s="1">
         <v>3</v>
@@ -3779,11 +3791,11 @@
         <v>939.5</v>
       </c>
       <c r="L41" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="M41" s="1">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="M41" s="1">
-        <f t="shared" si="17"/>
         <v>-17.63</v>
       </c>
       <c r="N41" s="1">
@@ -3792,22 +3804,22 @@
       </c>
       <c r="O41" s="1">
         <f t="shared" si="5"/>
-        <v>-19.399999999999999</v>
+        <v>-17.78</v>
       </c>
       <c r="P41" s="1">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Q41" s="1">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="Q41" s="1">
-        <f t="shared" si="19"/>
         <v>5</v>
       </c>
-      <c r="R41" s="12"/>
-      <c r="S41" s="13"/>
-      <c r="T41" s="14"/>
-      <c r="U41" s="12"/>
-      <c r="V41" s="13"/>
-      <c r="W41" s="14"/>
+      <c r="R41" s="15"/>
+      <c r="S41" s="16"/>
+      <c r="T41" s="17"/>
+      <c r="U41" s="15"/>
+      <c r="V41" s="16"/>
+      <c r="W41" s="17"/>
     </row>
     <row r="42" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A42" s="6" t="s">
@@ -3835,7 +3847,7 @@
         <v>3</v>
       </c>
       <c r="I42" s="2">
-        <v>777.61</v>
+        <v>779.27</v>
       </c>
       <c r="J42" s="1">
         <v>2</v>
@@ -3844,11 +3856,11 @@
         <v>825.52</v>
       </c>
       <c r="L42" s="1">
+        <f t="shared" si="15"/>
+        <v>-70</v>
+      </c>
+      <c r="M42" s="1">
         <f t="shared" si="16"/>
-        <v>-70</v>
-      </c>
-      <c r="M42" s="1">
-        <f t="shared" si="17"/>
         <v>-10.59</v>
       </c>
       <c r="N42" s="1">
@@ -3857,22 +3869,22 @@
       </c>
       <c r="O42" s="1">
         <f t="shared" si="5"/>
-        <v>-8.98</v>
+        <v>-8.7799999999999994</v>
       </c>
       <c r="P42" s="1">
+        <f t="shared" si="17"/>
+        <v>50</v>
+      </c>
+      <c r="Q42" s="1">
         <f t="shared" si="18"/>
-        <v>50</v>
-      </c>
-      <c r="Q42" s="1">
-        <f t="shared" si="19"/>
         <v>-7.48</v>
       </c>
-      <c r="R42" s="12"/>
-      <c r="S42" s="13"/>
-      <c r="T42" s="14"/>
-      <c r="U42" s="12"/>
-      <c r="V42" s="13"/>
-      <c r="W42" s="14"/>
+      <c r="R42" s="15"/>
+      <c r="S42" s="16"/>
+      <c r="T42" s="17"/>
+      <c r="U42" s="15"/>
+      <c r="V42" s="16"/>
+      <c r="W42" s="17"/>
     </row>
     <row r="43" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A43" s="6" t="s">
@@ -3900,7 +3912,7 @@
         <v>3</v>
       </c>
       <c r="I43" s="2">
-        <v>1059.71</v>
+        <v>1071.58</v>
       </c>
       <c r="J43" s="1">
         <v>3</v>
@@ -3909,11 +3921,11 @@
         <v>994.43</v>
       </c>
       <c r="L43" s="1">
+        <f t="shared" si="15"/>
+        <v>-25</v>
+      </c>
+      <c r="M43" s="1">
         <f t="shared" si="16"/>
-        <v>-25</v>
-      </c>
-      <c r="M43" s="1">
-        <f t="shared" si="17"/>
         <v>-20.16</v>
       </c>
       <c r="N43" s="1">
@@ -3922,22 +3934,22 @@
       </c>
       <c r="O43" s="1">
         <f t="shared" si="5"/>
-        <v>-20.78</v>
+        <v>-19.89</v>
       </c>
       <c r="P43" s="1">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Q43" s="1">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="Q43" s="1">
-        <f t="shared" si="19"/>
         <v>7.39</v>
       </c>
-      <c r="R43" s="12"/>
-      <c r="S43" s="13"/>
-      <c r="T43" s="14"/>
-      <c r="U43" s="12"/>
-      <c r="V43" s="13"/>
-      <c r="W43" s="14"/>
+      <c r="R43" s="15"/>
+      <c r="S43" s="16"/>
+      <c r="T43" s="17"/>
+      <c r="U43" s="15"/>
+      <c r="V43" s="16"/>
+      <c r="W43" s="17"/>
     </row>
     <row r="44" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A44" s="6" t="s">
@@ -3965,7 +3977,7 @@
         <v>3</v>
       </c>
       <c r="I44" s="2">
-        <v>931.88</v>
+        <v>972.48</v>
       </c>
       <c r="J44" s="1">
         <v>3</v>
@@ -3974,11 +3986,11 @@
         <v>906.14</v>
       </c>
       <c r="L44" s="1">
+        <f t="shared" si="15"/>
+        <v>-25</v>
+      </c>
+      <c r="M44" s="1">
         <f t="shared" si="16"/>
-        <v>-25</v>
-      </c>
-      <c r="M44" s="1">
-        <f t="shared" si="17"/>
         <v>-13.21</v>
       </c>
       <c r="N44" s="1">
@@ -3987,22 +3999,22 @@
       </c>
       <c r="O44" s="1">
         <f t="shared" si="5"/>
-        <v>-16.41</v>
+        <v>-12.76</v>
       </c>
       <c r="P44" s="1">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Q44" s="1">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="Q44" s="1">
-        <f t="shared" si="19"/>
         <v>6.77</v>
       </c>
-      <c r="R44" s="12"/>
-      <c r="S44" s="13"/>
-      <c r="T44" s="14"/>
-      <c r="U44" s="12"/>
-      <c r="V44" s="13"/>
-      <c r="W44" s="14"/>
+      <c r="R44" s="15"/>
+      <c r="S44" s="16"/>
+      <c r="T44" s="17"/>
+      <c r="U44" s="15"/>
+      <c r="V44" s="16"/>
+      <c r="W44" s="17"/>
     </row>
     <row r="45" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A45" s="6" t="s">
@@ -4030,7 +4042,7 @@
         <v>3</v>
       </c>
       <c r="I45" s="2">
-        <v>849.32</v>
+        <v>848.77</v>
       </c>
       <c r="J45" s="1">
         <v>2</v>
@@ -4039,11 +4051,11 @@
         <v>890.61</v>
       </c>
       <c r="L45" s="1">
+        <f t="shared" si="15"/>
+        <v>-25</v>
+      </c>
+      <c r="M45" s="1">
         <f t="shared" si="16"/>
-        <v>-25</v>
-      </c>
-      <c r="M45" s="1">
-        <f t="shared" si="17"/>
         <v>-19.149999999999999</v>
       </c>
       <c r="N45" s="1">
@@ -4052,22 +4064,22 @@
       </c>
       <c r="O45" s="1">
         <f t="shared" si="5"/>
-        <v>-19.55</v>
+        <v>-19.600000000000001</v>
       </c>
       <c r="P45" s="1">
+        <f t="shared" si="17"/>
+        <v>50</v>
+      </c>
+      <c r="Q45" s="1">
         <f t="shared" si="18"/>
-        <v>50</v>
-      </c>
-      <c r="Q45" s="1">
-        <f t="shared" si="19"/>
         <v>-4.17</v>
       </c>
-      <c r="R45" s="12"/>
-      <c r="S45" s="13"/>
-      <c r="T45" s="14"/>
-      <c r="U45" s="12"/>
-      <c r="V45" s="13"/>
-      <c r="W45" s="14"/>
+      <c r="R45" s="15"/>
+      <c r="S45" s="16"/>
+      <c r="T45" s="17"/>
+      <c r="U45" s="15"/>
+      <c r="V45" s="16"/>
+      <c r="W45" s="17"/>
     </row>
     <row r="46" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A46" s="6" t="s">
@@ -4092,10 +4104,10 @@
         <v>739.55</v>
       </c>
       <c r="H46" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I46" s="2">
-        <v>728.84</v>
+        <v>814.22</v>
       </c>
       <c r="J46" s="1">
         <v>2</v>
@@ -4104,35 +4116,35 @@
         <v>726.82</v>
       </c>
       <c r="L46" s="1">
+        <f t="shared" si="15"/>
+        <v>-33.33</v>
+      </c>
+      <c r="M46" s="1">
         <f t="shared" si="16"/>
-        <v>-33.33</v>
-      </c>
-      <c r="M46" s="1">
-        <f t="shared" si="17"/>
         <v>-14.06</v>
       </c>
       <c r="N46" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-33.33</v>
       </c>
       <c r="O46" s="1">
         <f t="shared" si="5"/>
-        <v>-15.3</v>
+        <v>-5.38</v>
       </c>
       <c r="P46" s="1">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Q46" s="1">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="Q46" s="1">
-        <f t="shared" si="19"/>
         <v>1.75</v>
       </c>
-      <c r="R46" s="12"/>
-      <c r="S46" s="13"/>
-      <c r="T46" s="14"/>
-      <c r="U46" s="12"/>
-      <c r="V46" s="13"/>
-      <c r="W46" s="14"/>
+      <c r="R46" s="15"/>
+      <c r="S46" s="16"/>
+      <c r="T46" s="17"/>
+      <c r="U46" s="15"/>
+      <c r="V46" s="16"/>
+      <c r="W46" s="17"/>
     </row>
     <row r="47" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A47" s="6" t="s">
@@ -4160,7 +4172,7 @@
         <v>3</v>
       </c>
       <c r="I47" s="3">
-        <v>959.23</v>
+        <v>965.75</v>
       </c>
       <c r="J47" s="1">
         <v>3</v>
@@ -4169,11 +4181,11 @@
         <v>909.16</v>
       </c>
       <c r="L47" s="1">
+        <f t="shared" si="15"/>
+        <v>50</v>
+      </c>
+      <c r="M47" s="1">
         <f t="shared" si="16"/>
-        <v>50</v>
-      </c>
-      <c r="M47" s="1">
-        <f t="shared" si="17"/>
         <v>6.9</v>
       </c>
       <c r="N47" s="1">
@@ -4182,22 +4194,22 @@
       </c>
       <c r="O47" s="1">
         <f t="shared" si="5"/>
-        <v>7.12</v>
+        <v>7.85</v>
       </c>
       <c r="P47" s="1">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Q47" s="1">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="Q47" s="1">
-        <f t="shared" si="19"/>
         <v>5.29</v>
       </c>
-      <c r="R47" s="12"/>
-      <c r="S47" s="13"/>
-      <c r="T47" s="14"/>
-      <c r="U47" s="12"/>
-      <c r="V47" s="13"/>
-      <c r="W47" s="14"/>
+      <c r="R47" s="15"/>
+      <c r="S47" s="16"/>
+      <c r="T47" s="17"/>
+      <c r="U47" s="15"/>
+      <c r="V47" s="16"/>
+      <c r="W47" s="17"/>
     </row>
     <row r="48" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A48" s="6" t="s">
@@ -4225,7 +4237,7 @@
         <v>3</v>
       </c>
       <c r="I48" s="3">
-        <v>984.59</v>
+        <v>994.83</v>
       </c>
       <c r="J48" s="1">
         <v>3</v>
@@ -4234,11 +4246,11 @@
         <v>939.37</v>
       </c>
       <c r="L48" s="1">
+        <f t="shared" si="15"/>
+        <v>50</v>
+      </c>
+      <c r="M48" s="1">
         <f t="shared" si="16"/>
-        <v>50</v>
-      </c>
-      <c r="M48" s="1">
-        <f t="shared" si="17"/>
         <v>5.41</v>
       </c>
       <c r="N48" s="1">
@@ -4247,22 +4259,22 @@
       </c>
       <c r="O48" s="1">
         <f t="shared" si="5"/>
-        <v>4.42</v>
+        <v>5.5</v>
       </c>
       <c r="P48" s="1">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Q48" s="1">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="Q48" s="1">
-        <f t="shared" si="19"/>
         <v>5.81</v>
       </c>
-      <c r="R48" s="12"/>
-      <c r="S48" s="13"/>
-      <c r="T48" s="14"/>
-      <c r="U48" s="12"/>
-      <c r="V48" s="13"/>
-      <c r="W48" s="14"/>
+      <c r="R48" s="15"/>
+      <c r="S48" s="16"/>
+      <c r="T48" s="17"/>
+      <c r="U48" s="15"/>
+      <c r="V48" s="16"/>
+      <c r="W48" s="17"/>
     </row>
     <row r="49" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A49" s="6" t="s">
@@ -4290,7 +4302,7 @@
         <v>3</v>
       </c>
       <c r="I49" s="2">
-        <v>804.22</v>
+        <v>808.38</v>
       </c>
       <c r="J49" s="1">
         <v>2</v>
@@ -4299,11 +4311,11 @@
         <v>885.71</v>
       </c>
       <c r="L49" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="M49" s="1">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="M49" s="1">
-        <f t="shared" si="17"/>
         <v>-21.83</v>
       </c>
       <c r="N49" s="1">
@@ -4312,22 +4324,22 @@
       </c>
       <c r="O49" s="1">
         <f t="shared" si="5"/>
-        <v>-23.38</v>
+        <v>-22.98</v>
       </c>
       <c r="P49" s="1">
+        <f t="shared" si="17"/>
+        <v>50</v>
+      </c>
+      <c r="Q49" s="1">
         <f t="shared" si="18"/>
-        <v>50</v>
-      </c>
-      <c r="Q49" s="1">
-        <f t="shared" si="19"/>
         <v>-7.37</v>
       </c>
-      <c r="R49" s="12"/>
-      <c r="S49" s="13"/>
-      <c r="T49" s="14"/>
-      <c r="U49" s="12"/>
-      <c r="V49" s="13"/>
-      <c r="W49" s="14"/>
+      <c r="R49" s="15"/>
+      <c r="S49" s="16"/>
+      <c r="T49" s="17"/>
+      <c r="U49" s="15"/>
+      <c r="V49" s="16"/>
+      <c r="W49" s="17"/>
     </row>
     <row r="50" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A50" s="6" t="s">
@@ -4338,19 +4350,19 @@
         <v>3.27</v>
       </c>
       <c r="C50" s="1">
-        <f t="shared" ref="C50:K50" si="20">ROUND(SUM(C39:C49)/COUNTA(C39:C49),2)</f>
+        <f t="shared" ref="C50:K50" si="19">ROUND(SUM(C39:C49)/COUNTA(C39:C49),2)</f>
         <v>1329.44</v>
       </c>
       <c r="D50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>3.91</v>
       </c>
       <c r="E50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>1087.5899999999999</v>
       </c>
       <c r="F50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>3</v>
       </c>
       <c r="G50" s="1">
@@ -4359,73 +4371,76 @@
       </c>
       <c r="H50" s="1">
         <f>ROUND(SUM(H39:H49)/COUNTA(H39:H49),2)</f>
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="I50" s="1">
         <f>ROUND(SUM(I39:I49)/COUNTA(I39:I49),2)</f>
-        <v>953.14</v>
+        <v>995.42</v>
       </c>
       <c r="J50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>2.73</v>
       </c>
       <c r="K50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>951.03</v>
       </c>
-      <c r="L50" s="20"/>
-      <c r="M50" s="21"/>
-      <c r="N50" s="21"/>
-      <c r="O50" s="21"/>
-      <c r="P50" s="21"/>
-      <c r="Q50" s="22"/>
-      <c r="R50" s="15"/>
-      <c r="S50" s="16"/>
-      <c r="T50" s="17"/>
-      <c r="U50" s="15"/>
-      <c r="V50" s="16"/>
-      <c r="W50" s="17"/>
+      <c r="L50" s="9"/>
+      <c r="M50" s="10"/>
+      <c r="N50" s="10"/>
+      <c r="O50" s="10"/>
+      <c r="P50" s="10"/>
+      <c r="Q50" s="11"/>
+      <c r="R50" s="18"/>
+      <c r="S50" s="19"/>
+      <c r="T50" s="20"/>
+      <c r="U50" s="18"/>
+      <c r="V50" s="19"/>
+      <c r="W50" s="20"/>
     </row>
     <row r="51" spans="1:23" ht="18" customHeight="1" thickBot="1">
       <c r="A51" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B51" s="20" t="str">
+      <c r="B51" s="9" t="str">
         <f>COUNTA(A52:A59) &amp; " 筆"</f>
         <v>8 筆</v>
       </c>
-      <c r="C51" s="21"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="21"/>
-      <c r="G51" s="21"/>
-      <c r="H51" s="21"/>
-      <c r="I51" s="21"/>
-      <c r="J51" s="21"/>
-      <c r="K51" s="21"/>
-      <c r="L51" s="21"/>
-      <c r="M51" s="21"/>
-      <c r="N51" s="21"/>
-      <c r="O51" s="21"/>
-      <c r="P51" s="21"/>
-      <c r="Q51" s="22"/>
-      <c r="R51" s="1">
+      <c r="C51" s="10"/>
+      <c r="D51" s="10"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="10"/>
+      <c r="H51" s="10"/>
+      <c r="I51" s="10"/>
+      <c r="J51" s="10"/>
+      <c r="K51" s="10"/>
+      <c r="L51" s="10"/>
+      <c r="M51" s="10"/>
+      <c r="N51" s="10"/>
+      <c r="O51" s="10"/>
+      <c r="P51" s="10"/>
+      <c r="Q51" s="11"/>
+      <c r="R51" s="1" cm="1">
+        <f t="array" ref="R51">CountColor($F52:$F59,$Y$4)</f>
         <v>5</v>
       </c>
-      <c r="S51" s="1">
-        <v>0</v>
-      </c>
-      <c r="T51" s="1">
+      <c r="S51" s="1" cm="1">
+        <f t="array" ref="S51">CountColor($F52:$F59,$Y$5)</f>
+        <v>0</v>
+      </c>
+      <c r="T51" s="1" cm="1">
+        <f t="array" ref="T51">CountColor($F52:$F59,$Y$6)</f>
         <v>3</v>
       </c>
       <c r="U51" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V51" s="1">
         <v>0</v>
       </c>
       <c r="W51" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
@@ -4454,7 +4469,7 @@
         <v>15</v>
       </c>
       <c r="I52" s="2">
-        <v>1645.68</v>
+        <v>1649.47</v>
       </c>
       <c r="J52" s="1">
         <v>14</v>
@@ -4463,11 +4478,11 @@
         <v>1696.95</v>
       </c>
       <c r="L52" s="1">
-        <f t="shared" ref="L52:L59" si="21">ROUND(((F52-D52)/D52)*100,2)</f>
+        <f t="shared" ref="L52:L59" si="20">ROUND(((F52-D52)/D52)*100,2)</f>
         <v>-6.25</v>
       </c>
       <c r="M52" s="1">
-        <f t="shared" ref="M52:M59" si="22">ROUND(((G52-E52)/E52)*100,2)</f>
+        <f t="shared" ref="M52:M59" si="21">ROUND(((G52-E52)/E52)*100,2)</f>
         <v>1.89</v>
       </c>
       <c r="N52" s="1">
@@ -4476,22 +4491,22 @@
       </c>
       <c r="O52" s="1">
         <f t="shared" si="5"/>
-        <v>-0.66</v>
+        <v>-0.43</v>
       </c>
       <c r="P52" s="1">
-        <f t="shared" ref="P52:P59" si="23">ROUND(((F52-J52)/J52)*100,2)</f>
+        <f t="shared" ref="P52:P59" si="22">ROUND(((F52-J52)/J52)*100,2)</f>
         <v>7.14</v>
       </c>
       <c r="Q52" s="1">
-        <f t="shared" ref="Q52:Q59" si="24">ROUND(((G52-K52)/K52)*100,2)</f>
+        <f t="shared" ref="Q52:Q59" si="23">ROUND(((G52-K52)/K52)*100,2)</f>
         <v>-0.53</v>
       </c>
-      <c r="R52" s="9"/>
-      <c r="S52" s="10"/>
-      <c r="T52" s="11"/>
-      <c r="U52" s="9"/>
-      <c r="V52" s="10"/>
-      <c r="W52" s="11"/>
+      <c r="R52" s="12"/>
+      <c r="S52" s="13"/>
+      <c r="T52" s="14"/>
+      <c r="U52" s="12"/>
+      <c r="V52" s="13"/>
+      <c r="W52" s="14"/>
     </row>
     <row r="53" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A53" s="5" t="s">
@@ -4519,7 +4534,7 @@
         <v>13</v>
       </c>
       <c r="I53" s="2">
-        <v>1511.64</v>
+        <v>1497.51</v>
       </c>
       <c r="J53" s="1">
         <v>12</v>
@@ -4528,11 +4543,11 @@
         <v>1554.75</v>
       </c>
       <c r="L53" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="M53" s="1">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M53" s="1">
-        <f t="shared" si="22"/>
         <v>-1.59</v>
       </c>
       <c r="N53" s="1">
@@ -4541,22 +4556,22 @@
       </c>
       <c r="O53" s="1">
         <f t="shared" si="5"/>
-        <v>-1.35</v>
+        <v>-2.27</v>
       </c>
       <c r="P53" s="1">
+        <f t="shared" si="22"/>
+        <v>8.33</v>
+      </c>
+      <c r="Q53" s="1">
         <f t="shared" si="23"/>
-        <v>8.33</v>
-      </c>
-      <c r="Q53" s="1">
-        <f t="shared" si="24"/>
         <v>-3.01</v>
       </c>
-      <c r="R53" s="12"/>
-      <c r="S53" s="13"/>
-      <c r="T53" s="14"/>
-      <c r="U53" s="12"/>
-      <c r="V53" s="13"/>
-      <c r="W53" s="14"/>
+      <c r="R53" s="15"/>
+      <c r="S53" s="16"/>
+      <c r="T53" s="17"/>
+      <c r="U53" s="15"/>
+      <c r="V53" s="16"/>
+      <c r="W53" s="17"/>
     </row>
     <row r="54" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A54" s="5" t="s">
@@ -4581,10 +4596,10 @@
         <v>1516.36</v>
       </c>
       <c r="H54" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I54" s="2">
-        <v>1294.26</v>
+        <v>1316.11</v>
       </c>
       <c r="J54" s="1">
         <v>11</v>
@@ -4593,35 +4608,35 @@
         <v>1261.67</v>
       </c>
       <c r="L54" s="1">
+        <f t="shared" si="20"/>
+        <v>-8.33</v>
+      </c>
+      <c r="M54" s="1">
         <f t="shared" si="21"/>
-        <v>-8.33</v>
-      </c>
-      <c r="M54" s="1">
-        <f t="shared" si="22"/>
         <v>12.82</v>
       </c>
       <c r="N54" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-8.33</v>
       </c>
       <c r="O54" s="1">
         <f t="shared" si="5"/>
-        <v>-3.7</v>
+        <v>-2.08</v>
       </c>
       <c r="P54" s="1">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="Q54" s="1">
         <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="Q54" s="1">
-        <f t="shared" si="24"/>
         <v>20.190000000000001</v>
       </c>
-      <c r="R54" s="12"/>
-      <c r="S54" s="13"/>
-      <c r="T54" s="14"/>
-      <c r="U54" s="12"/>
-      <c r="V54" s="13"/>
-      <c r="W54" s="14"/>
+      <c r="R54" s="15"/>
+      <c r="S54" s="16"/>
+      <c r="T54" s="17"/>
+      <c r="U54" s="15"/>
+      <c r="V54" s="16"/>
+      <c r="W54" s="17"/>
     </row>
     <row r="55" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A55" s="5" t="s">
@@ -4646,10 +4661,10 @@
         <v>1336.1</v>
       </c>
       <c r="H55" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I55" s="2">
-        <v>1182.05</v>
+        <v>1169.0999999999999</v>
       </c>
       <c r="J55" s="1">
         <v>10</v>
@@ -4658,35 +4673,35 @@
         <v>1135.48</v>
       </c>
       <c r="L55" s="1">
+        <f t="shared" si="20"/>
+        <v>-9.09</v>
+      </c>
+      <c r="M55" s="1">
         <f t="shared" si="21"/>
-        <v>-9.09</v>
-      </c>
-      <c r="M55" s="1">
-        <f t="shared" si="22"/>
         <v>12.76</v>
       </c>
       <c r="N55" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-9.09</v>
       </c>
       <c r="O55" s="1">
         <f t="shared" si="5"/>
-        <v>-0.24</v>
+        <v>-1.33</v>
       </c>
       <c r="P55" s="1">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="Q55" s="1">
         <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="Q55" s="1">
-        <f t="shared" si="24"/>
         <v>17.670000000000002</v>
       </c>
-      <c r="R55" s="12"/>
-      <c r="S55" s="13"/>
-      <c r="T55" s="14"/>
-      <c r="U55" s="12"/>
-      <c r="V55" s="13"/>
-      <c r="W55" s="14"/>
+      <c r="R55" s="15"/>
+      <c r="S55" s="16"/>
+      <c r="T55" s="17"/>
+      <c r="U55" s="15"/>
+      <c r="V55" s="16"/>
+      <c r="W55" s="17"/>
     </row>
     <row r="56" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A56" s="5" t="s">
@@ -4710,11 +4725,11 @@
       <c r="G56" s="3">
         <v>1902.43</v>
       </c>
-      <c r="H56" s="3">
-        <v>15</v>
-      </c>
-      <c r="I56" s="3">
-        <v>1554.54</v>
+      <c r="H56" s="2">
+        <v>14</v>
+      </c>
+      <c r="I56" s="2">
+        <v>1595.23</v>
       </c>
       <c r="J56" s="1">
         <v>13</v>
@@ -4723,35 +4738,35 @@
         <v>1629.44</v>
       </c>
       <c r="L56" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="M56" s="1">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M56" s="1">
-        <f t="shared" si="22"/>
         <v>14.47</v>
       </c>
       <c r="N56" s="1">
         <f t="shared" si="4"/>
-        <v>7.14</v>
+        <v>0</v>
       </c>
       <c r="O56" s="1">
         <f t="shared" si="5"/>
-        <v>-6.47</v>
+        <v>-4.0199999999999996</v>
       </c>
       <c r="P56" s="1">
+        <f t="shared" si="22"/>
+        <v>7.69</v>
+      </c>
+      <c r="Q56" s="1">
         <f t="shared" si="23"/>
-        <v>7.69</v>
-      </c>
-      <c r="Q56" s="1">
-        <f t="shared" si="24"/>
         <v>16.75</v>
       </c>
-      <c r="R56" s="12"/>
-      <c r="S56" s="13"/>
-      <c r="T56" s="14"/>
-      <c r="U56" s="12"/>
-      <c r="V56" s="13"/>
-      <c r="W56" s="14"/>
+      <c r="R56" s="15"/>
+      <c r="S56" s="16"/>
+      <c r="T56" s="17"/>
+      <c r="U56" s="15"/>
+      <c r="V56" s="16"/>
+      <c r="W56" s="17"/>
     </row>
     <row r="57" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A57" s="5" t="s">
@@ -4776,10 +4791,10 @@
         <v>1663.23</v>
       </c>
       <c r="H57" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I57" s="3">
-        <v>1407.11</v>
+        <v>1424.21</v>
       </c>
       <c r="J57" s="1">
         <v>11</v>
@@ -4788,35 +4803,35 @@
         <v>1424.73</v>
       </c>
       <c r="L57" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="M57" s="1">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M57" s="1">
-        <f t="shared" si="22"/>
         <v>23.75</v>
       </c>
       <c r="N57" s="1">
         <f t="shared" si="4"/>
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="O57" s="1">
         <f t="shared" si="5"/>
-        <v>4.6900000000000004</v>
+        <v>5.97</v>
       </c>
       <c r="P57" s="1">
+        <f t="shared" si="22"/>
+        <v>9.09</v>
+      </c>
+      <c r="Q57" s="1">
         <f t="shared" si="23"/>
-        <v>9.09</v>
-      </c>
-      <c r="Q57" s="1">
-        <f t="shared" si="24"/>
         <v>16.739999999999998</v>
       </c>
-      <c r="R57" s="12"/>
-      <c r="S57" s="13"/>
-      <c r="T57" s="14"/>
-      <c r="U57" s="12"/>
-      <c r="V57" s="13"/>
-      <c r="W57" s="14"/>
+      <c r="R57" s="15"/>
+      <c r="S57" s="16"/>
+      <c r="T57" s="17"/>
+      <c r="U57" s="15"/>
+      <c r="V57" s="16"/>
+      <c r="W57" s="17"/>
     </row>
     <row r="58" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A58" s="5" t="s">
@@ -4841,10 +4856,10 @@
         <v>1529.97</v>
       </c>
       <c r="H58" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I58" s="2">
-        <v>1257.58</v>
+        <v>1262.21</v>
       </c>
       <c r="J58" s="1">
         <v>11</v>
@@ -4853,35 +4868,35 @@
         <v>1230.48</v>
       </c>
       <c r="L58" s="1">
+        <f t="shared" si="20"/>
+        <v>-8.33</v>
+      </c>
+      <c r="M58" s="1">
         <f t="shared" si="21"/>
-        <v>-8.33</v>
-      </c>
-      <c r="M58" s="1">
-        <f t="shared" si="22"/>
         <v>21.13</v>
       </c>
       <c r="N58" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-8.33</v>
       </c>
       <c r="O58" s="1">
         <f t="shared" si="5"/>
-        <v>-0.43</v>
+        <v>-7.0000000000000007E-2</v>
       </c>
       <c r="P58" s="1">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="Q58" s="1">
         <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="Q58" s="1">
-        <f t="shared" si="24"/>
         <v>24.34</v>
       </c>
-      <c r="R58" s="12"/>
-      <c r="S58" s="13"/>
-      <c r="T58" s="14"/>
-      <c r="U58" s="12"/>
-      <c r="V58" s="13"/>
-      <c r="W58" s="14"/>
+      <c r="R58" s="15"/>
+      <c r="S58" s="16"/>
+      <c r="T58" s="17"/>
+      <c r="U58" s="15"/>
+      <c r="V58" s="16"/>
+      <c r="W58" s="17"/>
     </row>
     <row r="59" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A59" s="5" t="s">
@@ -4909,7 +4924,7 @@
         <v>11</v>
       </c>
       <c r="I59" s="2">
-        <v>1137.42</v>
+        <v>1140.1600000000001</v>
       </c>
       <c r="J59" s="1">
         <v>10</v>
@@ -4918,11 +4933,11 @@
         <v>1139.82</v>
       </c>
       <c r="L59" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="M59" s="1">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M59" s="1">
-        <f t="shared" si="22"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="N59" s="1">
@@ -4931,22 +4946,22 @@
       </c>
       <c r="O59" s="1">
         <f t="shared" si="5"/>
-        <v>-0.66</v>
+        <v>-0.42</v>
       </c>
       <c r="P59" s="1">
+        <f t="shared" si="22"/>
+        <v>10</v>
+      </c>
+      <c r="Q59" s="1">
         <f t="shared" si="23"/>
-        <v>10</v>
-      </c>
-      <c r="Q59" s="1">
-        <f t="shared" si="24"/>
         <v>0.51</v>
       </c>
-      <c r="R59" s="12"/>
-      <c r="S59" s="13"/>
-      <c r="T59" s="14"/>
-      <c r="U59" s="12"/>
-      <c r="V59" s="13"/>
-      <c r="W59" s="14"/>
+      <c r="R59" s="15"/>
+      <c r="S59" s="16"/>
+      <c r="T59" s="17"/>
+      <c r="U59" s="15"/>
+      <c r="V59" s="16"/>
+      <c r="W59" s="17"/>
     </row>
     <row r="60" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A60" s="6" t="s">
@@ -4957,94 +4972,97 @@
         <v>14</v>
       </c>
       <c r="C60" s="1">
-        <f t="shared" ref="C60:K60" si="25">ROUND(SUM(C52:C59)/COUNTA(C52:C59),2)</f>
+        <f t="shared" ref="C60:K60" si="24">ROUND(SUM(C52:C59)/COUNTA(C52:C59),2)</f>
         <v>1559.4</v>
       </c>
       <c r="D60" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>12.63</v>
       </c>
       <c r="E60" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>1391.48</v>
       </c>
       <c r="F60" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>12.13</v>
       </c>
       <c r="G60" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>1536.21</v>
       </c>
       <c r="H60" s="1">
-        <f t="shared" ref="H60" si="26">ROUND(SUM(H52:H59)/COUNTA(H52:H59),2)</f>
-        <v>12.75</v>
+        <f>ROUND(SUM(H52:H59)/COUNTA(H52:H59),2)</f>
+        <v>12.13</v>
       </c>
       <c r="I60" s="1">
-        <f t="shared" ref="I60" si="27">ROUND(SUM(I52:I59)/COUNTA(I52:I59),2)</f>
-        <v>1373.79</v>
+        <f>ROUND(SUM(I52:I59)/COUNTA(I52:I59),2)</f>
+        <v>1381.75</v>
       </c>
       <c r="J60" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>11.5</v>
       </c>
       <c r="K60" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>1384.17</v>
       </c>
-      <c r="L60" s="20"/>
-      <c r="M60" s="21"/>
-      <c r="N60" s="21"/>
-      <c r="O60" s="21"/>
-      <c r="P60" s="21"/>
-      <c r="Q60" s="22"/>
-      <c r="R60" s="15"/>
-      <c r="S60" s="16"/>
-      <c r="T60" s="17"/>
-      <c r="U60" s="15"/>
-      <c r="V60" s="16"/>
-      <c r="W60" s="17"/>
+      <c r="L60" s="9"/>
+      <c r="M60" s="10"/>
+      <c r="N60" s="10"/>
+      <c r="O60" s="10"/>
+      <c r="P60" s="10"/>
+      <c r="Q60" s="11"/>
+      <c r="R60" s="18"/>
+      <c r="S60" s="19"/>
+      <c r="T60" s="20"/>
+      <c r="U60" s="18"/>
+      <c r="V60" s="19"/>
+      <c r="W60" s="20"/>
     </row>
     <row r="61" spans="1:23" ht="17.25" thickBot="1">
       <c r="A61" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B61" s="20" t="str">
+      <c r="B61" s="9" t="str">
         <f>COUNTA(A62:A69) &amp; " 筆"</f>
         <v>8 筆</v>
       </c>
-      <c r="C61" s="21"/>
-      <c r="D61" s="21"/>
-      <c r="E61" s="21"/>
-      <c r="F61" s="21"/>
-      <c r="G61" s="21"/>
-      <c r="H61" s="21"/>
-      <c r="I61" s="21"/>
-      <c r="J61" s="21"/>
-      <c r="K61" s="21"/>
-      <c r="L61" s="21"/>
-      <c r="M61" s="21"/>
-      <c r="N61" s="21"/>
-      <c r="O61" s="21"/>
-      <c r="P61" s="21"/>
-      <c r="Q61" s="22"/>
-      <c r="R61" s="1">
+      <c r="C61" s="10"/>
+      <c r="D61" s="10"/>
+      <c r="E61" s="10"/>
+      <c r="F61" s="10"/>
+      <c r="G61" s="10"/>
+      <c r="H61" s="10"/>
+      <c r="I61" s="10"/>
+      <c r="J61" s="10"/>
+      <c r="K61" s="10"/>
+      <c r="L61" s="10"/>
+      <c r="M61" s="10"/>
+      <c r="N61" s="10"/>
+      <c r="O61" s="10"/>
+      <c r="P61" s="10"/>
+      <c r="Q61" s="11"/>
+      <c r="R61" s="1" cm="1">
+        <f t="array" ref="R61">CountColor($F62:$F69,$Y$4)</f>
         <v>4</v>
       </c>
-      <c r="S61" s="1">
-        <v>0</v>
-      </c>
-      <c r="T61" s="1">
+      <c r="S61" s="1" cm="1">
+        <f t="array" ref="S61">CountColor($F62:$F69,$Y$5)</f>
+        <v>0</v>
+      </c>
+      <c r="T61" s="1" cm="1">
+        <f t="array" ref="T61">CountColor($F62:$F69,$Y$6)</f>
         <v>4</v>
       </c>
       <c r="U61" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V61" s="1">
         <v>0</v>
       </c>
       <c r="W61" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
@@ -5073,7 +5091,7 @@
         <v>4</v>
       </c>
       <c r="I62" s="3">
-        <v>1557.23</v>
+        <v>1495.19</v>
       </c>
       <c r="J62" s="1">
         <v>4</v>
@@ -5082,11 +5100,11 @@
         <v>1406.94</v>
       </c>
       <c r="L62" s="1">
-        <f t="shared" ref="L62:M69" si="28">ROUND(((F62-D62)/D62)*100,2)</f>
+        <f t="shared" ref="L62:M69" si="25">ROUND(((F62-D62)/D62)*100,2)</f>
         <v>0</v>
       </c>
       <c r="M62" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>1.61</v>
       </c>
       <c r="N62" s="1">
@@ -5095,22 +5113,22 @@
       </c>
       <c r="O62" s="1">
         <f t="shared" si="5"/>
-        <v>7.97</v>
+        <v>3.67</v>
       </c>
       <c r="P62" s="1">
-        <f t="shared" ref="P62:Q69" si="29">ROUND(((F62-J62)/J62)*100,2)</f>
+        <f t="shared" ref="P62:Q69" si="26">ROUND(((F62-J62)/J62)*100,2)</f>
         <v>0</v>
       </c>
       <c r="Q62" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>4.17</v>
       </c>
-      <c r="R62" s="9"/>
-      <c r="S62" s="10"/>
-      <c r="T62" s="11"/>
-      <c r="U62" s="9"/>
-      <c r="V62" s="10"/>
-      <c r="W62" s="11"/>
+      <c r="R62" s="12"/>
+      <c r="S62" s="13"/>
+      <c r="T62" s="14"/>
+      <c r="U62" s="12"/>
+      <c r="V62" s="13"/>
+      <c r="W62" s="14"/>
     </row>
     <row r="63" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A63" s="5" t="s">
@@ -5138,7 +5156,7 @@
         <v>4</v>
       </c>
       <c r="I63" s="2">
-        <v>1192.8699999999999</v>
+        <v>1209.52</v>
       </c>
       <c r="J63" s="1">
         <v>3</v>
@@ -5147,11 +5165,11 @@
         <v>1365.65</v>
       </c>
       <c r="L63" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="M63" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>3.24</v>
       </c>
       <c r="N63" s="1">
@@ -5160,22 +5178,22 @@
       </c>
       <c r="O63" s="1">
         <f t="shared" si="5"/>
-        <v>-1.62</v>
+        <v>-0.24</v>
       </c>
       <c r="P63" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>33.33</v>
       </c>
       <c r="Q63" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>-8.34</v>
       </c>
-      <c r="R63" s="12"/>
-      <c r="S63" s="13"/>
-      <c r="T63" s="14"/>
-      <c r="U63" s="12"/>
-      <c r="V63" s="13"/>
-      <c r="W63" s="14"/>
+      <c r="R63" s="15"/>
+      <c r="S63" s="16"/>
+      <c r="T63" s="17"/>
+      <c r="U63" s="15"/>
+      <c r="V63" s="16"/>
+      <c r="W63" s="17"/>
     </row>
     <row r="64" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A64" s="5" t="s">
@@ -5203,7 +5221,7 @@
         <v>3</v>
       </c>
       <c r="I64" s="3">
-        <v>1264.51</v>
+        <v>1136.33</v>
       </c>
       <c r="J64" s="1">
         <v>3</v>
@@ -5212,11 +5230,11 @@
         <v>1049.6199999999999</v>
       </c>
       <c r="L64" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="M64" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>-5.27</v>
       </c>
       <c r="N64" s="1">
@@ -5225,22 +5243,22 @@
       </c>
       <c r="O64" s="1">
         <f t="shared" si="5"/>
-        <v>5.58</v>
+        <v>-5.12</v>
       </c>
       <c r="P64" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="Q64" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>8.09</v>
       </c>
-      <c r="R64" s="12"/>
-      <c r="S64" s="13"/>
-      <c r="T64" s="14"/>
-      <c r="U64" s="12"/>
-      <c r="V64" s="13"/>
-      <c r="W64" s="14"/>
+      <c r="R64" s="15"/>
+      <c r="S64" s="16"/>
+      <c r="T64" s="17"/>
+      <c r="U64" s="15"/>
+      <c r="V64" s="16"/>
+      <c r="W64" s="17"/>
     </row>
     <row r="65" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A65" s="5" t="s">
@@ -5268,7 +5286,7 @@
         <v>3</v>
       </c>
       <c r="I65" s="2">
-        <v>861.84</v>
+        <v>823.83</v>
       </c>
       <c r="J65" s="1">
         <v>3</v>
@@ -5277,11 +5295,11 @@
         <v>798.46</v>
       </c>
       <c r="L65" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>-70</v>
       </c>
       <c r="M65" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>-4.28</v>
       </c>
       <c r="N65" s="1">
@@ -5290,22 +5308,22 @@
       </c>
       <c r="O65" s="1">
         <f t="shared" si="5"/>
-        <v>0.88</v>
+        <v>-3.57</v>
       </c>
       <c r="P65" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="Q65" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>2.42</v>
       </c>
-      <c r="R65" s="12"/>
-      <c r="S65" s="13"/>
-      <c r="T65" s="14"/>
-      <c r="U65" s="12"/>
-      <c r="V65" s="13"/>
-      <c r="W65" s="14"/>
+      <c r="R65" s="15"/>
+      <c r="S65" s="16"/>
+      <c r="T65" s="17"/>
+      <c r="U65" s="15"/>
+      <c r="V65" s="16"/>
+      <c r="W65" s="17"/>
     </row>
     <row r="66" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A66" s="5" t="s">
@@ -5333,7 +5351,7 @@
         <v>4</v>
       </c>
       <c r="I66" s="3">
-        <v>1496.11</v>
+        <v>1374.6</v>
       </c>
       <c r="J66" s="1">
         <v>4</v>
@@ -5342,11 +5360,11 @@
         <v>1297.6500000000001</v>
       </c>
       <c r="L66" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="M66" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>3.15</v>
       </c>
       <c r="N66" s="1">
@@ -5355,22 +5373,22 @@
       </c>
       <c r="O66" s="1">
         <f t="shared" si="5"/>
-        <v>11.85</v>
+        <v>2.76</v>
       </c>
       <c r="P66" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="Q66" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>6.33</v>
       </c>
-      <c r="R66" s="12"/>
-      <c r="S66" s="13"/>
-      <c r="T66" s="14"/>
-      <c r="U66" s="12"/>
-      <c r="V66" s="13"/>
-      <c r="W66" s="14"/>
+      <c r="R66" s="15"/>
+      <c r="S66" s="16"/>
+      <c r="T66" s="17"/>
+      <c r="U66" s="15"/>
+      <c r="V66" s="16"/>
+      <c r="W66" s="17"/>
     </row>
     <row r="67" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A67" s="5" t="s">
@@ -5394,11 +5412,11 @@
       <c r="G67" s="2">
         <v>1265.18</v>
       </c>
-      <c r="H67" s="3">
-        <v>4</v>
-      </c>
-      <c r="I67" s="3">
-        <v>1186.08</v>
+      <c r="H67" s="2">
+        <v>3</v>
+      </c>
+      <c r="I67" s="2">
+        <v>1258.08</v>
       </c>
       <c r="J67" s="1">
         <v>3</v>
@@ -5407,35 +5425,35 @@
         <v>1146.32</v>
       </c>
       <c r="L67" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>-25</v>
       </c>
       <c r="M67" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>13.49</v>
       </c>
       <c r="N67" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="O67" s="1">
         <f t="shared" si="5"/>
-        <v>6.4</v>
+        <v>12.86</v>
       </c>
       <c r="P67" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="Q67" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>10.37</v>
       </c>
-      <c r="R67" s="12"/>
-      <c r="S67" s="13"/>
-      <c r="T67" s="14"/>
-      <c r="U67" s="12"/>
-      <c r="V67" s="13"/>
-      <c r="W67" s="14"/>
+      <c r="R67" s="15"/>
+      <c r="S67" s="16"/>
+      <c r="T67" s="17"/>
+      <c r="U67" s="15"/>
+      <c r="V67" s="16"/>
+      <c r="W67" s="17"/>
     </row>
     <row r="68" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A68" s="5" t="s">
@@ -5460,10 +5478,10 @@
         <v>1117.1400000000001</v>
       </c>
       <c r="H68" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I68" s="3">
-        <v>1087.31</v>
+        <v>1160.47</v>
       </c>
       <c r="J68" s="1">
         <v>3</v>
@@ -5472,35 +5490,35 @@
         <v>1061.1400000000001</v>
       </c>
       <c r="L68" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>-25</v>
       </c>
       <c r="M68" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>5.82</v>
       </c>
       <c r="N68" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="O68" s="1">
         <f t="shared" si="5"/>
-        <v>2.99</v>
+        <v>9.92</v>
       </c>
       <c r="P68" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="Q68" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>5.28</v>
       </c>
-      <c r="R68" s="12"/>
-      <c r="S68" s="13"/>
-      <c r="T68" s="14"/>
-      <c r="U68" s="12"/>
-      <c r="V68" s="13"/>
-      <c r="W68" s="14"/>
+      <c r="R68" s="15"/>
+      <c r="S68" s="16"/>
+      <c r="T68" s="17"/>
+      <c r="U68" s="15"/>
+      <c r="V68" s="16"/>
+      <c r="W68" s="17"/>
     </row>
     <row r="69" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A69" s="5" t="s">
@@ -5528,7 +5546,7 @@
         <v>3</v>
       </c>
       <c r="I69" s="3">
-        <v>878.71</v>
+        <v>883.61</v>
       </c>
       <c r="J69" s="1">
         <v>3</v>
@@ -5537,35 +5555,35 @@
         <v>828.14</v>
       </c>
       <c r="L69" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="M69" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>1.1599999999999999</v>
       </c>
       <c r="N69" s="1">
-        <f t="shared" ref="N69:O69" si="30">ROUND(((H69-D69)/D69)*100,2)</f>
+        <f>ROUND(((H69-D69)/D69)*100,2)</f>
         <v>0</v>
       </c>
       <c r="O69" s="1">
-        <f t="shared" si="30"/>
-        <v>2.11</v>
+        <f>ROUND(((I69-E69)/E69)*100,2)</f>
+        <v>2.68</v>
       </c>
       <c r="P69" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="Q69" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>5.12</v>
       </c>
-      <c r="R69" s="12"/>
-      <c r="S69" s="13"/>
-      <c r="T69" s="14"/>
-      <c r="U69" s="12"/>
-      <c r="V69" s="13"/>
-      <c r="W69" s="14"/>
+      <c r="R69" s="15"/>
+      <c r="S69" s="16"/>
+      <c r="T69" s="17"/>
+      <c r="U69" s="15"/>
+      <c r="V69" s="16"/>
+      <c r="W69" s="17"/>
     </row>
     <row r="70" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A70" s="6" t="s">
@@ -5576,123 +5594,104 @@
         <v>4</v>
       </c>
       <c r="C70" s="1">
-        <f t="shared" ref="C70:K70" si="31">ROUND(SUM(C62:C69)/COUNTA(C62:C69),2)</f>
+        <f t="shared" ref="C70:K70" si="27">ROUND(SUM(C62:C69)/COUNTA(C62:C69),2)</f>
         <v>1609.24</v>
       </c>
       <c r="D70" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="27"/>
         <v>4.5</v>
       </c>
       <c r="E70" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="27"/>
         <v>1134.43</v>
       </c>
       <c r="F70" s="1">
-        <f t="shared" ref="F70:H70" si="32">ROUND(SUM(F62:F69)/COUNTA(F62:F69),2)</f>
+        <f>ROUND(SUM(F62:F69)/COUNTA(F62:F69),2)</f>
         <v>3.38</v>
       </c>
       <c r="G70" s="1">
-        <f t="shared" ref="G70:I70" si="33">ROUND(SUM(G62:G69)/COUNTA(G62:G69),2)</f>
+        <f>ROUND(SUM(G62:G69)/COUNTA(G62:G69),2)</f>
         <v>1162.79</v>
       </c>
       <c r="H70" s="1">
-        <f t="shared" si="32"/>
-        <v>3.63</v>
+        <f>ROUND(SUM(H62:H69)/COUNTA(H62:H69),2)</f>
+        <v>3.38</v>
       </c>
       <c r="I70" s="1">
-        <f t="shared" si="33"/>
-        <v>1190.58</v>
+        <f>ROUND(SUM(I62:I69)/COUNTA(I62:I69),2)</f>
+        <v>1167.7</v>
       </c>
       <c r="J70" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="27"/>
         <v>3.25</v>
       </c>
       <c r="K70" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="27"/>
         <v>1119.24</v>
       </c>
-      <c r="L70" s="20"/>
-      <c r="M70" s="21"/>
-      <c r="N70" s="21"/>
-      <c r="O70" s="21"/>
-      <c r="P70" s="21"/>
-      <c r="Q70" s="22"/>
-      <c r="R70" s="15"/>
-      <c r="S70" s="16"/>
-      <c r="T70" s="17"/>
-      <c r="U70" s="15"/>
-      <c r="V70" s="16"/>
-      <c r="W70" s="17"/>
+      <c r="L70" s="9"/>
+      <c r="M70" s="10"/>
+      <c r="N70" s="10"/>
+      <c r="O70" s="10"/>
+      <c r="P70" s="10"/>
+      <c r="Q70" s="11"/>
+      <c r="R70" s="18"/>
+      <c r="S70" s="19"/>
+      <c r="T70" s="20"/>
+      <c r="U70" s="18"/>
+      <c r="V70" s="19"/>
+      <c r="W70" s="20"/>
     </row>
     <row r="71" spans="1:23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A71" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B71" s="20" t="str">
+      <c r="B71" s="9" t="str">
         <f>"總共 " &amp; SUM(R71:T71) &amp; " 筆"</f>
         <v>總共 56 筆</v>
       </c>
-      <c r="C71" s="21"/>
-      <c r="D71" s="21"/>
-      <c r="E71" s="21"/>
-      <c r="F71" s="21"/>
-      <c r="G71" s="21"/>
-      <c r="H71" s="21"/>
-      <c r="I71" s="21"/>
-      <c r="J71" s="21"/>
-      <c r="K71" s="21"/>
-      <c r="L71" s="21"/>
-      <c r="M71" s="21"/>
-      <c r="N71" s="21"/>
-      <c r="O71" s="21"/>
-      <c r="P71" s="21"/>
-      <c r="Q71" s="22"/>
+      <c r="C71" s="10"/>
+      <c r="D71" s="10"/>
+      <c r="E71" s="10"/>
+      <c r="F71" s="10"/>
+      <c r="G71" s="10"/>
+      <c r="H71" s="10"/>
+      <c r="I71" s="10"/>
+      <c r="J71" s="10"/>
+      <c r="K71" s="10"/>
+      <c r="L71" s="10"/>
+      <c r="M71" s="10"/>
+      <c r="N71" s="10"/>
+      <c r="O71" s="10"/>
+      <c r="P71" s="10"/>
+      <c r="Q71" s="11"/>
       <c r="R71" s="1">
-        <f t="shared" ref="R71:W71" si="34">R3+R14+R24+R38+R51+R61</f>
+        <f t="shared" ref="R71:W71" si="28">R3+R14+R24+R38+R51+R61</f>
         <v>25</v>
       </c>
       <c r="S71" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="28"/>
         <v>12</v>
       </c>
       <c r="T71" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="28"/>
         <v>19</v>
       </c>
       <c r="U71" s="1">
-        <f t="shared" si="34"/>
-        <v>23</v>
+        <f t="shared" si="28"/>
+        <v>28</v>
       </c>
       <c r="V71" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="28"/>
         <v>12</v>
       </c>
       <c r="W71" s="1">
-        <f t="shared" si="34"/>
-        <v>21</v>
+        <f t="shared" si="28"/>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="L13:Q13"/>
-    <mergeCell ref="R4:T13"/>
-    <mergeCell ref="R15:T23"/>
-    <mergeCell ref="B71:Q71"/>
-    <mergeCell ref="B38:Q38"/>
-    <mergeCell ref="B51:Q51"/>
-    <mergeCell ref="B61:Q61"/>
-    <mergeCell ref="B14:Q14"/>
-    <mergeCell ref="B24:Q24"/>
-    <mergeCell ref="L23:Q23"/>
-    <mergeCell ref="L70:Q70"/>
-    <mergeCell ref="R62:T70"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="H1:I1"/>
     <mergeCell ref="U52:W60"/>
     <mergeCell ref="U62:W70"/>
     <mergeCell ref="N1:O1"/>
@@ -5709,6 +5708,25 @@
     <mergeCell ref="U39:W50"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="B3:Q3"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="R4:T13"/>
+    <mergeCell ref="R15:T23"/>
+    <mergeCell ref="B71:Q71"/>
+    <mergeCell ref="B38:Q38"/>
+    <mergeCell ref="B51:Q51"/>
+    <mergeCell ref="B61:Q61"/>
+    <mergeCell ref="B14:Q14"/>
+    <mergeCell ref="B24:Q24"/>
+    <mergeCell ref="L23:Q23"/>
+    <mergeCell ref="L70:Q70"/>
+    <mergeCell ref="R62:T70"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5729,14 +5747,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.25" thickBot="1">
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="19"/>
-      <c r="D1" s="18" t="s">
+      <c r="C1" s="22"/>
+      <c r="D1" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="E1" s="19"/>
+      <c r="E1" s="22"/>
     </row>
     <row r="2" spans="1:5" ht="17.25" thickBot="1">
       <c r="A2" s="5" t="s">
@@ -5759,13 +5777,13 @@
       <c r="A3" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="9">
         <f>COUNTA(A4:A12)</f>
         <v>9</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="22"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="11"/>
     </row>
     <row r="4" spans="1:5" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A4" s="6" t="s">
@@ -5814,7 +5832,7 @@
         <v>10</v>
       </c>
       <c r="C7" s="1">
-        <v>826.37</v>
+        <v>824.78</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -5894,7 +5912,7 @@
       </c>
       <c r="C13" s="2">
         <f>ROUND(SUM(C4:C12)/$B3,2)</f>
-        <v>828.56</v>
+        <v>828.38</v>
       </c>
       <c r="D13" s="1">
         <v>10</v>
@@ -5907,12 +5925,12 @@
       <c r="A14" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B14" s="20">
+      <c r="B14" s="9">
         <v>8</v>
       </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="22"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="11"/>
     </row>
     <row r="15" spans="1:5" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A15" s="6" t="s">
@@ -5945,7 +5963,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="1">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="C17" s="1">
         <v>591.16999999999996</v>
@@ -5961,7 +5979,7 @@
         <v>3</v>
       </c>
       <c r="C18" s="1">
-        <v>593.92999999999995</v>
+        <v>612.39</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -6024,11 +6042,11 @@
       </c>
       <c r="B23" s="3">
         <f>ROUND(SUM(B15:B22)/$B14, 2)</f>
-        <v>3.05</v>
+        <v>3.01</v>
       </c>
       <c r="C23" s="3">
         <f>ROUND(SUM(C15:C22)/$B14, 2)</f>
-        <v>590.28</v>
+        <v>592.58000000000004</v>
       </c>
       <c r="D23" s="1">
         <v>3</v>
@@ -6041,22 +6059,22 @@
       <c r="A24" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B24" s="20">
+      <c r="B24" s="9">
         <v>12</v>
       </c>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="22"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="11"/>
     </row>
     <row r="25" spans="1:5" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A25" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B25" s="1">
-        <v>19.8</v>
+        <v>19</v>
       </c>
       <c r="C25" s="1">
-        <v>1653.16</v>
+        <v>1653.53</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
@@ -6066,10 +6084,10 @@
         <v>20</v>
       </c>
       <c r="B26" s="1">
-        <v>18</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="C26" s="1">
-        <v>1486.68</v>
+        <v>1497.23</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
@@ -6079,10 +6097,10 @@
         <v>21</v>
       </c>
       <c r="B27" s="1">
-        <v>13.6</v>
+        <v>13.2</v>
       </c>
       <c r="C27" s="1">
-        <v>1572.9</v>
+        <v>1322.8</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -6095,7 +6113,7 @@
         <v>10.8</v>
       </c>
       <c r="C28" s="1">
-        <v>1026</v>
+        <v>1015.76</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -6105,10 +6123,10 @@
         <v>23</v>
       </c>
       <c r="B29" s="1">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="C29" s="1">
-        <v>1688.63</v>
+        <v>1436.85</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
@@ -6118,10 +6136,10 @@
         <v>24</v>
       </c>
       <c r="B30" s="1">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="C30" s="1">
-        <v>1285.3599999999999</v>
+        <v>1324.48</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
@@ -6131,10 +6149,10 @@
         <v>25</v>
       </c>
       <c r="B31" s="1">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="C31" s="1">
-        <v>1127.3900000000001</v>
+        <v>1106.51</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
@@ -6144,10 +6162,10 @@
         <v>26</v>
       </c>
       <c r="B32" s="1">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="C32" s="1">
-        <v>1005.63</v>
+        <v>983.23</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
@@ -6160,7 +6178,7 @@
         <v>12</v>
       </c>
       <c r="C33" s="1">
-        <v>1255.48</v>
+        <v>1214.8399999999999</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
@@ -6170,10 +6188,10 @@
         <v>28</v>
       </c>
       <c r="B34" s="1">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="C34" s="1">
-        <v>1151.1199999999999</v>
+        <v>1119.33</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
@@ -6183,10 +6201,10 @@
         <v>29</v>
       </c>
       <c r="B35" s="1">
-        <v>11.1</v>
+        <v>11.3</v>
       </c>
       <c r="C35" s="1">
-        <v>1161.68</v>
+        <v>1138.82</v>
       </c>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
@@ -6196,10 +6214,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="1">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="C36" s="1">
-        <v>1035.94</v>
+        <v>1005.83</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
@@ -6208,13 +6226,13 @@
       <c r="A37" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B37" s="3">
+      <c r="B37" s="2">
         <f>ROUND(SUM(B25:B36)/$B24,2)</f>
-        <v>12.98</v>
-      </c>
-      <c r="C37" s="3">
+        <v>12.79</v>
+      </c>
+      <c r="C37" s="2">
         <f>ROUND(SUM(C25:C36)/$B24,2)</f>
-        <v>1287.5</v>
+        <v>1234.93</v>
       </c>
       <c r="D37" s="1">
         <v>12.83</v>
@@ -6227,12 +6245,12 @@
       <c r="A38" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B38" s="20">
+      <c r="B38" s="9">
         <v>11</v>
       </c>
-      <c r="C38" s="21"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="22"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="11"/>
     </row>
     <row r="39" spans="1:5" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A39" s="6" t="s">
@@ -6242,7 +6260,7 @@
         <v>4</v>
       </c>
       <c r="C39" s="1">
-        <v>1308.44</v>
+        <v>1302.83</v>
       </c>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
@@ -6252,10 +6270,10 @@
         <v>32</v>
       </c>
       <c r="B40" s="1">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="C40" s="1">
-        <v>1759.75</v>
+        <v>1406.77</v>
       </c>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
@@ -6268,7 +6286,7 @@
         <v>3</v>
       </c>
       <c r="C41" s="1">
-        <v>986.47</v>
+        <v>984.76</v>
       </c>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
@@ -6281,7 +6299,7 @@
         <v>3</v>
       </c>
       <c r="C42" s="1">
-        <v>763.8</v>
+        <v>779.27</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
@@ -6294,7 +6312,7 @@
         <v>3</v>
       </c>
       <c r="C43" s="1">
-        <v>1067.95</v>
+        <v>1071.58</v>
       </c>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
@@ -6307,7 +6325,7 @@
         <v>3</v>
       </c>
       <c r="C44" s="1">
-        <v>967.52</v>
+        <v>972.48</v>
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
@@ -6320,7 +6338,7 @@
         <v>3</v>
       </c>
       <c r="C45" s="1">
-        <v>853.49</v>
+        <v>848.77</v>
       </c>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
@@ -6330,10 +6348,10 @@
         <v>38</v>
       </c>
       <c r="B46" s="1">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="C46" s="1">
-        <v>739.55</v>
+        <v>814.22</v>
       </c>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
@@ -6346,7 +6364,7 @@
         <v>3</v>
       </c>
       <c r="C47" s="1">
-        <v>957.21</v>
+        <v>965.75</v>
       </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -6359,7 +6377,7 @@
         <v>3</v>
       </c>
       <c r="C48" s="1">
-        <v>993.95</v>
+        <v>994.83</v>
       </c>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -6372,7 +6390,7 @@
         <v>3</v>
       </c>
       <c r="C49" s="1">
-        <v>820.45</v>
+        <v>808.38</v>
       </c>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
@@ -6383,11 +6401,11 @@
       </c>
       <c r="B50" s="2">
         <f>ROUND(SUM(B39:B49)/$B38,2)</f>
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="C50" s="2">
         <f>ROUND(SUM(C39:C49)/$B38,2)</f>
-        <v>1019.87</v>
+        <v>995.42</v>
       </c>
       <c r="D50" s="1">
         <v>4.72</v>
@@ -6400,22 +6418,22 @@
       <c r="A51" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B51" s="20">
+      <c r="B51" s="9">
         <v>8</v>
       </c>
-      <c r="C51" s="21"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="22"/>
+      <c r="C51" s="10"/>
+      <c r="D51" s="10"/>
+      <c r="E51" s="11"/>
     </row>
     <row r="52" spans="1:5" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A52" s="5" t="s">
         <v>42</v>
       </c>
       <c r="B52" s="1">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="C52" s="1">
-        <v>1687.93</v>
+        <v>1649.47</v>
       </c>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -6428,7 +6446,7 @@
         <v>13</v>
       </c>
       <c r="C53" s="1">
-        <v>1507.94</v>
+        <v>1497.51</v>
       </c>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -6441,7 +6459,7 @@
         <v>11.9</v>
       </c>
       <c r="C54" s="1">
-        <v>1516.36</v>
+        <v>1316.11</v>
       </c>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
@@ -6451,10 +6469,10 @@
         <v>45</v>
       </c>
       <c r="B55" s="1">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="C55" s="1">
-        <v>1336.1</v>
+        <v>1169.0999999999999</v>
       </c>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
@@ -6464,10 +6482,10 @@
         <v>46</v>
       </c>
       <c r="B56" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C56" s="1">
-        <v>1902.43</v>
+        <v>1595.23</v>
       </c>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
@@ -6477,10 +6495,10 @@
         <v>47</v>
       </c>
       <c r="B57" s="1">
-        <v>12.9</v>
+        <v>12.6</v>
       </c>
       <c r="C57" s="1">
-        <v>1663.23</v>
+        <v>1424.21</v>
       </c>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
@@ -6490,10 +6508,10 @@
         <v>48</v>
       </c>
       <c r="B58" s="1">
-        <v>11.8</v>
+        <v>11</v>
       </c>
       <c r="C58" s="1">
-        <v>1529.97</v>
+        <v>1262.21</v>
       </c>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
@@ -6506,7 +6524,7 @@
         <v>11</v>
       </c>
       <c r="C59" s="1">
-        <v>1145.69</v>
+        <v>1140.1600000000001</v>
       </c>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
@@ -6517,11 +6535,11 @@
       </c>
       <c r="B60" s="3">
         <f>ROUND(SUM(B52:B59)/$B51,2)</f>
-        <v>12.7</v>
+        <v>12.44</v>
       </c>
       <c r="C60" s="3">
         <f>ROUND(SUM(C52:C59)/$B51,2)</f>
-        <v>1536.21</v>
+        <v>1381.75</v>
       </c>
       <c r="D60" s="1">
         <v>12.26</v>
@@ -6534,22 +6552,22 @@
       <c r="A61" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B61" s="20">
+      <c r="B61" s="9">
         <v>8</v>
       </c>
-      <c r="C61" s="21"/>
-      <c r="D61" s="21"/>
-      <c r="E61" s="22"/>
+      <c r="C61" s="10"/>
+      <c r="D61" s="10"/>
+      <c r="E61" s="11"/>
     </row>
     <row r="62" spans="1:5" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A62" s="5" t="s">
         <v>50</v>
       </c>
       <c r="B62" s="1">
-        <v>4</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C62" s="1">
-        <v>1465.57</v>
+        <v>1495.19</v>
       </c>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
@@ -6562,7 +6580,7 @@
         <v>4</v>
       </c>
       <c r="C63" s="1">
-        <v>1251.74</v>
+        <v>1209.52</v>
       </c>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
@@ -6575,7 +6593,7 @@
         <v>3</v>
       </c>
       <c r="C64" s="1">
-        <v>1134.53</v>
+        <v>1136.33</v>
       </c>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
@@ -6588,7 +6606,7 @@
         <v>3</v>
       </c>
       <c r="C65" s="1">
-        <v>817.78</v>
+        <v>823.83</v>
       </c>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
@@ -6601,7 +6619,7 @@
         <v>4</v>
       </c>
       <c r="C66" s="1">
-        <v>1379.81</v>
+        <v>1374.6</v>
       </c>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
@@ -6611,10 +6629,10 @@
         <v>55</v>
       </c>
       <c r="B67" s="1">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="C67" s="1">
-        <v>1265.18</v>
+        <v>1258.08</v>
       </c>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
@@ -6624,10 +6642,10 @@
         <v>56</v>
       </c>
       <c r="B68" s="1">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="C68" s="1">
-        <v>1117.1400000000001</v>
+        <v>1160.47</v>
       </c>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
@@ -6640,7 +6658,7 @@
         <v>3</v>
       </c>
       <c r="C69" s="1">
-        <v>870.55</v>
+        <v>883.61</v>
       </c>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
@@ -6651,11 +6669,11 @@
       </c>
       <c r="B70" s="2">
         <f>ROUND(SUM(B62:B69)/$B61,2)</f>
-        <v>3.38</v>
+        <v>3.46</v>
       </c>
       <c r="C70" s="2">
         <f>ROUND(SUM(C62:C69)/$B61,2)</f>
-        <v>1162.79</v>
+        <v>1167.7</v>
       </c>
       <c r="D70" s="1">
         <v>5</v>

--- a/docs/Baseline比較結果.xlsx
+++ b/docs/Baseline比較結果.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff0\OneDrive\桌面\115_NTUT_Thesis\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4F020FC-B152-4C7C-B817-480E83A24099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52700AC9-6C93-4A60-8BFF-9731B507DC0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{9DD6E340-DFE3-4B7E-9025-343BD89F474F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{9DD6E340-DFE3-4B7E-9025-343BD89F474F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -857,15 +857,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -899,10 +890,19 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1262,48 +1262,48 @@
   <sheetData>
     <row r="1" spans="1:26" ht="17.25" customHeight="1" thickBot="1">
       <c r="A1" s="4"/>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="22"/>
-      <c r="D1" s="21" t="s">
+      <c r="C1" s="19"/>
+      <c r="D1" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="22"/>
-      <c r="F1" s="23" t="s">
+      <c r="E1" s="19"/>
+      <c r="F1" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="22"/>
-      <c r="H1" s="21" t="s">
+      <c r="G1" s="19"/>
+      <c r="H1" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="I1" s="22"/>
-      <c r="J1" s="21" t="s">
+      <c r="I1" s="19"/>
+      <c r="J1" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="K1" s="22"/>
-      <c r="L1" s="21" t="s">
+      <c r="K1" s="19"/>
+      <c r="L1" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="M1" s="22"/>
-      <c r="N1" s="21" t="s">
+      <c r="M1" s="19"/>
+      <c r="N1" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="O1" s="22"/>
-      <c r="P1" s="21" t="s">
+      <c r="O1" s="19"/>
+      <c r="P1" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="21" t="s">
+      <c r="Q1" s="19"/>
+      <c r="R1" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="S1" s="24"/>
-      <c r="T1" s="24"/>
-      <c r="U1" s="21" t="s">
+      <c r="S1" s="23"/>
+      <c r="T1" s="23"/>
+      <c r="U1" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="V1" s="24"/>
-      <c r="W1" s="24"/>
+      <c r="V1" s="23"/>
+      <c r="W1" s="23"/>
     </row>
     <row r="2" spans="1:26" ht="17.25" thickBot="1">
       <c r="A2" s="5" t="s">
@@ -1380,25 +1380,25 @@
       <c r="A3" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="9" t="str">
+      <c r="B3" s="20" t="str">
         <f>COUNTA(A4:A12) &amp; " 筆"</f>
         <v>9 筆</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="11"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="21"/>
+      <c r="N3" s="21"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="21"/>
+      <c r="Q3" s="22"/>
       <c r="R3" s="1" cm="1">
         <f t="array" ref="R3">CountColor($F4:$F12,$Y$4)</f>
         <v>4</v>
@@ -1482,12 +1482,12 @@
         <f t="shared" ref="Q4:Q12" si="3">ROUND(((G4-K4)/K4)*100,2)</f>
         <v>0</v>
       </c>
-      <c r="R4" s="12"/>
-      <c r="S4" s="13"/>
-      <c r="T4" s="14"/>
-      <c r="U4" s="12"/>
-      <c r="V4" s="13"/>
-      <c r="W4" s="14"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="10"/>
+      <c r="T4" s="11"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="10"/>
+      <c r="W4" s="11"/>
       <c r="Y4" s="2"/>
       <c r="Z4" t="s">
         <v>83</v>
@@ -1551,12 +1551,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R5" s="15"/>
-      <c r="S5" s="16"/>
-      <c r="T5" s="17"/>
-      <c r="U5" s="15"/>
-      <c r="V5" s="16"/>
-      <c r="W5" s="17"/>
+      <c r="R5" s="12"/>
+      <c r="S5" s="13"/>
+      <c r="T5" s="14"/>
+      <c r="U5" s="12"/>
+      <c r="V5" s="13"/>
+      <c r="W5" s="14"/>
       <c r="Y5" s="7"/>
       <c r="Z5" t="s">
         <v>85</v>
@@ -1620,12 +1620,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R6" s="15"/>
-      <c r="S6" s="16"/>
-      <c r="T6" s="17"/>
-      <c r="U6" s="15"/>
-      <c r="V6" s="16"/>
-      <c r="W6" s="17"/>
+      <c r="R6" s="12"/>
+      <c r="S6" s="13"/>
+      <c r="T6" s="14"/>
+      <c r="U6" s="12"/>
+      <c r="V6" s="13"/>
+      <c r="W6" s="14"/>
       <c r="Y6" s="3"/>
       <c r="Z6" t="s">
         <v>84</v>
@@ -1689,12 +1689,12 @@
         <f t="shared" si="3"/>
         <v>0.19</v>
       </c>
-      <c r="R7" s="15"/>
-      <c r="S7" s="16"/>
-      <c r="T7" s="17"/>
-      <c r="U7" s="15"/>
-      <c r="V7" s="16"/>
-      <c r="W7" s="17"/>
+      <c r="R7" s="12"/>
+      <c r="S7" s="13"/>
+      <c r="T7" s="14"/>
+      <c r="U7" s="12"/>
+      <c r="V7" s="13"/>
+      <c r="W7" s="14"/>
     </row>
     <row r="8" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A8" s="6" t="s">
@@ -1754,12 +1754,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R8" s="15"/>
-      <c r="S8" s="16"/>
-      <c r="T8" s="17"/>
-      <c r="U8" s="15"/>
-      <c r="V8" s="16"/>
-      <c r="W8" s="17"/>
+      <c r="R8" s="12"/>
+      <c r="S8" s="13"/>
+      <c r="T8" s="14"/>
+      <c r="U8" s="12"/>
+      <c r="V8" s="13"/>
+      <c r="W8" s="14"/>
     </row>
     <row r="9" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A9" s="6" t="s">
@@ -1819,12 +1819,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R9" s="15"/>
-      <c r="S9" s="16"/>
-      <c r="T9" s="17"/>
-      <c r="U9" s="15"/>
-      <c r="V9" s="16"/>
-      <c r="W9" s="17"/>
+      <c r="R9" s="12"/>
+      <c r="S9" s="13"/>
+      <c r="T9" s="14"/>
+      <c r="U9" s="12"/>
+      <c r="V9" s="13"/>
+      <c r="W9" s="14"/>
     </row>
     <row r="10" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A10" s="6" t="s">
@@ -1884,12 +1884,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R10" s="15"/>
-      <c r="S10" s="16"/>
-      <c r="T10" s="17"/>
-      <c r="U10" s="15"/>
-      <c r="V10" s="16"/>
-      <c r="W10" s="17"/>
+      <c r="R10" s="12"/>
+      <c r="S10" s="13"/>
+      <c r="T10" s="14"/>
+      <c r="U10" s="12"/>
+      <c r="V10" s="13"/>
+      <c r="W10" s="14"/>
     </row>
     <row r="11" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A11" s="6" t="s">
@@ -1949,12 +1949,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R11" s="15"/>
-      <c r="S11" s="16"/>
-      <c r="T11" s="17"/>
-      <c r="U11" s="15"/>
-      <c r="V11" s="16"/>
-      <c r="W11" s="17"/>
+      <c r="R11" s="12"/>
+      <c r="S11" s="13"/>
+      <c r="T11" s="14"/>
+      <c r="U11" s="12"/>
+      <c r="V11" s="13"/>
+      <c r="W11" s="14"/>
     </row>
     <row r="12" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A12" s="6" t="s">
@@ -2014,12 +2014,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R12" s="15"/>
-      <c r="S12" s="16"/>
-      <c r="T12" s="17"/>
-      <c r="U12" s="15"/>
-      <c r="V12" s="16"/>
-      <c r="W12" s="17"/>
+      <c r="R12" s="12"/>
+      <c r="S12" s="13"/>
+      <c r="T12" s="14"/>
+      <c r="U12" s="12"/>
+      <c r="V12" s="13"/>
+      <c r="W12" s="14"/>
     </row>
     <row r="13" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A13" s="6" t="s">
@@ -2063,42 +2063,42 @@
         <f t="shared" si="6"/>
         <v>828.38000000000022</v>
       </c>
-      <c r="L13" s="9"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="10"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="18"/>
-      <c r="S13" s="19"/>
-      <c r="T13" s="20"/>
-      <c r="U13" s="18"/>
-      <c r="V13" s="19"/>
-      <c r="W13" s="20"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="21"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="22"/>
+      <c r="R13" s="15"/>
+      <c r="S13" s="16"/>
+      <c r="T13" s="17"/>
+      <c r="U13" s="15"/>
+      <c r="V13" s="16"/>
+      <c r="W13" s="17"/>
     </row>
     <row r="14" spans="1:26" ht="17.25" customHeight="1" thickBot="1">
       <c r="A14" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B14" s="9" t="str">
+      <c r="B14" s="20" t="str">
         <f>COUNTA(A15:A22) &amp; " 筆"</f>
         <v>8 筆</v>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="10"/>
-      <c r="Q14" s="11"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="22"/>
       <c r="R14" s="1" cm="1">
         <f t="array" ref="R14">CountColor($F15:$F22,$Y$4)</f>
         <v>1</v>
@@ -2182,12 +2182,12 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="R15" s="12"/>
-      <c r="S15" s="13"/>
-      <c r="T15" s="14"/>
-      <c r="U15" s="12"/>
-      <c r="V15" s="13"/>
-      <c r="W15" s="14"/>
+      <c r="R15" s="9"/>
+      <c r="S15" s="10"/>
+      <c r="T15" s="11"/>
+      <c r="U15" s="9"/>
+      <c r="V15" s="10"/>
+      <c r="W15" s="11"/>
     </row>
     <row r="16" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A16" s="6" t="s">
@@ -2247,12 +2247,12 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="R16" s="15"/>
-      <c r="S16" s="16"/>
-      <c r="T16" s="17"/>
-      <c r="U16" s="15"/>
-      <c r="V16" s="16"/>
-      <c r="W16" s="17"/>
+      <c r="R16" s="12"/>
+      <c r="S16" s="13"/>
+      <c r="T16" s="14"/>
+      <c r="U16" s="12"/>
+      <c r="V16" s="13"/>
+      <c r="W16" s="14"/>
     </row>
     <row r="17" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A17" s="6" t="s">
@@ -2312,12 +2312,12 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="R17" s="15"/>
-      <c r="S17" s="16"/>
-      <c r="T17" s="17"/>
-      <c r="U17" s="15"/>
-      <c r="V17" s="16"/>
-      <c r="W17" s="17"/>
+      <c r="R17" s="12"/>
+      <c r="S17" s="13"/>
+      <c r="T17" s="14"/>
+      <c r="U17" s="12"/>
+      <c r="V17" s="13"/>
+      <c r="W17" s="14"/>
     </row>
     <row r="18" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A18" s="6" t="s">
@@ -2377,12 +2377,12 @@
         <f t="shared" si="8"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="R18" s="15"/>
-      <c r="S18" s="16"/>
-      <c r="T18" s="17"/>
-      <c r="U18" s="15"/>
-      <c r="V18" s="16"/>
-      <c r="W18" s="17"/>
+      <c r="R18" s="12"/>
+      <c r="S18" s="13"/>
+      <c r="T18" s="14"/>
+      <c r="U18" s="12"/>
+      <c r="V18" s="13"/>
+      <c r="W18" s="14"/>
     </row>
     <row r="19" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A19" s="6" t="s">
@@ -2442,12 +2442,12 @@
         <f t="shared" si="8"/>
         <v>0.01</v>
       </c>
-      <c r="R19" s="15"/>
-      <c r="S19" s="16"/>
-      <c r="T19" s="17"/>
-      <c r="U19" s="15"/>
-      <c r="V19" s="16"/>
-      <c r="W19" s="17"/>
+      <c r="R19" s="12"/>
+      <c r="S19" s="13"/>
+      <c r="T19" s="14"/>
+      <c r="U19" s="12"/>
+      <c r="V19" s="13"/>
+      <c r="W19" s="14"/>
     </row>
     <row r="20" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A20" s="6" t="s">
@@ -2507,12 +2507,12 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="R20" s="15"/>
-      <c r="S20" s="16"/>
-      <c r="T20" s="17"/>
-      <c r="U20" s="15"/>
-      <c r="V20" s="16"/>
-      <c r="W20" s="17"/>
+      <c r="R20" s="12"/>
+      <c r="S20" s="13"/>
+      <c r="T20" s="14"/>
+      <c r="U20" s="12"/>
+      <c r="V20" s="13"/>
+      <c r="W20" s="14"/>
     </row>
     <row r="21" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A21" s="6" t="s">
@@ -2572,12 +2572,12 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="R21" s="15"/>
-      <c r="S21" s="16"/>
-      <c r="T21" s="17"/>
-      <c r="U21" s="15"/>
-      <c r="V21" s="16"/>
-      <c r="W21" s="17"/>
+      <c r="R21" s="12"/>
+      <c r="S21" s="13"/>
+      <c r="T21" s="14"/>
+      <c r="U21" s="12"/>
+      <c r="V21" s="13"/>
+      <c r="W21" s="14"/>
     </row>
     <row r="22" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A22" s="6" t="s">
@@ -2637,12 +2637,12 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="R22" s="15"/>
-      <c r="S22" s="16"/>
-      <c r="T22" s="17"/>
-      <c r="U22" s="15"/>
-      <c r="V22" s="16"/>
-      <c r="W22" s="17"/>
+      <c r="R22" s="12"/>
+      <c r="S22" s="13"/>
+      <c r="T22" s="14"/>
+      <c r="U22" s="12"/>
+      <c r="V22" s="13"/>
+      <c r="W22" s="14"/>
     </row>
     <row r="23" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A23" s="6" t="s">
@@ -2686,42 +2686,42 @@
         <f t="shared" si="9"/>
         <v>589.86</v>
       </c>
-      <c r="L23" s="9"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
-      <c r="O23" s="10"/>
-      <c r="P23" s="10"/>
-      <c r="Q23" s="11"/>
-      <c r="R23" s="18"/>
-      <c r="S23" s="19"/>
-      <c r="T23" s="20"/>
-      <c r="U23" s="18"/>
-      <c r="V23" s="19"/>
-      <c r="W23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="21"/>
+      <c r="N23" s="21"/>
+      <c r="O23" s="21"/>
+      <c r="P23" s="21"/>
+      <c r="Q23" s="22"/>
+      <c r="R23" s="15"/>
+      <c r="S23" s="16"/>
+      <c r="T23" s="17"/>
+      <c r="U23" s="15"/>
+      <c r="V23" s="16"/>
+      <c r="W23" s="17"/>
     </row>
     <row r="24" spans="1:23" ht="17.25" customHeight="1" thickBot="1">
       <c r="A24" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B24" s="9" t="str">
+      <c r="B24" s="20" t="str">
         <f>COUNTA(A25:A36) &amp; " 筆"</f>
         <v>12 筆</v>
       </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="10"/>
-      <c r="N24" s="10"/>
-      <c r="O24" s="10"/>
-      <c r="P24" s="10"/>
-      <c r="Q24" s="11"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="21"/>
+      <c r="L24" s="21"/>
+      <c r="M24" s="21"/>
+      <c r="N24" s="21"/>
+      <c r="O24" s="21"/>
+      <c r="P24" s="21"/>
+      <c r="Q24" s="22"/>
       <c r="R24" s="1" cm="1">
         <f t="array" ref="R24">CountColor($F25:$F36,$Y$4)</f>
         <v>2</v>
@@ -2802,12 +2802,12 @@
         <f t="shared" ref="Q25:Q36" si="13">ROUND(((G25-K25)/K25)*100,2)</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="R25" s="12"/>
-      <c r="S25" s="13"/>
-      <c r="T25" s="14"/>
-      <c r="U25" s="12"/>
-      <c r="V25" s="13"/>
-      <c r="W25" s="14"/>
+      <c r="R25" s="9"/>
+      <c r="S25" s="10"/>
+      <c r="T25" s="11"/>
+      <c r="U25" s="9"/>
+      <c r="V25" s="10"/>
+      <c r="W25" s="11"/>
     </row>
     <row r="26" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A26" s="6" t="s">
@@ -2867,12 +2867,12 @@
         <f t="shared" si="13"/>
         <v>0.04</v>
       </c>
-      <c r="R26" s="15"/>
-      <c r="S26" s="16"/>
-      <c r="T26" s="17"/>
-      <c r="U26" s="15"/>
-      <c r="V26" s="16"/>
-      <c r="W26" s="17"/>
+      <c r="R26" s="12"/>
+      <c r="S26" s="13"/>
+      <c r="T26" s="14"/>
+      <c r="U26" s="12"/>
+      <c r="V26" s="13"/>
+      <c r="W26" s="14"/>
     </row>
     <row r="27" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A27" s="6" t="s">
@@ -2932,12 +2932,12 @@
         <f t="shared" si="13"/>
         <v>21.68</v>
       </c>
-      <c r="R27" s="15"/>
-      <c r="S27" s="16"/>
-      <c r="T27" s="17"/>
-      <c r="U27" s="15"/>
-      <c r="V27" s="16"/>
-      <c r="W27" s="17"/>
+      <c r="R27" s="12"/>
+      <c r="S27" s="13"/>
+      <c r="T27" s="14"/>
+      <c r="U27" s="12"/>
+      <c r="V27" s="13"/>
+      <c r="W27" s="14"/>
     </row>
     <row r="28" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A28" s="6" t="s">
@@ -2997,12 +2997,12 @@
         <f t="shared" si="13"/>
         <v>1.86</v>
       </c>
-      <c r="R28" s="15"/>
-      <c r="S28" s="16"/>
-      <c r="T28" s="17"/>
-      <c r="U28" s="15"/>
-      <c r="V28" s="16"/>
-      <c r="W28" s="17"/>
+      <c r="R28" s="12"/>
+      <c r="S28" s="13"/>
+      <c r="T28" s="14"/>
+      <c r="U28" s="12"/>
+      <c r="V28" s="13"/>
+      <c r="W28" s="14"/>
     </row>
     <row r="29" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A29" s="6" t="s">
@@ -3062,12 +3062,12 @@
         <f t="shared" si="13"/>
         <v>22.62</v>
       </c>
-      <c r="R29" s="15"/>
-      <c r="S29" s="16"/>
-      <c r="T29" s="17"/>
-      <c r="U29" s="15"/>
-      <c r="V29" s="16"/>
-      <c r="W29" s="17"/>
+      <c r="R29" s="12"/>
+      <c r="S29" s="13"/>
+      <c r="T29" s="14"/>
+      <c r="U29" s="12"/>
+      <c r="V29" s="13"/>
+      <c r="W29" s="14"/>
     </row>
     <row r="30" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A30" s="6" t="s">
@@ -3127,12 +3127,12 @@
         <f t="shared" si="13"/>
         <v>2.66</v>
       </c>
-      <c r="R30" s="15"/>
-      <c r="S30" s="16"/>
-      <c r="T30" s="17"/>
-      <c r="U30" s="15"/>
-      <c r="V30" s="16"/>
-      <c r="W30" s="17"/>
+      <c r="R30" s="12"/>
+      <c r="S30" s="13"/>
+      <c r="T30" s="14"/>
+      <c r="U30" s="12"/>
+      <c r="V30" s="13"/>
+      <c r="W30" s="14"/>
     </row>
     <row r="31" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A31" s="6" t="s">
@@ -3192,12 +3192,12 @@
         <f t="shared" si="13"/>
         <v>2.06</v>
       </c>
-      <c r="R31" s="15"/>
-      <c r="S31" s="16"/>
-      <c r="T31" s="17"/>
-      <c r="U31" s="15"/>
-      <c r="V31" s="16"/>
-      <c r="W31" s="17"/>
+      <c r="R31" s="12"/>
+      <c r="S31" s="13"/>
+      <c r="T31" s="14"/>
+      <c r="U31" s="12"/>
+      <c r="V31" s="13"/>
+      <c r="W31" s="14"/>
     </row>
     <row r="32" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A32" s="6" t="s">
@@ -3257,12 +3257,12 @@
         <f t="shared" si="13"/>
         <v>4.66</v>
       </c>
-      <c r="R32" s="15"/>
-      <c r="S32" s="16"/>
-      <c r="T32" s="17"/>
-      <c r="U32" s="15"/>
-      <c r="V32" s="16"/>
-      <c r="W32" s="17"/>
+      <c r="R32" s="12"/>
+      <c r="S32" s="13"/>
+      <c r="T32" s="14"/>
+      <c r="U32" s="12"/>
+      <c r="V32" s="13"/>
+      <c r="W32" s="14"/>
     </row>
     <row r="33" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A33" s="6" t="s">
@@ -3322,12 +3322,12 @@
         <f t="shared" si="13"/>
         <v>5.08</v>
       </c>
-      <c r="R33" s="15"/>
-      <c r="S33" s="16"/>
-      <c r="T33" s="17"/>
-      <c r="U33" s="15"/>
-      <c r="V33" s="16"/>
-      <c r="W33" s="17"/>
+      <c r="R33" s="12"/>
+      <c r="S33" s="13"/>
+      <c r="T33" s="14"/>
+      <c r="U33" s="12"/>
+      <c r="V33" s="13"/>
+      <c r="W33" s="14"/>
     </row>
     <row r="34" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A34" s="6" t="s">
@@ -3387,12 +3387,12 @@
         <f t="shared" si="13"/>
         <v>2.89</v>
       </c>
-      <c r="R34" s="15"/>
-      <c r="S34" s="16"/>
-      <c r="T34" s="17"/>
-      <c r="U34" s="15"/>
-      <c r="V34" s="16"/>
-      <c r="W34" s="17"/>
+      <c r="R34" s="12"/>
+      <c r="S34" s="13"/>
+      <c r="T34" s="14"/>
+      <c r="U34" s="12"/>
+      <c r="V34" s="13"/>
+      <c r="W34" s="14"/>
     </row>
     <row r="35" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A35" s="6" t="s">
@@ -3452,12 +3452,12 @@
         <f t="shared" si="13"/>
         <v>5.92</v>
       </c>
-      <c r="R35" s="15"/>
-      <c r="S35" s="16"/>
-      <c r="T35" s="17"/>
-      <c r="U35" s="15"/>
-      <c r="V35" s="16"/>
-      <c r="W35" s="17"/>
+      <c r="R35" s="12"/>
+      <c r="S35" s="13"/>
+      <c r="T35" s="14"/>
+      <c r="U35" s="12"/>
+      <c r="V35" s="13"/>
+      <c r="W35" s="14"/>
     </row>
     <row r="36" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A36" s="6" t="s">
@@ -3517,12 +3517,12 @@
         <f t="shared" si="13"/>
         <v>5.48</v>
       </c>
-      <c r="R36" s="15"/>
-      <c r="S36" s="16"/>
-      <c r="T36" s="17"/>
-      <c r="U36" s="15"/>
-      <c r="V36" s="16"/>
-      <c r="W36" s="17"/>
+      <c r="R36" s="12"/>
+      <c r="S36" s="13"/>
+      <c r="T36" s="14"/>
+      <c r="U36" s="12"/>
+      <c r="V36" s="13"/>
+      <c r="W36" s="14"/>
     </row>
     <row r="37" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A37" s="6" t="s">
@@ -3568,42 +3568,42 @@
         <f t="shared" si="14"/>
         <v>1210.3399999999999</v>
       </c>
-      <c r="L37" s="9"/>
-      <c r="M37" s="10"/>
-      <c r="N37" s="10"/>
-      <c r="O37" s="10"/>
-      <c r="P37" s="10"/>
-      <c r="Q37" s="11"/>
-      <c r="R37" s="18"/>
-      <c r="S37" s="19"/>
-      <c r="T37" s="20"/>
-      <c r="U37" s="18"/>
-      <c r="V37" s="19"/>
-      <c r="W37" s="20"/>
+      <c r="L37" s="20"/>
+      <c r="M37" s="21"/>
+      <c r="N37" s="21"/>
+      <c r="O37" s="21"/>
+      <c r="P37" s="21"/>
+      <c r="Q37" s="22"/>
+      <c r="R37" s="15"/>
+      <c r="S37" s="16"/>
+      <c r="T37" s="17"/>
+      <c r="U37" s="15"/>
+      <c r="V37" s="16"/>
+      <c r="W37" s="17"/>
     </row>
     <row r="38" spans="1:23" ht="18" customHeight="1" thickBot="1">
       <c r="A38" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B38" s="9" t="str">
+      <c r="B38" s="20" t="str">
         <f>COUNTA(A39:A49) &amp; " 筆"</f>
         <v>11 筆</v>
       </c>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="10"/>
-      <c r="K38" s="10"/>
-      <c r="L38" s="10"/>
-      <c r="M38" s="10"/>
-      <c r="N38" s="10"/>
-      <c r="O38" s="10"/>
-      <c r="P38" s="10"/>
-      <c r="Q38" s="11"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
+      <c r="I38" s="21"/>
+      <c r="J38" s="21"/>
+      <c r="K38" s="21"/>
+      <c r="L38" s="21"/>
+      <c r="M38" s="21"/>
+      <c r="N38" s="21"/>
+      <c r="O38" s="21"/>
+      <c r="P38" s="21"/>
+      <c r="Q38" s="22"/>
       <c r="R38" s="1" cm="1">
         <f t="array" ref="R38">CountColor($F39:$F49,$Y$4)</f>
         <v>9</v>
@@ -3684,12 +3684,12 @@
         <f t="shared" ref="Q39:Q49" si="18">ROUND(((G39-K39)/K39)*100,2)</f>
         <v>4.4800000000000004</v>
       </c>
-      <c r="R39" s="12"/>
-      <c r="S39" s="13"/>
-      <c r="T39" s="14"/>
-      <c r="U39" s="12"/>
-      <c r="V39" s="13"/>
-      <c r="W39" s="14"/>
+      <c r="R39" s="9"/>
+      <c r="S39" s="10"/>
+      <c r="T39" s="11"/>
+      <c r="U39" s="9"/>
+      <c r="V39" s="10"/>
+      <c r="W39" s="11"/>
     </row>
     <row r="40" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A40" s="6" t="s">
@@ -3749,12 +3749,12 @@
         <f t="shared" si="18"/>
         <v>47.67</v>
       </c>
-      <c r="R40" s="15"/>
-      <c r="S40" s="16"/>
-      <c r="T40" s="17"/>
-      <c r="U40" s="15"/>
-      <c r="V40" s="16"/>
-      <c r="W40" s="17"/>
+      <c r="R40" s="12"/>
+      <c r="S40" s="13"/>
+      <c r="T40" s="14"/>
+      <c r="U40" s="12"/>
+      <c r="V40" s="13"/>
+      <c r="W40" s="14"/>
     </row>
     <row r="41" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A41" s="6" t="s">
@@ -3814,12 +3814,12 @@
         <f t="shared" si="18"/>
         <v>5</v>
       </c>
-      <c r="R41" s="15"/>
-      <c r="S41" s="16"/>
-      <c r="T41" s="17"/>
-      <c r="U41" s="15"/>
-      <c r="V41" s="16"/>
-      <c r="W41" s="17"/>
+      <c r="R41" s="12"/>
+      <c r="S41" s="13"/>
+      <c r="T41" s="14"/>
+      <c r="U41" s="12"/>
+      <c r="V41" s="13"/>
+      <c r="W41" s="14"/>
     </row>
     <row r="42" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A42" s="6" t="s">
@@ -3879,12 +3879,12 @@
         <f t="shared" si="18"/>
         <v>-7.48</v>
       </c>
-      <c r="R42" s="15"/>
-      <c r="S42" s="16"/>
-      <c r="T42" s="17"/>
-      <c r="U42" s="15"/>
-      <c r="V42" s="16"/>
-      <c r="W42" s="17"/>
+      <c r="R42" s="12"/>
+      <c r="S42" s="13"/>
+      <c r="T42" s="14"/>
+      <c r="U42" s="12"/>
+      <c r="V42" s="13"/>
+      <c r="W42" s="14"/>
     </row>
     <row r="43" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A43" s="6" t="s">
@@ -3944,12 +3944,12 @@
         <f t="shared" si="18"/>
         <v>7.39</v>
       </c>
-      <c r="R43" s="15"/>
-      <c r="S43" s="16"/>
-      <c r="T43" s="17"/>
-      <c r="U43" s="15"/>
-      <c r="V43" s="16"/>
-      <c r="W43" s="17"/>
+      <c r="R43" s="12"/>
+      <c r="S43" s="13"/>
+      <c r="T43" s="14"/>
+      <c r="U43" s="12"/>
+      <c r="V43" s="13"/>
+      <c r="W43" s="14"/>
     </row>
     <row r="44" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A44" s="6" t="s">
@@ -4009,12 +4009,12 @@
         <f t="shared" si="18"/>
         <v>6.77</v>
       </c>
-      <c r="R44" s="15"/>
-      <c r="S44" s="16"/>
-      <c r="T44" s="17"/>
-      <c r="U44" s="15"/>
-      <c r="V44" s="16"/>
-      <c r="W44" s="17"/>
+      <c r="R44" s="12"/>
+      <c r="S44" s="13"/>
+      <c r="T44" s="14"/>
+      <c r="U44" s="12"/>
+      <c r="V44" s="13"/>
+      <c r="W44" s="14"/>
     </row>
     <row r="45" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A45" s="6" t="s">
@@ -4074,12 +4074,12 @@
         <f t="shared" si="18"/>
         <v>-4.17</v>
       </c>
-      <c r="R45" s="15"/>
-      <c r="S45" s="16"/>
-      <c r="T45" s="17"/>
-      <c r="U45" s="15"/>
-      <c r="V45" s="16"/>
-      <c r="W45" s="17"/>
+      <c r="R45" s="12"/>
+      <c r="S45" s="13"/>
+      <c r="T45" s="14"/>
+      <c r="U45" s="12"/>
+      <c r="V45" s="13"/>
+      <c r="W45" s="14"/>
     </row>
     <row r="46" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A46" s="6" t="s">
@@ -4139,12 +4139,12 @@
         <f t="shared" si="18"/>
         <v>1.75</v>
       </c>
-      <c r="R46" s="15"/>
-      <c r="S46" s="16"/>
-      <c r="T46" s="17"/>
-      <c r="U46" s="15"/>
-      <c r="V46" s="16"/>
-      <c r="W46" s="17"/>
+      <c r="R46" s="12"/>
+      <c r="S46" s="13"/>
+      <c r="T46" s="14"/>
+      <c r="U46" s="12"/>
+      <c r="V46" s="13"/>
+      <c r="W46" s="14"/>
     </row>
     <row r="47" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A47" s="6" t="s">
@@ -4204,12 +4204,12 @@
         <f t="shared" si="18"/>
         <v>5.29</v>
       </c>
-      <c r="R47" s="15"/>
-      <c r="S47" s="16"/>
-      <c r="T47" s="17"/>
-      <c r="U47" s="15"/>
-      <c r="V47" s="16"/>
-      <c r="W47" s="17"/>
+      <c r="R47" s="12"/>
+      <c r="S47" s="13"/>
+      <c r="T47" s="14"/>
+      <c r="U47" s="12"/>
+      <c r="V47" s="13"/>
+      <c r="W47" s="14"/>
     </row>
     <row r="48" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A48" s="6" t="s">
@@ -4269,12 +4269,12 @@
         <f t="shared" si="18"/>
         <v>5.81</v>
       </c>
-      <c r="R48" s="15"/>
-      <c r="S48" s="16"/>
-      <c r="T48" s="17"/>
-      <c r="U48" s="15"/>
-      <c r="V48" s="16"/>
-      <c r="W48" s="17"/>
+      <c r="R48" s="12"/>
+      <c r="S48" s="13"/>
+      <c r="T48" s="14"/>
+      <c r="U48" s="12"/>
+      <c r="V48" s="13"/>
+      <c r="W48" s="14"/>
     </row>
     <row r="49" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A49" s="6" t="s">
@@ -4334,12 +4334,12 @@
         <f t="shared" si="18"/>
         <v>-7.37</v>
       </c>
-      <c r="R49" s="15"/>
-      <c r="S49" s="16"/>
-      <c r="T49" s="17"/>
-      <c r="U49" s="15"/>
-      <c r="V49" s="16"/>
-      <c r="W49" s="17"/>
+      <c r="R49" s="12"/>
+      <c r="S49" s="13"/>
+      <c r="T49" s="14"/>
+      <c r="U49" s="12"/>
+      <c r="V49" s="13"/>
+      <c r="W49" s="14"/>
     </row>
     <row r="50" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A50" s="6" t="s">
@@ -4385,42 +4385,42 @@
         <f t="shared" si="19"/>
         <v>951.03</v>
       </c>
-      <c r="L50" s="9"/>
-      <c r="M50" s="10"/>
-      <c r="N50" s="10"/>
-      <c r="O50" s="10"/>
-      <c r="P50" s="10"/>
-      <c r="Q50" s="11"/>
-      <c r="R50" s="18"/>
-      <c r="S50" s="19"/>
-      <c r="T50" s="20"/>
-      <c r="U50" s="18"/>
-      <c r="V50" s="19"/>
-      <c r="W50" s="20"/>
+      <c r="L50" s="20"/>
+      <c r="M50" s="21"/>
+      <c r="N50" s="21"/>
+      <c r="O50" s="21"/>
+      <c r="P50" s="21"/>
+      <c r="Q50" s="22"/>
+      <c r="R50" s="15"/>
+      <c r="S50" s="16"/>
+      <c r="T50" s="17"/>
+      <c r="U50" s="15"/>
+      <c r="V50" s="16"/>
+      <c r="W50" s="17"/>
     </row>
     <row r="51" spans="1:23" ht="18" customHeight="1" thickBot="1">
       <c r="A51" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B51" s="9" t="str">
+      <c r="B51" s="20" t="str">
         <f>COUNTA(A52:A59) &amp; " 筆"</f>
         <v>8 筆</v>
       </c>
-      <c r="C51" s="10"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
-      <c r="K51" s="10"/>
-      <c r="L51" s="10"/>
-      <c r="M51" s="10"/>
-      <c r="N51" s="10"/>
-      <c r="O51" s="10"/>
-      <c r="P51" s="10"/>
-      <c r="Q51" s="11"/>
+      <c r="C51" s="21"/>
+      <c r="D51" s="21"/>
+      <c r="E51" s="21"/>
+      <c r="F51" s="21"/>
+      <c r="G51" s="21"/>
+      <c r="H51" s="21"/>
+      <c r="I51" s="21"/>
+      <c r="J51" s="21"/>
+      <c r="K51" s="21"/>
+      <c r="L51" s="21"/>
+      <c r="M51" s="21"/>
+      <c r="N51" s="21"/>
+      <c r="O51" s="21"/>
+      <c r="P51" s="21"/>
+      <c r="Q51" s="22"/>
       <c r="R51" s="1" cm="1">
         <f t="array" ref="R51">CountColor($F52:$F59,$Y$4)</f>
         <v>5</v>
@@ -4501,12 +4501,12 @@
         <f t="shared" ref="Q52:Q59" si="23">ROUND(((G52-K52)/K52)*100,2)</f>
         <v>-0.53</v>
       </c>
-      <c r="R52" s="12"/>
-      <c r="S52" s="13"/>
-      <c r="T52" s="14"/>
-      <c r="U52" s="12"/>
-      <c r="V52" s="13"/>
-      <c r="W52" s="14"/>
+      <c r="R52" s="9"/>
+      <c r="S52" s="10"/>
+      <c r="T52" s="11"/>
+      <c r="U52" s="9"/>
+      <c r="V52" s="10"/>
+      <c r="W52" s="11"/>
     </row>
     <row r="53" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A53" s="5" t="s">
@@ -4566,12 +4566,12 @@
         <f t="shared" si="23"/>
         <v>-3.01</v>
       </c>
-      <c r="R53" s="15"/>
-      <c r="S53" s="16"/>
-      <c r="T53" s="17"/>
-      <c r="U53" s="15"/>
-      <c r="V53" s="16"/>
-      <c r="W53" s="17"/>
+      <c r="R53" s="12"/>
+      <c r="S53" s="13"/>
+      <c r="T53" s="14"/>
+      <c r="U53" s="12"/>
+      <c r="V53" s="13"/>
+      <c r="W53" s="14"/>
     </row>
     <row r="54" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A54" s="5" t="s">
@@ -4631,12 +4631,12 @@
         <f t="shared" si="23"/>
         <v>20.190000000000001</v>
       </c>
-      <c r="R54" s="15"/>
-      <c r="S54" s="16"/>
-      <c r="T54" s="17"/>
-      <c r="U54" s="15"/>
-      <c r="V54" s="16"/>
-      <c r="W54" s="17"/>
+      <c r="R54" s="12"/>
+      <c r="S54" s="13"/>
+      <c r="T54" s="14"/>
+      <c r="U54" s="12"/>
+      <c r="V54" s="13"/>
+      <c r="W54" s="14"/>
     </row>
     <row r="55" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A55" s="5" t="s">
@@ -4696,12 +4696,12 @@
         <f t="shared" si="23"/>
         <v>17.670000000000002</v>
       </c>
-      <c r="R55" s="15"/>
-      <c r="S55" s="16"/>
-      <c r="T55" s="17"/>
-      <c r="U55" s="15"/>
-      <c r="V55" s="16"/>
-      <c r="W55" s="17"/>
+      <c r="R55" s="12"/>
+      <c r="S55" s="13"/>
+      <c r="T55" s="14"/>
+      <c r="U55" s="12"/>
+      <c r="V55" s="13"/>
+      <c r="W55" s="14"/>
     </row>
     <row r="56" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A56" s="5" t="s">
@@ -4761,12 +4761,12 @@
         <f t="shared" si="23"/>
         <v>16.75</v>
       </c>
-      <c r="R56" s="15"/>
-      <c r="S56" s="16"/>
-      <c r="T56" s="17"/>
-      <c r="U56" s="15"/>
-      <c r="V56" s="16"/>
-      <c r="W56" s="17"/>
+      <c r="R56" s="12"/>
+      <c r="S56" s="13"/>
+      <c r="T56" s="14"/>
+      <c r="U56" s="12"/>
+      <c r="V56" s="13"/>
+      <c r="W56" s="14"/>
     </row>
     <row r="57" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A57" s="5" t="s">
@@ -4826,12 +4826,12 @@
         <f t="shared" si="23"/>
         <v>16.739999999999998</v>
       </c>
-      <c r="R57" s="15"/>
-      <c r="S57" s="16"/>
-      <c r="T57" s="17"/>
-      <c r="U57" s="15"/>
-      <c r="V57" s="16"/>
-      <c r="W57" s="17"/>
+      <c r="R57" s="12"/>
+      <c r="S57" s="13"/>
+      <c r="T57" s="14"/>
+      <c r="U57" s="12"/>
+      <c r="V57" s="13"/>
+      <c r="W57" s="14"/>
     </row>
     <row r="58" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A58" s="5" t="s">
@@ -4891,12 +4891,12 @@
         <f t="shared" si="23"/>
         <v>24.34</v>
       </c>
-      <c r="R58" s="15"/>
-      <c r="S58" s="16"/>
-      <c r="T58" s="17"/>
-      <c r="U58" s="15"/>
-      <c r="V58" s="16"/>
-      <c r="W58" s="17"/>
+      <c r="R58" s="12"/>
+      <c r="S58" s="13"/>
+      <c r="T58" s="14"/>
+      <c r="U58" s="12"/>
+      <c r="V58" s="13"/>
+      <c r="W58" s="14"/>
     </row>
     <row r="59" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A59" s="5" t="s">
@@ -4956,12 +4956,12 @@
         <f t="shared" si="23"/>
         <v>0.51</v>
       </c>
-      <c r="R59" s="15"/>
-      <c r="S59" s="16"/>
-      <c r="T59" s="17"/>
-      <c r="U59" s="15"/>
-      <c r="V59" s="16"/>
-      <c r="W59" s="17"/>
+      <c r="R59" s="12"/>
+      <c r="S59" s="13"/>
+      <c r="T59" s="14"/>
+      <c r="U59" s="12"/>
+      <c r="V59" s="13"/>
+      <c r="W59" s="14"/>
     </row>
     <row r="60" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A60" s="6" t="s">
@@ -5007,42 +5007,42 @@
         <f t="shared" si="24"/>
         <v>1384.17</v>
       </c>
-      <c r="L60" s="9"/>
-      <c r="M60" s="10"/>
-      <c r="N60" s="10"/>
-      <c r="O60" s="10"/>
-      <c r="P60" s="10"/>
-      <c r="Q60" s="11"/>
-      <c r="R60" s="18"/>
-      <c r="S60" s="19"/>
-      <c r="T60" s="20"/>
-      <c r="U60" s="18"/>
-      <c r="V60" s="19"/>
-      <c r="W60" s="20"/>
+      <c r="L60" s="20"/>
+      <c r="M60" s="21"/>
+      <c r="N60" s="21"/>
+      <c r="O60" s="21"/>
+      <c r="P60" s="21"/>
+      <c r="Q60" s="22"/>
+      <c r="R60" s="15"/>
+      <c r="S60" s="16"/>
+      <c r="T60" s="17"/>
+      <c r="U60" s="15"/>
+      <c r="V60" s="16"/>
+      <c r="W60" s="17"/>
     </row>
     <row r="61" spans="1:23" ht="17.25" thickBot="1">
       <c r="A61" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B61" s="9" t="str">
+      <c r="B61" s="20" t="str">
         <f>COUNTA(A62:A69) &amp; " 筆"</f>
         <v>8 筆</v>
       </c>
-      <c r="C61" s="10"/>
-      <c r="D61" s="10"/>
-      <c r="E61" s="10"/>
-      <c r="F61" s="10"/>
-      <c r="G61" s="10"/>
-      <c r="H61" s="10"/>
-      <c r="I61" s="10"/>
-      <c r="J61" s="10"/>
-      <c r="K61" s="10"/>
-      <c r="L61" s="10"/>
-      <c r="M61" s="10"/>
-      <c r="N61" s="10"/>
-      <c r="O61" s="10"/>
-      <c r="P61" s="10"/>
-      <c r="Q61" s="11"/>
+      <c r="C61" s="21"/>
+      <c r="D61" s="21"/>
+      <c r="E61" s="21"/>
+      <c r="F61" s="21"/>
+      <c r="G61" s="21"/>
+      <c r="H61" s="21"/>
+      <c r="I61" s="21"/>
+      <c r="J61" s="21"/>
+      <c r="K61" s="21"/>
+      <c r="L61" s="21"/>
+      <c r="M61" s="21"/>
+      <c r="N61" s="21"/>
+      <c r="O61" s="21"/>
+      <c r="P61" s="21"/>
+      <c r="Q61" s="22"/>
       <c r="R61" s="1" cm="1">
         <f t="array" ref="R61">CountColor($F62:$F69,$Y$4)</f>
         <v>4</v>
@@ -5123,12 +5123,12 @@
         <f t="shared" si="26"/>
         <v>4.17</v>
       </c>
-      <c r="R62" s="12"/>
-      <c r="S62" s="13"/>
-      <c r="T62" s="14"/>
-      <c r="U62" s="12"/>
-      <c r="V62" s="13"/>
-      <c r="W62" s="14"/>
+      <c r="R62" s="9"/>
+      <c r="S62" s="10"/>
+      <c r="T62" s="11"/>
+      <c r="U62" s="9"/>
+      <c r="V62" s="10"/>
+      <c r="W62" s="11"/>
     </row>
     <row r="63" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A63" s="5" t="s">
@@ -5188,12 +5188,12 @@
         <f t="shared" si="26"/>
         <v>-8.34</v>
       </c>
-      <c r="R63" s="15"/>
-      <c r="S63" s="16"/>
-      <c r="T63" s="17"/>
-      <c r="U63" s="15"/>
-      <c r="V63" s="16"/>
-      <c r="W63" s="17"/>
+      <c r="R63" s="12"/>
+      <c r="S63" s="13"/>
+      <c r="T63" s="14"/>
+      <c r="U63" s="12"/>
+      <c r="V63" s="13"/>
+      <c r="W63" s="14"/>
     </row>
     <row r="64" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A64" s="5" t="s">
@@ -5253,12 +5253,12 @@
         <f t="shared" si="26"/>
         <v>8.09</v>
       </c>
-      <c r="R64" s="15"/>
-      <c r="S64" s="16"/>
-      <c r="T64" s="17"/>
-      <c r="U64" s="15"/>
-      <c r="V64" s="16"/>
-      <c r="W64" s="17"/>
+      <c r="R64" s="12"/>
+      <c r="S64" s="13"/>
+      <c r="T64" s="14"/>
+      <c r="U64" s="12"/>
+      <c r="V64" s="13"/>
+      <c r="W64" s="14"/>
     </row>
     <row r="65" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A65" s="5" t="s">
@@ -5318,12 +5318,12 @@
         <f t="shared" si="26"/>
         <v>2.42</v>
       </c>
-      <c r="R65" s="15"/>
-      <c r="S65" s="16"/>
-      <c r="T65" s="17"/>
-      <c r="U65" s="15"/>
-      <c r="V65" s="16"/>
-      <c r="W65" s="17"/>
+      <c r="R65" s="12"/>
+      <c r="S65" s="13"/>
+      <c r="T65" s="14"/>
+      <c r="U65" s="12"/>
+      <c r="V65" s="13"/>
+      <c r="W65" s="14"/>
     </row>
     <row r="66" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A66" s="5" t="s">
@@ -5383,12 +5383,12 @@
         <f t="shared" si="26"/>
         <v>6.33</v>
       </c>
-      <c r="R66" s="15"/>
-      <c r="S66" s="16"/>
-      <c r="T66" s="17"/>
-      <c r="U66" s="15"/>
-      <c r="V66" s="16"/>
-      <c r="W66" s="17"/>
+      <c r="R66" s="12"/>
+      <c r="S66" s="13"/>
+      <c r="T66" s="14"/>
+      <c r="U66" s="12"/>
+      <c r="V66" s="13"/>
+      <c r="W66" s="14"/>
     </row>
     <row r="67" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A67" s="5" t="s">
@@ -5448,12 +5448,12 @@
         <f t="shared" si="26"/>
         <v>10.37</v>
       </c>
-      <c r="R67" s="15"/>
-      <c r="S67" s="16"/>
-      <c r="T67" s="17"/>
-      <c r="U67" s="15"/>
-      <c r="V67" s="16"/>
-      <c r="W67" s="17"/>
+      <c r="R67" s="12"/>
+      <c r="S67" s="13"/>
+      <c r="T67" s="14"/>
+      <c r="U67" s="12"/>
+      <c r="V67" s="13"/>
+      <c r="W67" s="14"/>
     </row>
     <row r="68" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A68" s="5" t="s">
@@ -5513,12 +5513,12 @@
         <f t="shared" si="26"/>
         <v>5.28</v>
       </c>
-      <c r="R68" s="15"/>
-      <c r="S68" s="16"/>
-      <c r="T68" s="17"/>
-      <c r="U68" s="15"/>
-      <c r="V68" s="16"/>
-      <c r="W68" s="17"/>
+      <c r="R68" s="12"/>
+      <c r="S68" s="13"/>
+      <c r="T68" s="14"/>
+      <c r="U68" s="12"/>
+      <c r="V68" s="13"/>
+      <c r="W68" s="14"/>
     </row>
     <row r="69" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A69" s="5" t="s">
@@ -5578,12 +5578,12 @@
         <f t="shared" si="26"/>
         <v>5.12</v>
       </c>
-      <c r="R69" s="15"/>
-      <c r="S69" s="16"/>
-      <c r="T69" s="17"/>
-      <c r="U69" s="15"/>
-      <c r="V69" s="16"/>
-      <c r="W69" s="17"/>
+      <c r="R69" s="12"/>
+      <c r="S69" s="13"/>
+      <c r="T69" s="14"/>
+      <c r="U69" s="12"/>
+      <c r="V69" s="13"/>
+      <c r="W69" s="14"/>
     </row>
     <row r="70" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A70" s="6" t="s">
@@ -5629,42 +5629,42 @@
         <f t="shared" si="27"/>
         <v>1119.24</v>
       </c>
-      <c r="L70" s="9"/>
-      <c r="M70" s="10"/>
-      <c r="N70" s="10"/>
-      <c r="O70" s="10"/>
-      <c r="P70" s="10"/>
-      <c r="Q70" s="11"/>
-      <c r="R70" s="18"/>
-      <c r="S70" s="19"/>
-      <c r="T70" s="20"/>
-      <c r="U70" s="18"/>
-      <c r="V70" s="19"/>
-      <c r="W70" s="20"/>
+      <c r="L70" s="20"/>
+      <c r="M70" s="21"/>
+      <c r="N70" s="21"/>
+      <c r="O70" s="21"/>
+      <c r="P70" s="21"/>
+      <c r="Q70" s="22"/>
+      <c r="R70" s="15"/>
+      <c r="S70" s="16"/>
+      <c r="T70" s="17"/>
+      <c r="U70" s="15"/>
+      <c r="V70" s="16"/>
+      <c r="W70" s="17"/>
     </row>
     <row r="71" spans="1:23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A71" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B71" s="9" t="str">
+      <c r="B71" s="20" t="str">
         <f>"總共 " &amp; SUM(R71:T71) &amp; " 筆"</f>
         <v>總共 56 筆</v>
       </c>
-      <c r="C71" s="10"/>
-      <c r="D71" s="10"/>
-      <c r="E71" s="10"/>
-      <c r="F71" s="10"/>
-      <c r="G71" s="10"/>
-      <c r="H71" s="10"/>
-      <c r="I71" s="10"/>
-      <c r="J71" s="10"/>
-      <c r="K71" s="10"/>
-      <c r="L71" s="10"/>
-      <c r="M71" s="10"/>
-      <c r="N71" s="10"/>
-      <c r="O71" s="10"/>
-      <c r="P71" s="10"/>
-      <c r="Q71" s="11"/>
+      <c r="C71" s="21"/>
+      <c r="D71" s="21"/>
+      <c r="E71" s="21"/>
+      <c r="F71" s="21"/>
+      <c r="G71" s="21"/>
+      <c r="H71" s="21"/>
+      <c r="I71" s="21"/>
+      <c r="J71" s="21"/>
+      <c r="K71" s="21"/>
+      <c r="L71" s="21"/>
+      <c r="M71" s="21"/>
+      <c r="N71" s="21"/>
+      <c r="O71" s="21"/>
+      <c r="P71" s="21"/>
+      <c r="Q71" s="22"/>
       <c r="R71" s="1">
         <f t="shared" ref="R71:W71" si="28">R3+R14+R24+R38+R51+R61</f>
         <v>25</v>
@@ -5692,6 +5692,25 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="R4:T13"/>
+    <mergeCell ref="R15:T23"/>
+    <mergeCell ref="B71:Q71"/>
+    <mergeCell ref="B38:Q38"/>
+    <mergeCell ref="B51:Q51"/>
+    <mergeCell ref="B61:Q61"/>
+    <mergeCell ref="B14:Q14"/>
+    <mergeCell ref="B24:Q24"/>
+    <mergeCell ref="L23:Q23"/>
+    <mergeCell ref="L70:Q70"/>
+    <mergeCell ref="R62:T70"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="H1:I1"/>
     <mergeCell ref="U52:W60"/>
     <mergeCell ref="U62:W70"/>
     <mergeCell ref="N1:O1"/>
@@ -5708,25 +5727,6 @@
     <mergeCell ref="U39:W50"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="B3:Q3"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="L13:Q13"/>
-    <mergeCell ref="R4:T13"/>
-    <mergeCell ref="R15:T23"/>
-    <mergeCell ref="B71:Q71"/>
-    <mergeCell ref="B38:Q38"/>
-    <mergeCell ref="B51:Q51"/>
-    <mergeCell ref="B61:Q61"/>
-    <mergeCell ref="B14:Q14"/>
-    <mergeCell ref="B24:Q24"/>
-    <mergeCell ref="L23:Q23"/>
-    <mergeCell ref="L70:Q70"/>
-    <mergeCell ref="R62:T70"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5747,14 +5747,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.25" thickBot="1">
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="22"/>
-      <c r="D1" s="21" t="s">
+      <c r="C1" s="19"/>
+      <c r="D1" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="E1" s="22"/>
+      <c r="E1" s="19"/>
     </row>
     <row r="2" spans="1:5" ht="17.25" thickBot="1">
       <c r="A2" s="5" t="s">
@@ -5777,13 +5777,13 @@
       <c r="A3" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="9">
+      <c r="B3" s="20">
         <f>COUNTA(A4:A12)</f>
         <v>9</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="11"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="22"/>
     </row>
     <row r="4" spans="1:5" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A4" s="6" t="s">
@@ -5925,12 +5925,12 @@
       <c r="A14" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="20">
         <v>8</v>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="11"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="22"/>
     </row>
     <row r="15" spans="1:5" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A15" s="6" t="s">
@@ -6059,12 +6059,12 @@
       <c r="A24" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B24" s="9">
+      <c r="B24" s="20">
         <v>12</v>
       </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="11"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="22"/>
     </row>
     <row r="25" spans="1:5" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A25" s="6" t="s">
@@ -6245,12 +6245,12 @@
       <c r="A38" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B38" s="9">
+      <c r="B38" s="20">
         <v>11</v>
       </c>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="11"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="22"/>
     </row>
     <row r="39" spans="1:5" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A39" s="6" t="s">
@@ -6418,12 +6418,12 @@
       <c r="A51" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B51" s="9">
+      <c r="B51" s="20">
         <v>8</v>
       </c>
-      <c r="C51" s="10"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="11"/>
+      <c r="C51" s="21"/>
+      <c r="D51" s="21"/>
+      <c r="E51" s="22"/>
     </row>
     <row r="52" spans="1:5" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A52" s="5" t="s">
@@ -6552,12 +6552,12 @@
       <c r="A61" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B61" s="9">
+      <c r="B61" s="20">
         <v>8</v>
       </c>
-      <c r="C61" s="10"/>
-      <c r="D61" s="10"/>
-      <c r="E61" s="11"/>
+      <c r="C61" s="21"/>
+      <c r="D61" s="21"/>
+      <c r="E61" s="22"/>
     </row>
     <row r="62" spans="1:5" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A62" s="5" t="s">

--- a/docs/Baseline比較結果.xlsx
+++ b/docs/Baseline比較結果.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff0\OneDrive\桌面\115_NTUT_Thesis\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52700AC9-6C93-4A60-8BFF-9731B507DC0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC86233-BD5B-4442-9438-B7BF1BAB99D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{9DD6E340-DFE3-4B7E-9025-343BD89F474F}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="94">
   <si>
     <t>Distance</t>
   </si>
@@ -549,9 +549,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Min L</t>
-  </si>
-  <si>
     <t>HGA</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -569,6 +566,42 @@
   </si>
   <si>
     <t>Tie</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Total Average</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RC1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RC2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Baseline</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本研究</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -857,6 +890,24 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -884,24 +935,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -921,6 +954,2325 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Number of Vehicles </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="zh-TW" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Comparison</a:t>
+            </a:r>
+            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>工作表2!$B$80</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>本研究</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表2!$A$81:$A$86</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>R1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>R2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>C1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>C2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>RC1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>RC2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表2!$B$81:$B$86</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>12.79</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.15</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.01</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12.44</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.46</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-14B7-433B-8AD8-A7AC622239D0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>工作表2!$D$80</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Baseline</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表2!$A$81:$A$86</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>R1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>R2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>C1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>C2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>RC1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>RC2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表2!$D$81:$D$86</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>12.83</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.72</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12.26</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-14B7-433B-8AD8-A7AC622239D0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1242555375"/>
+        <c:axId val="799262831"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1242555375"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="799262831"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="799262831"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="zh-TW"/>
+                  <a:t>Number</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="zh-TW" baseline="0"/>
+                  <a:t> of Vehicles</a:t>
+                </a:r>
+                <a:endParaRPr lang="zh-TW" altLang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1242555375"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:dTable>
+        <c:showHorzBorder val="1"/>
+        <c:showVertBorder val="1"/>
+        <c:showOutline val="1"/>
+        <c:showKeys val="1"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr rtl="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+      </c:dTable>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="zh-TW" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Travel Distance Comparison</a:t>
+            </a:r>
+            <a:endParaRPr lang="zh-TW" altLang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>工作表2!$C$80</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>本研究</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表2!$A$81:$A$86</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>R1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>R2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>C1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>C2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>RC1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>RC2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表2!$C$81:$C$86</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1234.93</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>995.42</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>828.38</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>592.58000000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1381.75</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1167.7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A3F8-4EEA-846B-9F72B6293A2A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>工作表2!$E$80</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Baseline</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表2!$A$81:$A$86</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>R1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>R2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>C1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>C2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>RC1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>RC2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表2!$E$81:$E$86</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1209.0999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1087.5999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>838.75</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>590.35</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1391.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1134.43</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-A3F8-4EEA-846B-9F72B6293A2A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="790149007"/>
+        <c:axId val="1249616111"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="790149007"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1249616111"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1249616111"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="zh-TW"/>
+                  <a:t>Travel Distance</a:t>
+                </a:r>
+                <a:endParaRPr lang="zh-TW" altLang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="790149007"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:dTable>
+        <c:showHorzBorder val="1"/>
+        <c:showVertBorder val="1"/>
+        <c:showOutline val="1"/>
+        <c:showKeys val="1"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr rtl="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+      </c:dTable>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>185737</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>14287</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="圖表 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB71A5D6-ABAF-0921-5D4F-6AC62D887932}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>595312</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>176212</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>366712</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>4762</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="圖表 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{989E5ED4-340A-3698-66C2-9D626AD9A03C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1262,48 +3614,48 @@
   <sheetData>
     <row r="1" spans="1:26" ht="17.25" customHeight="1" thickBot="1">
       <c r="A1" s="4"/>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="19"/>
-      <c r="D1" s="18" t="s">
+      <c r="C1" s="13"/>
+      <c r="D1" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="19"/>
+      <c r="E1" s="13"/>
       <c r="F1" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="19"/>
-      <c r="H1" s="18" t="s">
+      <c r="G1" s="13"/>
+      <c r="H1" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="I1" s="19"/>
-      <c r="J1" s="18" t="s">
+      <c r="I1" s="13"/>
+      <c r="J1" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="K1" s="19"/>
-      <c r="L1" s="18" t="s">
+      <c r="K1" s="13"/>
+      <c r="L1" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="M1" s="19"/>
-      <c r="N1" s="18" t="s">
+      <c r="M1" s="13"/>
+      <c r="N1" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="O1" s="19"/>
-      <c r="P1" s="18" t="s">
+      <c r="O1" s="13"/>
+      <c r="P1" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="18" t="s">
+      <c r="Q1" s="13"/>
+      <c r="R1" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="S1" s="23"/>
-      <c r="T1" s="23"/>
-      <c r="U1" s="18" t="s">
+      <c r="S1" s="12"/>
+      <c r="T1" s="12"/>
+      <c r="U1" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="V1" s="23"/>
-      <c r="W1" s="23"/>
+      <c r="V1" s="12"/>
+      <c r="W1" s="12"/>
     </row>
     <row r="2" spans="1:26" ht="17.25" thickBot="1">
       <c r="A2" s="5" t="s">
@@ -1380,25 +3732,25 @@
       <c r="A3" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="20" t="str">
+      <c r="B3" s="9" t="str">
         <f>COUNTA(A4:A12) &amp; " 筆"</f>
         <v>9 筆</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
-      <c r="L3" s="21"/>
-      <c r="M3" s="21"/>
-      <c r="N3" s="21"/>
-      <c r="O3" s="21"/>
-      <c r="P3" s="21"/>
-      <c r="Q3" s="22"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="11"/>
       <c r="R3" s="1" cm="1">
         <f t="array" ref="R3">CountColor($F4:$F12,$Y$4)</f>
         <v>4</v>
@@ -1482,15 +3834,15 @@
         <f t="shared" ref="Q4:Q12" si="3">ROUND(((G4-K4)/K4)*100,2)</f>
         <v>0</v>
       </c>
-      <c r="R4" s="9"/>
-      <c r="S4" s="10"/>
-      <c r="T4" s="11"/>
-      <c r="U4" s="9"/>
-      <c r="V4" s="10"/>
-      <c r="W4" s="11"/>
+      <c r="R4" s="15"/>
+      <c r="S4" s="16"/>
+      <c r="T4" s="17"/>
+      <c r="U4" s="15"/>
+      <c r="V4" s="16"/>
+      <c r="W4" s="17"/>
       <c r="Y4" s="2"/>
       <c r="Z4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
@@ -1551,15 +3903,15 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R5" s="12"/>
-      <c r="S5" s="13"/>
-      <c r="T5" s="14"/>
-      <c r="U5" s="12"/>
-      <c r="V5" s="13"/>
-      <c r="W5" s="14"/>
+      <c r="R5" s="18"/>
+      <c r="S5" s="19"/>
+      <c r="T5" s="20"/>
+      <c r="U5" s="18"/>
+      <c r="V5" s="19"/>
+      <c r="W5" s="20"/>
       <c r="Y5" s="7"/>
       <c r="Z5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
@@ -1620,15 +3972,15 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R6" s="12"/>
-      <c r="S6" s="13"/>
-      <c r="T6" s="14"/>
-      <c r="U6" s="12"/>
-      <c r="V6" s="13"/>
-      <c r="W6" s="14"/>
+      <c r="R6" s="18"/>
+      <c r="S6" s="19"/>
+      <c r="T6" s="20"/>
+      <c r="U6" s="18"/>
+      <c r="V6" s="19"/>
+      <c r="W6" s="20"/>
       <c r="Y6" s="3"/>
       <c r="Z6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
@@ -1689,12 +4041,12 @@
         <f t="shared" si="3"/>
         <v>0.19</v>
       </c>
-      <c r="R7" s="12"/>
-      <c r="S7" s="13"/>
-      <c r="T7" s="14"/>
-      <c r="U7" s="12"/>
-      <c r="V7" s="13"/>
-      <c r="W7" s="14"/>
+      <c r="R7" s="18"/>
+      <c r="S7" s="19"/>
+      <c r="T7" s="20"/>
+      <c r="U7" s="18"/>
+      <c r="V7" s="19"/>
+      <c r="W7" s="20"/>
     </row>
     <row r="8" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A8" s="6" t="s">
@@ -1754,12 +4106,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R8" s="12"/>
-      <c r="S8" s="13"/>
-      <c r="T8" s="14"/>
-      <c r="U8" s="12"/>
-      <c r="V8" s="13"/>
-      <c r="W8" s="14"/>
+      <c r="R8" s="18"/>
+      <c r="S8" s="19"/>
+      <c r="T8" s="20"/>
+      <c r="U8" s="18"/>
+      <c r="V8" s="19"/>
+      <c r="W8" s="20"/>
     </row>
     <row r="9" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A9" s="6" t="s">
@@ -1819,12 +4171,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R9" s="12"/>
-      <c r="S9" s="13"/>
-      <c r="T9" s="14"/>
-      <c r="U9" s="12"/>
-      <c r="V9" s="13"/>
-      <c r="W9" s="14"/>
+      <c r="R9" s="18"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="20"/>
+      <c r="U9" s="18"/>
+      <c r="V9" s="19"/>
+      <c r="W9" s="20"/>
     </row>
     <row r="10" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A10" s="6" t="s">
@@ -1884,12 +4236,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R10" s="12"/>
-      <c r="S10" s="13"/>
-      <c r="T10" s="14"/>
-      <c r="U10" s="12"/>
-      <c r="V10" s="13"/>
-      <c r="W10" s="14"/>
+      <c r="R10" s="18"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="20"/>
+      <c r="U10" s="18"/>
+      <c r="V10" s="19"/>
+      <c r="W10" s="20"/>
     </row>
     <row r="11" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A11" s="6" t="s">
@@ -1949,12 +4301,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R11" s="12"/>
-      <c r="S11" s="13"/>
-      <c r="T11" s="14"/>
-      <c r="U11" s="12"/>
-      <c r="V11" s="13"/>
-      <c r="W11" s="14"/>
+      <c r="R11" s="18"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="20"/>
+      <c r="U11" s="18"/>
+      <c r="V11" s="19"/>
+      <c r="W11" s="20"/>
     </row>
     <row r="12" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A12" s="6" t="s">
@@ -2014,12 +4366,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R12" s="12"/>
-      <c r="S12" s="13"/>
-      <c r="T12" s="14"/>
-      <c r="U12" s="12"/>
-      <c r="V12" s="13"/>
-      <c r="W12" s="14"/>
+      <c r="R12" s="18"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="20"/>
+      <c r="U12" s="18"/>
+      <c r="V12" s="19"/>
+      <c r="W12" s="20"/>
     </row>
     <row r="13" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A13" s="6" t="s">
@@ -2063,42 +4415,42 @@
         <f t="shared" si="6"/>
         <v>828.38000000000022</v>
       </c>
-      <c r="L13" s="20"/>
-      <c r="M13" s="21"/>
-      <c r="N13" s="21"/>
-      <c r="O13" s="21"/>
-      <c r="P13" s="21"/>
-      <c r="Q13" s="22"/>
-      <c r="R13" s="15"/>
-      <c r="S13" s="16"/>
-      <c r="T13" s="17"/>
-      <c r="U13" s="15"/>
-      <c r="V13" s="16"/>
-      <c r="W13" s="17"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="11"/>
+      <c r="R13" s="21"/>
+      <c r="S13" s="22"/>
+      <c r="T13" s="23"/>
+      <c r="U13" s="21"/>
+      <c r="V13" s="22"/>
+      <c r="W13" s="23"/>
     </row>
     <row r="14" spans="1:26" ht="17.25" customHeight="1" thickBot="1">
       <c r="A14" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B14" s="20" t="str">
+      <c r="B14" s="9" t="str">
         <f>COUNTA(A15:A22) &amp; " 筆"</f>
         <v>8 筆</v>
       </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="21"/>
-      <c r="M14" s="21"/>
-      <c r="N14" s="21"/>
-      <c r="O14" s="21"/>
-      <c r="P14" s="21"/>
-      <c r="Q14" s="22"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="11"/>
       <c r="R14" s="1" cm="1">
         <f t="array" ref="R14">CountColor($F15:$F22,$Y$4)</f>
         <v>1</v>
@@ -2182,12 +4534,12 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="R15" s="9"/>
-      <c r="S15" s="10"/>
-      <c r="T15" s="11"/>
-      <c r="U15" s="9"/>
-      <c r="V15" s="10"/>
-      <c r="W15" s="11"/>
+      <c r="R15" s="15"/>
+      <c r="S15" s="16"/>
+      <c r="T15" s="17"/>
+      <c r="U15" s="15"/>
+      <c r="V15" s="16"/>
+      <c r="W15" s="17"/>
     </row>
     <row r="16" spans="1:26" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A16" s="6" t="s">
@@ -2247,12 +4599,12 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="R16" s="12"/>
-      <c r="S16" s="13"/>
-      <c r="T16" s="14"/>
-      <c r="U16" s="12"/>
-      <c r="V16" s="13"/>
-      <c r="W16" s="14"/>
+      <c r="R16" s="18"/>
+      <c r="S16" s="19"/>
+      <c r="T16" s="20"/>
+      <c r="U16" s="18"/>
+      <c r="V16" s="19"/>
+      <c r="W16" s="20"/>
     </row>
     <row r="17" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A17" s="6" t="s">
@@ -2312,12 +4664,12 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="R17" s="12"/>
-      <c r="S17" s="13"/>
-      <c r="T17" s="14"/>
-      <c r="U17" s="12"/>
-      <c r="V17" s="13"/>
-      <c r="W17" s="14"/>
+      <c r="R17" s="18"/>
+      <c r="S17" s="19"/>
+      <c r="T17" s="20"/>
+      <c r="U17" s="18"/>
+      <c r="V17" s="19"/>
+      <c r="W17" s="20"/>
     </row>
     <row r="18" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A18" s="6" t="s">
@@ -2377,12 +4729,12 @@
         <f t="shared" si="8"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="R18" s="12"/>
-      <c r="S18" s="13"/>
-      <c r="T18" s="14"/>
-      <c r="U18" s="12"/>
-      <c r="V18" s="13"/>
-      <c r="W18" s="14"/>
+      <c r="R18" s="18"/>
+      <c r="S18" s="19"/>
+      <c r="T18" s="20"/>
+      <c r="U18" s="18"/>
+      <c r="V18" s="19"/>
+      <c r="W18" s="20"/>
     </row>
     <row r="19" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A19" s="6" t="s">
@@ -2442,12 +4794,12 @@
         <f t="shared" si="8"/>
         <v>0.01</v>
       </c>
-      <c r="R19" s="12"/>
-      <c r="S19" s="13"/>
-      <c r="T19" s="14"/>
-      <c r="U19" s="12"/>
-      <c r="V19" s="13"/>
-      <c r="W19" s="14"/>
+      <c r="R19" s="18"/>
+      <c r="S19" s="19"/>
+      <c r="T19" s="20"/>
+      <c r="U19" s="18"/>
+      <c r="V19" s="19"/>
+      <c r="W19" s="20"/>
     </row>
     <row r="20" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A20" s="6" t="s">
@@ -2507,12 +4859,12 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="R20" s="12"/>
-      <c r="S20" s="13"/>
-      <c r="T20" s="14"/>
-      <c r="U20" s="12"/>
-      <c r="V20" s="13"/>
-      <c r="W20" s="14"/>
+      <c r="R20" s="18"/>
+      <c r="S20" s="19"/>
+      <c r="T20" s="20"/>
+      <c r="U20" s="18"/>
+      <c r="V20" s="19"/>
+      <c r="W20" s="20"/>
     </row>
     <row r="21" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A21" s="6" t="s">
@@ -2572,12 +4924,12 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="R21" s="12"/>
-      <c r="S21" s="13"/>
-      <c r="T21" s="14"/>
-      <c r="U21" s="12"/>
-      <c r="V21" s="13"/>
-      <c r="W21" s="14"/>
+      <c r="R21" s="18"/>
+      <c r="S21" s="19"/>
+      <c r="T21" s="20"/>
+      <c r="U21" s="18"/>
+      <c r="V21" s="19"/>
+      <c r="W21" s="20"/>
     </row>
     <row r="22" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A22" s="6" t="s">
@@ -2637,12 +4989,12 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="R22" s="12"/>
-      <c r="S22" s="13"/>
-      <c r="T22" s="14"/>
-      <c r="U22" s="12"/>
-      <c r="V22" s="13"/>
-      <c r="W22" s="14"/>
+      <c r="R22" s="18"/>
+      <c r="S22" s="19"/>
+      <c r="T22" s="20"/>
+      <c r="U22" s="18"/>
+      <c r="V22" s="19"/>
+      <c r="W22" s="20"/>
     </row>
     <row r="23" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A23" s="6" t="s">
@@ -2686,42 +5038,42 @@
         <f t="shared" si="9"/>
         <v>589.86</v>
       </c>
-      <c r="L23" s="20"/>
-      <c r="M23" s="21"/>
-      <c r="N23" s="21"/>
-      <c r="O23" s="21"/>
-      <c r="P23" s="21"/>
-      <c r="Q23" s="22"/>
-      <c r="R23" s="15"/>
-      <c r="S23" s="16"/>
-      <c r="T23" s="17"/>
-      <c r="U23" s="15"/>
-      <c r="V23" s="16"/>
-      <c r="W23" s="17"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="10"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="11"/>
+      <c r="R23" s="21"/>
+      <c r="S23" s="22"/>
+      <c r="T23" s="23"/>
+      <c r="U23" s="21"/>
+      <c r="V23" s="22"/>
+      <c r="W23" s="23"/>
     </row>
     <row r="24" spans="1:23" ht="17.25" customHeight="1" thickBot="1">
       <c r="A24" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B24" s="20" t="str">
+      <c r="B24" s="9" t="str">
         <f>COUNTA(A25:A36) &amp; " 筆"</f>
         <v>12 筆</v>
       </c>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="21"/>
-      <c r="I24" s="21"/>
-      <c r="J24" s="21"/>
-      <c r="K24" s="21"/>
-      <c r="L24" s="21"/>
-      <c r="M24" s="21"/>
-      <c r="N24" s="21"/>
-      <c r="O24" s="21"/>
-      <c r="P24" s="21"/>
-      <c r="Q24" s="22"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="10"/>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="11"/>
       <c r="R24" s="1" cm="1">
         <f t="array" ref="R24">CountColor($F25:$F36,$Y$4)</f>
         <v>2</v>
@@ -2802,12 +5154,12 @@
         <f t="shared" ref="Q25:Q36" si="13">ROUND(((G25-K25)/K25)*100,2)</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="R25" s="9"/>
-      <c r="S25" s="10"/>
-      <c r="T25" s="11"/>
-      <c r="U25" s="9"/>
-      <c r="V25" s="10"/>
-      <c r="W25" s="11"/>
+      <c r="R25" s="15"/>
+      <c r="S25" s="16"/>
+      <c r="T25" s="17"/>
+      <c r="U25" s="15"/>
+      <c r="V25" s="16"/>
+      <c r="W25" s="17"/>
     </row>
     <row r="26" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A26" s="6" t="s">
@@ -2867,12 +5219,12 @@
         <f t="shared" si="13"/>
         <v>0.04</v>
       </c>
-      <c r="R26" s="12"/>
-      <c r="S26" s="13"/>
-      <c r="T26" s="14"/>
-      <c r="U26" s="12"/>
-      <c r="V26" s="13"/>
-      <c r="W26" s="14"/>
+      <c r="R26" s="18"/>
+      <c r="S26" s="19"/>
+      <c r="T26" s="20"/>
+      <c r="U26" s="18"/>
+      <c r="V26" s="19"/>
+      <c r="W26" s="20"/>
     </row>
     <row r="27" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A27" s="6" t="s">
@@ -2932,12 +5284,12 @@
         <f t="shared" si="13"/>
         <v>21.68</v>
       </c>
-      <c r="R27" s="12"/>
-      <c r="S27" s="13"/>
-      <c r="T27" s="14"/>
-      <c r="U27" s="12"/>
-      <c r="V27" s="13"/>
-      <c r="W27" s="14"/>
+      <c r="R27" s="18"/>
+      <c r="S27" s="19"/>
+      <c r="T27" s="20"/>
+      <c r="U27" s="18"/>
+      <c r="V27" s="19"/>
+      <c r="W27" s="20"/>
     </row>
     <row r="28" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A28" s="6" t="s">
@@ -2997,12 +5349,12 @@
         <f t="shared" si="13"/>
         <v>1.86</v>
       </c>
-      <c r="R28" s="12"/>
-      <c r="S28" s="13"/>
-      <c r="T28" s="14"/>
-      <c r="U28" s="12"/>
-      <c r="V28" s="13"/>
-      <c r="W28" s="14"/>
+      <c r="R28" s="18"/>
+      <c r="S28" s="19"/>
+      <c r="T28" s="20"/>
+      <c r="U28" s="18"/>
+      <c r="V28" s="19"/>
+      <c r="W28" s="20"/>
     </row>
     <row r="29" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A29" s="6" t="s">
@@ -3062,12 +5414,12 @@
         <f t="shared" si="13"/>
         <v>22.62</v>
       </c>
-      <c r="R29" s="12"/>
-      <c r="S29" s="13"/>
-      <c r="T29" s="14"/>
-      <c r="U29" s="12"/>
-      <c r="V29" s="13"/>
-      <c r="W29" s="14"/>
+      <c r="R29" s="18"/>
+      <c r="S29" s="19"/>
+      <c r="T29" s="20"/>
+      <c r="U29" s="18"/>
+      <c r="V29" s="19"/>
+      <c r="W29" s="20"/>
     </row>
     <row r="30" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A30" s="6" t="s">
@@ -3127,12 +5479,12 @@
         <f t="shared" si="13"/>
         <v>2.66</v>
       </c>
-      <c r="R30" s="12"/>
-      <c r="S30" s="13"/>
-      <c r="T30" s="14"/>
-      <c r="U30" s="12"/>
-      <c r="V30" s="13"/>
-      <c r="W30" s="14"/>
+      <c r="R30" s="18"/>
+      <c r="S30" s="19"/>
+      <c r="T30" s="20"/>
+      <c r="U30" s="18"/>
+      <c r="V30" s="19"/>
+      <c r="W30" s="20"/>
     </row>
     <row r="31" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A31" s="6" t="s">
@@ -3192,12 +5544,12 @@
         <f t="shared" si="13"/>
         <v>2.06</v>
       </c>
-      <c r="R31" s="12"/>
-      <c r="S31" s="13"/>
-      <c r="T31" s="14"/>
-      <c r="U31" s="12"/>
-      <c r="V31" s="13"/>
-      <c r="W31" s="14"/>
+      <c r="R31" s="18"/>
+      <c r="S31" s="19"/>
+      <c r="T31" s="20"/>
+      <c r="U31" s="18"/>
+      <c r="V31" s="19"/>
+      <c r="W31" s="20"/>
     </row>
     <row r="32" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A32" s="6" t="s">
@@ -3257,12 +5609,12 @@
         <f t="shared" si="13"/>
         <v>4.66</v>
       </c>
-      <c r="R32" s="12"/>
-      <c r="S32" s="13"/>
-      <c r="T32" s="14"/>
-      <c r="U32" s="12"/>
-      <c r="V32" s="13"/>
-      <c r="W32" s="14"/>
+      <c r="R32" s="18"/>
+      <c r="S32" s="19"/>
+      <c r="T32" s="20"/>
+      <c r="U32" s="18"/>
+      <c r="V32" s="19"/>
+      <c r="W32" s="20"/>
     </row>
     <row r="33" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A33" s="6" t="s">
@@ -3322,12 +5674,12 @@
         <f t="shared" si="13"/>
         <v>5.08</v>
       </c>
-      <c r="R33" s="12"/>
-      <c r="S33" s="13"/>
-      <c r="T33" s="14"/>
-      <c r="U33" s="12"/>
-      <c r="V33" s="13"/>
-      <c r="W33" s="14"/>
+      <c r="R33" s="18"/>
+      <c r="S33" s="19"/>
+      <c r="T33" s="20"/>
+      <c r="U33" s="18"/>
+      <c r="V33" s="19"/>
+      <c r="W33" s="20"/>
     </row>
     <row r="34" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A34" s="6" t="s">
@@ -3387,12 +5739,12 @@
         <f t="shared" si="13"/>
         <v>2.89</v>
       </c>
-      <c r="R34" s="12"/>
-      <c r="S34" s="13"/>
-      <c r="T34" s="14"/>
-      <c r="U34" s="12"/>
-      <c r="V34" s="13"/>
-      <c r="W34" s="14"/>
+      <c r="R34" s="18"/>
+      <c r="S34" s="19"/>
+      <c r="T34" s="20"/>
+      <c r="U34" s="18"/>
+      <c r="V34" s="19"/>
+      <c r="W34" s="20"/>
     </row>
     <row r="35" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A35" s="6" t="s">
@@ -3452,12 +5804,12 @@
         <f t="shared" si="13"/>
         <v>5.92</v>
       </c>
-      <c r="R35" s="12"/>
-      <c r="S35" s="13"/>
-      <c r="T35" s="14"/>
-      <c r="U35" s="12"/>
-      <c r="V35" s="13"/>
-      <c r="W35" s="14"/>
+      <c r="R35" s="18"/>
+      <c r="S35" s="19"/>
+      <c r="T35" s="20"/>
+      <c r="U35" s="18"/>
+      <c r="V35" s="19"/>
+      <c r="W35" s="20"/>
     </row>
     <row r="36" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A36" s="6" t="s">
@@ -3517,12 +5869,12 @@
         <f t="shared" si="13"/>
         <v>5.48</v>
       </c>
-      <c r="R36" s="12"/>
-      <c r="S36" s="13"/>
-      <c r="T36" s="14"/>
-      <c r="U36" s="12"/>
-      <c r="V36" s="13"/>
-      <c r="W36" s="14"/>
+      <c r="R36" s="18"/>
+      <c r="S36" s="19"/>
+      <c r="T36" s="20"/>
+      <c r="U36" s="18"/>
+      <c r="V36" s="19"/>
+      <c r="W36" s="20"/>
     </row>
     <row r="37" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A37" s="6" t="s">
@@ -3568,42 +5920,42 @@
         <f t="shared" si="14"/>
         <v>1210.3399999999999</v>
       </c>
-      <c r="L37" s="20"/>
-      <c r="M37" s="21"/>
-      <c r="N37" s="21"/>
-      <c r="O37" s="21"/>
-      <c r="P37" s="21"/>
-      <c r="Q37" s="22"/>
-      <c r="R37" s="15"/>
-      <c r="S37" s="16"/>
-      <c r="T37" s="17"/>
-      <c r="U37" s="15"/>
-      <c r="V37" s="16"/>
-      <c r="W37" s="17"/>
+      <c r="L37" s="9"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="10"/>
+      <c r="P37" s="10"/>
+      <c r="Q37" s="11"/>
+      <c r="R37" s="21"/>
+      <c r="S37" s="22"/>
+      <c r="T37" s="23"/>
+      <c r="U37" s="21"/>
+      <c r="V37" s="22"/>
+      <c r="W37" s="23"/>
     </row>
     <row r="38" spans="1:23" ht="18" customHeight="1" thickBot="1">
       <c r="A38" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B38" s="20" t="str">
+      <c r="B38" s="9" t="str">
         <f>COUNTA(A39:A49) &amp; " 筆"</f>
         <v>11 筆</v>
       </c>
-      <c r="C38" s="21"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21"/>
-      <c r="G38" s="21"/>
-      <c r="H38" s="21"/>
-      <c r="I38" s="21"/>
-      <c r="J38" s="21"/>
-      <c r="K38" s="21"/>
-      <c r="L38" s="21"/>
-      <c r="M38" s="21"/>
-      <c r="N38" s="21"/>
-      <c r="O38" s="21"/>
-      <c r="P38" s="21"/>
-      <c r="Q38" s="22"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="10"/>
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="10"/>
+      <c r="O38" s="10"/>
+      <c r="P38" s="10"/>
+      <c r="Q38" s="11"/>
       <c r="R38" s="1" cm="1">
         <f t="array" ref="R38">CountColor($F39:$F49,$Y$4)</f>
         <v>9</v>
@@ -3684,12 +6036,12 @@
         <f t="shared" ref="Q39:Q49" si="18">ROUND(((G39-K39)/K39)*100,2)</f>
         <v>4.4800000000000004</v>
       </c>
-      <c r="R39" s="9"/>
-      <c r="S39" s="10"/>
-      <c r="T39" s="11"/>
-      <c r="U39" s="9"/>
-      <c r="V39" s="10"/>
-      <c r="W39" s="11"/>
+      <c r="R39" s="15"/>
+      <c r="S39" s="16"/>
+      <c r="T39" s="17"/>
+      <c r="U39" s="15"/>
+      <c r="V39" s="16"/>
+      <c r="W39" s="17"/>
     </row>
     <row r="40" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A40" s="6" t="s">
@@ -3749,12 +6101,12 @@
         <f t="shared" si="18"/>
         <v>47.67</v>
       </c>
-      <c r="R40" s="12"/>
-      <c r="S40" s="13"/>
-      <c r="T40" s="14"/>
-      <c r="U40" s="12"/>
-      <c r="V40" s="13"/>
-      <c r="W40" s="14"/>
+      <c r="R40" s="18"/>
+      <c r="S40" s="19"/>
+      <c r="T40" s="20"/>
+      <c r="U40" s="18"/>
+      <c r="V40" s="19"/>
+      <c r="W40" s="20"/>
     </row>
     <row r="41" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A41" s="6" t="s">
@@ -3814,12 +6166,12 @@
         <f t="shared" si="18"/>
         <v>5</v>
       </c>
-      <c r="R41" s="12"/>
-      <c r="S41" s="13"/>
-      <c r="T41" s="14"/>
-      <c r="U41" s="12"/>
-      <c r="V41" s="13"/>
-      <c r="W41" s="14"/>
+      <c r="R41" s="18"/>
+      <c r="S41" s="19"/>
+      <c r="T41" s="20"/>
+      <c r="U41" s="18"/>
+      <c r="V41" s="19"/>
+      <c r="W41" s="20"/>
     </row>
     <row r="42" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A42" s="6" t="s">
@@ -3879,12 +6231,12 @@
         <f t="shared" si="18"/>
         <v>-7.48</v>
       </c>
-      <c r="R42" s="12"/>
-      <c r="S42" s="13"/>
-      <c r="T42" s="14"/>
-      <c r="U42" s="12"/>
-      <c r="V42" s="13"/>
-      <c r="W42" s="14"/>
+      <c r="R42" s="18"/>
+      <c r="S42" s="19"/>
+      <c r="T42" s="20"/>
+      <c r="U42" s="18"/>
+      <c r="V42" s="19"/>
+      <c r="W42" s="20"/>
     </row>
     <row r="43" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A43" s="6" t="s">
@@ -3944,12 +6296,12 @@
         <f t="shared" si="18"/>
         <v>7.39</v>
       </c>
-      <c r="R43" s="12"/>
-      <c r="S43" s="13"/>
-      <c r="T43" s="14"/>
-      <c r="U43" s="12"/>
-      <c r="V43" s="13"/>
-      <c r="W43" s="14"/>
+      <c r="R43" s="18"/>
+      <c r="S43" s="19"/>
+      <c r="T43" s="20"/>
+      <c r="U43" s="18"/>
+      <c r="V43" s="19"/>
+      <c r="W43" s="20"/>
     </row>
     <row r="44" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A44" s="6" t="s">
@@ -4009,12 +6361,12 @@
         <f t="shared" si="18"/>
         <v>6.77</v>
       </c>
-      <c r="R44" s="12"/>
-      <c r="S44" s="13"/>
-      <c r="T44" s="14"/>
-      <c r="U44" s="12"/>
-      <c r="V44" s="13"/>
-      <c r="W44" s="14"/>
+      <c r="R44" s="18"/>
+      <c r="S44" s="19"/>
+      <c r="T44" s="20"/>
+      <c r="U44" s="18"/>
+      <c r="V44" s="19"/>
+      <c r="W44" s="20"/>
     </row>
     <row r="45" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A45" s="6" t="s">
@@ -4074,12 +6426,12 @@
         <f t="shared" si="18"/>
         <v>-4.17</v>
       </c>
-      <c r="R45" s="12"/>
-      <c r="S45" s="13"/>
-      <c r="T45" s="14"/>
-      <c r="U45" s="12"/>
-      <c r="V45" s="13"/>
-      <c r="W45" s="14"/>
+      <c r="R45" s="18"/>
+      <c r="S45" s="19"/>
+      <c r="T45" s="20"/>
+      <c r="U45" s="18"/>
+      <c r="V45" s="19"/>
+      <c r="W45" s="20"/>
     </row>
     <row r="46" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A46" s="6" t="s">
@@ -4139,12 +6491,12 @@
         <f t="shared" si="18"/>
         <v>1.75</v>
       </c>
-      <c r="R46" s="12"/>
-      <c r="S46" s="13"/>
-      <c r="T46" s="14"/>
-      <c r="U46" s="12"/>
-      <c r="V46" s="13"/>
-      <c r="W46" s="14"/>
+      <c r="R46" s="18"/>
+      <c r="S46" s="19"/>
+      <c r="T46" s="20"/>
+      <c r="U46" s="18"/>
+      <c r="V46" s="19"/>
+      <c r="W46" s="20"/>
     </row>
     <row r="47" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A47" s="6" t="s">
@@ -4204,12 +6556,12 @@
         <f t="shared" si="18"/>
         <v>5.29</v>
       </c>
-      <c r="R47" s="12"/>
-      <c r="S47" s="13"/>
-      <c r="T47" s="14"/>
-      <c r="U47" s="12"/>
-      <c r="V47" s="13"/>
-      <c r="W47" s="14"/>
+      <c r="R47" s="18"/>
+      <c r="S47" s="19"/>
+      <c r="T47" s="20"/>
+      <c r="U47" s="18"/>
+      <c r="V47" s="19"/>
+      <c r="W47" s="20"/>
     </row>
     <row r="48" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A48" s="6" t="s">
@@ -4269,12 +6621,12 @@
         <f t="shared" si="18"/>
         <v>5.81</v>
       </c>
-      <c r="R48" s="12"/>
-      <c r="S48" s="13"/>
-      <c r="T48" s="14"/>
-      <c r="U48" s="12"/>
-      <c r="V48" s="13"/>
-      <c r="W48" s="14"/>
+      <c r="R48" s="18"/>
+      <c r="S48" s="19"/>
+      <c r="T48" s="20"/>
+      <c r="U48" s="18"/>
+      <c r="V48" s="19"/>
+      <c r="W48" s="20"/>
     </row>
     <row r="49" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A49" s="6" t="s">
@@ -4334,12 +6686,12 @@
         <f t="shared" si="18"/>
         <v>-7.37</v>
       </c>
-      <c r="R49" s="12"/>
-      <c r="S49" s="13"/>
-      <c r="T49" s="14"/>
-      <c r="U49" s="12"/>
-      <c r="V49" s="13"/>
-      <c r="W49" s="14"/>
+      <c r="R49" s="18"/>
+      <c r="S49" s="19"/>
+      <c r="T49" s="20"/>
+      <c r="U49" s="18"/>
+      <c r="V49" s="19"/>
+      <c r="W49" s="20"/>
     </row>
     <row r="50" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A50" s="6" t="s">
@@ -4385,42 +6737,42 @@
         <f t="shared" si="19"/>
         <v>951.03</v>
       </c>
-      <c r="L50" s="20"/>
-      <c r="M50" s="21"/>
-      <c r="N50" s="21"/>
-      <c r="O50" s="21"/>
-      <c r="P50" s="21"/>
-      <c r="Q50" s="22"/>
-      <c r="R50" s="15"/>
-      <c r="S50" s="16"/>
-      <c r="T50" s="17"/>
-      <c r="U50" s="15"/>
-      <c r="V50" s="16"/>
-      <c r="W50" s="17"/>
+      <c r="L50" s="9"/>
+      <c r="M50" s="10"/>
+      <c r="N50" s="10"/>
+      <c r="O50" s="10"/>
+      <c r="P50" s="10"/>
+      <c r="Q50" s="11"/>
+      <c r="R50" s="21"/>
+      <c r="S50" s="22"/>
+      <c r="T50" s="23"/>
+      <c r="U50" s="21"/>
+      <c r="V50" s="22"/>
+      <c r="W50" s="23"/>
     </row>
     <row r="51" spans="1:23" ht="18" customHeight="1" thickBot="1">
       <c r="A51" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B51" s="20" t="str">
+      <c r="B51" s="9" t="str">
         <f>COUNTA(A52:A59) &amp; " 筆"</f>
         <v>8 筆</v>
       </c>
-      <c r="C51" s="21"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="21"/>
-      <c r="G51" s="21"/>
-      <c r="H51" s="21"/>
-      <c r="I51" s="21"/>
-      <c r="J51" s="21"/>
-      <c r="K51" s="21"/>
-      <c r="L51" s="21"/>
-      <c r="M51" s="21"/>
-      <c r="N51" s="21"/>
-      <c r="O51" s="21"/>
-      <c r="P51" s="21"/>
-      <c r="Q51" s="22"/>
+      <c r="C51" s="10"/>
+      <c r="D51" s="10"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="10"/>
+      <c r="H51" s="10"/>
+      <c r="I51" s="10"/>
+      <c r="J51" s="10"/>
+      <c r="K51" s="10"/>
+      <c r="L51" s="10"/>
+      <c r="M51" s="10"/>
+      <c r="N51" s="10"/>
+      <c r="O51" s="10"/>
+      <c r="P51" s="10"/>
+      <c r="Q51" s="11"/>
       <c r="R51" s="1" cm="1">
         <f t="array" ref="R51">CountColor($F52:$F59,$Y$4)</f>
         <v>5</v>
@@ -4501,12 +6853,12 @@
         <f t="shared" ref="Q52:Q59" si="23">ROUND(((G52-K52)/K52)*100,2)</f>
         <v>-0.53</v>
       </c>
-      <c r="R52" s="9"/>
-      <c r="S52" s="10"/>
-      <c r="T52" s="11"/>
-      <c r="U52" s="9"/>
-      <c r="V52" s="10"/>
-      <c r="W52" s="11"/>
+      <c r="R52" s="15"/>
+      <c r="S52" s="16"/>
+      <c r="T52" s="17"/>
+      <c r="U52" s="15"/>
+      <c r="V52" s="16"/>
+      <c r="W52" s="17"/>
     </row>
     <row r="53" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A53" s="5" t="s">
@@ -4566,12 +6918,12 @@
         <f t="shared" si="23"/>
         <v>-3.01</v>
       </c>
-      <c r="R53" s="12"/>
-      <c r="S53" s="13"/>
-      <c r="T53" s="14"/>
-      <c r="U53" s="12"/>
-      <c r="V53" s="13"/>
-      <c r="W53" s="14"/>
+      <c r="R53" s="18"/>
+      <c r="S53" s="19"/>
+      <c r="T53" s="20"/>
+      <c r="U53" s="18"/>
+      <c r="V53" s="19"/>
+      <c r="W53" s="20"/>
     </row>
     <row r="54" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A54" s="5" t="s">
@@ -4631,12 +6983,12 @@
         <f t="shared" si="23"/>
         <v>20.190000000000001</v>
       </c>
-      <c r="R54" s="12"/>
-      <c r="S54" s="13"/>
-      <c r="T54" s="14"/>
-      <c r="U54" s="12"/>
-      <c r="V54" s="13"/>
-      <c r="W54" s="14"/>
+      <c r="R54" s="18"/>
+      <c r="S54" s="19"/>
+      <c r="T54" s="20"/>
+      <c r="U54" s="18"/>
+      <c r="V54" s="19"/>
+      <c r="W54" s="20"/>
     </row>
     <row r="55" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A55" s="5" t="s">
@@ -4696,12 +7048,12 @@
         <f t="shared" si="23"/>
         <v>17.670000000000002</v>
       </c>
-      <c r="R55" s="12"/>
-      <c r="S55" s="13"/>
-      <c r="T55" s="14"/>
-      <c r="U55" s="12"/>
-      <c r="V55" s="13"/>
-      <c r="W55" s="14"/>
+      <c r="R55" s="18"/>
+      <c r="S55" s="19"/>
+      <c r="T55" s="20"/>
+      <c r="U55" s="18"/>
+      <c r="V55" s="19"/>
+      <c r="W55" s="20"/>
     </row>
     <row r="56" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A56" s="5" t="s">
@@ -4761,12 +7113,12 @@
         <f t="shared" si="23"/>
         <v>16.75</v>
       </c>
-      <c r="R56" s="12"/>
-      <c r="S56" s="13"/>
-      <c r="T56" s="14"/>
-      <c r="U56" s="12"/>
-      <c r="V56" s="13"/>
-      <c r="W56" s="14"/>
+      <c r="R56" s="18"/>
+      <c r="S56" s="19"/>
+      <c r="T56" s="20"/>
+      <c r="U56" s="18"/>
+      <c r="V56" s="19"/>
+      <c r="W56" s="20"/>
     </row>
     <row r="57" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A57" s="5" t="s">
@@ -4826,12 +7178,12 @@
         <f t="shared" si="23"/>
         <v>16.739999999999998</v>
       </c>
-      <c r="R57" s="12"/>
-      <c r="S57" s="13"/>
-      <c r="T57" s="14"/>
-      <c r="U57" s="12"/>
-      <c r="V57" s="13"/>
-      <c r="W57" s="14"/>
+      <c r="R57" s="18"/>
+      <c r="S57" s="19"/>
+      <c r="T57" s="20"/>
+      <c r="U57" s="18"/>
+      <c r="V57" s="19"/>
+      <c r="W57" s="20"/>
     </row>
     <row r="58" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A58" s="5" t="s">
@@ -4891,12 +7243,12 @@
         <f t="shared" si="23"/>
         <v>24.34</v>
       </c>
-      <c r="R58" s="12"/>
-      <c r="S58" s="13"/>
-      <c r="T58" s="14"/>
-      <c r="U58" s="12"/>
-      <c r="V58" s="13"/>
-      <c r="W58" s="14"/>
+      <c r="R58" s="18"/>
+      <c r="S58" s="19"/>
+      <c r="T58" s="20"/>
+      <c r="U58" s="18"/>
+      <c r="V58" s="19"/>
+      <c r="W58" s="20"/>
     </row>
     <row r="59" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A59" s="5" t="s">
@@ -4956,12 +7308,12 @@
         <f t="shared" si="23"/>
         <v>0.51</v>
       </c>
-      <c r="R59" s="12"/>
-      <c r="S59" s="13"/>
-      <c r="T59" s="14"/>
-      <c r="U59" s="12"/>
-      <c r="V59" s="13"/>
-      <c r="W59" s="14"/>
+      <c r="R59" s="18"/>
+      <c r="S59" s="19"/>
+      <c r="T59" s="20"/>
+      <c r="U59" s="18"/>
+      <c r="V59" s="19"/>
+      <c r="W59" s="20"/>
     </row>
     <row r="60" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A60" s="6" t="s">
@@ -5007,42 +7359,42 @@
         <f t="shared" si="24"/>
         <v>1384.17</v>
       </c>
-      <c r="L60" s="20"/>
-      <c r="M60" s="21"/>
-      <c r="N60" s="21"/>
-      <c r="O60" s="21"/>
-      <c r="P60" s="21"/>
-      <c r="Q60" s="22"/>
-      <c r="R60" s="15"/>
-      <c r="S60" s="16"/>
-      <c r="T60" s="17"/>
-      <c r="U60" s="15"/>
-      <c r="V60" s="16"/>
-      <c r="W60" s="17"/>
+      <c r="L60" s="9"/>
+      <c r="M60" s="10"/>
+      <c r="N60" s="10"/>
+      <c r="O60" s="10"/>
+      <c r="P60" s="10"/>
+      <c r="Q60" s="11"/>
+      <c r="R60" s="21"/>
+      <c r="S60" s="22"/>
+      <c r="T60" s="23"/>
+      <c r="U60" s="21"/>
+      <c r="V60" s="22"/>
+      <c r="W60" s="23"/>
     </row>
     <row r="61" spans="1:23" ht="17.25" thickBot="1">
       <c r="A61" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B61" s="20" t="str">
+      <c r="B61" s="9" t="str">
         <f>COUNTA(A62:A69) &amp; " 筆"</f>
         <v>8 筆</v>
       </c>
-      <c r="C61" s="21"/>
-      <c r="D61" s="21"/>
-      <c r="E61" s="21"/>
-      <c r="F61" s="21"/>
-      <c r="G61" s="21"/>
-      <c r="H61" s="21"/>
-      <c r="I61" s="21"/>
-      <c r="J61" s="21"/>
-      <c r="K61" s="21"/>
-      <c r="L61" s="21"/>
-      <c r="M61" s="21"/>
-      <c r="N61" s="21"/>
-      <c r="O61" s="21"/>
-      <c r="P61" s="21"/>
-      <c r="Q61" s="22"/>
+      <c r="C61" s="10"/>
+      <c r="D61" s="10"/>
+      <c r="E61" s="10"/>
+      <c r="F61" s="10"/>
+      <c r="G61" s="10"/>
+      <c r="H61" s="10"/>
+      <c r="I61" s="10"/>
+      <c r="J61" s="10"/>
+      <c r="K61" s="10"/>
+      <c r="L61" s="10"/>
+      <c r="M61" s="10"/>
+      <c r="N61" s="10"/>
+      <c r="O61" s="10"/>
+      <c r="P61" s="10"/>
+      <c r="Q61" s="11"/>
       <c r="R61" s="1" cm="1">
         <f t="array" ref="R61">CountColor($F62:$F69,$Y$4)</f>
         <v>4</v>
@@ -5123,12 +7475,12 @@
         <f t="shared" si="26"/>
         <v>4.17</v>
       </c>
-      <c r="R62" s="9"/>
-      <c r="S62" s="10"/>
-      <c r="T62" s="11"/>
-      <c r="U62" s="9"/>
-      <c r="V62" s="10"/>
-      <c r="W62" s="11"/>
+      <c r="R62" s="15"/>
+      <c r="S62" s="16"/>
+      <c r="T62" s="17"/>
+      <c r="U62" s="15"/>
+      <c r="V62" s="16"/>
+      <c r="W62" s="17"/>
     </row>
     <row r="63" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A63" s="5" t="s">
@@ -5188,12 +7540,12 @@
         <f t="shared" si="26"/>
         <v>-8.34</v>
       </c>
-      <c r="R63" s="12"/>
-      <c r="S63" s="13"/>
-      <c r="T63" s="14"/>
-      <c r="U63" s="12"/>
-      <c r="V63" s="13"/>
-      <c r="W63" s="14"/>
+      <c r="R63" s="18"/>
+      <c r="S63" s="19"/>
+      <c r="T63" s="20"/>
+      <c r="U63" s="18"/>
+      <c r="V63" s="19"/>
+      <c r="W63" s="20"/>
     </row>
     <row r="64" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A64" s="5" t="s">
@@ -5253,12 +7605,12 @@
         <f t="shared" si="26"/>
         <v>8.09</v>
       </c>
-      <c r="R64" s="12"/>
-      <c r="S64" s="13"/>
-      <c r="T64" s="14"/>
-      <c r="U64" s="12"/>
-      <c r="V64" s="13"/>
-      <c r="W64" s="14"/>
+      <c r="R64" s="18"/>
+      <c r="S64" s="19"/>
+      <c r="T64" s="20"/>
+      <c r="U64" s="18"/>
+      <c r="V64" s="19"/>
+      <c r="W64" s="20"/>
     </row>
     <row r="65" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A65" s="5" t="s">
@@ -5318,12 +7670,12 @@
         <f t="shared" si="26"/>
         <v>2.42</v>
       </c>
-      <c r="R65" s="12"/>
-      <c r="S65" s="13"/>
-      <c r="T65" s="14"/>
-      <c r="U65" s="12"/>
-      <c r="V65" s="13"/>
-      <c r="W65" s="14"/>
+      <c r="R65" s="18"/>
+      <c r="S65" s="19"/>
+      <c r="T65" s="20"/>
+      <c r="U65" s="18"/>
+      <c r="V65" s="19"/>
+      <c r="W65" s="20"/>
     </row>
     <row r="66" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A66" s="5" t="s">
@@ -5383,12 +7735,12 @@
         <f t="shared" si="26"/>
         <v>6.33</v>
       </c>
-      <c r="R66" s="12"/>
-      <c r="S66" s="13"/>
-      <c r="T66" s="14"/>
-      <c r="U66" s="12"/>
-      <c r="V66" s="13"/>
-      <c r="W66" s="14"/>
+      <c r="R66" s="18"/>
+      <c r="S66" s="19"/>
+      <c r="T66" s="20"/>
+      <c r="U66" s="18"/>
+      <c r="V66" s="19"/>
+      <c r="W66" s="20"/>
     </row>
     <row r="67" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A67" s="5" t="s">
@@ -5448,12 +7800,12 @@
         <f t="shared" si="26"/>
         <v>10.37</v>
       </c>
-      <c r="R67" s="12"/>
-      <c r="S67" s="13"/>
-      <c r="T67" s="14"/>
-      <c r="U67" s="12"/>
-      <c r="V67" s="13"/>
-      <c r="W67" s="14"/>
+      <c r="R67" s="18"/>
+      <c r="S67" s="19"/>
+      <c r="T67" s="20"/>
+      <c r="U67" s="18"/>
+      <c r="V67" s="19"/>
+      <c r="W67" s="20"/>
     </row>
     <row r="68" spans="1:23" ht="17.25" outlineLevel="1" thickBot="1">
       <c r="A68" s="5" t="s">
@@ -5513,12 +7865,12 @@
         <f t="shared" si="26"/>
         <v>5.28</v>
       </c>
-      <c r="R68" s="12"/>
-      <c r="S68" s="13"/>
-      <c r="T68" s="14"/>
-      <c r="U68" s="12"/>
-      <c r="V68" s="13"/>
-      <c r="W68" s="14"/>
+      <c r="R68" s="18"/>
+      <c r="S68" s="19"/>
+      <c r="T68" s="20"/>
+      <c r="U68" s="18"/>
+      <c r="V68" s="19"/>
+      <c r="W68" s="20"/>
     </row>
     <row r="69" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A69" s="5" t="s">
@@ -5578,12 +7930,12 @@
         <f t="shared" si="26"/>
         <v>5.12</v>
       </c>
-      <c r="R69" s="12"/>
-      <c r="S69" s="13"/>
-      <c r="T69" s="14"/>
-      <c r="U69" s="12"/>
-      <c r="V69" s="13"/>
-      <c r="W69" s="14"/>
+      <c r="R69" s="18"/>
+      <c r="S69" s="19"/>
+      <c r="T69" s="20"/>
+      <c r="U69" s="18"/>
+      <c r="V69" s="19"/>
+      <c r="W69" s="20"/>
     </row>
     <row r="70" spans="1:23" ht="17.25" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A70" s="6" t="s">
@@ -5629,42 +7981,42 @@
         <f t="shared" si="27"/>
         <v>1119.24</v>
       </c>
-      <c r="L70" s="20"/>
-      <c r="M70" s="21"/>
-      <c r="N70" s="21"/>
-      <c r="O70" s="21"/>
-      <c r="P70" s="21"/>
-      <c r="Q70" s="22"/>
-      <c r="R70" s="15"/>
-      <c r="S70" s="16"/>
-      <c r="T70" s="17"/>
-      <c r="U70" s="15"/>
-      <c r="V70" s="16"/>
-      <c r="W70" s="17"/>
+      <c r="L70" s="9"/>
+      <c r="M70" s="10"/>
+      <c r="N70" s="10"/>
+      <c r="O70" s="10"/>
+      <c r="P70" s="10"/>
+      <c r="Q70" s="11"/>
+      <c r="R70" s="21"/>
+      <c r="S70" s="22"/>
+      <c r="T70" s="23"/>
+      <c r="U70" s="21"/>
+      <c r="V70" s="22"/>
+      <c r="W70" s="23"/>
     </row>
     <row r="71" spans="1:23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A71" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B71" s="20" t="str">
+      <c r="B71" s="9" t="str">
         <f>"總共 " &amp; SUM(R71:T71) &amp; " 筆"</f>
         <v>總共 56 筆</v>
       </c>
-      <c r="C71" s="21"/>
-      <c r="D71" s="21"/>
-      <c r="E71" s="21"/>
-      <c r="F71" s="21"/>
-      <c r="G71" s="21"/>
-      <c r="H71" s="21"/>
-      <c r="I71" s="21"/>
-      <c r="J71" s="21"/>
-      <c r="K71" s="21"/>
-      <c r="L71" s="21"/>
-      <c r="M71" s="21"/>
-      <c r="N71" s="21"/>
-      <c r="O71" s="21"/>
-      <c r="P71" s="21"/>
-      <c r="Q71" s="22"/>
+      <c r="C71" s="10"/>
+      <c r="D71" s="10"/>
+      <c r="E71" s="10"/>
+      <c r="F71" s="10"/>
+      <c r="G71" s="10"/>
+      <c r="H71" s="10"/>
+      <c r="I71" s="10"/>
+      <c r="J71" s="10"/>
+      <c r="K71" s="10"/>
+      <c r="L71" s="10"/>
+      <c r="M71" s="10"/>
+      <c r="N71" s="10"/>
+      <c r="O71" s="10"/>
+      <c r="P71" s="10"/>
+      <c r="Q71" s="11"/>
       <c r="R71" s="1">
         <f t="shared" ref="R71:W71" si="28">R3+R14+R24+R38+R51+R61</f>
         <v>25</v>
@@ -5737,9 +8089,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B952BE11-689F-4F20-B9C8-AF036BD8E39C}">
   <sheetPr codeName="工作表2"/>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E86"/>
   <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="1"/>
   <cols>
+    <col min="1" max="1" width="13.875" customWidth="1"/>
     <col min="2" max="2" width="7.25" customWidth="1"/>
     <col min="3" max="3" width="7.25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.5" bestFit="1" customWidth="1"/>
@@ -5747,43 +8100,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.25" thickBot="1">
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="19"/>
-      <c r="D1" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="E1" s="19"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" s="13"/>
     </row>
     <row r="2" spans="1:5" ht="17.25" thickBot="1">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>80</v>
+      <c r="C2" s="5" t="s">
+        <v>81</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="17.25" thickBot="1">
       <c r="A3" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="9">
         <f>COUNTA(A4:A12)</f>
         <v>9</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="22"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="11"/>
     </row>
     <row r="4" spans="1:5" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A4" s="6" t="s">
@@ -5925,12 +8278,12 @@
       <c r="A14" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B14" s="20">
+      <c r="B14" s="9">
         <v>8</v>
       </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="22"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="11"/>
     </row>
     <row r="15" spans="1:5" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A15" s="6" t="s">
@@ -6059,12 +8412,12 @@
       <c r="A24" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B24" s="20">
+      <c r="B24" s="9">
         <v>12</v>
       </c>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="22"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="11"/>
     </row>
     <row r="25" spans="1:5" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A25" s="6" t="s">
@@ -6245,12 +8598,12 @@
       <c r="A38" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B38" s="20">
+      <c r="B38" s="9">
         <v>11</v>
       </c>
-      <c r="C38" s="21"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="22"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="11"/>
     </row>
     <row r="39" spans="1:5" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A39" s="6" t="s">
@@ -6418,12 +8771,12 @@
       <c r="A51" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B51" s="20">
+      <c r="B51" s="9">
         <v>8</v>
       </c>
-      <c r="C51" s="21"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="22"/>
+      <c r="C51" s="10"/>
+      <c r="D51" s="10"/>
+      <c r="E51" s="11"/>
     </row>
     <row r="52" spans="1:5" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A52" s="5" t="s">
@@ -6552,12 +8905,12 @@
       <c r="A61" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B61" s="20">
+      <c r="B61" s="9">
         <v>8</v>
       </c>
-      <c r="C61" s="21"/>
-      <c r="D61" s="21"/>
-      <c r="E61" s="22"/>
+      <c r="C61" s="10"/>
+      <c r="D61" s="10"/>
+      <c r="E61" s="11"/>
     </row>
     <row r="62" spans="1:5" ht="17.25" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
       <c r="A62" s="5" t="s">
@@ -6679,6 +9032,169 @@
         <v>5</v>
       </c>
       <c r="E70" s="1">
+        <v>1134.43</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="18" customHeight="1" thickBot="1">
+      <c r="A71" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B71" s="1">
+        <f>ROUND(($B3*B13+$B14*B23+$B24*B37+$B38*B50+$B51*B60+$B61*B70)/56,2)</f>
+        <v>7.67</v>
+      </c>
+      <c r="C71" s="1">
+        <f t="shared" ref="C71:E71" si="0">ROUND(($B3*C13+$B14*C23+$B24*C37+$B38*C50+$B51*C60+$B61*C70)/56,2)</f>
+        <v>1042.1500000000001</v>
+      </c>
+      <c r="D71" s="1">
+        <f t="shared" si="0"/>
+        <v>8.18</v>
+      </c>
+      <c r="E71" s="1">
+        <f t="shared" si="0"/>
+        <v>1052.7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="17.25" thickBot="1"/>
+    <row r="80" spans="1:5" ht="26.25" thickBot="1">
+      <c r="A80" s="6"/>
+      <c r="B80" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A81" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B81" s="6">
+        <f>B37</f>
+        <v>12.79</v>
+      </c>
+      <c r="C81" s="6">
+        <f t="shared" ref="C81:E81" si="1">C37</f>
+        <v>1234.93</v>
+      </c>
+      <c r="D81" s="6">
+        <f t="shared" si="1"/>
+        <v>12.83</v>
+      </c>
+      <c r="E81" s="6">
+        <f t="shared" si="1"/>
+        <v>1209.0999999999999</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A82" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B82" s="6">
+        <f>B50</f>
+        <v>3.15</v>
+      </c>
+      <c r="C82" s="6">
+        <f t="shared" ref="C82:E82" si="2">C50</f>
+        <v>995.42</v>
+      </c>
+      <c r="D82" s="6">
+        <f t="shared" si="2"/>
+        <v>4.72</v>
+      </c>
+      <c r="E82" s="6">
+        <f t="shared" si="2"/>
+        <v>1087.5999999999999</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A83" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B83" s="6">
+        <f>B13</f>
+        <v>10</v>
+      </c>
+      <c r="C83" s="6">
+        <f t="shared" ref="C83:E83" si="3">C13</f>
+        <v>828.38</v>
+      </c>
+      <c r="D83" s="6">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="E83" s="6">
+        <f t="shared" si="3"/>
+        <v>838.75</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A84" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B84" s="6">
+        <f>B23</f>
+        <v>3.01</v>
+      </c>
+      <c r="C84" s="6">
+        <f t="shared" ref="C84:E84" si="4">C23</f>
+        <v>592.58000000000004</v>
+      </c>
+      <c r="D84" s="6">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="E84" s="6">
+        <f t="shared" si="4"/>
+        <v>590.35</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A85" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B85" s="6">
+        <f>B60</f>
+        <v>12.44</v>
+      </c>
+      <c r="C85" s="6">
+        <f t="shared" ref="C85:E85" si="5">C60</f>
+        <v>1381.75</v>
+      </c>
+      <c r="D85" s="6">
+        <f t="shared" si="5"/>
+        <v>12.26</v>
+      </c>
+      <c r="E85" s="6">
+        <f t="shared" si="5"/>
+        <v>1391.4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A86" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B86" s="6">
+        <f>B70</f>
+        <v>3.46</v>
+      </c>
+      <c r="C86" s="6">
+        <f t="shared" ref="C86:E86" si="6">C70</f>
+        <v>1167.7</v>
+      </c>
+      <c r="D86" s="6">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="E86" s="6">
+        <f t="shared" si="6"/>
         <v>1134.43</v>
       </c>
     </row>
@@ -6695,5 +9211,6 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs/Baseline比較結果.xlsx
+++ b/docs/Baseline比較結果.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff0\OneDrive\桌面\115_NTUT_Thesis\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC86233-BD5B-4442-9438-B7BF1BAB99D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB31615-88F4-40D9-98AD-FB0EED856E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{9DD6E340-DFE3-4B7E-9025-343BD89F474F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{9DD6E340-DFE3-4B7E-9025-343BD89F474F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
     <sheet name="工作表2" sheetId="2" r:id="rId2"/>
+    <sheet name="工作表3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -59,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="94">
   <si>
     <t>Distance</t>
   </si>
@@ -1033,7 +1034,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="zh-TW"/>
+          <a:endParaRPr lang="zh-TW" altLang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1047,15 +1048,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:strRef>
-              <c:f>工作表2!$B$80</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>本研究</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>Proposed Method</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
@@ -1380,7 +1373,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="zh-TW"/>
+              <a:endParaRPr lang="zh-TW" altLang="en-US"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -1607,7 +1600,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="zh-TW"/>
+          <a:endParaRPr lang="zh-TW" altLang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1621,15 +1614,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:strRef>
-              <c:f>工作表2!$C$80</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>本研究</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>Proposed Method</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
@@ -1814,7 +1799,6 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -1951,7 +1935,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="zh-TW"/>
+              <a:endParaRPr lang="zh-TW" altLang="en-US"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -2112,6 +2096,2072 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Baseline</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表3!$A$1:$A$56</c:f>
+              <c:strCache>
+                <c:ptCount val="56"/>
+                <c:pt idx="0">
+                  <c:v>c101.txt</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>c102.txt</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>c103.txt</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>c104.txt</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>c105.txt</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>c106.txt</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>c107.txt</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>c108.txt</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>c109.txt</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>c201.txt</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>c202.txt</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>c203.txt</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>c204.txt</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>c205.txt</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>c206.txt</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>c207.txt</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>c208.txt</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>r101.txt</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>r102.txt</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>r103.txt</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>r104.txt</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>r105.txt</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>r106.txt</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>r107.txt</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>r108.txt</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>r109.txt</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>r110.txt</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>r111.txt</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>r112.txt</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>r201.txt</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>r202.txt</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>r203.txt</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>r204.txt</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>r205.txt</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>r206.txt</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>r207.txt</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>r208.txt</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>r209.txt</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>r210.txt</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>r211.txt</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>rc101.txt</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>rc102.txt</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>rc103.txt</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>rc104.txt</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>rc105.txt</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>rc106.txt</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>rc107.txt</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>rc108.txt</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>rc201.txt</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>rc202.txt</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>rc203.txt</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>rc204.txt</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>rc205.txt</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>rc206.txt</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>rc207.txt</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>rc208.txt</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表3!$B$1:$B$56</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="56"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2D2D-4BE9-B88B-014802BDD819}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Proposed Method</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表3!$A$1:$A$56</c:f>
+              <c:strCache>
+                <c:ptCount val="56"/>
+                <c:pt idx="0">
+                  <c:v>c101.txt</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>c102.txt</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>c103.txt</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>c104.txt</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>c105.txt</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>c106.txt</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>c107.txt</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>c108.txt</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>c109.txt</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>c201.txt</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>c202.txt</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>c203.txt</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>c204.txt</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>c205.txt</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>c206.txt</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>c207.txt</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>c208.txt</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>r101.txt</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>r102.txt</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>r103.txt</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>r104.txt</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>r105.txt</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>r106.txt</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>r107.txt</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>r108.txt</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>r109.txt</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>r110.txt</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>r111.txt</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>r112.txt</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>r201.txt</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>r202.txt</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>r203.txt</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>r204.txt</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>r205.txt</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>r206.txt</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>r207.txt</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>r208.txt</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>r209.txt</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>r210.txt</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>r211.txt</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>rc101.txt</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>rc102.txt</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>rc103.txt</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>rc104.txt</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>rc105.txt</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>rc106.txt</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>rc107.txt</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>rc108.txt</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>rc201.txt</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>rc202.txt</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>rc203.txt</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>rc204.txt</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>rc205.txt</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>rc206.txt</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>rc207.txt</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>rc208.txt</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表3!$D$1:$D$56</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="56"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-2D2D-4BE9-B88B-014802BDD819}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="394649136"/>
+        <c:axId val="394661136"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="394649136"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="394661136"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="394661136"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="394649136"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Baseline</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表3!$A$1:$A$56</c:f>
+              <c:strCache>
+                <c:ptCount val="56"/>
+                <c:pt idx="0">
+                  <c:v>c101.txt</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>c102.txt</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>c103.txt</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>c104.txt</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>c105.txt</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>c106.txt</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>c107.txt</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>c108.txt</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>c109.txt</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>c201.txt</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>c202.txt</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>c203.txt</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>c204.txt</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>c205.txt</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>c206.txt</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>c207.txt</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>c208.txt</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>r101.txt</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>r102.txt</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>r103.txt</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>r104.txt</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>r105.txt</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>r106.txt</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>r107.txt</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>r108.txt</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>r109.txt</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>r110.txt</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>r111.txt</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>r112.txt</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>r201.txt</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>r202.txt</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>r203.txt</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>r204.txt</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>r205.txt</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>r206.txt</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>r207.txt</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>r208.txt</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>r209.txt</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>r210.txt</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>r211.txt</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>rc101.txt</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>rc102.txt</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>rc103.txt</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>rc104.txt</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>rc105.txt</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>rc106.txt</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>rc107.txt</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>rc108.txt</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>rc201.txt</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>rc202.txt</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>rc203.txt</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>rc204.txt</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>rc205.txt</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>rc206.txt</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>rc207.txt</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>rc208.txt</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表3!$C$1:$C$56</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="56"/>
+                <c:pt idx="0">
+                  <c:v>828.94</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>828.94</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>830.77</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>864.22</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>828.94</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>828.94</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>828.94</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>854.31</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>854.78</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>591.55999999999995</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>591.55999999999995</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>591.16999999999996</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>594.51</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>588.88</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>588.49</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>588.29</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>588.32000000000005</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1656.55</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1476.85</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1230.07</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1010.55</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1395.68</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1261.6099999999999</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1103.77</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>966.99</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1200.2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1127.28</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1096.3800000000001</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>982.14</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1442.28</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1212.49</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1197.67</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>854.31</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1337.65</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1114.76</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1055.71</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>860.53</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>895.46749999999997</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>942.94849999999997</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1049.6199999999999</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1656.59</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1532.25</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1344.03</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1184.9000000000001</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1662.01</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1344.03</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1263.07</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1144.94</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1442.28</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1212.49</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1197.67</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>854.31</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>1337.65</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>1114.76</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1055.71</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>860.53</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-AE5D-493C-85AB-1F445F279F85}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Proposed Method</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表3!$A$1:$A$56</c:f>
+              <c:strCache>
+                <c:ptCount val="56"/>
+                <c:pt idx="0">
+                  <c:v>c101.txt</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>c102.txt</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>c103.txt</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>c104.txt</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>c105.txt</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>c106.txt</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>c107.txt</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>c108.txt</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>c109.txt</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>c201.txt</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>c202.txt</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>c203.txt</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>c204.txt</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>c205.txt</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>c206.txt</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>c207.txt</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>c208.txt</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>r101.txt</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>r102.txt</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>r103.txt</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>r104.txt</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>r105.txt</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>r106.txt</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>r107.txt</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>r108.txt</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>r109.txt</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>r110.txt</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>r111.txt</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>r112.txt</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>r201.txt</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>r202.txt</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>r203.txt</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>r204.txt</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>r205.txt</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>r206.txt</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>r207.txt</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>r208.txt</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>r209.txt</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>r210.txt</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>r211.txt</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>rc101.txt</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>rc102.txt</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>rc103.txt</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>rc104.txt</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>rc105.txt</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>rc106.txt</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>rc107.txt</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>rc108.txt</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>rc201.txt</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>rc202.txt</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>rc203.txt</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>rc204.txt</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>rc205.txt</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>rc206.txt</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>rc207.txt</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>rc208.txt</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表3!$E$1:$E$56</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="56"/>
+                <c:pt idx="0">
+                  <c:v>828.94</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>828.94</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>828.06</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>824.78</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>828.94</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>828.94</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>828.94</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>828.94</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>828.94</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>591.55999999999995</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>591.55999999999995</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>591.16999999999996</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>612.39</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>588.88</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>588.49</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>588.29</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>588.32000000000005</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1653.53</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1497.23</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1322.8</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1015.76</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1436.85</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1324.48</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1106.51</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>983.23</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1214.8399999999999</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1119.33</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1138.82</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1005.83</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1302.83</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1406.77</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>984.76</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>779.27</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1071.58</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>972.48</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>848.77</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>814.22</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>965.75</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>994.83</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>808.38</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1649.47</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1497.51</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1316.11</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1169.0999999999999</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1595.23</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1424.21</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1262.21</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1140.1600000000001</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1495.19</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1209.52</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1136.33</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>823.83</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>1374.6</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>1258.08</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1160.47</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>883.61</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-AE5D-493C-85AB-1F445F279F85}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="394669776"/>
+        <c:axId val="394670256"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="394669776"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="394670256"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="394670256"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="394669776"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -2153,6 +4203,86 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -3198,6 +5328,1012 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -3255,6 +6391,83 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{989E5ED4-340A-3698-66C2-9D626AD9A03C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>681037</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>157162</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>452437</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>52387</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="圖表 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C76AA358-3BFB-1681-BF12-95245FFE71D8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>14287</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>214312</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>471487</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>109537</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="圖表 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B88DB5E-3A60-7451-9903-5CAAE45F8AE7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9213,4 +12426,1004 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D009E977-1C82-468E-A0F6-C3C6E7A94314}">
+  <dimension ref="A1:E58"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetData>
+    <row r="1" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1">
+        <v>828.94</v>
+      </c>
+      <c r="D1" s="1">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1">
+        <v>828.94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1">
+        <v>828.94</v>
+      </c>
+      <c r="D2" s="1">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1">
+        <v>828.94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1">
+        <v>830.77</v>
+      </c>
+      <c r="D3" s="1">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1">
+        <v>828.06</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1">
+        <v>864.22</v>
+      </c>
+      <c r="D4" s="1">
+        <v>10</v>
+      </c>
+      <c r="E4" s="1">
+        <v>824.78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A5" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1">
+        <v>828.94</v>
+      </c>
+      <c r="D5" s="1">
+        <v>10</v>
+      </c>
+      <c r="E5" s="1">
+        <v>828.94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1">
+        <v>10</v>
+      </c>
+      <c r="C6" s="1">
+        <v>828.94</v>
+      </c>
+      <c r="D6" s="1">
+        <v>10</v>
+      </c>
+      <c r="E6" s="1">
+        <v>828.94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A7" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1">
+        <v>10</v>
+      </c>
+      <c r="C7" s="1">
+        <v>828.94</v>
+      </c>
+      <c r="D7" s="1">
+        <v>10</v>
+      </c>
+      <c r="E7" s="1">
+        <v>828.94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1">
+        <v>10</v>
+      </c>
+      <c r="C8" s="1">
+        <v>854.31</v>
+      </c>
+      <c r="D8" s="1">
+        <v>10</v>
+      </c>
+      <c r="E8" s="1">
+        <v>828.94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A9" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="1">
+        <v>10</v>
+      </c>
+      <c r="C9" s="1">
+        <v>854.78</v>
+      </c>
+      <c r="D9" s="1">
+        <v>10</v>
+      </c>
+      <c r="E9" s="1">
+        <v>828.94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A10" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1">
+        <v>3</v>
+      </c>
+      <c r="C10" s="1">
+        <v>591.55999999999995</v>
+      </c>
+      <c r="D10" s="1">
+        <v>3</v>
+      </c>
+      <c r="E10" s="1">
+        <v>591.55999999999995</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="1">
+        <v>3</v>
+      </c>
+      <c r="C11" s="1">
+        <v>591.55999999999995</v>
+      </c>
+      <c r="D11" s="1">
+        <v>3</v>
+      </c>
+      <c r="E11" s="1">
+        <v>591.55999999999995</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1">
+        <v>3</v>
+      </c>
+      <c r="C12" s="1">
+        <v>591.16999999999996</v>
+      </c>
+      <c r="D12" s="1">
+        <v>3</v>
+      </c>
+      <c r="E12" s="1">
+        <v>591.16999999999996</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A13" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1">
+        <v>3</v>
+      </c>
+      <c r="C13" s="1">
+        <v>594.51</v>
+      </c>
+      <c r="D13" s="1">
+        <v>3</v>
+      </c>
+      <c r="E13" s="1">
+        <v>612.39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A14" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="1">
+        <v>3</v>
+      </c>
+      <c r="C14" s="1">
+        <v>588.88</v>
+      </c>
+      <c r="D14" s="1">
+        <v>3</v>
+      </c>
+      <c r="E14" s="1">
+        <v>588.88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A15" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="1">
+        <v>3</v>
+      </c>
+      <c r="C15" s="1">
+        <v>588.49</v>
+      </c>
+      <c r="D15" s="1">
+        <v>3</v>
+      </c>
+      <c r="E15" s="1">
+        <v>588.49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A16" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="1">
+        <v>3</v>
+      </c>
+      <c r="C16" s="1">
+        <v>588.29</v>
+      </c>
+      <c r="D16" s="1">
+        <v>3</v>
+      </c>
+      <c r="E16" s="1">
+        <v>588.29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="1">
+        <v>3</v>
+      </c>
+      <c r="C17" s="1">
+        <v>588.32000000000005</v>
+      </c>
+      <c r="D17" s="1">
+        <v>3</v>
+      </c>
+      <c r="E17" s="1">
+        <v>588.32000000000005</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A18" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="1">
+        <v>19</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1656.55</v>
+      </c>
+      <c r="D18" s="1">
+        <v>19</v>
+      </c>
+      <c r="E18" s="1">
+        <v>1653.53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A19" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="1">
+        <v>18</v>
+      </c>
+      <c r="C19" s="1">
+        <v>1476.85</v>
+      </c>
+      <c r="D19" s="1">
+        <v>17</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1497.23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A20" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="1">
+        <v>14</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1230.07</v>
+      </c>
+      <c r="D20" s="1">
+        <v>13</v>
+      </c>
+      <c r="E20" s="1">
+        <v>1322.8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A21" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="1">
+        <v>10</v>
+      </c>
+      <c r="C21" s="1">
+        <v>1010.55</v>
+      </c>
+      <c r="D21" s="1">
+        <v>10</v>
+      </c>
+      <c r="E21" s="1">
+        <v>1015.76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A22" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="1">
+        <v>14</v>
+      </c>
+      <c r="C22" s="1">
+        <v>1395.68</v>
+      </c>
+      <c r="D22" s="1">
+        <v>14</v>
+      </c>
+      <c r="E22" s="1">
+        <v>1436.85</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A23" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="1">
+        <v>13</v>
+      </c>
+      <c r="C23" s="1">
+        <v>1261.6099999999999</v>
+      </c>
+      <c r="D23" s="1">
+        <v>12</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1324.48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A24" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="1">
+        <v>11</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1103.77</v>
+      </c>
+      <c r="D24" s="1">
+        <v>11</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1106.51</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A25" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="1">
+        <v>10</v>
+      </c>
+      <c r="C25" s="1">
+        <v>966.99</v>
+      </c>
+      <c r="D25" s="1">
+        <v>10</v>
+      </c>
+      <c r="E25" s="1">
+        <v>983.23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A26" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="1">
+        <v>12</v>
+      </c>
+      <c r="C26" s="1">
+        <v>1200.2</v>
+      </c>
+      <c r="D26" s="1">
+        <v>12</v>
+      </c>
+      <c r="E26" s="1">
+        <v>1214.8399999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A27" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="1">
+        <v>11</v>
+      </c>
+      <c r="C27" s="1">
+        <v>1127.28</v>
+      </c>
+      <c r="D27" s="1">
+        <v>11</v>
+      </c>
+      <c r="E27" s="1">
+        <v>1119.33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A28" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" s="1">
+        <v>11</v>
+      </c>
+      <c r="C28" s="1">
+        <v>1096.3800000000001</v>
+      </c>
+      <c r="D28" s="1">
+        <v>11</v>
+      </c>
+      <c r="E28" s="1">
+        <v>1138.82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A29" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" s="1">
+        <v>9</v>
+      </c>
+      <c r="C29" s="1">
+        <v>982.14</v>
+      </c>
+      <c r="D29" s="1">
+        <v>10</v>
+      </c>
+      <c r="E29" s="1">
+        <v>1005.83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A30" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" s="1">
+        <v>4</v>
+      </c>
+      <c r="C30" s="1">
+        <v>1442.28</v>
+      </c>
+      <c r="D30" s="1">
+        <v>4</v>
+      </c>
+      <c r="E30" s="1">
+        <v>1302.83</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A31" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" s="1">
+        <v>4</v>
+      </c>
+      <c r="C31" s="1">
+        <v>1212.49</v>
+      </c>
+      <c r="D31" s="1">
+        <v>3</v>
+      </c>
+      <c r="E31" s="1">
+        <v>1406.77</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A32" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" s="1">
+        <v>3</v>
+      </c>
+      <c r="C32" s="1">
+        <v>1197.67</v>
+      </c>
+      <c r="D32" s="1">
+        <v>3</v>
+      </c>
+      <c r="E32" s="1">
+        <v>984.76</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A33" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" s="1">
+        <v>10</v>
+      </c>
+      <c r="C33" s="1">
+        <v>854.31</v>
+      </c>
+      <c r="D33" s="1">
+        <v>3</v>
+      </c>
+      <c r="E33" s="1">
+        <v>779.27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A34" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="1">
+        <v>4</v>
+      </c>
+      <c r="C34" s="1">
+        <v>1337.65</v>
+      </c>
+      <c r="D34" s="1">
+        <v>3</v>
+      </c>
+      <c r="E34" s="1">
+        <v>1071.58</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A35" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="1">
+        <v>4</v>
+      </c>
+      <c r="C35" s="1">
+        <v>1114.76</v>
+      </c>
+      <c r="D35" s="1">
+        <v>3</v>
+      </c>
+      <c r="E35" s="1">
+        <v>972.48</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A36" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="1">
+        <v>4</v>
+      </c>
+      <c r="C36" s="1">
+        <v>1055.71</v>
+      </c>
+      <c r="D36" s="1">
+        <v>3</v>
+      </c>
+      <c r="E36" s="1">
+        <v>848.77</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A37" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="1">
+        <v>3</v>
+      </c>
+      <c r="C37" s="1">
+        <v>860.53</v>
+      </c>
+      <c r="D37" s="1">
+        <v>2</v>
+      </c>
+      <c r="E37" s="1">
+        <v>814.22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A38" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="1">
+        <v>2</v>
+      </c>
+      <c r="C38" s="1">
+        <v>895.46749999999997</v>
+      </c>
+      <c r="D38" s="1">
+        <v>3</v>
+      </c>
+      <c r="E38" s="1">
+        <v>965.75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A39" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="1">
+        <v>2</v>
+      </c>
+      <c r="C39" s="1">
+        <v>942.94849999999997</v>
+      </c>
+      <c r="D39" s="1">
+        <v>3</v>
+      </c>
+      <c r="E39" s="1">
+        <v>994.83</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A40" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="1">
+        <v>3</v>
+      </c>
+      <c r="C40" s="1">
+        <v>1049.6199999999999</v>
+      </c>
+      <c r="D40" s="1">
+        <v>3</v>
+      </c>
+      <c r="E40" s="1">
+        <v>808.38</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A41" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="1">
+        <v>16</v>
+      </c>
+      <c r="C41" s="1">
+        <v>1656.59</v>
+      </c>
+      <c r="D41" s="1">
+        <v>15</v>
+      </c>
+      <c r="E41" s="1">
+        <v>1649.47</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A42" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="1">
+        <v>13</v>
+      </c>
+      <c r="C42" s="1">
+        <v>1532.25</v>
+      </c>
+      <c r="D42" s="1">
+        <v>13</v>
+      </c>
+      <c r="E42" s="1">
+        <v>1497.51</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A43" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" s="1">
+        <v>12</v>
+      </c>
+      <c r="C43" s="1">
+        <v>1344.03</v>
+      </c>
+      <c r="D43" s="1">
+        <v>11</v>
+      </c>
+      <c r="E43" s="1">
+        <v>1316.11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A44" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="1">
+        <v>11</v>
+      </c>
+      <c r="C44" s="1">
+        <v>1184.9000000000001</v>
+      </c>
+      <c r="D44" s="1">
+        <v>10</v>
+      </c>
+      <c r="E44" s="1">
+        <v>1169.0999999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A45" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45" s="1">
+        <v>14</v>
+      </c>
+      <c r="C45" s="1">
+        <v>1662.01</v>
+      </c>
+      <c r="D45" s="1">
+        <v>14</v>
+      </c>
+      <c r="E45" s="1">
+        <v>1595.23</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A46" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B46" s="1">
+        <v>12</v>
+      </c>
+      <c r="C46" s="1">
+        <v>1344.03</v>
+      </c>
+      <c r="D46" s="1">
+        <v>12</v>
+      </c>
+      <c r="E46" s="1">
+        <v>1424.21</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A47" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B47" s="1">
+        <v>12</v>
+      </c>
+      <c r="C47" s="1">
+        <v>1263.07</v>
+      </c>
+      <c r="D47" s="1">
+        <v>11</v>
+      </c>
+      <c r="E47" s="1">
+        <v>1262.21</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A48" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B48" s="1">
+        <v>11</v>
+      </c>
+      <c r="C48" s="1">
+        <v>1144.94</v>
+      </c>
+      <c r="D48" s="1">
+        <v>11</v>
+      </c>
+      <c r="E48" s="1">
+        <v>1140.1600000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B49" s="1">
+        <v>4</v>
+      </c>
+      <c r="C49" s="1">
+        <v>1442.28</v>
+      </c>
+      <c r="D49" s="1">
+        <v>4</v>
+      </c>
+      <c r="E49" s="1">
+        <v>1495.19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A50" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B50" s="1">
+        <v>4</v>
+      </c>
+      <c r="C50" s="1">
+        <v>1212.49</v>
+      </c>
+      <c r="D50" s="1">
+        <v>4</v>
+      </c>
+      <c r="E50" s="1">
+        <v>1209.52</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A51" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B51" s="1">
+        <v>3</v>
+      </c>
+      <c r="C51" s="1">
+        <v>1197.67</v>
+      </c>
+      <c r="D51" s="1">
+        <v>3</v>
+      </c>
+      <c r="E51" s="1">
+        <v>1136.33</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A52" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B52" s="1">
+        <v>10</v>
+      </c>
+      <c r="C52" s="1">
+        <v>854.31</v>
+      </c>
+      <c r="D52" s="1">
+        <v>3</v>
+      </c>
+      <c r="E52" s="1">
+        <v>823.83</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A53" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B53" s="1">
+        <v>4</v>
+      </c>
+      <c r="C53" s="1">
+        <v>1337.65</v>
+      </c>
+      <c r="D53" s="1">
+        <v>4</v>
+      </c>
+      <c r="E53" s="1">
+        <v>1374.6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A54" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B54" s="1">
+        <v>4</v>
+      </c>
+      <c r="C54" s="1">
+        <v>1114.76</v>
+      </c>
+      <c r="D54" s="1">
+        <v>3</v>
+      </c>
+      <c r="E54" s="1">
+        <v>1258.08</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A55" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B55" s="1">
+        <v>4</v>
+      </c>
+      <c r="C55" s="1">
+        <v>1055.71</v>
+      </c>
+      <c r="D55" s="1">
+        <v>3</v>
+      </c>
+      <c r="E55" s="1">
+        <v>1160.47</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A56" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B56" s="1">
+        <v>3</v>
+      </c>
+      <c r="C56" s="1">
+        <v>860.53</v>
+      </c>
+      <c r="D56" s="1">
+        <v>3</v>
+      </c>
+      <c r="E56" s="1">
+        <v>883.61</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="B57">
+        <f>SUM(B2:B56)</f>
+        <v>436</v>
+      </c>
+      <c r="C57">
+        <f t="shared" ref="C57:E57" si="0">SUM(C2:C56)</f>
+        <v>58121.345999999998</v>
+      </c>
+      <c r="D57">
+        <f t="shared" si="0"/>
+        <v>411</v>
+      </c>
+      <c r="E57">
+        <f t="shared" si="0"/>
+        <v>57531.62000000001</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="B58">
+        <f>B57/56</f>
+        <v>7.7857142857142856</v>
+      </c>
+      <c r="C58">
+        <f t="shared" ref="C58:E58" si="1">C57/56</f>
+        <v>1037.8811785714286</v>
+      </c>
+      <c r="D58">
+        <f t="shared" si="1"/>
+        <v>7.3392857142857144</v>
+      </c>
+      <c r="E58">
+        <f t="shared" si="1"/>
+        <v>1027.3503571428573</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>